--- a/Results/Ammonia/ammonia ozone depletion results.xlsx
+++ b/Results/Ammonia/ammonia ozone depletion results.xlsx
@@ -515,22 +515,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.53243936892106e-07</v>
+        <v>1.532439368921057e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>3.774060095740669e-07</v>
+        <v>3.774060095740672e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>1.485097586161193e-07</v>
+        <v>1.485097586161192e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>4.058999400513867e-07</v>
+        <v>4.058999400513865e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>2.678144857726845e-07</v>
+        <v>2.678144857726844e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>1.607877181742151e-07</v>
+        <v>1.60787718174215e-07</v>
       </c>
       <c r="H2" t="n">
         <v>1.532102772363284e-07</v>
@@ -542,10 +542,10 @@
         <v>3.340020463574413e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>1.293349615575167e-07</v>
+        <v>1.293349615575168e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>1.496742031740362e-07</v>
+        <v>1.496742031740363e-07</v>
       </c>
     </row>
     <row r="3">
@@ -555,37 +555,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.721212512284777e-07</v>
+        <v>1.721212512284779e-07</v>
       </c>
       <c r="C3" t="n">
         <v>3.968756695462126e-07</v>
       </c>
       <c r="D3" t="n">
-        <v>1.666759655290178e-07</v>
+        <v>1.666759655290179e-07</v>
       </c>
       <c r="E3" t="n">
-        <v>4.253736608412741e-07</v>
+        <v>4.253736608412742e-07</v>
       </c>
       <c r="F3" t="n">
-        <v>2.872882065625716e-07</v>
+        <v>2.872882065625717e-07</v>
       </c>
       <c r="G3" t="n">
-        <v>1.807981623924886e-07</v>
+        <v>1.807981623924882e-07</v>
       </c>
       <c r="H3" t="n">
-        <v>1.720879947055951e-07</v>
+        <v>1.720879947055952e-07</v>
       </c>
       <c r="I3" t="n">
-        <v>1.766948733212925e-07</v>
+        <v>1.766948733212924e-07</v>
       </c>
       <c r="J3" t="n">
-        <v>3.598079046223885e-07</v>
+        <v>3.598079046223883e-07</v>
       </c>
       <c r="K3" t="n">
-        <v>1.48506769700048e-07</v>
+        <v>1.485067697000477e-07</v>
       </c>
       <c r="L3" t="n">
-        <v>1.680154053063829e-07</v>
+        <v>1.68015405306383e-07</v>
       </c>
     </row>
     <row r="4">
@@ -595,37 +595,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.780203198021209e-08</v>
+        <v>2.067154776891501e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>8.229739940462799e-08</v>
+        <v>2.340764277108326e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>7.498776359928842e-08</v>
+        <v>1.785727938799153e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>8.372133757460755e-08</v>
+        <v>2.365825705235671e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>8.372133757460758e-08</v>
+        <v>2.365825705235672e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>8.274987570531708e-08</v>
+        <v>2.523756191572207e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>7.77843736760311e-08</v>
+        <v>2.06538894647342e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>8.324985078723852e-08</v>
+        <v>2.357509547865112e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>1.052223365085863e-07</v>
+        <v>4.809185229728938e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>7.896751637777677e-08</v>
+        <v>2.183703216647987e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>7.568309605077471e-08</v>
+        <v>1.855261183947784e-08</v>
       </c>
     </row>
     <row r="5">
@@ -635,37 +635,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.736395815067291e-07</v>
+        <v>1.255389559173433e-07</v>
       </c>
       <c r="C5" t="n">
-        <v>9.253458508499052e-07</v>
+        <v>1.717841694214579e-07</v>
       </c>
       <c r="D5" t="n">
-        <v>3.943053223401814e-07</v>
+        <v>7.405716942186349e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>9.253458522633939e-07</v>
+        <v>1.717841708349472e-07</v>
       </c>
       <c r="F5" t="n">
-        <v>9.253458522633939e-07</v>
+        <v>1.717841708349472e-07</v>
       </c>
       <c r="G5" t="n">
-        <v>1.183241294162218e-06</v>
+        <v>2.189240505146275e-07</v>
       </c>
       <c r="H5" t="n">
-        <v>7.668137017287276e-07</v>
+        <v>1.419230505448992e-07</v>
       </c>
       <c r="I5" t="n">
-        <v>9.253456339386661e-07</v>
+        <v>1.717839525102164e-07</v>
       </c>
       <c r="J5" t="n">
-        <v>3.745996780670414e-06</v>
+        <v>6.888681509976575e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>8.097324008282363e-07</v>
+        <v>1.50451651132848e-07</v>
       </c>
       <c r="L5" t="n">
-        <v>5.346946860540258e-07</v>
+        <v>5.093679088736724e-07</v>
       </c>
     </row>
     <row r="6">
@@ -675,37 +675,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.301043103945276e-07</v>
+        <v>2.384501117770803e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>1.007327003327812e-07</v>
+        <v>2.665225571685694e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>9.167414650306623e-08</v>
+        <v>2.079404098703779e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>9.879685572615491e-08</v>
+        <v>2.631154823265192e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>1.014310136064417e-07</v>
+        <v>2.677516001707023e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>1.350521541196326e-07</v>
+        <v>3.444276286676227e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>1.395355097192579e-07</v>
+        <v>3.152208934945174e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>1.35552129201554e-07</v>
+        <v>2.674855888744406e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>1.260841223775304e-07</v>
+        <v>5.176352659032823e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>9.650214596076079e-08</v>
+        <v>2.492312695636272e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>9.372487764179161e-08</v>
+        <v>2.172796538229085e-08</v>
       </c>
     </row>
     <row r="7">
@@ -715,37 +715,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.040571023272158e-07</v>
+        <v>2.529244012494908e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>1.095051380454838e-07</v>
+        <v>2.819620474592652e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>1.012412164275703e-07</v>
+        <v>2.24778870607319e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>1.096609915057584e-07</v>
+        <v>2.822363611950126e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>1.096609915057584e-07</v>
+        <v>2.822363611950126e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>1.09004946052321e-07</v>
+        <v>2.985845427175597e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>1.04039444023035e-07</v>
+        <v>2.527478182076817e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>1.095049211342422e-07</v>
+        <v>2.8195987834685e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>1.314774068555901e-07</v>
+        <v>5.271274465332334e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>1.052225867247805e-07</v>
+        <v>2.645792452251378e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>1.019381663977786e-07</v>
+        <v>2.317350419551173e-08</v>
       </c>
     </row>
     <row r="8">
@@ -755,37 +755,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.34956405296542e-07</v>
+        <v>3.073071741808258e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>1.877255849862376e-07</v>
+        <v>4.196300333290233e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>1.890828700311471e-07</v>
+        <v>3.79380180111891e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>1.748105876663255e-07</v>
+        <v>3.968996498162954e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>1.419933271943647e-07</v>
+        <v>3.391412716986145e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>1.870657398055447e-07</v>
+        <v>4.359715389787882e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>1.821002377763499e-07</v>
+        <v>3.901348144690704e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>1.875657148874661e-07</v>
+        <v>4.193468746080779e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>2.095474690374423e-07</v>
+        <v>6.645307552287585e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>1.35245840802912e-07</v>
+        <v>3.174201721163248e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>2.292630807104853e-07</v>
+        <v>4.558268899312172e-08</v>
       </c>
     </row>
     <row r="9">
@@ -795,37 +795,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.534875599835347e-07</v>
+        <v>6.91922004345859e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>4.398986694489215e-07</v>
+        <v>8.634546595784385e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>4.316363984682092e-07</v>
+        <v>8.062743878479508e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>5.333283488056461e-07</v>
+        <v>1.027890906002408e-07</v>
       </c>
       <c r="F9" t="n">
-        <v>4.398986529385198e-07</v>
+        <v>8.634546421672808e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>4.393984774557587e-07</v>
+        <v>8.800771548367318e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>4.34432975426473e-07</v>
+        <v>8.342404303268532e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>4.398984525376802e-07</v>
+        <v>8.634524904660224e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>4.618709382590279e-07</v>
+        <v>1.108620058652405e-07</v>
       </c>
       <c r="K9" t="n">
-        <v>3.336691478394528e-07</v>
+        <v>7.635097140113312e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>4.323316978012164e-07</v>
+        <v>8.132276540742907e-08</v>
       </c>
     </row>
   </sheetData>
@@ -911,37 +911,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.434797567663534e-07</v>
+        <v>1.434797567663535e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>3.729657246632787e-07</v>
+        <v>3.729657246632785e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>1.494235930085793e-07</v>
+        <v>1.494235930085791e-07</v>
       </c>
       <c r="E2" t="n">
         <v>4.009619679516359e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>2.643371702810097e-07</v>
+        <v>2.6433717028101e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>1.525271205731722e-07</v>
+        <v>1.525271205731724e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>1.470796998240458e-07</v>
+        <v>1.470796998240462e-07</v>
       </c>
       <c r="I2" t="n">
         <v>1.54111866279206e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>3.204879704105067e-07</v>
+        <v>3.204879704105068e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>1.241650231834446e-07</v>
+        <v>1.241650231834447e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>1.436726253770106e-07</v>
+        <v>1.436726253770105e-07</v>
       </c>
     </row>
     <row r="3">
@@ -954,34 +954,34 @@
         <v>1.606998102876532e-07</v>
       </c>
       <c r="C3" t="n">
-        <v>3.917783896394298e-07</v>
+        <v>3.917783896394295e-07</v>
       </c>
       <c r="D3" t="n">
-        <v>1.675364532281813e-07</v>
+        <v>1.675364532281812e-07</v>
       </c>
       <c r="E3" t="n">
-        <v>4.197794978405151e-07</v>
+        <v>4.197794978405152e-07</v>
       </c>
       <c r="F3" t="n">
         <v>2.831547001698892e-07</v>
       </c>
       <c r="G3" t="n">
-        <v>1.711061528212618e-07</v>
+        <v>1.711061528212615e-07</v>
       </c>
       <c r="H3" t="n">
-        <v>1.648426612779234e-07</v>
+        <v>1.648426612779235e-07</v>
       </c>
       <c r="I3" t="n">
-        <v>1.729238010079285e-07</v>
+        <v>1.729238010079286e-07</v>
       </c>
       <c r="J3" t="n">
-        <v>3.44588889506523e-07</v>
+        <v>3.445888895065227e-07</v>
       </c>
       <c r="K3" t="n">
-        <v>1.426339794883353e-07</v>
+        <v>1.426339794883355e-07</v>
       </c>
       <c r="L3" t="n">
-        <v>1.609216724988835e-07</v>
+        <v>1.609216724988838e-07</v>
       </c>
     </row>
     <row r="4">
@@ -991,37 +991,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.735049022734381e-08</v>
+        <v>1.249216551545988e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>6.367553730244607e-08</v>
+        <v>1.88148133891288e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>6.088384901164059e-08</v>
+        <v>1.60255242997567e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>6.471180098015079e-08</v>
+        <v>1.899720715022509e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>6.471180098015079e-08</v>
+        <v>1.89972071502251e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>6.319839795943473e-08</v>
+        <v>1.795309539285512e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>5.949219308658729e-08</v>
+        <v>1.463386837470339e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>6.679793184892136e-08</v>
+        <v>1.936476718121491e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>8.458210359698481e-08</v>
+        <v>3.972377888510091e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>6.2293129691772e-08</v>
+        <v>1.743480497988813e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>5.746723935364275e-08</v>
+        <v>1.260891464175887e-08</v>
       </c>
     </row>
     <row r="5">
@@ -1031,37 +1031,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.504238105513703e-07</v>
+        <v>2.887306980372705e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>6.930719024231408e-07</v>
+        <v>1.295885730501324e-07</v>
       </c>
       <c r="D5" t="n">
-        <v>4.503701442723436e-07</v>
+        <v>8.457511189419758e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>6.930719162032485e-07</v>
+        <v>1.2958858683024e-07</v>
       </c>
       <c r="F5" t="n">
-        <v>6.930719162032485e-07</v>
+        <v>1.2958858683024e-07</v>
       </c>
       <c r="G5" t="n">
-        <v>6.269116962237416e-07</v>
+        <v>1.171666353497743e-07</v>
       </c>
       <c r="H5" t="n">
-        <v>3.726429403614791e-07</v>
+        <v>6.974839959644071e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>6.930724028538248e-07</v>
+        <v>1.295890734808163e-07</v>
       </c>
       <c r="J5" t="n">
-        <v>2.756237684345866e-06</v>
+        <v>5.099351585490149e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>5.525042107755178e-07</v>
+        <v>1.037119547831258e-07</v>
       </c>
       <c r="L5" t="n">
-        <v>5.018920366508894e-07</v>
+        <v>3.388464814137216e-08</v>
       </c>
     </row>
     <row r="6">
@@ -1071,37 +1071,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9.080972544901002e-08</v>
+        <v>1.838099088256402e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>7.847343675618361e-08</v>
+        <v>2.141924367887427e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>7.221722433712632e-08</v>
+        <v>2.223978320071486e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>7.745167216291326e-08</v>
+        <v>2.123942446624156e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>7.891659482128786e-08</v>
+        <v>2.149725085271843e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>9.665763318110113e-08</v>
+        <v>2.007837148241637e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>9.95579701806145e-08</v>
+        <v>2.16854451050426e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>7.887336424140555e-08</v>
+        <v>2.149004327077614e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>1.223559273862518e-07</v>
+        <v>4.637197183598822e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>7.415161002677276e-08</v>
+        <v>1.952189750753916e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>6.968070556901847e-08</v>
+        <v>1.475848468401736e-08</v>
       </c>
     </row>
     <row r="7">
@@ -1111,37 +1111,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7.321951186090292e-08</v>
+        <v>1.528511330783295e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>8.266645305179664e-08</v>
+        <v>2.215721454290417e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>7.675230604120893e-08</v>
+        <v>1.881837272182794e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>8.202644936686974e-08</v>
+        <v>2.204458524977564e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>8.202644936686975e-08</v>
+        <v>2.204458524977564e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>7.906741959299396e-08</v>
+        <v>2.074604318522822e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>7.536121472014637e-08</v>
+        <v>1.742681616707648e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>8.266695348248076e-08</v>
+        <v>2.215771497358799e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>1.004511252305439e-07</v>
+        <v>4.251672667747401e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>7.816215132533115e-08</v>
+        <v>2.022775277226122e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>7.333626098720186e-08</v>
+        <v>1.540186243413195e-08</v>
       </c>
     </row>
     <row r="8">
@@ -1151,37 +1151,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9.261373389464477e-08</v>
+        <v>1.869849636727526e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>1.296979678617544e-07</v>
+        <v>3.043476110460331e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>1.302475037633392e-07</v>
+        <v>2.823352746990552e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>1.22038489184639e-07</v>
+        <v>2.90867042195442e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>1.025745110615008e-07</v>
+        <v>2.566104408843418e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>1.267055038858169e-07</v>
+        <v>2.913034597533343e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>1.229992990131415e-07</v>
+        <v>2.581111895721202e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>1.303050377753037e-07</v>
+        <v>3.054201776369321e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>1.480947601767857e-07</v>
+        <v>5.090200638257574e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>9.703172912311899e-08</v>
+        <v>2.354879844667603e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>1.504774210545251e-07</v>
+        <v>2.897870653241302e-08</v>
       </c>
     </row>
     <row r="9">
@@ -1191,37 +1191,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.173566283291614e-07</v>
+        <v>4.065324566878607e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>2.73595071195245e-07</v>
+        <v>5.576065115406698e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>2.67681509366654e-07</v>
+        <v>5.24219123250215e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>3.27591495269868e-07</v>
+        <v>6.526403309451373e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>2.735950776948494e-07</v>
+        <v>5.576066365280547e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>2.699960377364428e-07</v>
+        <v>5.434947979639103e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>2.662898328635957e-07</v>
+        <v>5.10302527782393e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>2.735955716259287e-07</v>
+        <v>5.576115158475082e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>2.91379743373993e-07</v>
+        <v>7.612016328863684e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>2.419795982887939e-07</v>
+        <v>4.905962328160162e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>2.64264879130651e-07</v>
+        <v>4.900529904529478e-08</v>
       </c>
     </row>
   </sheetData>
@@ -1307,37 +1307,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.097862591961698e-07</v>
+        <v>1.097862591961746e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>2.17458429813864e-07</v>
+        <v>2.174584298138646e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>1.092037597414125e-07</v>
+        <v>1.092037597414144e-07</v>
       </c>
       <c r="E2" t="n">
         <v>1.47770645786464e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>1.477706457864642e-07</v>
+        <v>1.47770645786464e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>1.137324558677752e-07</v>
+        <v>1.137324558677777e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>1.115604013204265e-07</v>
+        <v>1.115604013204287e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>1.134446627450524e-07</v>
+        <v>1.134446627450511e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>2.601963395074086e-07</v>
+        <v>2.601963395074088e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>1.173622521211665e-07</v>
+        <v>1.173622521211738e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>1.142288308742881e-07</v>
+        <v>1.142288308742898e-07</v>
       </c>
     </row>
     <row r="3">
@@ -1347,37 +1347,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.233137995881681e-07</v>
+        <v>1.233137995881706e-07</v>
       </c>
       <c r="C3" t="n">
-        <v>2.311635893861237e-07</v>
+        <v>2.311635893861243e-07</v>
       </c>
       <c r="D3" t="n">
-        <v>1.22643804550797e-07</v>
+        <v>1.226438045507977e-07</v>
       </c>
       <c r="E3" t="n">
-        <v>1.61847917039002e-07</v>
+        <v>1.618479170390023e-07</v>
       </c>
       <c r="F3" t="n">
-        <v>1.61847917039002e-07</v>
+        <v>1.618479170390023e-07</v>
       </c>
       <c r="G3" t="n">
-        <v>1.278527432126902e-07</v>
+        <v>1.278527432126921e-07</v>
       </c>
       <c r="H3" t="n">
-        <v>1.253593160185761e-07</v>
+        <v>1.253593160185767e-07</v>
       </c>
       <c r="I3" t="n">
-        <v>1.275297421566125e-07</v>
+        <v>1.275297421566161e-07</v>
       </c>
       <c r="J3" t="n">
-        <v>2.760936684621488e-07</v>
+        <v>2.7609366846215e-07</v>
       </c>
       <c r="K3" t="n">
-        <v>1.316316676928302e-07</v>
+        <v>1.316316676928419e-07</v>
       </c>
       <c r="L3" t="n">
-        <v>1.284231248140833e-07</v>
+        <v>1.284231248140853e-07</v>
       </c>
     </row>
     <row r="4">
@@ -1387,37 +1387,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.323598215387309e-08</v>
+        <v>1.467035277897836e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>6.017973144262726e-08</v>
+        <v>1.472308863787625e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>6.288971091061347e-08</v>
+        <v>1.432408153571908e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>6.68846626135706e-08</v>
+        <v>1.710522057969079e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>6.688466261357091e-08</v>
+        <v>1.710522057969079e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>6.574039393476681e-08</v>
+        <v>1.704410693861057e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>6.429170534484725e-08</v>
+        <v>1.572607596995175e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>6.646651688155587e-08</v>
+        <v>1.703181867416284e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>7.261462285070901e-08</v>
+        <v>2.404899347581403e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>6.617201655855667e-08</v>
+        <v>1.76063871836617e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>6.587692747232048e-08</v>
+        <v>1.731129809742554e-08</v>
       </c>
     </row>
     <row r="5">
@@ -1427,37 +1427,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.727086477907589e-07</v>
+        <v>5.153754173130132e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>3.427435178614691e-07</v>
+        <v>6.445431477811877e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>2.317471928520251e-07</v>
+        <v>4.404299819637716e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>4.816763666017839e-07</v>
+        <v>9.010856008604081e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>4.816763666017839e-07</v>
+        <v>9.010856008604081e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>5.062433374589336e-07</v>
+        <v>9.457262457877324e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>4.097845397889443e-07</v>
+        <v>7.653281450262226e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>4.816765992994875e-07</v>
+        <v>9.010879278374417e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>1.234090804744042e-06</v>
+        <v>2.284688003813705e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>5.521046992468413e-07</v>
+        <v>1.031305388733918e-07</v>
       </c>
       <c r="L5" t="n">
-        <v>5.945820590998654e-07</v>
+        <v>1.103634007596612e-07</v>
       </c>
     </row>
     <row r="6">
@@ -1467,37 +1467,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.051209470853563e-07</v>
+        <v>1.653964889732587e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>7.356376701285963e-08</v>
+        <v>1.7078678885473e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>7.282228555915611e-08</v>
+        <v>1.607215673724646e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>7.536528284239747e-08</v>
+        <v>1.859780973187712e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>7.717392920268919e-08</v>
+        <v>1.891613148956448e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>1.076253588662736e-07</v>
+        <v>2.441586072661103e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>1.145523903680801e-07</v>
+        <v>2.457195648610894e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>1.083514818130613e-07</v>
+        <v>2.440357246216327e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>1.161957525152519e-07</v>
+        <v>3.171927225521084e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>7.662615228684871e-08</v>
+        <v>1.944631506187206e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>7.659873490928656e-08</v>
+        <v>1.919833619610656e-08</v>
       </c>
     </row>
     <row r="7">
@@ -1507,37 +1507,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>8.514900348481751e-08</v>
+        <v>1.852704451232647e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>8.581547521456822e-08</v>
+        <v>1.923497951729034e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>8.480179899281967e-08</v>
+        <v>1.818060901728992e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>8.854873361444498e-08</v>
+        <v>2.091809705518415e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>8.854873361444498e-08</v>
+        <v>2.091809705518415e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>8.765341526570522e-08</v>
+        <v>2.090079867195872e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>8.620472667579336e-08</v>
+        <v>1.958276770329984e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>8.837953821249719e-08</v>
+        <v>2.08885104075109e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>9.45276441816484e-08</v>
+        <v>2.790568520916213e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>8.808503788949152e-08</v>
+        <v>2.146307891700978e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>8.778994880326382e-08</v>
+        <v>2.116798983077362e-08</v>
       </c>
     </row>
     <row r="8">
@@ -1547,37 +1547,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.130013779315607e-07</v>
+        <v>2.342906238839026e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>1.551596292046038e-07</v>
+        <v>3.143955055374051e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>1.625442109798428e-07</v>
+        <v>3.186327345286559e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>1.464046035227517e-07</v>
+        <v>3.110073010387037e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>1.176431188000869e-07</v>
+        <v>2.603870882011041e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>1.568267282299829e-07</v>
+        <v>3.307530168770087e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>1.553780396405216e-07</v>
+        <v>3.175727071912368e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>1.575528511767694e-07</v>
+        <v>3.306301342325351e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>1.637090777612319e-07</v>
+        <v>4.008161745319277e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>1.151698547002346e-07</v>
+        <v>2.623000664986867e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>2.001264371276953e-07</v>
+        <v>4.093921166873967e-08</v>
       </c>
     </row>
     <row r="9">
@@ -1587,37 +1587,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.674450183698953e-07</v>
+        <v>5.06111429582525e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>3.288087226942249e-07</v>
+        <v>6.200179084196836e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>3.277960054238843e-07</v>
+        <v>6.094758911742838e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>4.014158868777762e-07</v>
+        <v>7.598271573115789e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>3.313725459734458e-07</v>
+        <v>6.365508779879153e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>3.306466627453478e-07</v>
+        <v>6.366760999663662e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>3.291979741553909e-07</v>
+        <v>6.234957902797776e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>3.313727856921132e-07</v>
+        <v>6.365532173218888e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>3.375208916612367e-07</v>
+        <v>7.067249653384006e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>2.546496284533016e-07</v>
+        <v>5.804028634813091e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>3.307831962828587e-07</v>
+        <v>6.393480115545158e-08</v>
       </c>
     </row>
   </sheetData>
@@ -1706,34 +1706,34 @@
         <v>1.061092542005931e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>2.158623065862816e-07</v>
+        <v>2.158623065862813e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>1.058115199970536e-07</v>
+        <v>1.058115199970539e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>1.442231433804926e-07</v>
+        <v>1.442231433804929e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>1.442231433804926e-07</v>
+        <v>1.442231433804929e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>1.094728179275062e-07</v>
+        <v>1.094728179275061e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>1.074504357841874e-07</v>
+        <v>1.074504357841872e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>1.07995973130976e-07</v>
+        <v>1.079959731309763e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>2.561018494887698e-07</v>
+        <v>2.561018494887697e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>1.134110014240706e-07</v>
+        <v>1.134110014240704e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>1.099876077365271e-07</v>
+        <v>1.099876077365269e-07</v>
       </c>
     </row>
     <row r="3">
@@ -1743,37 +1743,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.19282858406505e-07</v>
+        <v>1.192828584065053e-07</v>
       </c>
       <c r="C3" t="n">
-        <v>2.292081517533299e-07</v>
+        <v>2.292081517533294e-07</v>
       </c>
       <c r="D3" t="n">
-        <v>1.189404023969802e-07</v>
+        <v>1.1894040239698e-07</v>
       </c>
       <c r="E3" t="n">
-        <v>1.576802653816976e-07</v>
+        <v>1.576802653816977e-07</v>
       </c>
       <c r="F3" t="n">
         <v>1.576802653816976e-07</v>
       </c>
       <c r="G3" t="n">
-        <v>1.231516534525819e-07</v>
+        <v>1.23151653452582e-07</v>
       </c>
       <c r="H3" t="n">
         <v>1.208294673325034e-07</v>
       </c>
       <c r="I3" t="n">
-        <v>1.214565291801645e-07</v>
+        <v>1.214565291801641e-07</v>
       </c>
       <c r="J3" t="n">
-        <v>2.71348591693322e-07</v>
+        <v>2.713485916933215e-07</v>
       </c>
       <c r="K3" t="n">
         <v>1.270359760419469e-07</v>
       </c>
       <c r="L3" t="n">
-        <v>1.237433032961052e-07</v>
+        <v>1.237433032961053e-07</v>
       </c>
     </row>
     <row r="4">
@@ -1783,37 +1783,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.847688958748317e-08</v>
+        <v>1.311799961947404e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>5.592962585351795e-08</v>
+        <v>1.324185053307582e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>5.829989921954695e-08</v>
+        <v>1.294100925149651e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>6.045258039587206e-08</v>
+        <v>1.439028701993056e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>6.045258039587207e-08</v>
+        <v>1.439028701993047e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>6.063212563775028e-08</v>
+        <v>1.514490595826818e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>5.927516590161593e-08</v>
+        <v>1.391627593365315e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>6.063527670943039e-08</v>
+        <v>1.442249677757196e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>6.668151033292067e-08</v>
+        <v>2.132262036486524e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>6.026322655507129e-08</v>
+        <v>1.490433658703726e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>6.078229166429432e-08</v>
+        <v>1.542340169629889e-08</v>
       </c>
     </row>
     <row r="5">
@@ -1823,37 +1823,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.964502110048183e-07</v>
+        <v>3.740130405731602e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>2.608668098220493e-07</v>
+        <v>4.931079471609454e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>1.750204975868747e-07</v>
+        <v>3.348383445279332e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>2.979391924837258e-07</v>
+        <v>5.618793052090845e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>2.979391924837258e-07</v>
+        <v>5.618793052090845e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>3.850059922304042e-07</v>
+        <v>7.223470616922999e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>2.933212819412782e-07</v>
+        <v>5.510839213334397e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>2.979392594820621e-07</v>
+        <v>5.61879975192439e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>9.925854791343866e-07</v>
+        <v>1.842817179909891e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>3.56725279576656e-07</v>
+        <v>6.708165763612209e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>4.582360355354372e-07</v>
+        <v>8.537526023859917e-08</v>
       </c>
     </row>
     <row r="6">
@@ -1863,37 +1863,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9.448116722969147e-08</v>
+        <v>1.945475245012609e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>6.666305261806668e-08</v>
+        <v>1.513093363340004e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>6.606306129505871e-08</v>
+        <v>1.948350419473457e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>6.741521167624544e-08</v>
+        <v>1.561571011863501e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>6.897938015163589e-08</v>
+        <v>1.589100376881304e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>6.896631206037286e-08</v>
+        <v>1.661172276073266e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>1.028036069914149e-07</v>
+        <v>2.15772815238496e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>6.896946313205543e-08</v>
+        <v>1.588931358000509e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>7.625353232775144e-08</v>
+        <v>2.30072962268417e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>6.816593553709362e-08</v>
+        <v>1.629521336040607e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>6.925911709916937e-08</v>
+        <v>1.691532296466974e-08</v>
       </c>
     </row>
     <row r="7">
@@ -1903,37 +1903,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7.750632865923129e-08</v>
+        <v>1.646718087798137e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>7.815209209938197e-08</v>
+        <v>1.715300457115488e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>7.732845382485819e-08</v>
+        <v>1.629003484391192e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>7.968460203704556e-08</v>
+        <v>1.777512281043512e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>7.968460203704556e-08</v>
+        <v>1.777512281043512e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>7.966156470949831e-08</v>
+        <v>1.849408721679478e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>7.830460497336477e-08</v>
+        <v>1.726545719212236e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>7.966471578117925e-08</v>
+        <v>1.777167803605103e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>8.571094940466919e-08</v>
+        <v>2.467180162335319e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>7.929266562682021e-08</v>
+        <v>1.825351784552405e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>7.981173073604283e-08</v>
+        <v>1.877258295480732e-08</v>
       </c>
     </row>
     <row r="8">
@@ -1943,37 +1943,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.022911267035696e-07</v>
+        <v>2.082930531013131e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>1.388660166605627e-07</v>
+        <v>2.783865523632191e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>1.454608566470982e-07</v>
+        <v>2.828133767563618e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>1.305568248297187e-07</v>
+        <v>2.67286339734302e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>1.055999209907328e-07</v>
+        <v>2.233621892157023e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>1.403485339863509e-07</v>
+        <v>2.917499375160454e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>1.389915742507678e-07</v>
+        <v>2.794636372695436e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>1.403516850580333e-07</v>
+        <v>2.845258457090235e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>1.464049743834732e-07</v>
+        <v>3.535394996176213e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>1.034105624169401e-07</v>
+        <v>2.249826765764553e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>1.780015198623394e-07</v>
+        <v>3.605398574734265e-08</v>
       </c>
     </row>
     <row r="9">
@@ -1983,37 +1983,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.277460891086288e-07</v>
+        <v>4.290937857377392e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>2.787135849344575e-07</v>
+        <v>5.245182711885705e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>2.77890853226414e-07</v>
+        <v>5.158901694729292e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>3.382963656565068e-07</v>
+        <v>6.329079296083015e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>2.802261351224256e-07</v>
+        <v>5.307043244221144e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>2.802230575445715e-07</v>
+        <v>5.379290976448328e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>2.788660978084384e-07</v>
+        <v>5.256427973976946e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>2.802262086162534e-07</v>
+        <v>5.307050058375359e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>2.862724422397446e-07</v>
+        <v>5.997062417106045e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>2.506975583841276e-07</v>
+        <v>4.842077880736352e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>2.803732235711178e-07</v>
+        <v>5.407140550243641e-08</v>
       </c>
     </row>
   </sheetData>
@@ -2099,19 +2099,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.020697189530272e-07</v>
+        <v>1.02069718953027e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>2.144347377334153e-07</v>
+        <v>2.144347377334151e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>1.020716038434292e-07</v>
+        <v>1.020716038434291e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>1.416752070437095e-07</v>
+        <v>1.416752070437093e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>1.416752070437095e-07</v>
+        <v>1.416752070437093e-07</v>
       </c>
       <c r="G2" t="n">
         <v>1.052264079328105e-07</v>
@@ -2120,16 +2120,16 @@
         <v>1.034397850722308e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>1.028889910797144e-07</v>
+        <v>1.028889910797142e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>2.53794512537586e-07</v>
+        <v>2.537945125375858e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>1.101735099288043e-07</v>
+        <v>1.10173509928804e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>1.04274430787059e-07</v>
+        <v>1.042744307870591e-07</v>
       </c>
     </row>
     <row r="3">
@@ -2139,34 +2139,34 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.148977215290033e-07</v>
+        <v>1.148977215290031e-07</v>
       </c>
       <c r="C3" t="n">
         <v>2.274232340739318e-07</v>
       </c>
       <c r="D3" t="n">
-        <v>1.148998895434195e-07</v>
+        <v>1.148998895434192e-07</v>
       </c>
       <c r="E3" t="n">
-        <v>1.546263063133114e-07</v>
+        <v>1.546263063133113e-07</v>
       </c>
       <c r="F3" t="n">
-        <v>1.546263063133114e-07</v>
+        <v>1.546263063133113e-07</v>
       </c>
       <c r="G3" t="n">
-        <v>1.185285677619066e-07</v>
+        <v>1.185285677619062e-07</v>
       </c>
       <c r="H3" t="n">
-        <v>1.164767201596825e-07</v>
+        <v>1.164767201596824e-07</v>
       </c>
       <c r="I3" t="n">
-        <v>1.158377796214478e-07</v>
+        <v>1.158377796214476e-07</v>
       </c>
       <c r="J3" t="n">
-        <v>2.686535538533043e-07</v>
+        <v>2.686535538533042e-07</v>
       </c>
       <c r="K3" t="n">
-        <v>1.232436495153088e-07</v>
+        <v>1.232436495153087e-07</v>
       </c>
       <c r="L3" t="n">
         <v>1.17433155889255e-07</v>
@@ -2179,37 +2179,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.423953669344492e-08</v>
+        <v>1.177068453260482e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>5.276298087687674e-08</v>
+        <v>1.204089537115573e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>5.424065718091948e-08</v>
+        <v>1.177180502007924e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>5.48600042603438e-08</v>
+        <v>1.228131134591388e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>5.486000426034381e-08</v>
+        <v>1.228131134591388e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>5.627115845135468e-08</v>
+        <v>1.367450066054425e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>5.50548892699786e-08</v>
+        <v>1.258603710913805e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>5.575794046206887e-08</v>
+        <v>1.243930654670624e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>6.227754602509858e-08</v>
+        <v>1.980869386425835e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>5.519781459926845e-08</v>
+        <v>1.272896243842843e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>5.555023629862788e-08</v>
+        <v>1.308138413778783e-08</v>
       </c>
     </row>
     <row r="5">
@@ -2219,37 +2219,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.45781509447796e-07</v>
+        <v>2.788207165006924e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>2.054839300372183e-07</v>
+        <v>3.891978227772984e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>1.421066480188792e-07</v>
+        <v>2.723621932376424e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>1.892320865488189e-07</v>
+        <v>3.593079770053816e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>1.892320865488189e-07</v>
+        <v>3.593079770053816e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>3.226631327579275e-07</v>
+        <v>6.055948788444682e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>2.395206478875451e-07</v>
+        <v>4.505201044990952e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>1.892320360999687e-07</v>
+        <v>3.593074725168516e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>9.246775608220715e-07</v>
+        <v>1.715910956460767e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>2.308323946163564e-07</v>
+        <v>4.36406483539378e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>2.959928492823809e-07</v>
+        <v>5.539928379362444e-08</v>
       </c>
     </row>
     <row r="6">
@@ -2259,37 +2259,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8.652811010287601e-08</v>
+        <v>1.294970145129605e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>6.098037904753748e-08</v>
+        <v>1.348715744135499e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>6.0354338059134e-08</v>
+        <v>1.28478128488131e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>6.102964282832377e-08</v>
+        <v>1.336716772799454e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>6.239560663388989e-08</v>
+        <v>1.360757735647144e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>6.297011825294462e-08</v>
+        <v>1.935728954981147e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>9.234310935683846e-08</v>
+        <v>1.914876380886475e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>6.245690026365914e-08</v>
+        <v>1.812209543597333e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>6.998074292714438e-08</v>
+        <v>2.555515893312904e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>6.130067911872501e-08</v>
+        <v>1.38030665880326e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>6.242060836654097e-08</v>
+        <v>1.429056961518834e-08</v>
       </c>
     </row>
     <row r="7">
@@ -2299,37 +2299,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7.128577500176172e-08</v>
+        <v>1.4770822458612e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>7.188389398476031e-08</v>
+        <v>1.540617605990815e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>7.128586846444246e-08</v>
+        <v>1.477176218972373e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>7.261183313731671e-08</v>
+        <v>1.540563321133158e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>7.261183313731671e-08</v>
+        <v>1.540563321133158e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>7.331739675967026e-08</v>
+        <v>1.667463858655155e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>7.210112757829489e-08</v>
+        <v>1.558617503514524e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>7.280417877038574e-08</v>
+        <v>1.543944447271343e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>7.932378433341476e-08</v>
+        <v>2.280883179026552e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>7.224405290758553e-08</v>
+        <v>1.572910036443561e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>7.259647460694505e-08</v>
+        <v>1.608152206379501e-08</v>
       </c>
     </row>
     <row r="8">
@@ -2339,37 +2339,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9.384721739826438e-08</v>
+        <v>1.874163629888009e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>1.260967975717952e-07</v>
+        <v>2.494764703925702e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>1.322761722358115e-07</v>
+        <v>2.550605559531962e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>1.183310766318332e-07</v>
+        <v>2.345222002276528e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>9.626041157715996e-08</v>
+        <v>1.956778299419093e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>1.277069147058439e-07</v>
+        <v>2.62471936932078e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>1.264906455247419e-07</v>
+        <v>2.515873014185013e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>1.271936967165582e-07</v>
+        <v>2.50119995793699e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>1.337195573328388e-07</v>
+        <v>3.238248778628832e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>9.421427246629771e-08</v>
+        <v>1.959585898581652e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>1.602330788170945e-07</v>
+        <v>3.150556432120473e-08</v>
       </c>
     </row>
     <row r="9">
@@ -2379,37 +2379,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.04477443183222e-07</v>
+        <v>3.821255593152748e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>2.495241767338915e-07</v>
+        <v>4.667086565434421e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>2.489271973473069e-07</v>
+        <v>4.603663590369584e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>3.017372791290065e-07</v>
+        <v>5.573171148735781e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>2.504445048790439e-07</v>
+        <v>4.670418326828116e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>2.50957679508802e-07</v>
+        <v>4.793932818098757e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>2.497414103274259e-07</v>
+        <v>4.685086462958134e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>2.504444615195166e-07</v>
+        <v>4.670413406714956e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>2.569640670825465e-07</v>
+        <v>5.407352138470155e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>2.230857811853816e-07</v>
+        <v>3.714329093748671e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>2.50236757356076e-07</v>
+        <v>4.734621165823111e-08</v>
       </c>
     </row>
   </sheetData>
@@ -2495,37 +2495,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.056065160558009e-07</v>
+        <v>1.056065160557992e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>2.155964267699516e-07</v>
+        <v>2.155964267699513e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>1.053836972807465e-07</v>
+        <v>1.053836972807448e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>1.459735817260544e-07</v>
+        <v>1.45973581726054e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>1.459735817260544e-07</v>
+        <v>1.45973581726054e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>1.092484050737849e-07</v>
+        <v>1.092484050737831e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>1.074953879075962e-07</v>
+        <v>1.074953879075944e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>1.084992319943408e-07</v>
+        <v>1.08499231994339e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>2.576614385838703e-07</v>
+        <v>2.576614385838697e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>1.152954701170889e-07</v>
+        <v>1.152954701170809e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>1.078851350962272e-07</v>
+        <v>1.078851350962255e-07</v>
       </c>
     </row>
     <row r="3">
@@ -2535,37 +2535,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.190180232472781e-07</v>
+        <v>1.190180232472762e-07</v>
       </c>
       <c r="C3" t="n">
-        <v>2.290574108978236e-07</v>
+        <v>2.290574108978231e-07</v>
       </c>
       <c r="D3" t="n">
-        <v>1.187617354991954e-07</v>
+        <v>1.187617354991934e-07</v>
       </c>
       <c r="E3" t="n">
-        <v>1.598197901270581e-07</v>
+        <v>1.598197901270578e-07</v>
       </c>
       <c r="F3" t="n">
-        <v>1.598197901270581e-07</v>
+        <v>1.598197901270578e-07</v>
       </c>
       <c r="G3" t="n">
-        <v>1.23206950032997e-07</v>
+        <v>1.23206950032995e-07</v>
       </c>
       <c r="H3" t="n">
-        <v>1.211955864320139e-07</v>
+        <v>1.211955864320119e-07</v>
       </c>
       <c r="I3" t="n">
-        <v>1.22348720763197e-07</v>
+        <v>1.223487207631951e-07</v>
       </c>
       <c r="J3" t="n">
-        <v>2.731970998694065e-07</v>
+        <v>2.731970998694056e-07</v>
       </c>
       <c r="K3" t="n">
-        <v>1.292960184026986e-07</v>
+        <v>1.292960184026905e-07</v>
       </c>
       <c r="L3" t="n">
-        <v>1.216384318897076e-07</v>
+        <v>1.216384318897057e-07</v>
       </c>
     </row>
     <row r="4">
@@ -2575,37 +2575,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.261913567728439e-08</v>
+        <v>1.408429267818363e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>5.860635826167612e-08</v>
+        <v>1.355235340174776e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>6.2486679357147e-08</v>
+        <v>1.39518363580462e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>6.512818894050451e-08</v>
+        <v>1.594346860381682e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>6.51281889405055e-08</v>
+        <v>1.594346860381682e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>6.494056008252179e-08</v>
+        <v>1.62767811031971e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>6.37429658321142e-08</v>
+        <v>1.520812283301341e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>6.538181271081211e-08</v>
+        <v>1.598824243113652e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>7.10256569788336e-08</v>
+        <v>2.24908139797328e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>6.495031613126563e-08</v>
+        <v>1.641547313216467e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>6.397409504489894e-08</v>
+        <v>1.543925204579816e-08</v>
       </c>
     </row>
     <row r="5">
@@ -2615,37 +2615,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.189218699647047e-07</v>
+        <v>4.159357376370734e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>2.387271484654064e-07</v>
+        <v>4.525361230582745e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>2.002962530159894e-07</v>
+        <v>3.820632119057666e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>3.843609236386732e-07</v>
+        <v>7.212842960625047e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>3.843609236386732e-07</v>
+        <v>7.212842960625047e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>4.344384286987561e-07</v>
+        <v>8.130840562727265e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>3.582172106172657e-07</v>
+        <v>6.70355896343669e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>3.843610887405998e-07</v>
+        <v>7.212859470817715e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>1.079936052284801e-06</v>
+        <v>2.000590425914104e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>4.408101395012984e-07</v>
+        <v>8.256680168683885e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>3.903142554612116e-07</v>
+        <v>7.287511996784633e-08</v>
       </c>
     </row>
     <row r="6">
@@ -2655,37 +2655,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.046717427265487e-07</v>
+        <v>1.598868122052801e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>7.250381279983035e-08</v>
+        <v>1.599830538720907e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>7.269689388247279e-08</v>
+        <v>1.57488341047665e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>7.426599585050842e-08</v>
+        <v>1.755172261126305e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>7.623141691854126e-08</v>
+        <v>1.789763671736191e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>7.576094958629244e-08</v>
+        <v>1.818116964554149e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>1.148088114047338e-07</v>
+        <v>2.419571160509412e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>1.074344197600737e-07</v>
+        <v>1.7892630973481e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>1.149773747256063e-07</v>
+        <v>3.0226316261249e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>7.562986855836667e-08</v>
+        <v>1.829507434914948e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>7.484881840832269e-08</v>
+        <v>1.735320334738967e-08</v>
       </c>
     </row>
     <row r="7">
@@ -2695,37 +2695,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>8.406096882910174e-08</v>
+        <v>1.785805529245472e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>8.421910316130854e-08</v>
+        <v>1.806019647965651e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>8.3927696327503e-08</v>
+        <v>1.772545532438091e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>8.681617248987529e-08</v>
+        <v>1.976055368782224e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>8.681617248987529e-08</v>
+        <v>1.976055368782224e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>8.638239323433927e-08</v>
+        <v>2.005054371746817e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>8.518479898393152e-08</v>
+        <v>1.898188544728448e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>8.682364586262997e-08</v>
+        <v>1.976200504540773e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>9.246749013065092e-08</v>
+        <v>2.626457659400387e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>8.639214928308317e-08</v>
+        <v>2.018923574643573e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>8.54159281967163e-08</v>
+        <v>1.92130146600692e-08</v>
       </c>
     </row>
     <row r="8">
@@ -2735,37 +2735,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.12136687181905e-07</v>
+        <v>2.27993816957729e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>1.536551334296522e-07</v>
+        <v>3.028093774066532e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>1.619387429750876e-07</v>
+        <v>3.14553994599582e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>1.449482828347894e-07</v>
+        <v>2.999180505308738e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>1.162063284525945e-07</v>
+        <v>2.493322110923198e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>1.55816659395462e-07</v>
+        <v>3.227097449560773e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>1.546190651455742e-07</v>
+        <v>3.120231622551558e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>1.562579120237527e-07</v>
+        <v>3.198243582354743e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>1.619098842912976e-07</v>
+        <v>3.84864379000519e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>1.136996113885083e-07</v>
+        <v>2.499534905094811e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>1.980526557606032e-07</v>
+        <v>3.90370786038939e-08</v>
       </c>
     </row>
     <row r="9">
@@ -2775,37 +2775,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.647375562786113e-07</v>
+        <v>4.965713451125922e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>3.250996648913087e-07</v>
+        <v>6.045517511441345e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>3.248091000629832e-07</v>
+        <v>6.012058215210124e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>3.971781677967468e-07</v>
+        <v>7.438426456584399e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>3.277040362286715e-07</v>
+        <v>6.21568174761179e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>3.272629549643317e-07</v>
+        <v>6.244552235222517e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>3.260653607139303e-07</v>
+        <v>6.137686408204143e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>3.277042075926414e-07</v>
+        <v>6.215698368016466e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>3.333480518606535e-07</v>
+        <v>6.865955522876084e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>2.514651543295197e-07</v>
+        <v>4.924208447717974e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>3.26296489926715e-07</v>
+        <v>6.160799329482618e-08</v>
       </c>
     </row>
   </sheetData>
@@ -2891,13 +2891,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9.834689150825144e-08</v>
+        <v>9.83468915082516e-08</v>
       </c>
       <c r="C2" t="n">
         <v>2.13487766369352e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>9.883834744901421e-08</v>
+        <v>9.883834744901406e-08</v>
       </c>
       <c r="E2" t="n">
         <v>1.423447521284537e-07</v>
@@ -2906,22 +2906,22 @@
         <v>1.423447521284537e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>1.002038996589822e-07</v>
+        <v>1.00203899658982e-07</v>
       </c>
       <c r="H2" t="n">
         <v>9.94234258830829e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>9.966245043818162e-08</v>
+        <v>9.966245043818158e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>2.492191349076506e-07</v>
+        <v>2.492191349076508e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>1.102017242506274e-07</v>
+        <v>1.102017242506275e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>9.954209302687536e-08</v>
+        <v>9.954209302687537e-08</v>
       </c>
     </row>
     <row r="3">
@@ -2931,34 +2931,34 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.114200992142839e-07</v>
+        <v>1.114200992142837e-07</v>
       </c>
       <c r="C3" t="n">
-        <v>2.265725569752532e-07</v>
+        <v>2.26572556975253e-07</v>
       </c>
       <c r="D3" t="n">
-        <v>1.119853753509524e-07</v>
+        <v>1.119853753509522e-07</v>
       </c>
       <c r="E3" t="n">
-        <v>1.556157274047802e-07</v>
+        <v>1.556157274047798e-07</v>
       </c>
       <c r="F3" t="n">
-        <v>1.556157274047801e-07</v>
+        <v>1.556157274047798e-07</v>
       </c>
       <c r="G3" t="n">
-        <v>1.135560432657038e-07</v>
+        <v>1.135560432657035e-07</v>
       </c>
       <c r="H3" t="n">
         <v>1.126625744046795e-07</v>
       </c>
       <c r="I3" t="n">
-        <v>1.129345296562519e-07</v>
+        <v>1.12934529656252e-07</v>
       </c>
       <c r="J3" t="n">
-        <v>2.634768605247877e-07</v>
+        <v>2.634768605247878e-07</v>
       </c>
       <c r="K3" t="n">
-        <v>1.234310941496435e-07</v>
+        <v>1.234310941496432e-07</v>
       </c>
       <c r="L3" t="n">
         <v>1.127943239843909e-07</v>
@@ -2971,37 +2971,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.850934790218127e-08</v>
+        <v>1.246791747887187e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>5.422810564216429e-08</v>
+        <v>1.176627515079516e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>5.880149763421e-08</v>
+        <v>1.276006721090066e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>5.976283976480668e-08</v>
+        <v>1.333346205993625e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>5.976283976480675e-08</v>
+        <v>1.333346205993625e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>5.976913841555748e-08</v>
+        <v>1.359926463885699e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>5.915002201192764e-08</v>
+        <v>1.310859158861823e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>6.03304997418769e-08</v>
+        <v>1.343353054759363e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>6.319717873310781e-08</v>
+        <v>1.715574830979845e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>5.912737312242545e-08</v>
+        <v>1.308594269911607e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>5.921994150043491e-08</v>
+        <v>1.317851107712551e-08</v>
       </c>
     </row>
     <row r="5">
@@ -3011,37 +3011,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.238720196291545e-07</v>
+        <v>2.397174764048444e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>1.287581787161232e-07</v>
+        <v>2.488356794073456e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>1.476872447372841e-07</v>
+        <v>2.840395861627363e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>1.952785595650281e-07</v>
+        <v>3.718422861553661e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>1.952785595650281e-07</v>
+        <v>3.718422861553661e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>2.276934725790584e-07</v>
+        <v>4.315394729148649e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>1.97186307228915e-07</v>
+        <v>3.740297765516637e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>1.952787541429823e-07</v>
+        <v>3.718442319348632e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>5.7821150687105e-07</v>
+        <v>1.077982695709204e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>1.781759420446195e-07</v>
+        <v>3.40384907158887e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>2.076267055639832e-07</v>
+        <v>3.929810141077833e-08</v>
       </c>
     </row>
     <row r="6">
@@ -3051,37 +3051,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6.772149417727044e-08</v>
+        <v>1.408925521450221e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>6.675278390574542e-08</v>
+        <v>1.397061851324098e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>9.785928403860654e-08</v>
+        <v>1.432540652822884e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>6.777468136048561e-08</v>
+        <v>1.474354617313506e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>6.952575138406609e-08</v>
+        <v>1.505173449561523e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>6.898128469064674e-08</v>
+        <v>2.016759405456602e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>1.054266067400961e-07</v>
+        <v>2.125327045664309e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>6.954264601696614e-08</v>
+        <v>2.000185996330269e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>7.373592127368382e-08</v>
+        <v>1.901056698688928e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>6.803179117275805e-08</v>
+        <v>1.465312026748269e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>6.848233484490387e-08</v>
+        <v>1.480869229691835e-08</v>
       </c>
     </row>
     <row r="7">
@@ -3091,37 +3091,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7.716800686320428e-08</v>
+        <v>1.575184143821765e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>7.718067731232686e-08</v>
+        <v>1.580592774285453e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>7.745953957425603e-08</v>
+        <v>1.604388257455506e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>7.89026564492694e-08</v>
+        <v>1.670206977814853e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>7.89026564492694e-08</v>
+        <v>1.670206977814853e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>7.84277973765806e-08</v>
+        <v>1.688318859820229e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>7.780868097295064e-08</v>
+        <v>1.639251554796403e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>7.898915870289994e-08</v>
+        <v>1.671745450693943e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>8.185583769413088e-08</v>
+        <v>2.043967226914422e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>7.778603208344851e-08</v>
+        <v>1.636986665846183e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>7.787860046145797e-08</v>
+        <v>1.64624350364713e-08</v>
       </c>
     </row>
     <row r="8">
@@ -3131,37 +3131,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.025842432494367e-07</v>
+        <v>2.022509901795573e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>1.393097780103897e-07</v>
+        <v>2.67406494064626e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>1.47292313014995e-07</v>
+        <v>2.833445063352733e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>1.310650516602056e-07</v>
+        <v>2.588265128552738e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>1.055201965685888e-07</v>
+        <v>2.138675681376426e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>1.406317758358645e-07</v>
+        <v>2.783108874771389e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>1.400126594328921e-07</v>
+        <v>2.734041569759136e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>1.411931371621839e-07</v>
+        <v>2.766535465645101e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>1.440670458741305e-07</v>
+        <v>3.138884484949492e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>1.025189172841169e-07</v>
+        <v>2.072285443019229e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>1.785104515434081e-07</v>
+        <v>3.417364073092452e-08</v>
       </c>
     </row>
     <row r="9">
@@ -3171,37 +3171,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.248489987967652e-07</v>
+        <v>4.174369587768475e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>2.74686582655959e-07</v>
+        <v>5.056696689497744e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>2.74966082968881e-07</v>
+        <v>5.080503402365213e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>3.339917758379314e-07</v>
+        <v>6.159775454728101e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>2.764948644623929e-07</v>
+        <v>5.147829820001963e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>2.759337027202127e-07</v>
+        <v>5.164422775032538e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>2.753145863165829e-07</v>
+        <v>5.115355470008692e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>2.764950640465321e-07</v>
+        <v>5.147849365906237e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>2.79361743037763e-07</v>
+        <v>5.520071142126723e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>2.464231957648908e-07</v>
+        <v>4.008893600412368e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>2.753845058050902e-07</v>
+        <v>5.122347418859434e-08</v>
       </c>
     </row>
   </sheetData>
@@ -3287,37 +3287,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.990903701160592e-08</v>
+        <v>8.990903701160585e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>2.128377353039319e-07</v>
+        <v>2.128377353039321e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>9.037161511455278e-08</v>
+        <v>9.037161511455274e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>1.408342396933718e-07</v>
+        <v>1.408342396933717e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>1.408342396933718e-07</v>
+        <v>1.408342396933717e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>9.058878265473358e-08</v>
+        <v>9.058878265473349e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>9.079717553629253e-08</v>
+        <v>9.079717553629245e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>9.065237370466722e-08</v>
+        <v>9.06523737046672e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>2.422702513348343e-07</v>
+        <v>2.422702513348341e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>1.078339248319998e-07</v>
+        <v>1.078339248319997e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>9.024002295931514e-08</v>
+        <v>9.02400229593151e-08</v>
       </c>
     </row>
     <row r="3">
@@ -3348,7 +3348,7 @@
         <v>1.03699806368947e-07</v>
       </c>
       <c r="I3" t="n">
-        <v>1.035273106430812e-07</v>
+        <v>1.035273106430811e-07</v>
       </c>
       <c r="J3" t="n">
         <v>2.554328283660024e-07</v>
@@ -3367,37 +3367,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.313907680908307e-08</v>
+        <v>1.119965072344851e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>4.923651167165346e-08</v>
+        <v>1.062895636503081e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>5.341405989018812e-08</v>
+        <v>1.147463380455349e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>5.347942829035527e-08</v>
+        <v>1.162395412062144e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>5.347942829035527e-08</v>
+        <v>1.162395412062242e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>5.37006784886856e-08</v>
+        <v>1.163145452372479e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>5.366744945455715e-08</v>
+        <v>1.172802336892244e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>5.462867520740298e-08</v>
+        <v>1.182644842030576e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>5.470766283329231e-08</v>
+        <v>1.276823674765779e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>5.314923083042369e-08</v>
+        <v>1.120980474478915e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>5.333571200548206e-08</v>
+        <v>1.139628591984745e-08</v>
       </c>
     </row>
     <row r="5">
@@ -3407,37 +3407,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.086259700583255e-07</v>
+        <v>2.096534388239871e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>1.207816991788842e-07</v>
+        <v>2.322090929807402e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>1.310487974244816e-07</v>
+        <v>2.513834753655085e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>1.484961536398034e-07</v>
+        <v>2.834689769150478e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>1.484961536398034e-07</v>
+        <v>2.834689769150478e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>1.46028338709559e-07</v>
+        <v>2.788112263454743e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>1.687959794481702e-07</v>
+        <v>3.199064453800289e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>1.484964289351586e-07</v>
+        <v>2.83471729868686e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>2.607276208915172e-07</v>
+        <v>4.902774916942997e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>1.069691844812011e-07</v>
+        <v>2.068211653599924e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>1.360835992162753e-07</v>
+        <v>2.595991399003248e-08</v>
       </c>
     </row>
     <row r="6">
@@ -3447,37 +3447,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8.550940944471643e-08</v>
+        <v>1.689682923644887e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>5.97101023256961e-08</v>
+        <v>1.247230831015388e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>6.056329899809638e-08</v>
+        <v>1.27328998807273e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>6.048437444060108e-08</v>
+        <v>1.285682463638584e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>6.184932127637993e-08</v>
+        <v>1.309705527818069e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>8.60710111243188e-08</v>
+        <v>1.732863303672547e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>9.227386031386606e-08</v>
+        <v>1.852275164334245e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>6.191247229568141e-08</v>
+        <v>1.310839670089668e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>8.798076322561988e-08</v>
+        <v>1.862430238497547e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>6.000228479847475e-08</v>
+        <v>1.241594223663079e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>6.067188564256839e-08</v>
+        <v>1.268745247297833e-08</v>
       </c>
     </row>
     <row r="7">
@@ -3487,37 +3487,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6.915160531906343e-08</v>
+        <v>1.40178557259343e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>6.924956523909359e-08</v>
+        <v>1.415125377381429e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>6.942595258858516e-08</v>
+        <v>1.429272690420123e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>7.036086972841316e-08</v>
+        <v>1.459508779762204e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>7.036086972841316e-08</v>
+        <v>1.459508779762204e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>6.971320699866597e-08</v>
+        <v>1.444965952621019e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>6.96799779645373e-08</v>
+        <v>1.454622837140825e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>7.064120371738333e-08</v>
+        <v>1.464465342279288e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>7.072019134327285e-08</v>
+        <v>1.55864417501436e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>6.916175934040409e-08</v>
+        <v>1.402800974727494e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>6.934824051546237e-08</v>
+        <v>1.421449092233326e-08</v>
       </c>
     </row>
     <row r="8">
@@ -3527,37 +3527,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9.143372811500925e-08</v>
+        <v>1.793950931677087e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>1.225485490349331e-07</v>
+        <v>2.353187487105216e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>1.294724978363602e-07</v>
+        <v>2.486091881054478e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>1.1541351230981e-07</v>
+        <v>2.252435284898222e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>9.374782861390082e-08</v>
+        <v>1.871119253916477e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>1.232734039971192e-07</v>
+        <v>2.387625414685891e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>1.23240174963387e-07</v>
+        <v>2.397282299212673e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>1.242014007158365e-07</v>
+        <v>2.407124804344251e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>1.242865352893284e-07</v>
+        <v>2.501411823356452e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>9.086287585713504e-08</v>
+        <v>1.784740623352381e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>1.555810013663849e-07</v>
+        <v>2.939145674985762e-08</v>
       </c>
     </row>
     <row r="9">
@@ -3567,37 +3567,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.000846401221856e-07</v>
+        <v>3.706206972641633e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>2.438444379860768e-07</v>
+        <v>4.487995121077656e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>2.440214775620374e-07</v>
+        <v>4.502153913302152e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>2.956206445564551e-07</v>
+        <v>5.424080795253119e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>2.45235795842638e-07</v>
+        <v>4.537307462694971e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>2.443080797456488e-07</v>
+        <v>4.517835696317266e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>2.442748507115201e-07</v>
+        <v>4.527492580837048e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>2.45236076464366e-07</v>
+        <v>4.537335085975369e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>2.453150640902556e-07</v>
+        <v>4.631513918710585e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>2.184587986134794e-07</v>
+        <v>4.0123648150166e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>2.439431132624449e-07</v>
+        <v>4.49431883592955e-08</v>
       </c>
     </row>
   </sheetData>
@@ -3683,37 +3683,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.004053293809179e-07</v>
+        <v>1.004053293809182e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>2.133634322171047e-07</v>
+        <v>2.133634322171046e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>1.003939183432681e-07</v>
+        <v>1.003939183432686e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>1.440756876922427e-07</v>
+        <v>1.440756876922425e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>1.440756876922427e-07</v>
+        <v>1.440756876922425e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>1.038573810600546e-07</v>
+        <v>1.03857381060055e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>1.026188066099513e-07</v>
+        <v>1.026188066099517e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>1.022951070261368e-07</v>
+        <v>1.022951070261372e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>2.575995464950281e-07</v>
+        <v>2.575995464950279e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>1.134771654975207e-07</v>
+        <v>1.134771654975234e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>1.023054270066437e-07</v>
+        <v>1.023054270066431e-07</v>
       </c>
     </row>
     <row r="3">
@@ -3723,37 +3723,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.136827272201112e-07</v>
+        <v>1.136827272201114e-07</v>
       </c>
       <c r="C3" t="n">
         <v>2.265494916303551e-07</v>
       </c>
       <c r="D3" t="n">
-        <v>1.136696021630248e-07</v>
+        <v>1.136696021630251e-07</v>
       </c>
       <c r="E3" t="n">
-        <v>1.576371086312556e-07</v>
+        <v>1.576371086312557e-07</v>
       </c>
       <c r="F3" t="n">
-        <v>1.576371086312556e-07</v>
+        <v>1.576371086312555e-07</v>
       </c>
       <c r="G3" t="n">
-        <v>1.176533017414696e-07</v>
+        <v>1.176533017414697e-07</v>
       </c>
       <c r="H3" t="n">
-        <v>1.162334814311471e-07</v>
+        <v>1.162334814311475e-07</v>
       </c>
       <c r="I3" t="n">
-        <v>1.15858342469015e-07</v>
+        <v>1.158583424690152e-07</v>
       </c>
       <c r="J3" t="n">
-        <v>2.731185422917825e-07</v>
+        <v>2.731185422917824e-07</v>
       </c>
       <c r="K3" t="n">
-        <v>1.272087467685665e-07</v>
+        <v>1.272087467685692e-07</v>
       </c>
       <c r="L3" t="n">
-        <v>1.158677634061756e-07</v>
+        <v>1.158677634061753e-07</v>
       </c>
     </row>
     <row r="4">
@@ -3763,37 +3763,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.145807268190228e-08</v>
+        <v>1.35074054800105e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>5.692978940633288e-08</v>
+        <v>1.242545611169527e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>6.14512893035463e-08</v>
+        <v>1.350062210165459e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>6.319641746718286e-08</v>
+        <v>1.473956780415945e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>6.319641746718287e-08</v>
+        <v>1.473956780415945e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>6.366494322923724e-08</v>
+        <v>1.558674381685895e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>6.277473849898645e-08</v>
+        <v>1.482407129709496e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>6.361339692716292e-08</v>
+        <v>1.481300001484448e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>7.032938810692479e-08</v>
+        <v>2.23787209050328e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>6.325554241602239e-08</v>
+        <v>1.530487521413072e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>6.258801749284171e-08</v>
+        <v>1.463735029094989e-08</v>
       </c>
     </row>
     <row r="5">
@@ -3803,37 +3803,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.799094287181145e-07</v>
+        <v>3.435484402941996e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>1.442875227687229e-07</v>
+        <v>2.78004171001651e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>1.746148802640062e-07</v>
+        <v>3.341741400277429e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>2.876914541579533e-07</v>
+        <v>5.425069404764191e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>2.876914541579533e-07</v>
+        <v>5.425069404764191e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>3.8418186338264e-07</v>
+        <v>7.1997721458189e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>3.365817976883477e-07</v>
+        <v>6.301411345329886e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>2.876915073450001e-07</v>
+        <v>5.425074723468734e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>1.087547282985087e-06</v>
+        <v>2.014090694334945e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>3.508195337918534e-07</v>
+        <v>6.591613742203553e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>3.21451847650899e-07</v>
+        <v>6.019738415189589e-08</v>
       </c>
     </row>
     <row r="6">
@@ -3843,37 +3843,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.026702590665428e-07</v>
+        <v>1.535257597567248e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>7.03843881833333e-08</v>
+        <v>1.479346548361607e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>7.138356364894432e-08</v>
+        <v>1.524870237697237e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>7.209160726127153e-08</v>
+        <v>1.630512119943578e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>7.409229644022859e-08</v>
+        <v>1.665724249302433e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>1.048771296138777e-07</v>
+        <v>2.284008858125167e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>1.130021068588834e-07</v>
+        <v>2.36640880805363e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>7.409732025478006e-08</v>
+        <v>2.206634477923769e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>1.134079201236013e-07</v>
+        <v>2.996054249888529e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>7.35106301003111e-08</v>
+        <v>1.710977063678583e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>7.312231605665167e-08</v>
+        <v>1.649138682813439e-08</v>
       </c>
     </row>
     <row r="7">
@@ -3883,37 +3883,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>8.228538824968249e-08</v>
+        <v>1.717301300007731e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>8.188486937132623e-08</v>
+        <v>1.681755016173493e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>8.227777994058522e-08</v>
+        <v>1.716608443391206e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>8.439586833784021e-08</v>
+        <v>1.847067113717759e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>8.439586833784021e-08</v>
+        <v>1.847067113717759e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>8.449225879701743e-08</v>
+        <v>1.925235133692569e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>8.36020540667666e-08</v>
+        <v>1.848967881716154e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>8.44407124949431e-08</v>
+        <v>1.847860753491148e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>9.11567036747049e-08</v>
+        <v>2.604432842509981e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>8.408285798380251e-08</v>
+        <v>1.897048273419711e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>8.341533306062195e-08</v>
+        <v>1.83029578110168e-08</v>
       </c>
     </row>
     <row r="8">
@@ -3923,37 +3923,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.099076949170477e-07</v>
+        <v>2.203453894719173e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>1.499796779068911e-07</v>
+        <v>2.880223639905436e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>1.58806946074929e-07</v>
+        <v>3.063521760057232e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>1.414609968009227e-07</v>
+        <v>2.851413369225891e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>1.133207381918498e-07</v>
+        <v>2.356144820389879e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>1.526212707846649e-07</v>
+        <v>3.124305738177902e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>1.517310660549516e-07</v>
+        <v>3.048038486210972e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>1.525697244825904e-07</v>
+        <v>3.046931357976492e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>1.592936762519159e-07</v>
+        <v>3.80364355337084e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>1.109527318152158e-07</v>
+        <v>2.369958050290181e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>1.938569857437703e-07</v>
+        <v>3.774068857792615e-08</v>
       </c>
     </row>
     <row r="9">
@@ -3963,37 +3963,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.615377970548891e-07</v>
+        <v>4.872143677884904e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>3.207020152323788e-07</v>
+        <v>5.884936760553165e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>3.210957757772432e-07</v>
+        <v>5.919805147341373e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>3.919942633310872e-07</v>
+        <v>7.260798836264699e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>3.232577987178405e-07</v>
+        <v>6.051037065626643e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>3.2330940465807e-07</v>
+        <v>6.128416878072233e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>3.224191999278191e-07</v>
+        <v>6.052149626095832e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>3.232578583559957e-07</v>
+        <v>6.051042497870833e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>3.299738495357574e-07</v>
+        <v>6.807614586889643e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>2.869877740482974e-07</v>
+        <v>5.492818257095809e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>3.222324789216745e-07</v>
+        <v>6.033477525481339e-08</v>
       </c>
     </row>
   </sheetData>
@@ -4079,37 +4079,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.795514146741702e-08</v>
+        <v>7.795514146741952e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>2.123106631064701e-07</v>
+        <v>2.123106631064706e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>7.837419367133432e-08</v>
+        <v>7.837419367133641e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>1.409687076024567e-07</v>
+        <v>1.409687076024574e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>1.409687076024567e-07</v>
+        <v>1.409687076024574e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>7.862486432881672e-08</v>
+        <v>7.862486432881873e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>7.891112394524861e-08</v>
+        <v>7.891112394525106e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>7.875494806265793e-08</v>
+        <v>7.875494806266016e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>2.418362256939367e-07</v>
+        <v>2.418362256939369e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>1.085426807112648e-07</v>
+        <v>1.085426807112779e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>7.821850100120056e-08</v>
+        <v>7.821850100120281e-08</v>
       </c>
     </row>
     <row r="3">
@@ -4119,37 +4119,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9.090944064621661e-08</v>
+        <v>9.090944064621904e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>2.252787979762045e-07</v>
+        <v>2.252787979762051e-07</v>
       </c>
       <c r="D3" t="n">
-        <v>9.139143748712393e-08</v>
+        <v>9.139143748712614e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>1.540432834617855e-07</v>
+        <v>1.540432834617857e-07</v>
       </c>
       <c r="F3" t="n">
-        <v>1.540432834617854e-07</v>
+        <v>1.540432834617861e-07</v>
       </c>
       <c r="G3" t="n">
-        <v>9.167976066949929e-08</v>
+        <v>9.167976066950113e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>9.201275924315201e-08</v>
+        <v>9.201275924315458e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>9.182782578960567e-08</v>
+        <v>9.182782578960816e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>2.549607055518282e-07</v>
+        <v>2.549607055518286e-07</v>
       </c>
       <c r="K3" t="n">
-        <v>1.215091549711413e-07</v>
+        <v>1.215091549711544e-07</v>
       </c>
       <c r="L3" t="n">
-        <v>9.121184618797094e-08</v>
+        <v>9.121184618797325e-08</v>
       </c>
     </row>
     <row r="4">
@@ -4159,37 +4159,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.680794424213632e-08</v>
+        <v>1.206258281197867e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>5.277612627953169e-08</v>
+        <v>1.141113836994236e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>5.705705302059488e-08</v>
+        <v>1.23116915904591e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>5.736142500026693e-08</v>
+        <v>1.255222374218273e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>5.736142500026697e-08</v>
+        <v>1.255222374218273e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>5.736217179664059e-08</v>
+        <v>1.248817927615156e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>5.737667423149531e-08</v>
+        <v>1.263131280149303e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>5.83231776799017e-08</v>
+        <v>1.272172209267409e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>5.748144881885205e-08</v>
+        <v>1.273608738864783e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>5.685612816542373e-08</v>
+        <v>1.21107667355027e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>5.696445243225699e-08</v>
+        <v>1.221909100207616e-08</v>
       </c>
     </row>
     <row r="5">
@@ -4199,37 +4199,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.217144887079316e-07</v>
+        <v>2.348613457606376e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>1.272786265084084e-07</v>
+        <v>2.452357833917522e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>1.415090950417314e-07</v>
+        <v>2.71752509056641e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>1.645734103356767e-07</v>
+        <v>3.142153305896547e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>1.645734103356767e-07</v>
+        <v>3.142153305896547e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>1.586303734952429e-07</v>
+        <v>3.031138267855531e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>1.872968868562334e-07</v>
+        <v>3.549727009950459e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>1.645736893159961e-07</v>
+        <v>3.142181203929642e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>1.875543235328552e-07</v>
+        <v>3.562891321424191e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>1.233627236125817e-07</v>
+        <v>2.381592747072587e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>1.463767257111757e-07</v>
+        <v>2.795565101389713e-08</v>
       </c>
     </row>
     <row r="6">
@@ -4239,37 +4239,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9.181241908799545e-08</v>
+        <v>1.348879091662546e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>6.409431807015638e-08</v>
+        <v>1.3403140114299e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>6.489324419648792e-08</v>
+        <v>1.369080626879345e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>6.480588643708564e-08</v>
+        <v>1.386244894796356e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>6.637938387617812e-08</v>
+        <v>1.41393844957433e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>6.546562698092784e-08</v>
+        <v>1.391438738079777e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>1.013035733320772e-07</v>
+        <v>2.0362447001295e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>6.642663286384538e-08</v>
+        <v>1.888250963215307e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>6.667776724851913e-08</v>
+        <v>1.91738915082965e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>6.445390423294896e-08</v>
+        <v>1.344797531609854e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>6.511743560300961e-08</v>
+        <v>1.365401603238351e-08</v>
       </c>
     </row>
     <row r="7">
@@ -4279,37 +4279,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7.415335042059936e-08</v>
+        <v>1.511537428283781e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>7.417767658219045e-08</v>
+        <v>1.517781120280123e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>7.440182163081611e-08</v>
+        <v>1.536437084934313e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>7.545835999261322e-08</v>
+        <v>1.573728428357852e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>7.545835999261322e-08</v>
+        <v>1.573728428357852e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>7.470757797458331e-08</v>
+        <v>1.554097074701066e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>7.472208041032822e-08</v>
+        <v>1.568410427235218e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>7.566858385830957e-08</v>
+        <v>1.577451356353297e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>7.482685499738934e-08</v>
+        <v>1.578887885950698e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>7.42015343441835e-08</v>
+        <v>1.516355820636183e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>7.430985861079403e-08</v>
+        <v>1.52718824729353e-08</v>
       </c>
     </row>
     <row r="8">
@@ -4319,37 +4319,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9.829923179070694e-08</v>
+        <v>1.93650493809916e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>1.326676745220138e-07</v>
+        <v>2.547205078442996e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>1.402475222187235e-07</v>
+        <v>2.695321408991223e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>1.247332197792825e-07</v>
+        <v>2.440965955903995e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>1.007841125455513e-07</v>
+        <v>2.01946167087425e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>1.333910471739611e-07</v>
+        <v>2.586926127010076e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>1.334055496104083e-07</v>
+        <v>2.601239479557311e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>1.343520530574844e-07</v>
+        <v>2.610280408662291e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>1.335171117072591e-07</v>
+        <v>2.611836398448121e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>9.770586229843336e-08</v>
+        <v>1.930031990390874e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>1.690707261785696e-07</v>
+        <v>3.194979507452617e-08</v>
       </c>
     </row>
     <row r="9">
@@ -4359,37 +4359,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.205187484233153e-07</v>
+        <v>4.087568419173972e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>2.693760922794383e-07</v>
+        <v>4.953273217936335e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>2.696008929516891e-07</v>
+        <v>4.971940721567351e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>3.272189973938355e-07</v>
+        <v>6.004715622609884e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>2.708667153788172e-07</v>
+        <v>5.012915464519647e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>2.699059936723563e-07</v>
+        <v>4.989589172357289e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>2.69920496107435e-07</v>
+        <v>5.003902524891436e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>2.708669995555576e-07</v>
+        <v>5.01294345400955e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>2.700252706946445e-07</v>
+        <v>5.014379983606917e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>2.079104594218125e-07</v>
+        <v>4.45387291132463e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>2.69508274308123e-07</v>
+        <v>4.96268034494975e-08</v>
       </c>
     </row>
   </sheetData>
@@ -4475,37 +4475,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.52519470086792e-08</v>
+        <v>8.525194700867863e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>2.11241663515843e-07</v>
+        <v>2.112416635158429e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>8.562368080421149e-08</v>
+        <v>8.562368080421096e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>1.398408941086835e-07</v>
+        <v>1.398408941086834e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>1.398408941086835e-07</v>
+        <v>1.398408941086834e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>8.563816371646444e-08</v>
+        <v>8.563816371646391e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>8.611052017531903e-08</v>
+        <v>8.611052017531826e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>8.562361262783162e-08</v>
+        <v>8.562361262783097e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>2.398156473563047e-07</v>
+        <v>2.398156473563049e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>1.072442791598591e-07</v>
+        <v>1.07244279159854e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>8.552936782835847e-08</v>
+        <v>8.552936782835797e-08</v>
       </c>
     </row>
     <row r="3">
@@ -4515,37 +4515,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9.787312997034366e-08</v>
+        <v>9.787312997034314e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>2.238909546422295e-07</v>
+        <v>2.238909546422294e-07</v>
       </c>
       <c r="D3" t="n">
-        <v>9.830070083962971e-08</v>
+        <v>9.830070083962911e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>1.525179634687965e-07</v>
+        <v>1.525179634687963e-07</v>
       </c>
       <c r="F3" t="n">
-        <v>1.525179634687965e-07</v>
+        <v>1.525179634687963e-07</v>
       </c>
       <c r="G3" t="n">
-        <v>9.831735918884671e-08</v>
+        <v>9.831735918884666e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>9.886315229537317e-08</v>
+        <v>9.886315229537237e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>9.829702804294931e-08</v>
+        <v>9.82970280429486e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>2.525639132150171e-07</v>
+        <v>2.525639132150173e-07</v>
       </c>
       <c r="K3" t="n">
-        <v>1.198710695709313e-07</v>
+        <v>1.198710695709262e-07</v>
       </c>
       <c r="L3" t="n">
-        <v>9.819162901873225e-08</v>
+        <v>9.819162901873138e-08</v>
       </c>
     </row>
     <row r="4">
@@ -4555,37 +4555,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.114123894779727e-08</v>
+        <v>1.075233437947176e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>4.745878122039371e-08</v>
+        <v>1.020717666805376e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>5.136221893754399e-08</v>
+        <v>1.097331436921863e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>5.121641381509028e-08</v>
+        <v>1.094781351812156e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>5.121641381509115e-08</v>
+        <v>1.094781351812156e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>5.152867145654841e-08</v>
+        <v>1.100970422198943e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>5.1651920242092e-08</v>
+        <v>1.126301567376642e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>5.241098984423672e-08</v>
+        <v>1.115827486592582e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>5.164418037002395e-08</v>
+        <v>1.125527580169836e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>5.116343090789302e-08</v>
+        <v>1.077452633956743e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>5.130594166056524e-08</v>
+        <v>1.091703709223966e-08</v>
       </c>
     </row>
     <row r="5">
@@ -4595,37 +4595,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.061617520130518e-07</v>
+        <v>2.043594462648524e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>1.167832476004582e-07</v>
+        <v>2.240828268483194e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>1.2358935912467e-07</v>
+        <v>2.368529097327197e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>1.254628820741955e-07</v>
+        <v>2.401519186091682e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>1.254628820741955e-07</v>
+        <v>2.401519186091682e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>1.269706319306635e-07</v>
+        <v>2.428748919348703e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>1.642437170014524e-07</v>
+        <v>3.107917179603738e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>1.254631441710546e-07</v>
+        <v>2.401545395777792e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>1.550505428893864e-07</v>
+        <v>2.945479550648946e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>1.055765008182877e-07</v>
+        <v>2.035122659190405e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>1.299450732785397e-07</v>
+        <v>2.475752418200639e-08</v>
       </c>
     </row>
     <row r="6">
@@ -4635,37 +4635,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8.103723567638547e-08</v>
+        <v>1.184840692180794e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>5.669464286910273e-08</v>
+        <v>1.183268830941844e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>5.729929387358611e-08</v>
+        <v>1.201823955229964e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>5.737002560346297e-08</v>
+        <v>1.203084918700671e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>5.85645572014953e-08</v>
+        <v>1.224108674712078e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>8.142466818513715e-08</v>
+        <v>1.627139961770979e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>8.798656405233184e-08</v>
+        <v>1.765791294971737e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>5.86386747776215e-08</v>
+        <v>1.641997026164609e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>8.224368840276342e-08</v>
+        <v>1.249516941227595e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>5.683911728391546e-08</v>
+        <v>1.177344713633434e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>5.756245983199006e-08</v>
+        <v>1.201818428444342e-08</v>
       </c>
     </row>
     <row r="7">
@@ -4675,37 +4675,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6.600398429703629e-08</v>
+        <v>1.336817754676363e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>6.60885750022809e-08</v>
+        <v>1.348602035589932e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>6.622429074737348e-08</v>
+        <v>1.358903899357505e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>6.697416055577148e-08</v>
+        <v>1.372117692945373e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>6.697416055577148e-08</v>
+        <v>1.372117692945373e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>6.639141680578775e-08</v>
+        <v>1.362554738928135e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>6.651466559133092e-08</v>
+        <v>1.387885884105831e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>6.727373519347608e-08</v>
+        <v>1.37741180332177e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>6.650692571926289e-08</v>
+        <v>1.387111896899023e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>6.602617625713201e-08</v>
+        <v>1.33903695068593e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>6.616868700980415e-08</v>
+        <v>1.353288025953155e-08</v>
       </c>
     </row>
     <row r="8">
@@ -4715,37 +4715,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>8.695580926490402e-08</v>
+        <v>1.705569872112701e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>1.156769686802354e-07</v>
+        <v>2.221357759592807e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>1.22089444672073e-07</v>
+        <v>2.342130603104492e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>1.089832920482042e-07</v>
+        <v>2.111478403205895e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>8.896375728067946e-08</v>
+        <v>1.75913459320664e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>1.162598500880255e-07</v>
+        <v>2.240239159939684e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>1.163830988740909e-07</v>
+        <v>2.265570305126561e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>1.171421684757142e-07</v>
+        <v>2.255096224333336e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>1.163810418692298e-07</v>
+        <v>2.264896336382057e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>8.644086038552577e-08</v>
+        <v>1.698335389398733e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>1.462429355767456e-07</v>
+        <v>2.762594793094825e-08</v>
       </c>
     </row>
     <row r="9">
@@ -4755,37 +4755,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.964597067317535e-07</v>
+        <v>3.63283845708587e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>2.394141980251839e-07</v>
+        <v>4.399132984263039e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>2.395506021129218e-07</v>
+        <v>4.409446962861109e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>2.900700591642802e-07</v>
+        <v>5.2986054871786e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>2.405990908178511e-07</v>
+        <v>4.427916448999455e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>2.3971703982869e-07</v>
+        <v>4.413085687601229e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>2.398402886142336e-07</v>
+        <v>4.438416832778943e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>2.405993582163784e-07</v>
+        <v>4.427942751994883e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>2.398325487421651e-07</v>
+        <v>4.437642845572133e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>2.135050672438568e-07</v>
+        <v>3.9346654179873e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>2.394943100327066e-07</v>
+        <v>4.403818974626267e-08</v>
       </c>
     </row>
   </sheetData>
@@ -4871,13 +4871,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.478869597436291e-07</v>
+        <v>1.478869597436293e-07</v>
       </c>
       <c r="C2" t="n">
         <v>3.732555823088587e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>1.464128921206034e-07</v>
+        <v>1.464128921206035e-07</v>
       </c>
       <c r="E2" t="n">
         <v>4.01691181531555e-07</v>
@@ -4886,19 +4886,19 @@
         <v>2.638127103639794e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>1.556618573788221e-07</v>
+        <v>1.55661857378822e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>1.49311164289218e-07</v>
+        <v>1.493111642892181e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>1.533080508107495e-07</v>
+        <v>1.533080508107494e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>3.529528443471391e-07</v>
+        <v>3.529528443471387e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>1.264951152782646e-07</v>
+        <v>1.264951152782647e-07</v>
       </c>
       <c r="L2" t="n">
         <v>1.484308858033812e-07</v>
@@ -4914,13 +4914,13 @@
         <v>1.659272470966602e-07</v>
       </c>
       <c r="C3" t="n">
-        <v>3.921073475925794e-07</v>
+        <v>3.921073475925796e-07</v>
       </c>
       <c r="D3" t="n">
         <v>1.642317639779923e-07</v>
       </c>
       <c r="E3" t="n">
-        <v>4.20546311154799e-07</v>
+        <v>4.205463111547988e-07</v>
       </c>
       <c r="F3" t="n">
         <v>2.826678399872232e-07</v>
@@ -4929,7 +4929,7 @@
         <v>1.748699899423251e-07</v>
       </c>
       <c r="H3" t="n">
-        <v>1.675697784609576e-07</v>
+        <v>1.675697784609578e-07</v>
       </c>
       <c r="I3" t="n">
         <v>1.72176156435315e-07</v>
@@ -4941,7 +4941,7 @@
         <v>1.45254950105737e-07</v>
       </c>
       <c r="L3" t="n">
-        <v>1.665527345453487e-07</v>
+        <v>1.665527345453488e-07</v>
       </c>
     </row>
     <row r="4">
@@ -4951,37 +4951,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.00508869095753e-08</v>
+        <v>1.67410717321485e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>7.597676896202659e-08</v>
+        <v>2.044126936011949e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>6.917461616923007e-08</v>
+        <v>1.586480099180328e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>7.717018811793926e-08</v>
+        <v>2.06513104501668e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>7.717018811793928e-08</v>
+        <v>2.06513104501668e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>7.514019653524424e-08</v>
+        <v>2.144519231348112e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>7.089952457031434e-08</v>
+        <v>1.758970939288751e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>7.638861024232059e-08</v>
+        <v>2.051371555901334e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>1.12154063993769e-07</v>
+        <v>5.884424881634207e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>7.289855751326952e-08</v>
+        <v>1.958874233584274e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>7.037620623864857e-08</v>
+        <v>1.706639106122176e-08</v>
       </c>
     </row>
     <row r="5">
@@ -4991,37 +4991,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.6145064406395e-07</v>
+        <v>6.802742871341891e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>6.616814127026146e-07</v>
+        <v>1.235252860998916e-07</v>
       </c>
       <c r="D5" t="n">
-        <v>2.82201806591208e-07</v>
+        <v>5.335758630291295e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>6.616814118770615e-07</v>
+        <v>1.235252852743392e-07</v>
       </c>
       <c r="F5" t="n">
-        <v>6.616814118770615e-07</v>
+        <v>1.235252852743392e-07</v>
       </c>
       <c r="G5" t="n">
-        <v>8.331035684409985e-07</v>
+        <v>1.548467450460437e-07</v>
       </c>
       <c r="H5" t="n">
-        <v>5.004071141614832e-07</v>
+        <v>9.31830447513233e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>6.616813667486764e-07</v>
+        <v>1.235252401459532e-07</v>
       </c>
       <c r="J5" t="n">
-        <v>4.732222671111348e-06</v>
+        <v>8.71976319262993e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>6.426590438073416e-07</v>
+        <v>1.198665873802335e-07</v>
       </c>
       <c r="L5" t="n">
-        <v>9.293843238821752e-07</v>
+        <v>1.682518189472684e-07</v>
       </c>
     </row>
     <row r="6">
@@ -5031,37 +5031,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.152422122948856e-07</v>
+        <v>2.469474495686573e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>9.231090738055784e-08</v>
+        <v>2.331607770620354e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>8.388597903842207e-08</v>
+        <v>1.84540008427513e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>9.056826039651411e-08</v>
+        <v>2.300937115841858e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>9.283549603368835e-08</v>
+        <v>2.340840462839903e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>9.153649966879788e-08</v>
+        <v>2.939886553819787e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>8.729587505372864e-08</v>
+        <v>2.699036136773197e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>1.21579935627631e-07</v>
+        <v>2.846738878373013e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>1.618200890501435e-07</v>
+        <v>6.758546917889889e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>8.902339157340441e-08</v>
+        <v>2.242671311504865e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>8.675158805248237e-08</v>
+        <v>1.994845824483967e-08</v>
       </c>
     </row>
     <row r="7">
@@ -5071,37 +5071,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9.211874556815292e-08</v>
+        <v>2.062501483501282e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>9.845651485483651e-08</v>
+        <v>2.439770461581568e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>9.124101695449816e-08</v>
+        <v>1.974848750896646e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>9.869233645213383e-08</v>
+        <v>2.443920853645994e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>9.869233645213383e-08</v>
+        <v>2.443920853645994e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>9.720805519382184e-08</v>
+        <v>2.532913541634525e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>9.296738322889191e-08</v>
+        <v>2.147365249575185e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>9.845646890089827e-08</v>
+        <v>2.439765866187743e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>1.342219226523465e-07</v>
+        <v>6.272819191920637e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>9.496641617184712e-08</v>
+        <v>2.347268543870697e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>9.244406489722613e-08</v>
+        <v>2.0950334164086e-08</v>
       </c>
     </row>
     <row r="8">
@@ -5111,37 +5111,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.18366858505105e-07</v>
+        <v>2.524468268688429e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>1.647057742346008e-07</v>
+        <v>3.6057574203474e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>1.655031232194486e-07</v>
+        <v>3.281861814077583e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>1.538052800994325e-07</v>
+        <v>3.413908656582473e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>1.261067179604898e-07</v>
+        <v>2.92641396557862e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>1.632228276819411e-07</v>
+        <v>3.694773531129764e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>1.589821557171714e-07</v>
+        <v>3.30922523907324e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>1.644712413890176e-07</v>
+        <v>3.601625855682987e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>2.002445102980978e-07</v>
+        <v>7.434816728189455e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>1.204758430020776e-07</v>
+        <v>2.796234453649968e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>1.999984384001967e-07</v>
+        <v>3.987990379803696e-08</v>
       </c>
     </row>
     <row r="9">
@@ -5151,37 +5151,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.88637090312124e-07</v>
+        <v>5.5212243322537e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>3.593725107926897e-07</v>
+        <v>7.031891965204893e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>3.521584966107081e-07</v>
+        <v>6.566996367962909e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>4.336860396684092e-07</v>
+        <v>8.339809998304946e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>3.593724958158877e-07</v>
+        <v>7.031891633587662e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>3.581240511316751e-07</v>
+        <v>7.125035045257844e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>3.538833791667451e-07</v>
+        <v>6.739486753198502e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>3.593724648387516e-07</v>
+        <v>7.031887369811074e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>3.951379185901998e-07</v>
+        <v>1.086494069554396e-07</v>
       </c>
       <c r="K9" t="n">
-        <v>3.185701709691957e-07</v>
+        <v>6.282694606979508e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>3.533600608350792e-07</v>
+        <v>6.687154920031924e-08</v>
       </c>
     </row>
   </sheetData>
@@ -5270,34 +5270,34 @@
         <v>1.447054623720318e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>3.713764481412739e-07</v>
+        <v>3.71376448141274e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>1.458709969085538e-07</v>
+        <v>1.458709969085536e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>3.996024987591927e-07</v>
+        <v>3.996024987591929e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>2.623295514511805e-07</v>
+        <v>2.623295514511806e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>1.526736956127121e-07</v>
+        <v>1.52673695612712e-07</v>
       </c>
       <c r="H2" t="n">
         <v>1.484872143486829e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>1.520003859032244e-07</v>
+        <v>1.520003859032245e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>3.443127993726603e-07</v>
+        <v>3.443127993726602e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>1.243246464362619e-07</v>
+        <v>1.24324646436262e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>1.468979566754966e-07</v>
+        <v>1.468979566754965e-07</v>
       </c>
     </row>
     <row r="3">
@@ -5307,22 +5307,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.62213223770142e-07</v>
+        <v>1.622132237701421e-07</v>
       </c>
       <c r="C3" t="n">
         <v>3.899762094452743e-07</v>
       </c>
       <c r="D3" t="n">
-        <v>1.63553829926894e-07</v>
+        <v>1.635538299268938e-07</v>
       </c>
       <c r="E3" t="n">
-        <v>4.182065170860688e-07</v>
+        <v>4.182065170860689e-07</v>
       </c>
       <c r="F3" t="n">
-        <v>2.809335697780563e-07</v>
+        <v>2.809335697780565e-07</v>
       </c>
       <c r="G3" t="n">
-        <v>1.713783426114674e-07</v>
+        <v>1.713783426114675e-07</v>
       </c>
       <c r="H3" t="n">
         <v>1.665661336765494e-07</v>
@@ -5331,10 +5331,10 @@
         <v>1.706068779732987e-07</v>
       </c>
       <c r="J3" t="n">
-        <v>3.718581416649308e-07</v>
+        <v>3.718581416649306e-07</v>
       </c>
       <c r="K3" t="n">
-        <v>1.428225190790278e-07</v>
+        <v>1.428225190790279e-07</v>
       </c>
       <c r="L3" t="n">
         <v>1.647348458168196e-07</v>
@@ -5347,37 +5347,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.144278198355568e-08</v>
+        <v>1.374158269643737e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>6.694479096104687e-08</v>
+        <v>1.828487936770512e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>6.213564287763034e-08</v>
+        <v>1.443444359051179e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>6.802863504733092e-08</v>
+        <v>1.847564192667506e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>6.802863504733094e-08</v>
+        <v>1.847564192667506e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>6.664731274344907e-08</v>
+        <v>1.856068437330652e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>6.369229976097871e-08</v>
+        <v>1.599110047386023e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>6.889560125788648e-08</v>
+        <v>1.862837844289902e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>1.011673659197203e-07</v>
+        <v>5.346616663260141e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>6.536123182313335e-08</v>
+        <v>1.76600325360147e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>6.274758154315054e-08</v>
+        <v>1.504638225603215e-08</v>
       </c>
     </row>
     <row r="5">
@@ -5387,37 +5387,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.004354959937352e-07</v>
+        <v>3.820430022967531e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>5.72753255388678e-07</v>
+        <v>1.073071686245919e-07</v>
       </c>
       <c r="D5" t="n">
-        <v>2.63746505828884e-07</v>
+        <v>4.991795527766009e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>5.727532626712233e-07</v>
+        <v>1.073071759071376e-07</v>
       </c>
       <c r="F5" t="n">
-        <v>5.727532626712233e-07</v>
+        <v>1.073071759071376e-07</v>
       </c>
       <c r="G5" t="n">
-        <v>6.376822446133177e-07</v>
+        <v>1.190628318378226e-07</v>
       </c>
       <c r="H5" t="n">
-        <v>4.512941533599078e-07</v>
+        <v>8.420902633762572e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>5.727534452731562e-07</v>
+        <v>1.073073585090705e-07</v>
       </c>
       <c r="J5" t="n">
-        <v>4.035759942839897e-06</v>
+        <v>7.459544564182326e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>5.308408843513216e-07</v>
+        <v>9.958445093705976e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>3.659826852910106e-07</v>
+        <v>1.836976007801316e-07</v>
       </c>
     </row>
     <row r="6">
@@ -5427,37 +5427,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7.579259289073852e-08</v>
+        <v>2.043584388172025e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>8.254379675830813e-08</v>
+        <v>2.103030437314675e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>7.5021987396717e-08</v>
+        <v>1.670244021358129e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>8.117100503700451e-08</v>
+        <v>2.078869903232408e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>8.307824996786355e-08</v>
+        <v>2.112437413833638e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>8.099712365063171e-08</v>
+        <v>2.525494555858933e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>1.085886188489483e-07</v>
+        <v>2.389285259052646e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>8.324541216506897e-08</v>
+        <v>2.53226396281818e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>1.178950465903401e-07</v>
+        <v>6.084502666006187e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>7.953194361624106e-08</v>
+        <v>2.015407779808748e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>7.70050112376957e-08</v>
+        <v>1.755568986867511e-08</v>
       </c>
     </row>
     <row r="7">
@@ -5467,37 +5467,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7.922680986622552e-08</v>
+        <v>1.687157158682711e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>8.667943925607768e-08</v>
+        <v>2.175817744881013e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>7.99188470556279e-08</v>
+        <v>1.756428750887995e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>8.642620474990374e-08</v>
+        <v>2.17136141767826e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>8.642620474990374e-08</v>
+        <v>2.17136141767826e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>8.443134062611906e-08</v>
+        <v>2.169067326369627e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>8.147632764364875e-08</v>
+        <v>1.91210893642499e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>8.667962914055635e-08</v>
+        <v>2.175836733328875e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>1.189513938023896e-07</v>
+        <v>5.659615552299105e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>8.314525970580323e-08</v>
+        <v>2.079002142640444e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>8.053160942582052e-08</v>
+        <v>1.817637114642181e-08</v>
       </c>
     </row>
     <row r="8">
@@ -5507,37 +5507,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.008051788729314e-07</v>
+        <v>2.066936451142871e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>1.400391154165849e-07</v>
+        <v>3.114948040232857e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>1.401538280503523e-07</v>
+        <v>2.816564410650683e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>1.313082384891716e-07</v>
+        <v>2.961285207209086e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>1.091221216129419e-07</v>
+        <v>2.570809552303279e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>1.380265893448472e-07</v>
+        <v>3.112343698707999e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>1.350715763626131e-07</v>
+        <v>2.855385308767523e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>1.402748778592845e-07</v>
+        <v>3.11911310566725e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>1.725529346576149e-07</v>
+        <v>6.60300266623923e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>1.041288987424953e-07</v>
+        <v>2.448314187685076e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>1.675711661214506e-07</v>
+        <v>3.349533304184531e-08</v>
       </c>
     </row>
     <row r="9">
@@ -5547,37 +5547,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.388287276889169e-07</v>
+        <v>4.496150897141259e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>2.983879127708342e-07</v>
+        <v>5.90188685855063e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>2.916281624933007e-07</v>
+        <v>5.482512682400868e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>3.585177804486903e-07</v>
+        <v>6.960173124028225e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>2.983879068495538e-07</v>
+        <v>5.901887354417856e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>2.961398141408754e-07</v>
+        <v>5.895136440039253e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>2.93184801158405e-07</v>
+        <v>5.638178050094612e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>2.983881026553132e-07</v>
+        <v>5.901905846998489e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>3.30659867317146e-07</v>
+        <v>9.385684665968725e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>2.292422738951803e-07</v>
+        <v>4.650309578440588e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>2.922400829405767e-07</v>
+        <v>5.543706228311806e-08</v>
       </c>
     </row>
   </sheetData>
@@ -5663,37 +5663,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.453943319517161e-07</v>
+        <v>1.453943319517156e-07</v>
       </c>
       <c r="C2" t="n">
         <v>3.719619805008427e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>1.4663088553844e-07</v>
+        <v>1.466308855384402e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>4.000469870682367e-07</v>
+        <v>4.000469870682374e-07</v>
       </c>
       <c r="F2" t="n">
         <v>2.631666670023152e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>1.523841594287436e-07</v>
+        <v>1.523841594287359e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>1.481369228069665e-07</v>
+        <v>1.481369228069668e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>1.529465385845195e-07</v>
+        <v>1.529465385845197e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>3.372490009737661e-07</v>
+        <v>3.37249000973766e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>1.209087173182223e-07</v>
+        <v>1.209087173182221e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>1.459218234036358e-07</v>
+        <v>1.45921823403636e-07</v>
       </c>
     </row>
     <row r="3">
@@ -5703,37 +5703,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.629569683224956e-07</v>
+        <v>1.629569683224947e-07</v>
       </c>
       <c r="C3" t="n">
-        <v>3.906534971648027e-07</v>
+        <v>3.906534971648034e-07</v>
       </c>
       <c r="D3" t="n">
         <v>1.643792610985317e-07</v>
       </c>
       <c r="E3" t="n">
-        <v>4.187444773620206e-07</v>
+        <v>4.187444773620203e-07</v>
       </c>
       <c r="F3" t="n">
-        <v>2.818641572960986e-07</v>
+        <v>2.818641572960987e-07</v>
       </c>
       <c r="G3" t="n">
-        <v>1.70996717859476e-07</v>
+        <v>1.709967178594814e-07</v>
       </c>
       <c r="H3" t="n">
-        <v>1.661139684365588e-07</v>
+        <v>1.661139684365587e-07</v>
       </c>
       <c r="I3" t="n">
-        <v>1.716327118255587e-07</v>
+        <v>1.716327118255593e-07</v>
       </c>
       <c r="J3" t="n">
-        <v>3.63830675808436e-07</v>
+        <v>3.638306758084356e-07</v>
       </c>
       <c r="K3" t="n">
-        <v>1.389530746846537e-07</v>
+        <v>1.389530746846534e-07</v>
       </c>
       <c r="L3" t="n">
-        <v>1.635635696363545e-07</v>
+        <v>1.635635696363546e-07</v>
       </c>
     </row>
     <row r="4">
@@ -5743,37 +5743,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.884494704997782e-08</v>
+        <v>1.366528419841214e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>6.244318150116112e-08</v>
+        <v>1.799937432643013e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>5.958002576006578e-08</v>
+        <v>1.44003629084997e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>6.359979674898412e-08</v>
+        <v>1.820295358174068e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>6.359979674898416e-08</v>
+        <v>1.820295358174053e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>6.346730549692733e-08</v>
+        <v>1.790266803544131e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>6.047671645502617e-08</v>
+        <v>1.529705360345978e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>6.644711998725858e-08</v>
+        <v>1.870436627827185e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>9.453856230051778e-08</v>
+        <v>4.935889944895157e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>6.075139904547041e-08</v>
+        <v>1.557173619390439e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>5.916008573055621e-08</v>
+        <v>1.398042287899002e-08</v>
       </c>
     </row>
     <row r="5">
@@ -5783,37 +5783,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.43882609208557e-07</v>
+        <v>4.623191256185422e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>6.234918687622965e-07</v>
+        <v>1.167439427493324e-07</v>
       </c>
       <c r="D5" t="n">
-        <v>3.091504831898493e-07</v>
+        <v>5.832476317813272e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>6.234918869331661e-07</v>
+        <v>1.167439609202031e-07</v>
       </c>
       <c r="F5" t="n">
-        <v>6.234918869331661e-07</v>
+        <v>1.167439609202031e-07</v>
       </c>
       <c r="G5" t="n">
-        <v>6.198431696923547e-07</v>
+        <v>1.158248196031219e-07</v>
       </c>
       <c r="H5" t="n">
-        <v>4.309652733607352e-07</v>
+        <v>8.050303926553948e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>6.234922313619402e-07</v>
+        <v>1.16744305348975e-07</v>
       </c>
       <c r="J5" t="n">
-        <v>3.703779781047273e-06</v>
+        <v>6.845853505063394e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>3.897437366043141e-07</v>
+        <v>7.347438729050909e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>3.133394878729021e-07</v>
+        <v>5.871599741363974e-08</v>
       </c>
     </row>
     <row r="6">
@@ -5823,37 +5823,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7.242722891942972e-08</v>
+        <v>1.605576579448227e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>7.923603273916525e-08</v>
+        <v>2.095491612830384e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>9.689944446387042e-08</v>
+        <v>2.096858056477831e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>7.804891953762854e-08</v>
+        <v>2.074599917876256e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>7.987438181977037e-08</v>
+        <v>2.106728053867857e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>7.704958736637843e-08</v>
+        <v>2.029314963151034e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>1.030235627589905e-07</v>
+        <v>2.278529851238176e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>1.022728106794002e-07</v>
+        <v>2.500968780592239e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>1.343653929577199e-07</v>
+        <v>5.215851352706684e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>7.401454585851208e-08</v>
+        <v>1.790605002035053e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>7.277809167885056e-08</v>
+        <v>1.637719191290265e-08</v>
       </c>
     </row>
     <row r="7">
@@ -5863,37 +5863,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7.532113810643144e-08</v>
+        <v>1.656509380863545e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>8.29229484440674e-08</v>
+        <v>2.160381328885068e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>7.605581302674308e-08</v>
+        <v>1.730010145172227e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>8.207701478173409e-08</v>
+        <v>2.145494393788341e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>8.207701478173409e-08</v>
+        <v>2.145494393788341e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>7.994349655337986e-08</v>
+        <v>2.0802477645649e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>7.69529075114788e-08</v>
+        <v>1.819686321368316e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>8.292331104371124e-08</v>
+        <v>2.160417588849442e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>1.110147533569704e-07</v>
+        <v>5.225870905917435e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>7.722759010192254e-08</v>
+        <v>1.847154580412686e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>7.563627678700875e-08</v>
+        <v>1.688023248921243e-08</v>
       </c>
     </row>
     <row r="8">
@@ -5903,37 +5903,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9.58366030904294e-08</v>
+        <v>2.017581562625297e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>1.32438084262144e-07</v>
+        <v>3.031847714561085e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>1.325546095289392e-07</v>
+        <v>2.724388958222697e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>1.243731178155983e-07</v>
+        <v>2.889905803150591e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>1.038787324197761e-07</v>
+        <v>2.529204622138755e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>1.302620290703745e-07</v>
+        <v>2.965853932065823e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>1.27271440028717e-07</v>
+        <v>2.705292488872941e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>1.332418435607055e-07</v>
+        <v>3.04602375634976e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>1.61339142946868e-07</v>
+        <v>6.111580157900313e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>9.718944781239829e-08</v>
+        <v>2.198483274213305e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>1.570866053571842e-07</v>
+        <v>3.121549023988706e-08</v>
       </c>
     </row>
     <row r="9">
@@ -5943,37 +5943,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.18885284186766e-07</v>
+        <v>4.183238338186044e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>2.734887052839708e-07</v>
+        <v>5.514338631093496e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>2.666219914914411e-07</v>
+        <v>5.083974867977128e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>3.277275872747835e-07</v>
+        <v>6.468944446238921e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>2.734887118356874e-07</v>
+        <v>5.514340243683467e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>2.705092533932832e-07</v>
+        <v>5.434205066773831e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>2.675186643513823e-07</v>
+        <v>5.173643623576846e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>2.734890678836149e-07</v>
+        <v>5.514374891058114e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>3.01580510196874e-07</v>
+        <v>8.579828208125974e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>2.405604365794996e-07</v>
+        <v>4.721812662841421e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>2.662020336269125e-07</v>
+        <v>5.041980551129709e-08</v>
       </c>
     </row>
   </sheetData>
@@ -6062,19 +6062,19 @@
         <v>1.481329194312053e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>3.678209271549111e-07</v>
+        <v>3.678209271549114e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>1.46389853676783e-07</v>
+        <v>1.463898536767829e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>3.960599139930792e-07</v>
+        <v>3.960599139930794e-07</v>
       </c>
       <c r="F2" t="n">
         <v>2.587446149738272e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>1.521008094027649e-07</v>
+        <v>1.521008094027648e-07</v>
       </c>
       <c r="H2" t="n">
         <v>1.473614570508666e-07</v>
@@ -6083,7 +6083,7 @@
         <v>1.485334064830803e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>3.419718084803675e-07</v>
+        <v>3.419718084803672e-07</v>
       </c>
       <c r="K2" t="n">
         <v>1.245396328159713e-07</v>
@@ -6099,13 +6099,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.661406710082116e-07</v>
+        <v>1.661406710082115e-07</v>
       </c>
       <c r="C3" t="n">
-        <v>3.858838018499617e-07</v>
+        <v>3.85883801849962e-07</v>
       </c>
       <c r="D3" t="n">
-        <v>1.641357843156426e-07</v>
+        <v>1.641357843156425e-07</v>
       </c>
       <c r="E3" t="n">
         <v>4.141282332647656e-07</v>
@@ -6114,19 +6114,19 @@
         <v>2.768129342455134e-07</v>
       </c>
       <c r="G3" t="n">
-        <v>1.707045664214362e-07</v>
+        <v>1.707045664214363e-07</v>
       </c>
       <c r="H3" t="n">
         <v>1.652561281353573e-07</v>
       </c>
       <c r="I3" t="n">
-        <v>1.665963069738113e-07</v>
+        <v>1.665963069738114e-07</v>
       </c>
       <c r="J3" t="n">
-        <v>3.691535602099753e-07</v>
+        <v>3.691535602099752e-07</v>
       </c>
       <c r="K3" t="n">
-        <v>1.43066362738638e-07</v>
+        <v>1.430663627386378e-07</v>
       </c>
       <c r="L3" t="n">
         <v>1.667458213520369e-07</v>
@@ -6139,37 +6139,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.418560493581417e-08</v>
+        <v>1.589597957816952e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>6.417191689606067e-08</v>
+        <v>1.609107436794786e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>6.314942620477128e-08</v>
+        <v>1.485980084712675e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>6.550940972016071e-08</v>
+        <v>1.632648352398401e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>6.55094097201607e-08</v>
+        <v>1.632648352398401e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>6.700556359201381e-08</v>
+        <v>1.833589608359002e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>6.372859216788249e-08</v>
+        <v>1.543896681023783e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>6.749841899073389e-08</v>
+        <v>1.667637240220308e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>1.004924943083739e-07</v>
+        <v>5.220286895072917e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>6.623950607699782e-08</v>
+        <v>1.794988071935309e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>6.449942580750939e-08</v>
+        <v>1.620980044986481e-08</v>
       </c>
     </row>
     <row r="5">
@@ -6179,37 +6179,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.024898427373628e-07</v>
+        <v>7.543752510860999e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>4.287581394381817e-07</v>
+        <v>8.025824918766462e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>3.064156604655449e-07</v>
+        <v>5.767465784502603e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>4.287581520841405e-07</v>
+        <v>8.025826183362338e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>4.287581520841405e-07</v>
+        <v>8.025826183362338e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>6.280510029021319e-07</v>
+        <v>1.170798928671168e-07</v>
       </c>
       <c r="H5" t="n">
-        <v>3.934833923606757e-07</v>
+        <v>7.34758113296908e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>4.287579375798871e-07</v>
+        <v>8.025804732937007e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>4.180281438377453e-06</v>
+        <v>7.702457192160959e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>5.828854154316416e-07</v>
+        <v>1.088795602730586e-07</v>
       </c>
       <c r="L5" t="n">
-        <v>1.712647836872545e-06</v>
+        <v>9.21314824517318e-08</v>
       </c>
     </row>
     <row r="6">
@@ -6219,37 +6219,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7.851024161670458e-08</v>
+        <v>1.841711562034515e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>8.069694999270865e-08</v>
+        <v>1.899948017719844e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>7.614312946150789e-08</v>
+        <v>2.221909476091599e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>7.93138525572042e-08</v>
+        <v>1.875606545013872e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>8.160509812051776e-08</v>
+        <v>1.91593246670968e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>1.065875306534073e-07</v>
+        <v>2.085703212576567e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>1.11705833319535e-07</v>
+        <v>2.388296120717399e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>1.070803860521274e-07</v>
+        <v>1.919750844437869e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>1.450236240168175e-07</v>
+        <v>6.0040347736947e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>8.041744802226361e-08</v>
+        <v>2.04451984881987e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>7.885653094353992e-08</v>
+        <v>1.873665094011421e-08</v>
       </c>
     </row>
     <row r="7">
@@ -6259,37 +6259,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>8.288702276035807e-08</v>
+        <v>1.918742909745417e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>8.620003867357245e-08</v>
+        <v>1.99680237797823e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>8.185018590674196e-08</v>
+        <v>1.815113453683907e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>8.566593462513575e-08</v>
+        <v>1.987403188803686e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>8.566593462513575e-08</v>
+        <v>1.987403188803686e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>8.570698141655788e-08</v>
+        <v>2.162734560287473e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>8.243000999242645e-08</v>
+        <v>1.873041632952259e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>8.6199836815278e-08</v>
+        <v>1.996782192148776e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>1.191939121329178e-07</v>
+        <v>5.549431847001387e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>8.494092390154164e-08</v>
+        <v>2.124133023863778e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>8.320084363205341e-08</v>
+        <v>1.950124996914954e-08</v>
       </c>
     </row>
     <row r="8">
@@ -6299,37 +6299,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.06460618377612e-07</v>
+        <v>2.333638190360927e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>1.439490903358877e-07</v>
+        <v>3.013185681709441e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>1.472947492867746e-07</v>
+        <v>2.966937762931208e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>1.345186026861651e-07</v>
+        <v>2.847210142018852e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>1.105546941416875e-07</v>
+        <v>2.425445353921422e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>1.43959902609742e-07</v>
+        <v>3.187985967732085e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>1.406829311857764e-07</v>
+        <v>2.898293040399779e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>1.444527580084621e-07</v>
+        <v>3.022033599593388e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>1.77453648696535e-07</v>
+        <v>6.574803204964967e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>1.07870333250373e-07</v>
+        <v>2.527690626216482e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>1.776792201260849e-07</v>
+        <v>3.612944414199742e-08</v>
       </c>
     </row>
     <row r="9">
@@ -6339,37 +6339,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.744530627927011e-07</v>
+        <v>5.290305196045489e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>3.393195170322952e-07</v>
+        <v>6.451705172952395e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>3.34970347226074e-07</v>
+        <v>6.27002826876474e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>4.103509017448972e-07</v>
+        <v>7.701858579147117e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>3.393195192211904e-07</v>
+        <v>6.451706253503958e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>3.388264597752807e-07</v>
+        <v>6.617637355261646e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>3.355494883511497e-07</v>
+        <v>6.327944427926425e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>3.393193151740006e-07</v>
+        <v>6.45168498712294e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>3.723133904916408e-07</v>
+        <v>1.000433464197555e-07</v>
       </c>
       <c r="K9" t="n">
-        <v>2.605536297199905e-07</v>
+        <v>5.951344257368974e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>3.36320321990777e-07</v>
+        <v>6.405027791889111e-08</v>
       </c>
     </row>
   </sheetData>
@@ -6455,37 +6455,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.439643543519587e-07</v>
+        <v>1.439643543519589e-07</v>
       </c>
       <c r="C2" t="n">
         <v>3.694493664377654e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>1.51254978847794e-07</v>
+        <v>1.512549788477943e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>3.974397849965341e-07</v>
+        <v>3.97439784996534e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>2.608362134054412e-07</v>
+        <v>2.608362134054413e-07</v>
       </c>
       <c r="G2" t="n">
         <v>1.540195964462815e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>1.467534820289275e-07</v>
+        <v>1.467534820289276e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>1.507490773053553e-07</v>
+        <v>1.507490773053555e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>3.182406687460463e-07</v>
+        <v>3.18240668746046e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>1.213529020039614e-07</v>
+        <v>1.213529020039613e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>1.431310772233748e-07</v>
+        <v>1.431310772233749e-07</v>
       </c>
     </row>
     <row r="3">
@@ -6495,37 +6495,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.612154392554749e-07</v>
+        <v>1.61215439255475e-07</v>
       </c>
       <c r="C3" t="n">
         <v>3.877151918024673e-07</v>
       </c>
       <c r="D3" t="n">
-        <v>1.69601167674e-07</v>
+        <v>1.696011676740001e-07</v>
       </c>
       <c r="E3" t="n">
         <v>4.157103072777814e-07</v>
       </c>
       <c r="F3" t="n">
-        <v>2.791067356866884e-07</v>
+        <v>2.791067356866886e-07</v>
       </c>
       <c r="G3" t="n">
-        <v>1.727810506010706e-07</v>
+        <v>1.727810506010708e-07</v>
       </c>
       <c r="H3" t="n">
-        <v>1.644259449916248e-07</v>
+        <v>1.644259449916247e-07</v>
       </c>
       <c r="I3" t="n">
-        <v>1.690123921162227e-07</v>
+        <v>1.690123921162226e-07</v>
       </c>
       <c r="J3" t="n">
-        <v>3.419859052319355e-07</v>
+        <v>3.419859052319353e-07</v>
       </c>
       <c r="K3" t="n">
-        <v>1.393800574092531e-07</v>
+        <v>1.393800574092529e-07</v>
       </c>
       <c r="L3" t="n">
-        <v>1.602571762309858e-07</v>
+        <v>1.602571762309859e-07</v>
       </c>
     </row>
     <row r="4">
@@ -6535,37 +6535,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.713389982064792e-08</v>
+        <v>1.268272955303494e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>6.121994100591495e-08</v>
+        <v>1.672629932387243e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>6.146786715345591e-08</v>
+        <v>1.701669688584347e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>6.224320400035882e-08</v>
+        <v>1.690640375336963e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>6.224320400035882e-08</v>
+        <v>1.690640375336963e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>6.357195758530797e-08</v>
+        <v>1.874121796619511e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>5.879406139823218e-08</v>
+        <v>1.434289113061983e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>6.423555759843532e-08</v>
+        <v>1.725691474474564e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>8.283505952719057e-08</v>
+        <v>3.838388925957751e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>6.020526513398682e-08</v>
+        <v>1.575409486637426e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>5.664117441010098e-08</v>
+        <v>1.219000414248838e-08</v>
       </c>
     </row>
     <row r="5">
@@ -6575,37 +6575,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.759753847773302e-07</v>
+        <v>3.359883079207519e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>5.18065527588747e-07</v>
+        <v>9.713112212676899e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>5.231769736768677e-07</v>
+        <v>9.827749919364334e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>5.180655398987603e-07</v>
+        <v>9.713113443678226e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>5.180655398987602e-07</v>
+        <v>9.713113443678226e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>6.83882705781254e-07</v>
+        <v>1.279159090571069e-07</v>
       </c>
       <c r="H5" t="n">
-        <v>3.403403636560254e-07</v>
+        <v>6.389504005948801e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>5.180653660638272e-07</v>
+        <v>9.713096060184875e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>2.498868946575327e-06</v>
+        <v>4.636058510759405e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>4.315794267516844e-07</v>
+        <v>8.111594695691889e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>5.656903968207811e-07</v>
+        <v>1.017826668013008e-07</v>
       </c>
     </row>
     <row r="6">
@@ -6615,37 +6615,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6.850432725712965e-08</v>
+        <v>1.850248042543261e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>7.482542974356002e-08</v>
+        <v>1.912086532872278e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>7.227415475334274e-08</v>
+        <v>1.891857653267415e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>7.387032435019244e-08</v>
+        <v>1.895277692385186e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>7.555310658371733e-08</v>
+        <v>1.924894659534741e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>7.494238502178981e-08</v>
+        <v>2.07424131841722e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>9.769656706611033e-08</v>
+        <v>1.63489111992531e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>7.560598503491768e-08</v>
+        <v>1.925810996272284e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>9.618291615309588e-08</v>
+        <v>4.495561731143066e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>7.089681972794449e-08</v>
+        <v>1.763580846471455e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>6.812852804716307e-08</v>
+        <v>1.421177837165607e-08</v>
       </c>
     </row>
     <row r="7">
@@ -6655,37 +6655,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7.292593746511182e-08</v>
+        <v>1.546212816340037e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>8.002775676781894e-08</v>
+        <v>2.0036474880031e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>7.725930764658217e-08</v>
+        <v>1.979599039757384e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>7.94642988625625e-08</v>
+        <v>1.993731643269416e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>7.94642988625625e-08</v>
+        <v>1.993731643269416e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>7.936399522977148e-08</v>
+        <v>2.152061657656021e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>7.458609904269587e-08</v>
+        <v>1.712228974098488e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>8.00275952428986e-08</v>
+        <v>2.003631335511072e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>9.862709717165322e-08</v>
+        <v>4.116328786994251e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>7.599730277845029e-08</v>
+        <v>1.853349347673936e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>7.243321205456463e-08</v>
+        <v>1.496940275285352e-08</v>
       </c>
     </row>
     <row r="8">
@@ -6695,37 +6695,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9.232612398642786e-08</v>
+        <v>1.887656097265029e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>1.270637223973834e-07</v>
+        <v>2.831480478597734e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>1.306702499060765e-07</v>
+        <v>2.919631618430801e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>1.19416893171945e-07</v>
+        <v>2.69689729930437e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>9.998509183235529e-08</v>
+        <v>2.354897597580752e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>1.269332918581784e-07</v>
+        <v>2.989281273779419e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>1.221553956710872e-07</v>
+        <v>2.549448590221621e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>1.275968918713058e-07</v>
+        <v>2.840850951634477e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>1.462019297640015e-07</v>
+        <v>4.953645836082507e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>9.487423362316574e-08</v>
+        <v>2.185583328740684e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>1.494274995855685e-07</v>
+        <v>2.852039728488282e-08</v>
       </c>
     </row>
     <row r="9">
@@ -6735,37 +6735,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.336096928839392e-07</v>
+        <v>4.374246896387405e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>2.920448805843022e-07</v>
+        <v>5.735148846953674e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>2.892770538251954e-07</v>
+        <v>5.711111352281374e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>3.512825251509895e-07</v>
+        <v>6.777732400023125e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>2.920448855175127e-07</v>
+        <v>5.735149948123274e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>2.913811190462538e-07</v>
+        <v>5.883563016606602e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>2.866032228591794e-07</v>
+        <v>5.443730333049076e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>2.920447190593819e-07</v>
+        <v>5.735132694461646e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>3.106442209881368e-07</v>
+        <v>7.847830145944836e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>2.57064980203293e-07</v>
+        <v>5.040140453083205e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>2.844503358710478e-07</v>
+        <v>5.228441634235906e-08</v>
       </c>
     </row>
   </sheetData>
@@ -6851,31 +6851,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.439497173958561e-07</v>
+        <v>1.439497173958562e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>3.718426961636567e-07</v>
+        <v>3.718426961636574e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>1.485741346071221e-07</v>
+        <v>1.485741346071223e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>3.997244663528952e-07</v>
+        <v>3.997244663528951e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>2.634315593229394e-07</v>
+        <v>2.634315593229395e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>1.522071372411179e-07</v>
+        <v>1.52207137241118e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>1.474978818965507e-07</v>
+        <v>1.474978818965508e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>1.532892472112401e-07</v>
+        <v>1.532892472112402e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>3.086408297065355e-07</v>
+        <v>3.086408297065353e-07</v>
       </c>
       <c r="K2" t="n">
         <v>1.18844149386959e-07</v>
@@ -6894,19 +6894,19 @@
         <v>1.610752456480753e-07</v>
       </c>
       <c r="C3" t="n">
-        <v>3.903672252922397e-07</v>
+        <v>3.903672252922401e-07</v>
       </c>
       <c r="D3" t="n">
-        <v>1.663942833861707e-07</v>
+        <v>1.663942833861706e-07</v>
       </c>
       <c r="E3" t="n">
-        <v>4.182532610555081e-07</v>
+        <v>4.182532610555082e-07</v>
       </c>
       <c r="F3" t="n">
-        <v>2.819603540255527e-07</v>
+        <v>2.819603540255528e-07</v>
       </c>
       <c r="G3" t="n">
-        <v>1.70572988989494e-07</v>
+        <v>1.705729889894941e-07</v>
       </c>
       <c r="H3" t="n">
         <v>1.65158394665563e-07</v>
@@ -6931,37 +6931,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.593076229539457e-08</v>
+        <v>1.251477235368977e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>6.182750989167855e-08</v>
+        <v>1.812871288188944e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>5.867978237431243e-08</v>
+        <v>1.52637924326079e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>6.275405138423347e-08</v>
+        <v>1.829179384776922e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>6.275405138423347e-08</v>
+        <v>1.829179384776922e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>6.130825143573574e-08</v>
+        <v>1.750596787193612e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>5.804154131484943e-08</v>
+        <v>1.462555137314437e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>6.460334112948313e-08</v>
+        <v>1.861761475764026e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>7.632329253253376e-08</v>
+        <v>3.290730259082886e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>5.768912789724237e-08</v>
+        <v>1.427313795553718e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>5.613810878517513e-08</v>
+        <v>1.272211884347012e-08</v>
       </c>
     </row>
     <row r="5">
@@ -6971,37 +6971,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.852607865487704e-07</v>
+        <v>3.527685649894521e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>6.641406338187696e-07</v>
+        <v>1.241358221186468e-07</v>
       </c>
       <c r="D5" t="n">
-        <v>4.173243594328389e-07</v>
+        <v>7.838523765287822e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>6.641406455470142e-07</v>
+        <v>1.241358338468917e-07</v>
       </c>
       <c r="F5" t="n">
-        <v>6.641406455470142e-07</v>
+        <v>1.241358338468917e-07</v>
       </c>
       <c r="G5" t="n">
-        <v>6.161654101438717e-07</v>
+        <v>1.151608272754175e-07</v>
       </c>
       <c r="H5" t="n">
-        <v>4.031629901307269e-07</v>
+        <v>7.536692603560541e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>6.641410653485565e-07</v>
+        <v>1.241362536484336e-07</v>
       </c>
       <c r="J5" t="n">
-        <v>2.068951330626582e-06</v>
+        <v>3.83609835395063e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>3.26860768190068e-07</v>
+        <v>6.16473463903726e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>5.298241527897454e-07</v>
+        <v>4.299137430500288e-08</v>
       </c>
     </row>
     <row r="6">
@@ -7011,37 +7011,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6.66443019508089e-08</v>
+        <v>1.440035532282541e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>7.498230044862586e-08</v>
+        <v>2.044395600736684e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>9.155171267703909e-08</v>
+        <v>1.703504218152682e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>7.414283879754663e-08</v>
+        <v>2.029622042165113e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>7.535776792897427e-08</v>
+        <v>2.051004794762376e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>7.202179109114902e-08</v>
+        <v>2.300426437892603e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>9.424224467542734e-08</v>
+        <v>2.099687513008249e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>7.53168807848973e-08</v>
+        <v>2.050319772677606e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>8.880622541542095e-08</v>
+        <v>3.912424441189511e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>6.761075850279016e-08</v>
+        <v>1.60193449326516e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>6.702309297830067e-08</v>
+        <v>1.463787605107953e-08</v>
       </c>
     </row>
     <row r="7">
@@ -7051,37 +7051,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7.084535828538201e-08</v>
+        <v>1.513974123370386e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>7.9517505589684e-08</v>
+        <v>2.124215210786791e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>7.359377656054459e-08</v>
+        <v>1.788865539516173e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>7.89473115906413e-08</v>
+        <v>2.11418076286539e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>7.89473115906413e-08</v>
+        <v>2.11418076286539e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>7.622284742572372e-08</v>
+        <v>2.013093675195021e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>7.295613730483685e-08</v>
+        <v>1.725052025315848e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>7.951793711947039e-08</v>
+        <v>2.124258363765436e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>9.123788852252121e-08</v>
+        <v>3.553227147084294e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>7.260372388722828e-08</v>
+        <v>1.689810683555127e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>7.105270477516253e-08</v>
+        <v>1.534708772348421e-08</v>
       </c>
     </row>
     <row r="8">
@@ -7091,37 +7091,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>8.895162671622309e-08</v>
+        <v>1.832644446026432e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>1.231910125472162e-07</v>
+        <v>2.892868929081373e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>1.23221622190509e-07</v>
+        <v>2.662315617870639e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>1.16108777938867e-07</v>
+        <v>2.768222567050168e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>9.811155460577313e-08</v>
+        <v>2.451471438104066e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>1.204365456207448e-07</v>
+        <v>2.791254759210872e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>1.171698354997339e-07</v>
+        <v>2.503213109329494e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>1.237316353144929e-07</v>
+        <v>2.902419447781287e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>1.354567175162599e-07</v>
+        <v>4.331478533157063e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>9.022503341107159e-08</v>
+        <v>1.999945729494266e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>1.425377963728964e-07</v>
+        <v>2.792846377651211e-08</v>
       </c>
     </row>
     <row r="9">
@@ -7131,37 +7131,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.147237330406294e-07</v>
+        <v>4.046233505341445e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>2.695421268583767e-07</v>
+        <v>5.468648526993631e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>2.636190193042194e-07</v>
+        <v>5.133309793682619e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>3.227939375270739e-07</v>
+        <v>6.405881356091582e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>2.695421314986636e-07</v>
+        <v>5.468649575070045e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>2.662474686944156e-07</v>
+        <v>5.35752699140186e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>2.629807585735287e-07</v>
+        <v>5.069485341522688e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>2.695425583881635e-07</v>
+        <v>5.468691679972276e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>2.812625097912129e-07</v>
+        <v>6.897660463291132e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>2.358910369693764e-07</v>
+        <v>4.544575476219452e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>2.610773260438544e-07</v>
+        <v>4.879142088555259e-08</v>
       </c>
     </row>
   </sheetData>
@@ -7253,10 +7253,10 @@
         <v>3.731600773213295e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>1.458823603766316e-07</v>
+        <v>1.458823603766315e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>4.014874816495872e-07</v>
+        <v>4.014874816495869e-07</v>
       </c>
       <c r="F2" t="n">
         <v>2.639059323750007e-07</v>
@@ -7271,10 +7271,10 @@
         <v>1.534671056885736e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>3.334563028854983e-07</v>
+        <v>3.334563028854979e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>1.260883270155403e-07</v>
+        <v>1.260883270155402e-07</v>
       </c>
       <c r="L2" t="n">
         <v>1.478403562318453e-07</v>
@@ -7287,37 +7287,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.689017787963966e-07</v>
+        <v>1.689017787963965e-07</v>
       </c>
       <c r="C3" t="n">
-        <v>3.920031239015602e-07</v>
+        <v>3.920031239015599e-07</v>
       </c>
       <c r="D3" t="n">
-        <v>1.635895589179102e-07</v>
+        <v>1.635895589179101e-07</v>
       </c>
       <c r="E3" t="n">
         <v>4.203344946458753e-07</v>
       </c>
       <c r="F3" t="n">
-        <v>2.827529453712889e-07</v>
+        <v>2.827529453712891e-07</v>
       </c>
       <c r="G3" t="n">
         <v>1.740094868687449e-07</v>
       </c>
       <c r="H3" t="n">
-        <v>1.675538391263256e-07</v>
+        <v>1.675538391263257e-07</v>
       </c>
       <c r="I3" t="n">
         <v>1.723215277979423e-07</v>
       </c>
       <c r="J3" t="n">
-        <v>3.592917191292125e-07</v>
+        <v>3.592917191292127e-07</v>
       </c>
       <c r="K3" t="n">
         <v>1.447996531089557e-07</v>
       </c>
       <c r="L3" t="n">
-        <v>1.658415326216655e-07</v>
+        <v>1.658415326216653e-07</v>
       </c>
     </row>
     <row r="4">
@@ -7327,37 +7327,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.988425124571248e-08</v>
+        <v>1.801573295381429e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>7.335983022539487e-08</v>
+        <v>2.008213492822444e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>6.713875481785355e-08</v>
+        <v>1.527023652595542e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>7.461011896517436e-08</v>
+        <v>2.030218899448278e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>7.461011896517437e-08</v>
+        <v>2.030218899448278e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>7.299204567423735e-08</v>
+        <v>2.073789938831079e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>6.918759382066705e-08</v>
+        <v>1.731907552876887e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>7.476626509805753e-08</v>
+        <v>2.032973190317557e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>9.93068707988348e-08</v>
+        <v>4.74383525069366e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>7.111267539175234e-08</v>
+        <v>1.924415709985416e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>6.830460355665946e-08</v>
+        <v>1.643608526476127e-08</v>
       </c>
     </row>
     <row r="5">
@@ -7367,37 +7367,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.131596747385956e-07</v>
+        <v>9.603220706582126e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>6.758073936627154e-07</v>
+        <v>1.261129055186538e-07</v>
       </c>
       <c r="D5" t="n">
-        <v>2.60237564384128e-07</v>
+        <v>4.925562682546642e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>6.75807397605979e-07</v>
+        <v>1.261129094619178e-07</v>
       </c>
       <c r="F5" t="n">
-        <v>6.75807397605979e-07</v>
+        <v>1.261129094619178e-07</v>
       </c>
       <c r="G5" t="n">
-        <v>7.814105909385269e-07</v>
+        <v>1.454195626792256e-07</v>
       </c>
       <c r="H5" t="n">
-        <v>4.904955369312772e-07</v>
+        <v>9.146927311444616e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>6.75807471865025e-07</v>
+        <v>1.261129837209642e-07</v>
       </c>
       <c r="J5" t="n">
-        <v>3.590482412309495e-06</v>
+        <v>6.618852444833668e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>6.325917826355034e-07</v>
+        <v>1.180644794392862e-07</v>
       </c>
       <c r="L5" t="n">
-        <v>4.257142560373199e-07</v>
+        <v>7.934018376050519e-08</v>
       </c>
     </row>
     <row r="6">
@@ -7407,37 +7407,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8.547437889589884e-08</v>
+        <v>2.07595954053792e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>8.987466589453985e-08</v>
+        <v>2.298874599024415e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>8.106465654410402e-08</v>
+        <v>1.772119521649473e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>8.827617955756383e-08</v>
+        <v>2.270741564571043e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>9.042537886269957e-08</v>
+        <v>2.30856747213646e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>1.165339370762609e-07</v>
+        <v>2.840127223354218e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>1.210020625976232e-07</v>
+        <v>2.643842198409903e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>9.035639274824389e-08</v>
+        <v>2.799310474840696e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>1.47602833966214e-07</v>
+        <v>5.593844197833675e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>8.653377348313925e-08</v>
+        <v>2.195827034923156e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>8.39426118155139e-08</v>
+        <v>1.91883747034061e-08</v>
       </c>
     </row>
     <row r="7">
@@ -7447,37 +7447,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9.061064848164931e-08</v>
+        <v>2.166357884757299e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>9.549258413168408e-08</v>
+        <v>2.397749959462394e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>8.786397299950947e-08</v>
+        <v>1.891787490616176e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>9.545409956879785e-08</v>
+        <v>2.397072956084219e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>9.545409956879784e-08</v>
+        <v>2.397072956084219e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>9.371844291017421e-08</v>
+        <v>2.438574528206947e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>8.991399105660397e-08</v>
+        <v>2.096692142252753e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>9.549266233399439e-08</v>
+        <v>2.397757779693425e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>1.200332680347717e-07</v>
+        <v>5.108619840069526e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>9.183907262768927e-08</v>
+        <v>2.289200299361284e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>8.903100079259634e-08</v>
+        <v>2.008393115851995e-08</v>
       </c>
     </row>
     <row r="8">
@@ -7487,37 +7487,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.157777928156494e-07</v>
+        <v>2.609299622635573e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>1.584315126599446e-07</v>
+        <v>3.505475095584309e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>1.586708287577177e-07</v>
+        <v>3.137988145207977e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>1.480968057240375e-07</v>
+        <v>3.323584579396039e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>1.218356891911846e-07</v>
+        <v>2.861388930922281e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>1.566859650411159e-07</v>
+        <v>3.546802911706477e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>1.528815131876648e-07</v>
+        <v>3.204920525754378e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>1.584601844649361e-07</v>
+        <v>3.505986163192952e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>1.830082188984042e-07</v>
+        <v>6.216978969263709e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>1.163040555474238e-07</v>
+        <v>2.719783996415451e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>1.914841782338827e-07</v>
+        <v>3.811569029047942e-08</v>
       </c>
     </row>
     <row r="9">
@@ -7527,37 +7527,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.865431159822445e-07</v>
+        <v>5.614769294082201e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>3.551037916772438e-07</v>
+        <v>6.966907187505795e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>3.474763854947564e-07</v>
+        <v>6.460965925773957e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>4.285877201547243e-07</v>
+        <v>8.260224646626433e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>3.55103783877173e-07</v>
+        <v>6.966907375149504e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>3.533296504557339e-07</v>
+        <v>7.00773175625035e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>3.495251986021636e-07</v>
+        <v>6.665849370296157e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>3.55103869879554e-07</v>
+        <v>6.966915007736828e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>3.796444755803315e-07</v>
+        <v>9.677777068112931e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>3.13057672743413e-07</v>
+        <v>6.20899319022117e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>3.48642208338156e-07</v>
+        <v>6.577550343895397e-08</v>
       </c>
     </row>
   </sheetData>
@@ -7643,34 +7643,34 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.446506909651487e-07</v>
+        <v>1.446506909651486e-07</v>
       </c>
       <c r="C2" t="n">
         <v>3.711206366524076e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>1.499484010040386e-07</v>
+        <v>1.499484010040387e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>3.992432600964813e-07</v>
+        <v>3.992432600964814e-07</v>
       </c>
       <c r="F2" t="n">
         <v>2.622623629504779e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>1.53597128430306e-07</v>
+        <v>1.535971284303061e-07</v>
       </c>
       <c r="H2" t="n">
         <v>1.466975562377995e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>1.520232644521561e-07</v>
+        <v>1.520232644521559e-07</v>
       </c>
       <c r="J2" t="n">
         <v>3.29550807370557e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>1.221500897778914e-07</v>
+        <v>1.221500897778913e-07</v>
       </c>
       <c r="L2" t="n">
         <v>1.515821131864731e-07</v>
@@ -7686,34 +7686,34 @@
         <v>1.621026039428046e-07</v>
       </c>
       <c r="C3" t="n">
-        <v>3.896760688772224e-07</v>
+        <v>3.896760688772225e-07</v>
       </c>
       <c r="D3" t="n">
-        <v>1.681960679048565e-07</v>
+        <v>1.681960679048566e-07</v>
       </c>
       <c r="E3" t="n">
-        <v>4.178030227809355e-07</v>
+        <v>4.178030227809353e-07</v>
       </c>
       <c r="F3" t="n">
-        <v>2.808221256349318e-07</v>
+        <v>2.808221256349317e-07</v>
       </c>
       <c r="G3" t="n">
-        <v>1.723928602766735e-07</v>
+        <v>1.723928602766737e-07</v>
       </c>
       <c r="H3" t="n">
         <v>1.644595997799792e-07</v>
       </c>
       <c r="I3" t="n">
-        <v>1.705822896219225e-07</v>
+        <v>1.705822896219226e-07</v>
       </c>
       <c r="J3" t="n">
         <v>3.549463788898258e-07</v>
       </c>
       <c r="K3" t="n">
-        <v>1.403272589451282e-07</v>
+        <v>1.403272589451283e-07</v>
       </c>
       <c r="L3" t="n">
-        <v>1.700748349339996e-07</v>
+        <v>1.700748349339997e-07</v>
       </c>
     </row>
     <row r="4">
@@ -7723,37 +7723,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.003395212259061e-08</v>
+        <v>1.34893742219578e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>6.517322731892496e-08</v>
+        <v>1.800663283309885e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>6.318321625769318e-08</v>
+        <v>1.663863835706119e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>6.62345481796669e-08</v>
+        <v>1.819343285283589e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>6.62345481796669e-08</v>
+        <v>1.819343285283591e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>6.581755485838945e-08</v>
+        <v>1.888954935880105e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>6.125278108927345e-08</v>
+        <v>1.470820318864203e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>6.751648825366745e-08</v>
+        <v>1.84191035626704e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>9.147165945704301e-08</v>
+        <v>4.492708155641102e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>6.290421545416453e-08</v>
+        <v>1.635963755353311e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>6.415498914319126e-08</v>
+        <v>1.761041124255881e-08</v>
       </c>
     </row>
     <row r="5">
@@ -7763,37 +7763,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.020040679790567e-07</v>
+        <v>3.847611447730255e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>5.758896253750371e-07</v>
+        <v>1.078927184039146e-07</v>
       </c>
       <c r="D5" t="n">
-        <v>4.646223499908423e-07</v>
+        <v>8.729192551125363e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>5.758896345367478e-07</v>
+        <v>1.078927275656361e-07</v>
       </c>
       <c r="F5" t="n">
-        <v>5.758896345367479e-07</v>
+        <v>1.078927275656361e-07</v>
       </c>
       <c r="G5" t="n">
-        <v>6.684588044158642e-07</v>
+        <v>1.249544087061983e-07</v>
       </c>
       <c r="H5" t="n">
-        <v>3.356779228269386e-07</v>
+        <v>6.300702787275868e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>5.758896943159268e-07</v>
+        <v>1.078927873448023e-07</v>
       </c>
       <c r="J5" t="n">
-        <v>3.238813729570483e-06</v>
+        <v>5.988592828948366e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>4.405403178139216e-07</v>
+        <v>8.282359120870808e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>6.52332506248328e-07</v>
+        <v>1.087390440264439e-07</v>
       </c>
     </row>
     <row r="6">
@@ -7803,37 +7803,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7.316444516875372e-08</v>
+        <v>1.985630942916781e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>8.002403508419727e-08</v>
+        <v>2.062037498562396e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>7.544593011078369e-08</v>
+        <v>1.879687598350961e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>7.881707790752444e-08</v>
+        <v>2.040795807293921e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>8.0610338751472e-08</v>
+        <v>2.072357197976378e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>1.01993323277196e-07</v>
+        <v>2.120051612240378e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>1.041518807549649e-07</v>
+        <v>2.225844468889188e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>1.036922566724738e-07</v>
+        <v>2.478603876988042e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>1.318521555604048e-07</v>
+        <v>4.762769208668774e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>7.561074511351846e-08</v>
+        <v>1.859598676146138e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>7.746372485044878e-08</v>
+        <v>1.995274871434406e-08</v>
       </c>
     </row>
     <row r="7">
@@ -7843,37 +7843,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7.688453324587015e-08</v>
+        <v>1.645507648358518e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>8.436700043605999e-08</v>
+        <v>2.138473688341001e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>8.003305673983987e-08</v>
+        <v>1.960421026584965e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>8.399805289097245e-08</v>
+        <v>2.131980966508512e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>8.399805289097252e-08</v>
+        <v>2.131980966508511e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>8.266813598167e-08</v>
+        <v>2.185525162042863e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>7.81033622125547e-08</v>
+        <v>1.767390545026942e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>8.436706937694777e-08</v>
+        <v>2.138480582429777e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>1.08322240580323e-07</v>
+        <v>4.789278381803837e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>7.975479657744604e-08</v>
+        <v>1.932533981516048e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>8.100557026647146e-08</v>
+        <v>2.057611350418616e-08</v>
       </c>
     </row>
     <row r="8">
@@ -7883,37 +7883,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9.755627072491796e-08</v>
+        <v>2.009330226018366e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>1.350708577200334e-07</v>
+        <v>3.030861571716767e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>1.373835700421608e-07</v>
+        <v>2.96979005523647e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>1.267998168033535e-07</v>
+        <v>2.885292007284524e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>1.057820492439089e-07</v>
+        <v>2.515379300242709e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>1.337186677536397e-07</v>
+        <v>3.084014516360962e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>1.291538939846828e-07</v>
+        <v>2.665879899347849e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>1.354176011489174e-07</v>
+        <v>3.036969936747887e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>1.593787425670416e-07</v>
+        <v>5.687872811900962e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>9.986223236323827e-08</v>
+        <v>2.286424849428409e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>1.637892928291888e-07</v>
+        <v>3.514604859627567e-08</v>
       </c>
     </row>
     <row r="9">
@@ -7923,37 +7923,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.375280322171673e-07</v>
+        <v>4.47283321493319e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>2.969428553638397e-07</v>
+        <v>5.879808714797116e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>2.926096758638639e-07</v>
+        <v>5.701769502894907e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>3.568717129236781e-07</v>
+        <v>6.934557357060875e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>2.969428561054339e-07</v>
+        <v>5.879809482775036e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>2.95243990909451e-07</v>
+        <v>5.926860188498956e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>2.906792171403336e-07</v>
+        <v>5.508725571483054e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>2.969429243047279e-07</v>
+        <v>5.879815608885894e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>3.208980955081034e-07</v>
+        <v>8.530613408259958e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>2.62240850417124e-07</v>
+        <v>4.52296784042231e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>2.935814251942509e-07</v>
+        <v>5.798946376874732e-08</v>
       </c>
     </row>
   </sheetData>

--- a/Results/Ammonia/ammonia ozone depletion results.xlsx
+++ b/Results/Ammonia/ammonia ozone depletion results.xlsx
@@ -515,37 +515,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.532439368921057e-07</v>
+        <v>1.939828529687403e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>3.774060095740672e-07</v>
+        <v>3.774485880753875e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>1.485097586161192e-07</v>
+        <v>1.937337025689106e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>4.058999400513865e-07</v>
+        <v>4.011908935608895e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>2.678144857726844e-07</v>
+        <v>2.862527666108519e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>1.60787718174215e-07</v>
+        <v>1.943798671944613e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>1.532102772363284e-07</v>
+        <v>1.939639977614305e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>1.57211244251282e-07</v>
+        <v>1.941918156394274e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>3.340020463574413e-07</v>
+        <v>3.084735688504398e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>1.293349615575168e-07</v>
+        <v>1.725530027851797e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>1.496742031740363e-07</v>
+        <v>1.937816314799711e-07</v>
       </c>
     </row>
     <row r="3">
@@ -555,37 +555,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.721212512284779e-07</v>
+        <v>1.993449700289529e-07</v>
       </c>
       <c r="C3" t="n">
-        <v>3.968756695462126e-07</v>
+        <v>5.033507094415488e-07</v>
       </c>
       <c r="D3" t="n">
-        <v>1.666759655290179e-07</v>
+        <v>1.97575506003899e-07</v>
       </c>
       <c r="E3" t="n">
-        <v>4.253736608412742e-07</v>
+        <v>5.42522551249911e-07</v>
       </c>
       <c r="F3" t="n">
-        <v>2.872882065625717e-07</v>
+        <v>3.527961376661241e-07</v>
       </c>
       <c r="G3" t="n">
-        <v>1.807981623924882e-07</v>
+        <v>2.021835214798418e-07</v>
       </c>
       <c r="H3" t="n">
-        <v>1.720879947055952e-07</v>
+        <v>1.993446854339371e-07</v>
       </c>
       <c r="I3" t="n">
-        <v>1.766948733212924e-07</v>
+        <v>2.008332677274542e-07</v>
       </c>
       <c r="J3" t="n">
-        <v>3.598079046223883e-07</v>
+        <v>4.016700398418609e-07</v>
       </c>
       <c r="K3" t="n">
-        <v>1.485067697000477e-07</v>
+        <v>1.645395983736422e-07</v>
       </c>
       <c r="L3" t="n">
-        <v>1.68015405306383e-07</v>
+        <v>1.980201999865488e-07</v>
       </c>
     </row>
     <row r="4">
@@ -595,37 +595,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.067154776891501e-08</v>
+        <v>2.067154776891522e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>2.340764277108326e-08</v>
+        <v>2.340764277108324e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>1.785727938799153e-08</v>
+        <v>1.78572793879916e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>2.365825705235671e-08</v>
+        <v>2.36582570523567e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>2.365825705235672e-08</v>
+        <v>2.36582570523567e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>2.523756191572207e-08</v>
+        <v>2.523756191572218e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>2.06538894647342e-08</v>
+        <v>2.065388946473424e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>2.357509547865112e-08</v>
+        <v>2.357509547865113e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>4.809185229728938e-08</v>
+        <v>4.809185229728946e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>2.183703216647987e-08</v>
+        <v>2.183703216647991e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>1.855261183947784e-08</v>
+        <v>1.855261183947787e-08</v>
       </c>
     </row>
     <row r="5">
@@ -635,37 +635,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.255389559173433e-07</v>
+        <v>1.25538955917345e-07</v>
       </c>
       <c r="C5" t="n">
-        <v>1.717841694214579e-07</v>
+        <v>1.717841694214576e-07</v>
       </c>
       <c r="D5" t="n">
-        <v>7.405716942186349e-08</v>
+        <v>7.405716942186374e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>1.717841708349472e-07</v>
+        <v>1.717841708349478e-07</v>
       </c>
       <c r="F5" t="n">
-        <v>1.717841708349472e-07</v>
+        <v>1.717841708349478e-07</v>
       </c>
       <c r="G5" t="n">
-        <v>2.189240505146275e-07</v>
+        <v>2.189240505146263e-07</v>
       </c>
       <c r="H5" t="n">
-        <v>1.419230505448992e-07</v>
+        <v>1.419230505448986e-07</v>
       </c>
       <c r="I5" t="n">
-        <v>1.717839525102164e-07</v>
+        <v>1.717839525102159e-07</v>
       </c>
       <c r="J5" t="n">
-        <v>6.888681509976575e-07</v>
+        <v>6.88868150997659e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>1.50451651132848e-07</v>
+        <v>1.504516511328487e-07</v>
       </c>
       <c r="L5" t="n">
-        <v>5.093679088736724e-07</v>
+        <v>9.933865124230263e-08</v>
       </c>
     </row>
     <row r="6">
@@ -675,37 +675,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.384501117770803e-08</v>
+        <v>2.384501117770813e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>2.665225571685694e-08</v>
+        <v>2.665225571685685e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>2.079404098703779e-08</v>
+        <v>2.079408276314312e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>2.631154823265192e-08</v>
+        <v>2.631154823265195e-08</v>
       </c>
       <c r="F6" t="n">
         <v>2.677516001707023e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>3.444276286676227e-08</v>
+        <v>3.444276286676229e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>3.152208934945174e-08</v>
+        <v>3.152208934945169e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>2.674855888744406e-08</v>
+        <v>3.278029642969132e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>5.176352659032823e-08</v>
+        <v>5.821677369809349e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>2.492312695636272e-08</v>
+        <v>2.492312695636273e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>2.172796538229085e-08</v>
+        <v>2.172796538229087e-08</v>
       </c>
     </row>
     <row r="7">
@@ -715,37 +715,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.529244012494908e-08</v>
+        <v>2.529244012494907e-08</v>
       </c>
       <c r="C7" t="n">
         <v>2.819620474592652e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>2.24778870607319e-08</v>
+        <v>2.247788706073192e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>2.822363611950126e-08</v>
+        <v>2.822363611950125e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>2.822363611950126e-08</v>
+        <v>2.822363611950125e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>2.985845427175597e-08</v>
+        <v>2.985845427175596e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>2.527478182076817e-08</v>
+        <v>2.527478182076812e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>2.8195987834685e-08</v>
+        <v>2.819598783468501e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>5.271274465332334e-08</v>
+        <v>5.271274465332333e-08</v>
       </c>
       <c r="K7" t="n">
         <v>2.645792452251378e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>2.317350419551173e-08</v>
+        <v>2.317350419551176e-08</v>
       </c>
     </row>
     <row r="8">
@@ -758,34 +758,34 @@
         <v>3.073071741808258e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>4.196300333290233e-08</v>
+        <v>4.196300333327895e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>3.79380180111891e-08</v>
+        <v>3.793801801118907e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>3.968996498162954e-08</v>
+        <v>3.968996498162951e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>3.391412716986145e-08</v>
+        <v>3.391412716986144e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>4.359715389787882e-08</v>
+        <v>4.359715389787876e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>3.901348144690704e-08</v>
+        <v>3.901348144690698e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>4.193468746080779e-08</v>
+        <v>4.193468746080781e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>6.645307552287585e-08</v>
+        <v>6.64530755228759e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>3.174201721163248e-08</v>
+        <v>3.174201721163249e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>4.558268899312172e-08</v>
+        <v>4.558268899312163e-08</v>
       </c>
     </row>
     <row r="9">
@@ -795,37 +795,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6.91922004345859e-08</v>
+        <v>6.919220043458579e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>8.634546595784385e-08</v>
+        <v>8.634546595784376e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>8.062743878479508e-08</v>
+        <v>8.0627438784795e-08</v>
       </c>
       <c r="E9" t="n">
         <v>1.027890906002408e-07</v>
       </c>
       <c r="F9" t="n">
-        <v>8.634546421672808e-08</v>
+        <v>8.63454642167281e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>8.800771548367318e-08</v>
+        <v>8.80077154836732e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>8.342404303268532e-08</v>
+        <v>8.342404303268531e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>8.634524904660224e-08</v>
+        <v>8.634524904660227e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>1.108620058652405e-07</v>
+        <v>1.108620058652406e-07</v>
       </c>
       <c r="K9" t="n">
-        <v>7.635097140113312e-08</v>
+        <v>6.666451906083247e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>8.132276540742907e-08</v>
+        <v>8.132276540742895e-08</v>
       </c>
     </row>
   </sheetData>
@@ -911,37 +911,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.434797567663535e-07</v>
+        <v>1.912664331524365e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>3.729657246632785e-07</v>
+        <v>3.739755976696588e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>1.494235930085791e-07</v>
+        <v>1.915792454484551e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>4.009619679516359e-07</v>
+        <v>3.972946891369217e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>2.6433717028101e-07</v>
+        <v>2.835723427090761e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>1.525271205731724e-07</v>
+        <v>1.917425779400778e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>1.470796998240462e-07</v>
+        <v>1.914437030816892e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>1.54111866279206e-07</v>
+        <v>1.918261402551369e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>3.204879704105068e-07</v>
+        <v>3.028833536885123e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>1.241650231834447e-07</v>
+        <v>1.687062499584337e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>1.436726253770105e-07</v>
+        <v>1.912669321688527e-07</v>
       </c>
     </row>
     <row r="3">
@@ -951,37 +951,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.606998102876532e-07</v>
+        <v>1.944170031471494e-07</v>
       </c>
       <c r="C3" t="n">
-        <v>3.917783896394295e-07</v>
+        <v>4.990720161742948e-07</v>
       </c>
       <c r="D3" t="n">
-        <v>1.675364532281812e-07</v>
+        <v>1.966364552831768e-07</v>
       </c>
       <c r="E3" t="n">
-        <v>4.197794978405152e-07</v>
+        <v>5.37552243721489e-07</v>
       </c>
       <c r="F3" t="n">
-        <v>2.831547001698892e-07</v>
+        <v>3.498327150209507e-07</v>
       </c>
       <c r="G3" t="n">
-        <v>1.711061528212615e-07</v>
+        <v>1.978019329461532e-07</v>
       </c>
       <c r="H3" t="n">
-        <v>1.648426612779235e-07</v>
+        <v>1.957636840239529e-07</v>
       </c>
       <c r="I3" t="n">
-        <v>1.729238010079286e-07</v>
+        <v>1.983891760122078e-07</v>
       </c>
       <c r="J3" t="n">
-        <v>3.445888895065227e-07</v>
+        <v>3.918868415174801e-07</v>
       </c>
       <c r="K3" t="n">
-        <v>1.426339794883355e-07</v>
+        <v>1.595537266062411e-07</v>
       </c>
       <c r="L3" t="n">
-        <v>1.609216724988838e-07</v>
+        <v>1.944866204042515e-07</v>
       </c>
     </row>
     <row r="4">
@@ -991,37 +991,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.249216551545988e-08</v>
+        <v>1.249216551546011e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>1.88148133891288e-08</v>
+        <v>1.881481338912854e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>1.60255242997567e-08</v>
+        <v>1.602552429975662e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>1.899720715022509e-08</v>
+        <v>1.899720715022492e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>1.89972071502251e-08</v>
+        <v>1.899720715022511e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>1.795309539285512e-08</v>
+        <v>1.795309539285533e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>1.463386837470339e-08</v>
+        <v>1.463386837470349e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>1.936476718121491e-08</v>
+        <v>1.936476718121467e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>3.972377888510091e-08</v>
+        <v>3.972377888510097e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>1.743480497988813e-08</v>
+        <v>1.743480497988839e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>1.260891464175887e-08</v>
+        <v>1.2608914641759e-08</v>
       </c>
     </row>
     <row r="5">
@@ -1031,37 +1031,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.887306980372705e-08</v>
+        <v>2.887306980372699e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>1.295885730501324e-07</v>
+        <v>1.29588573050132e-07</v>
       </c>
       <c r="D5" t="n">
-        <v>8.457511189419758e-08</v>
+        <v>8.457511189419743e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>1.2958858683024e-07</v>
+        <v>1.295885868302396e-07</v>
       </c>
       <c r="F5" t="n">
-        <v>1.2958858683024e-07</v>
+        <v>1.295885868302396e-07</v>
       </c>
       <c r="G5" t="n">
         <v>1.171666353497743e-07</v>
       </c>
       <c r="H5" t="n">
-        <v>6.974839959644071e-08</v>
+        <v>6.974839959644092e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>1.295890734808163e-07</v>
+        <v>1.295890734808158e-07</v>
       </c>
       <c r="J5" t="n">
-        <v>5.099351585490149e-07</v>
+        <v>5.099351585490165e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>1.037119547831258e-07</v>
+        <v>1.037119547831257e-07</v>
       </c>
       <c r="L5" t="n">
-        <v>3.388464814137216e-08</v>
+        <v>3.388464814137234e-08</v>
       </c>
     </row>
     <row r="6">
@@ -1071,37 +1071,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.838099088256402e-08</v>
+        <v>1.46174416050213e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>2.141924367887427e-08</v>
+        <v>2.141924367887406e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>2.223978320071486e-08</v>
+        <v>2.223978320071518e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>2.123942446624156e-08</v>
+        <v>2.123942446624117e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>2.149725085271843e-08</v>
+        <v>2.149725085271799e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>2.007837148241637e-08</v>
+        <v>2.384192075995921e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>2.16854451050426e-08</v>
+        <v>2.168544510504261e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>2.149004327077614e-08</v>
+        <v>2.149004327077587e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>4.637197183598822e-08</v>
+        <v>4.221249397393195e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>1.952189750753916e-08</v>
+        <v>1.952189750753946e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>1.475848468401736e-08</v>
+        <v>1.475848468401758e-08</v>
       </c>
     </row>
     <row r="7">
@@ -1111,37 +1111,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.528511330783295e-08</v>
+        <v>1.528511330783289e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>2.215721454290417e-08</v>
+        <v>2.215721454290397e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>1.881837272182794e-08</v>
+        <v>1.881837272182792e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>2.204458524977564e-08</v>
+        <v>2.204458524977524e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>2.204458524977564e-08</v>
+        <v>2.204458524977524e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>2.074604318522822e-08</v>
+        <v>2.074604318522825e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>1.742681616707648e-08</v>
+        <v>1.742681616707656e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>2.215771497358799e-08</v>
+        <v>2.215771497358797e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>4.251672667747401e-08</v>
+        <v>4.251672667747396e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>2.022775277226122e-08</v>
+        <v>2.02277527722611e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>1.540186243413195e-08</v>
+        <v>1.540186243413186e-08</v>
       </c>
     </row>
     <row r="8">
@@ -1151,37 +1151,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.869849636727526e-08</v>
+        <v>1.869849636727527e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>3.043476110460331e-08</v>
+        <v>3.043476110468898e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>2.823352746990552e-08</v>
+        <v>2.823352746990534e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>2.90867042195442e-08</v>
+        <v>2.908670421954435e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>2.566104408843418e-08</v>
+        <v>2.566104408843442e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>2.913034597533343e-08</v>
+        <v>2.913034597533347e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>2.581111895721202e-08</v>
+        <v>2.581111895721225e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>3.054201776369321e-08</v>
+        <v>3.054201776369306e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>5.090200638257574e-08</v>
+        <v>5.090200638257556e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>2.354879844667603e-08</v>
+        <v>2.354879844667612e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>2.897870653241302e-08</v>
+        <v>2.897870653241299e-08</v>
       </c>
     </row>
     <row r="9">
@@ -1191,37 +1191,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.065324566878607e-08</v>
+        <v>4.065324566878633e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>5.576065115406698e-08</v>
+        <v>5.576065115406671e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>5.24219123250215e-08</v>
+        <v>5.242191232502154e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>6.526403309451373e-08</v>
+        <v>6.52640330945136e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>5.576066365280547e-08</v>
+        <v>5.576066365280535e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>5.434947979639103e-08</v>
+        <v>5.434947979639113e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>5.10302527782393e-08</v>
+        <v>5.103025277823937e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>5.576115158475082e-08</v>
+        <v>5.576115158475077e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>7.612016328863684e-08</v>
+        <v>7.612016328863661e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>4.905962328160162e-08</v>
+        <v>4.90596232816014e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>4.900529904529478e-08</v>
+        <v>4.90052990452946e-08</v>
       </c>
     </row>
   </sheetData>
@@ -1307,37 +1307,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.097862591961746e-07</v>
+        <v>1.431291159746e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>2.174584298138646e-07</v>
+        <v>2.317959224429214e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>1.092037597414144e-07</v>
+        <v>1.43098460185233e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>1.47770645786464e-07</v>
+        <v>1.718932782533722e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>1.47770645786464e-07</v>
+        <v>1.718932868253196e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>1.137324558677777e-07</v>
+        <v>1.433367964676488e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>1.115604013204287e-07</v>
+        <v>1.432119013917055e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>1.134446627450511e-07</v>
+        <v>1.43321724938002e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>2.601963395074088e-07</v>
+        <v>2.560240479771768e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>1.173622521211738e-07</v>
+        <v>1.455839874042471e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>1.142288308742898e-07</v>
+        <v>1.433601947860985e-07</v>
       </c>
     </row>
     <row r="3">
@@ -1347,37 +1347,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.233137995881706e-07</v>
+        <v>1.461685475469527e-07</v>
       </c>
       <c r="C3" t="n">
-        <v>2.311635893861243e-07</v>
+        <v>2.928907412244925e-07</v>
       </c>
       <c r="D3" t="n">
-        <v>1.226438045507977e-07</v>
+        <v>1.459478403225792e-07</v>
       </c>
       <c r="E3" t="n">
-        <v>1.618479170390023e-07</v>
+        <v>1.94701374381938e-07</v>
       </c>
       <c r="F3" t="n">
-        <v>1.618479170390023e-07</v>
+        <v>1.947013829538846e-07</v>
       </c>
       <c r="G3" t="n">
-        <v>1.278527432126921e-07</v>
+        <v>1.476495562310534e-07</v>
       </c>
       <c r="H3" t="n">
-        <v>1.253593160185767e-07</v>
+        <v>1.468346897467069e-07</v>
       </c>
       <c r="I3" t="n">
-        <v>1.275297421566161e-07</v>
+        <v>1.475393353992756e-07</v>
       </c>
       <c r="J3" t="n">
-        <v>2.7609366846215e-07</v>
+        <v>3.370818933381487e-07</v>
       </c>
       <c r="K3" t="n">
-        <v>1.316316676928419e-07</v>
+        <v>1.516412289427225e-07</v>
       </c>
       <c r="L3" t="n">
-        <v>1.284231248140853e-07</v>
+        <v>1.478521584498601e-07</v>
       </c>
     </row>
     <row r="4">
@@ -1387,37 +1387,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.467035277897836e-08</v>
+        <v>1.467035277897833e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>1.472308863787625e-08</v>
+        <v>1.472308863787618e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>1.432408153571908e-08</v>
+        <v>1.432408153571925e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>1.710522057969079e-08</v>
+        <v>1.710522057969072e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>1.710522057969079e-08</v>
+        <v>1.710522057969078e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>1.704410693861057e-08</v>
+        <v>1.704410693861075e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>1.572607596995175e-08</v>
+        <v>1.572607596995207e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>1.703181867416284e-08</v>
+        <v>1.703181867416241e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>2.404899347581403e-08</v>
+        <v>2.404899347581385e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>1.76063871836617e-08</v>
+        <v>1.760638718366179e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>1.731129809742554e-08</v>
+        <v>1.731129809742546e-08</v>
       </c>
     </row>
     <row r="5">
@@ -1427,34 +1427,34 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.153754173130132e-08</v>
+        <v>5.153754173130083e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>6.445431477811877e-08</v>
+        <v>6.445431477811884e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>4.404299819637716e-08</v>
+        <v>4.404299819637745e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>9.010856008604081e-08</v>
+        <v>9.010856008604114e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>9.010856008604081e-08</v>
+        <v>9.010856008604114e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>9.457262457877324e-08</v>
+        <v>9.457262457877008e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>7.653281450262226e-08</v>
+        <v>7.65328145026228e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>9.010879278374417e-08</v>
+        <v>9.010879278374364e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>2.284688003813705e-07</v>
+        <v>2.284688003813708e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>1.031305388733918e-07</v>
+        <v>1.031305388733923e-07</v>
       </c>
       <c r="L5" t="n">
         <v>1.103634007596612e-07</v>
@@ -1467,37 +1467,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.653964889732587e-08</v>
+        <v>2.204210656697847e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>1.7078678885473e-08</v>
+        <v>1.707867888547362e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>1.607215673724646e-08</v>
+        <v>1.607221466438917e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>1.859780973187712e-08</v>
+        <v>1.859780973187631e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>1.891613148956448e-08</v>
+        <v>1.891613148956441e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>2.441586072661103e-08</v>
+        <v>1.891340305695881e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>2.457195648610894e-08</v>
+        <v>2.457195648610539e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>2.440357246216327e-08</v>
+        <v>1.89011147925073e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>3.171927225521084e-08</v>
+        <v>3.171927225521312e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>1.944631506187206e-08</v>
+        <v>1.944631506186962e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>1.919833619610656e-08</v>
+        <v>1.919833619610589e-08</v>
       </c>
     </row>
     <row r="7">
@@ -1507,37 +1507,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.852704451232647e-08</v>
+        <v>1.852704451232705e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>1.923497951729034e-08</v>
+        <v>1.923497951729123e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>1.818060901728992e-08</v>
+        <v>1.818060901729046e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>2.091809705518415e-08</v>
+        <v>2.091809705518394e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>2.091809705518415e-08</v>
+        <v>2.091809705518394e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>2.090079867195872e-08</v>
+        <v>2.090079867195814e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>1.958276770329984e-08</v>
+        <v>1.95827677033005e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>2.08885104075109e-08</v>
+        <v>2.08885104075111e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>2.790568520916213e-08</v>
+        <v>2.790568520916173e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>2.146307891700978e-08</v>
+        <v>2.14630789170098e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>2.116798983077362e-08</v>
+        <v>2.116798983077377e-08</v>
       </c>
     </row>
     <row r="8">
@@ -1547,37 +1547,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.342906238839026e-08</v>
+        <v>2.342906238839068e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>3.143955055374051e-08</v>
+        <v>3.143955055374137e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>3.186327345286559e-08</v>
+        <v>3.186327345286474e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>3.110073010387037e-08</v>
+        <v>3.110073010387096e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>2.603870882011041e-08</v>
+        <v>2.603870882011031e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>3.307530168770087e-08</v>
+        <v>3.307530168770118e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>3.175727071912368e-08</v>
+        <v>3.175727071912428e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>3.306301342325351e-08</v>
+        <v>3.306301342325361e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>4.008161745319277e-08</v>
+        <v>4.00816174531936e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>2.623000664986867e-08</v>
+        <v>2.623000664986847e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>4.093921166873967e-08</v>
+        <v>4.093921166874015e-08</v>
       </c>
     </row>
     <row r="9">
@@ -1587,37 +1587,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5.06111429582525e-08</v>
+        <v>5.06111429582508e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>6.200179084196836e-08</v>
+        <v>6.200179084196796e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>6.094758911742838e-08</v>
+        <v>6.094758911743028e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>7.598271573115789e-08</v>
+        <v>7.598271573115922e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>6.365508779879153e-08</v>
+        <v>6.365508779878957e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>6.366760999663662e-08</v>
+        <v>6.366760999663859e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>6.234957902797776e-08</v>
+        <v>6.234957902797621e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>6.365532173218888e-08</v>
+        <v>6.365532173218863e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>7.067249653384006e-08</v>
+        <v>7.067249653384025e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>5.804028634813091e-08</v>
+        <v>5.804028634812958e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>6.393480115545158e-08</v>
+        <v>6.393480115545305e-08</v>
       </c>
     </row>
   </sheetData>
@@ -1703,37 +1703,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.061092542005931e-07</v>
+        <v>1.406211312686572e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>2.158623065862813e-07</v>
+        <v>2.310514326509913e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>1.058115199970539e-07</v>
+        <v>1.406054621088727e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>1.442231433804929e-07</v>
+        <v>1.708749499219225e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>1.442231433804929e-07</v>
+        <v>1.708749491345869e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>1.094728179275061e-07</v>
+        <v>1.40798148947029e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>1.074504357841872e-07</v>
+        <v>1.406821675233036e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>1.079959731309763e-07</v>
+        <v>1.407204672757418e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>2.561018494887697e-07</v>
+        <v>2.547085064485532e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>1.134110014240704e-07</v>
+        <v>1.443557704243709e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>1.099876077365269e-07</v>
+        <v>1.408231446703122e-07</v>
       </c>
     </row>
     <row r="3">
@@ -1743,37 +1743,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.192828584065053e-07</v>
+        <v>1.422966769949385e-07</v>
       </c>
       <c r="C3" t="n">
-        <v>2.292081517533294e-07</v>
+        <v>2.919175361166917e-07</v>
       </c>
       <c r="D3" t="n">
-        <v>1.1894040239698e-07</v>
+        <v>1.421833265755543e-07</v>
       </c>
       <c r="E3" t="n">
-        <v>1.576802653816977e-07</v>
+        <v>1.927782528883521e-07</v>
       </c>
       <c r="F3" t="n">
-        <v>1.576802653816976e-07</v>
+        <v>1.927782521010162e-07</v>
       </c>
       <c r="G3" t="n">
-        <v>1.23151653452582e-07</v>
+        <v>1.435589834724974e-07</v>
       </c>
       <c r="H3" t="n">
-        <v>1.208294673325034e-07</v>
+        <v>1.42798356901174e-07</v>
       </c>
       <c r="I3" t="n">
-        <v>1.214565291801641e-07</v>
+        <v>1.430032483326222e-07</v>
       </c>
       <c r="J3" t="n">
-        <v>2.713485916933215e-07</v>
+        <v>3.34607289514754e-07</v>
       </c>
       <c r="K3" t="n">
-        <v>1.270359760419469e-07</v>
+        <v>1.4932533877479e-07</v>
       </c>
       <c r="L3" t="n">
-        <v>1.237433032961053e-07</v>
+        <v>1.437651534398646e-07</v>
       </c>
     </row>
     <row r="4">
@@ -1783,37 +1783,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.311799961947404e-08</v>
+        <v>1.311799961947066e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>1.324185053307582e-08</v>
+        <v>1.324185053307579e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>1.294100925149651e-08</v>
+        <v>1.294100925153483e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>1.439028701993056e-08</v>
+        <v>1.439028701993079e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>1.439028701993047e-08</v>
+        <v>1.439028701993079e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>1.514490595826818e-08</v>
+        <v>1.514490595828534e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>1.391627593365315e-08</v>
+        <v>1.391627593360301e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>1.442249677757196e-08</v>
+        <v>1.442249677757198e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>2.132262036486524e-08</v>
+        <v>2.132262036490899e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>1.490433658703726e-08</v>
+        <v>1.490433658705748e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>1.542340169629889e-08</v>
+        <v>1.542340169628255e-08</v>
       </c>
     </row>
     <row r="5">
@@ -1823,37 +1823,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.740130405731602e-08</v>
+        <v>3.740130405734024e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>4.931079471609454e-08</v>
+        <v>4.931079471609413e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>3.348383445279332e-08</v>
+        <v>3.348383445287092e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>5.618793052090845e-08</v>
+        <v>5.618793052090805e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>5.618793052090845e-08</v>
+        <v>5.618793052090805e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>7.223470616922999e-08</v>
+        <v>7.223470616924077e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>5.510839213334397e-08</v>
+        <v>5.510839213338025e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>5.61879975192439e-08</v>
+        <v>5.618799751924433e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>1.842817179909891e-07</v>
+        <v>1.84281717990956e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>6.708165763612209e-08</v>
+        <v>6.708165763612837e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>8.537526023859917e-08</v>
+        <v>8.537526023856225e-08</v>
       </c>
     </row>
     <row r="6">
@@ -1863,37 +1863,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.945475245012609e-08</v>
+        <v>1.945475245016327e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>1.513093363340004e-08</v>
+        <v>1.513093363340016e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>1.948350419473457e-08</v>
+        <v>1.948350419479827e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>1.561571011863501e-08</v>
+        <v>1.561571011863637e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>1.589100376881304e-08</v>
+        <v>1.589100376881341e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>1.661172276073266e-08</v>
+        <v>2.148165878897791e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>2.15772815238496e-08</v>
+        <v>2.157728152389593e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>1.588931358000509e-08</v>
+        <v>1.588931358000591e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>2.30072962268417e-08</v>
+        <v>2.300729622687071e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>1.629521336040607e-08</v>
+        <v>1.629521336035697e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>1.691532296466974e-08</v>
+        <v>1.691532296473642e-08</v>
       </c>
     </row>
     <row r="7">
@@ -1903,37 +1903,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.646718087798137e-08</v>
+        <v>1.64671808779506e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>1.715300457115488e-08</v>
+        <v>1.715300457115489e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>1.629003484391192e-08</v>
+        <v>1.629003484392273e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>1.777512281043512e-08</v>
+        <v>1.777512281043626e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>1.777512281043512e-08</v>
+        <v>1.777512281043625e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>1.849408721679478e-08</v>
+        <v>1.849408721676529e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>1.726545719212236e-08</v>
+        <v>1.726545719208292e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>1.777167803605103e-08</v>
+        <v>1.777167803605191e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>2.467180162335319e-08</v>
+        <v>2.46718016233889e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>1.825351784552405e-08</v>
+        <v>1.825351784553738e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>1.877258295480732e-08</v>
+        <v>1.877258295476245e-08</v>
       </c>
     </row>
     <row r="8">
@@ -1943,37 +1943,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.082930531013131e-08</v>
+        <v>2.082930531011744e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>2.783865523632191e-08</v>
+        <v>2.783865523602139e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>2.828133767563618e-08</v>
+        <v>2.828133767566046e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>2.67286339734302e-08</v>
+        <v>2.672863397343115e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>2.233621892157023e-08</v>
+        <v>2.233621892157044e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>2.917499375160454e-08</v>
+        <v>2.917499375161599e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>2.794636372695436e-08</v>
+        <v>2.794636372702979e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>2.845258457090235e-08</v>
+        <v>2.845258457090261e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>3.535394996176213e-08</v>
+        <v>3.535394996177586e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>2.249826765764553e-08</v>
+        <v>2.249826765759792e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>3.605398574734265e-08</v>
+        <v>3.60539857473494e-08</v>
       </c>
     </row>
     <row r="9">
@@ -1983,37 +1983,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.290937857377392e-08</v>
+        <v>4.290937857376453e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>5.245182711885705e-08</v>
+        <v>5.245182711885776e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>5.158901694729292e-08</v>
+        <v>5.158901694732507e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>6.329079296083015e-08</v>
+        <v>6.329079296083011e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>5.307043244221144e-08</v>
+        <v>5.307043244221191e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>5.379290976448328e-08</v>
+        <v>5.379290976446816e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>5.256427973976946e-08</v>
+        <v>5.256427973978576e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>5.307050058375359e-08</v>
+        <v>5.307050058375472e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>5.997062417106045e-08</v>
+        <v>5.997062417109172e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>4.842077880736352e-08</v>
+        <v>4.842077880735922e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>5.407140550243641e-08</v>
+        <v>5.407140550246533e-08</v>
       </c>
     </row>
   </sheetData>
@@ -2099,37 +2099,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.02069718953027e-07</v>
+        <v>1.376068834844599e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>2.144347377334151e-07</v>
+        <v>2.302801033525496e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>1.020716038434291e-07</v>
+        <v>1.37606982682498e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>1.416752070437093e-07</v>
+        <v>1.699349486497027e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>1.416752070437093e-07</v>
+        <v>1.699349364301613e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>1.052264079328105e-07</v>
+        <v>1.377730137557765e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>1.034397850722308e-07</v>
+        <v>1.376703298359379e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>1.028889910797142e-07</v>
+        <v>1.37650012819666e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>2.537945125375858e-07</v>
+        <v>2.53354629424318e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>1.10173509928804e-07</v>
+        <v>1.430952724525822e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>1.042744307870591e-07</v>
+        <v>1.377202879872075e-07</v>
       </c>
     </row>
     <row r="3">
@@ -2139,37 +2139,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.148977215290031e-07</v>
+        <v>1.376819553241704e-07</v>
       </c>
       <c r="C3" t="n">
-        <v>2.274232340739318e-07</v>
+        <v>2.909789826737826e-07</v>
       </c>
       <c r="D3" t="n">
-        <v>1.148998895434192e-07</v>
+        <v>1.376813787854503e-07</v>
       </c>
       <c r="E3" t="n">
-        <v>1.546263063133113e-07</v>
+        <v>1.912800843645565e-07</v>
       </c>
       <c r="F3" t="n">
-        <v>1.546263063133113e-07</v>
+        <v>1.912800721450149e-07</v>
       </c>
       <c r="G3" t="n">
-        <v>1.185285677619062e-07</v>
+        <v>1.388665948838403e-07</v>
       </c>
       <c r="H3" t="n">
-        <v>1.164767201596824e-07</v>
+        <v>1.381937038837309e-07</v>
       </c>
       <c r="I3" t="n">
-        <v>1.158377796214476e-07</v>
+        <v>1.379883260087878e-07</v>
       </c>
       <c r="J3" t="n">
-        <v>2.686535538533042e-07</v>
+        <v>3.326519548087884e-07</v>
       </c>
       <c r="K3" t="n">
-        <v>1.232436495153087e-07</v>
+        <v>1.472046987956958e-07</v>
       </c>
       <c r="L3" t="n">
-        <v>1.17433155889255e-07</v>
+        <v>1.385158549240617e-07</v>
       </c>
     </row>
     <row r="4">
@@ -2179,37 +2179,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.177068453260482e-08</v>
+        <v>1.177068453260468e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>1.204089537115573e-08</v>
+        <v>1.204089537115568e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>1.177180502007924e-08</v>
+        <v>1.177180502007904e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>1.228131134591388e-08</v>
+        <v>1.228131134591378e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>1.228131134591388e-08</v>
+        <v>1.22813113459138e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>1.367450066054425e-08</v>
+        <v>1.367450066054404e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>1.258603710913805e-08</v>
+        <v>1.258603710913789e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>1.243930654670624e-08</v>
+        <v>1.243930654670604e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>1.980869386425835e-08</v>
+        <v>1.980869386425819e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>1.272896243842843e-08</v>
+        <v>1.27289624384283e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>1.308138413778783e-08</v>
+        <v>1.308138413778765e-08</v>
       </c>
     </row>
     <row r="5">
@@ -2219,37 +2219,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.788207165006924e-08</v>
+        <v>2.788207165006908e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>3.891978227772984e-08</v>
+        <v>3.891978227772972e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>2.723621932376424e-08</v>
+        <v>2.723621932376381e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>3.593079770053816e-08</v>
+        <v>3.593079770053784e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>3.593079770053816e-08</v>
+        <v>3.593079770053784e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>6.055948788444682e-08</v>
+        <v>6.055948788444316e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>4.505201044990952e-08</v>
+        <v>4.505201044990932e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>3.593074725168516e-08</v>
+        <v>3.593074725168482e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>1.715910956460767e-07</v>
+        <v>1.715910956460764e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>4.36406483539378e-08</v>
+        <v>4.364064835393818e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>5.539928379362444e-08</v>
+        <v>5.539928379362417e-08</v>
       </c>
     </row>
     <row r="6">
@@ -2259,37 +2259,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.294970145129605e-08</v>
+        <v>1.294970145129609e-08</v>
       </c>
       <c r="C6" t="n">
         <v>1.348715744135499e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>1.28478128488131e-08</v>
+        <v>1.284776803244139e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>1.336716772799454e-08</v>
+        <v>1.336716772799443e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>1.360757735647144e-08</v>
+        <v>1.360757735647147e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>1.935728954981147e-08</v>
+        <v>1.935728954981137e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>1.914876380886475e-08</v>
+        <v>1.914876380886459e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>1.812209543597333e-08</v>
+        <v>1.812209543597364e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>2.555515893312904e-08</v>
+        <v>2.555515893312892e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>1.38030665880326e-08</v>
+        <v>1.380306658803253e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>1.429056961518834e-08</v>
+        <v>1.429056961518824e-08</v>
       </c>
     </row>
     <row r="7">
@@ -2299,37 +2299,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.4770822458612e-08</v>
+        <v>1.477082245861171e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>1.540617605990815e-08</v>
+        <v>1.540617605990792e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>1.477176218972373e-08</v>
+        <v>1.477176218972341e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>1.540563321133158e-08</v>
+        <v>1.540563321133128e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>1.540563321133158e-08</v>
+        <v>1.540563321133128e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>1.667463858655155e-08</v>
+        <v>1.667463858655106e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>1.558617503514524e-08</v>
+        <v>1.558617503514495e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>1.543944447271343e-08</v>
+        <v>1.543944447271307e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>2.280883179026552e-08</v>
+        <v>2.280883179026528e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>1.572910036443561e-08</v>
+        <v>1.572910036443533e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>1.608152206379501e-08</v>
+        <v>1.608152206379471e-08</v>
       </c>
     </row>
     <row r="8">
@@ -2339,37 +2339,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.874163629888009e-08</v>
+        <v>1.874163629887981e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>2.494764703925702e-08</v>
+        <v>2.494764703952437e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>2.550605559531962e-08</v>
+        <v>2.550605559531908e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>2.345222002276528e-08</v>
+        <v>2.345222002276482e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>1.956778299419093e-08</v>
+        <v>1.956778299419069e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>2.62471936932078e-08</v>
+        <v>2.624719369320738e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>2.515873014185013e-08</v>
+        <v>2.515873014184948e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>2.50119995793699e-08</v>
+        <v>2.501199957936906e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>3.238248778628832e-08</v>
+        <v>3.238248778628768e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>1.959585898581652e-08</v>
+        <v>1.959585898581635e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>3.150556432120473e-08</v>
+        <v>3.150556432120432e-08</v>
       </c>
     </row>
     <row r="9">
@@ -2379,37 +2379,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.821255593152748e-08</v>
+        <v>3.821255593152837e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>4.667086565434421e-08</v>
+        <v>4.667086565434541e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>4.603663590369584e-08</v>
+        <v>4.603663590369701e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>5.573171148735781e-08</v>
+        <v>5.573171148735943e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>4.670418326828116e-08</v>
+        <v>4.670418326828233e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>4.793932818098757e-08</v>
+        <v>4.793932818098866e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>4.685086462958134e-08</v>
+        <v>4.685086462958258e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>4.670413406714956e-08</v>
+        <v>4.670413406715066e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>5.407352138470155e-08</v>
+        <v>5.407352138470278e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>3.714329093748671e-08</v>
+        <v>4.22772443974748e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>4.734621165823111e-08</v>
+        <v>4.734621165823227e-08</v>
       </c>
     </row>
   </sheetData>
@@ -2495,37 +2495,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.056065160557992e-07</v>
+        <v>1.403153706868169e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>2.155964267699513e-07</v>
+        <v>2.315748206890791e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>1.053836972807448e-07</v>
+        <v>1.403036441772396e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>1.45973581726054e-07</v>
+        <v>1.716599060585056e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>1.45973581726054e-07</v>
+        <v>1.716599184206518e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>1.092484050737831e-07</v>
+        <v>1.405070360724592e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>1.074953879075944e-07</v>
+        <v>1.404047130244351e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>1.08499231994339e-07</v>
+        <v>1.404676767612367e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>2.576614385838697e-07</v>
+        <v>2.558545340678017e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>1.152954701170809e-07</v>
+        <v>1.45322384628633e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>1.078851350962255e-07</v>
+        <v>1.404313563036363e-07</v>
       </c>
     </row>
     <row r="3">
@@ -2535,37 +2535,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.190180232472762e-07</v>
+        <v>1.413522491734683e-07</v>
       </c>
       <c r="C3" t="n">
-        <v>2.290574108978231e-07</v>
+        <v>2.921087725948305e-07</v>
       </c>
       <c r="D3" t="n">
-        <v>1.187617354991934e-07</v>
+        <v>1.412668726355786e-07</v>
       </c>
       <c r="E3" t="n">
-        <v>1.598197901270578e-07</v>
+        <v>1.939241623461013e-07</v>
       </c>
       <c r="F3" t="n">
-        <v>1.598197901270578e-07</v>
+        <v>1.939241747082473e-07</v>
       </c>
       <c r="G3" t="n">
-        <v>1.23206950032995e-07</v>
+        <v>1.427190448598757e-07</v>
       </c>
       <c r="H3" t="n">
-        <v>1.211955864320119e-07</v>
+        <v>1.420604511984624e-07</v>
       </c>
       <c r="I3" t="n">
-        <v>1.223487207631951e-07</v>
+        <v>1.424361999823637e-07</v>
       </c>
       <c r="J3" t="n">
-        <v>2.731970998694056e-07</v>
+        <v>3.361575387421808e-07</v>
       </c>
       <c r="K3" t="n">
-        <v>1.292960184026905e-07</v>
+        <v>1.507450942594519e-07</v>
       </c>
       <c r="L3" t="n">
-        <v>1.216384318897057e-07</v>
+        <v>1.422154799974043e-07</v>
       </c>
     </row>
     <row r="4">
@@ -2575,34 +2575,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.408429267818363e-08</v>
+        <v>1.408429267818364e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>1.355235340174776e-08</v>
+        <v>1.355235340174775e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>1.39518363580462e-08</v>
+        <v>1.395183635804622e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>1.594346860381682e-08</v>
+        <v>1.594346860381679e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>1.594346860381682e-08</v>
+        <v>1.59434686038168e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>1.62767811031971e-08</v>
+        <v>1.627678110319711e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>1.520812283301341e-08</v>
+        <v>1.520812283301342e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>1.598824243113652e-08</v>
+        <v>1.598824243113657e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>2.24908139797328e-08</v>
+        <v>2.249081397973278e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>1.641547313216467e-08</v>
+        <v>1.641547313216468e-08</v>
       </c>
       <c r="L4" t="n">
         <v>1.543925204579816e-08</v>
@@ -2615,37 +2615,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.159357376370734e-08</v>
+        <v>4.159357376370729e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>4.525361230582745e-08</v>
+        <v>4.525361230582738e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>3.820632119057666e-08</v>
+        <v>3.820632119057654e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>7.212842960625047e-08</v>
+        <v>7.212842960624937e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>7.212842960625047e-08</v>
+        <v>7.212842960624937e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>8.130840562727265e-08</v>
+        <v>8.130840562727278e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>6.70355896343669e-08</v>
+        <v>6.703558963436697e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>7.212859470817715e-08</v>
+        <v>7.212859470817588e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>2.000590425914104e-07</v>
+        <v>2.000590425914103e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>8.256680168683885e-08</v>
+        <v>8.256680168683891e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>7.287511996784633e-08</v>
+        <v>7.287511996784632e-08</v>
       </c>
     </row>
     <row r="6">
@@ -2655,37 +2655,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.598868122052801e-08</v>
+        <v>1.598868122052802e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>1.599830538720907e-08</v>
+        <v>1.599830538720904e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>1.57488341047665e-08</v>
+        <v>1.574877445614261e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>1.755172261126305e-08</v>
+        <v>1.755172261126268e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>1.789763671736191e-08</v>
+        <v>1.78976367173617e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>1.818116964554149e-08</v>
+        <v>1.818116964554148e-08</v>
       </c>
       <c r="H6" t="n">
         <v>2.419571160509412e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>1.7892630973481e-08</v>
+        <v>2.338950123170136e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>3.0226316261249e-08</v>
+        <v>2.467873841729774e-08</v>
       </c>
       <c r="K6" t="n">
         <v>1.829507434914948e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>1.735320334738967e-08</v>
+        <v>1.735320334738968e-08</v>
       </c>
     </row>
     <row r="7">
@@ -2695,37 +2695,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.785805529245472e-08</v>
+        <v>1.785805529245471e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>1.806019647965651e-08</v>
+        <v>1.80601964796565e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>1.772545532438091e-08</v>
+        <v>1.772545532438093e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>1.976055368782224e-08</v>
+        <v>1.976055368782207e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>1.976055368782224e-08</v>
+        <v>1.976055368782207e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>2.005054371746817e-08</v>
+        <v>2.005054371746818e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>1.898188544728448e-08</v>
+        <v>1.898188544728449e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>1.976200504540773e-08</v>
+        <v>1.976200504540765e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>2.626457659400387e-08</v>
+        <v>2.626457659400385e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>2.018923574643573e-08</v>
+        <v>2.018923574643575e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>1.92130146600692e-08</v>
+        <v>1.921301466006923e-08</v>
       </c>
     </row>
     <row r="8">
@@ -2735,37 +2735,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.27993816957729e-08</v>
+        <v>2.279938169577293e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>3.028093774066532e-08</v>
+        <v>3.028093774100545e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>3.14553994599582e-08</v>
+        <v>3.145539945995824e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>2.999180505308738e-08</v>
+        <v>2.999180505308754e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>2.493322110923198e-08</v>
+        <v>2.49332211092319e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>3.227097449560773e-08</v>
+        <v>3.227097449560774e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>3.120231622551558e-08</v>
+        <v>3.120231622551559e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>3.198243582354743e-08</v>
+        <v>3.198243582354723e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>3.84864379000519e-08</v>
+        <v>3.848643790005194e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>2.499534905094811e-08</v>
+        <v>2.499534905094815e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>3.90370786038939e-08</v>
+        <v>3.903707860389397e-08</v>
       </c>
     </row>
     <row r="9">
@@ -2778,31 +2778,31 @@
         <v>4.965713451125922e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>6.045517511441345e-08</v>
+        <v>6.045517511441343e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>6.012058215210124e-08</v>
+        <v>6.012058215210118e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>7.438426456584399e-08</v>
+        <v>7.438426456584381e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>6.21568174761179e-08</v>
+        <v>6.21568174761177e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>6.244552235222517e-08</v>
+        <v>6.244552235222513e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>6.137686408204143e-08</v>
+        <v>6.137686408204147e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>6.215698368016466e-08</v>
+        <v>6.215698368016461e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>6.865955522876084e-08</v>
+        <v>6.865955522876079e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>4.924208447717974e-08</v>
+        <v>5.644491055790178e-08</v>
       </c>
       <c r="L9" t="n">
         <v>6.160799329482618e-08</v>
@@ -2891,37 +2891,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9.83468915082516e-08</v>
+        <v>1.351782065610463e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>2.13487766369352e-07</v>
+        <v>2.309226864796251e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>9.883834744901406e-08</v>
+        <v>1.352040709111041e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>1.423447521284537e-07</v>
+        <v>1.707748074425265e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>1.423447521284537e-07</v>
+        <v>1.707748156411621e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>1.00203899658982e-07</v>
+        <v>1.352759372117062e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>9.94234258830829e-08</v>
+        <v>1.352265750359589e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>9.966245043818158e-08</v>
+        <v>1.352474982989548e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>2.492191349076508e-07</v>
+        <v>2.546106963683099e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>1.102017242506275e-07</v>
+        <v>1.442351527040745e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>9.954209302687537e-08</v>
+        <v>1.352384210288733e-07</v>
       </c>
     </row>
     <row r="3">
@@ -2931,37 +2931,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.114200992142837e-07</v>
+        <v>1.329528823540035e-07</v>
       </c>
       <c r="C3" t="n">
-        <v>2.26572556975253e-07</v>
+        <v>2.91038716262606e-07</v>
       </c>
       <c r="D3" t="n">
-        <v>1.119853753509522e-07</v>
+        <v>1.331360593234495e-07</v>
       </c>
       <c r="E3" t="n">
-        <v>1.556157274047798e-07</v>
+        <v>1.92089686370914e-07</v>
       </c>
       <c r="F3" t="n">
-        <v>1.556157274047798e-07</v>
+        <v>1.920896945695494e-07</v>
       </c>
       <c r="G3" t="n">
-        <v>1.135560432657035e-07</v>
+        <v>1.336496773827212e-07</v>
       </c>
       <c r="H3" t="n">
-        <v>1.126625744046795e-07</v>
+        <v>1.333533939245334e-07</v>
       </c>
       <c r="I3" t="n">
-        <v>1.12934529656252e-07</v>
+        <v>1.334458515854021e-07</v>
       </c>
       <c r="J3" t="n">
-        <v>2.634768605247878e-07</v>
+        <v>3.323767825678263e-07</v>
       </c>
       <c r="K3" t="n">
-        <v>1.234310941496432e-07</v>
+        <v>1.482015463908876e-07</v>
       </c>
       <c r="L3" t="n">
-        <v>1.127943239843909e-07</v>
+        <v>1.334044992271889e-07</v>
       </c>
     </row>
     <row r="4">
@@ -2971,37 +2971,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.246791747887187e-08</v>
+        <v>1.246791747887201e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>1.176627515079516e-08</v>
+        <v>1.176627515079523e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>1.276006721090066e-08</v>
+        <v>1.27600672109007e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>1.333346205993625e-08</v>
+        <v>1.333346205993614e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>1.333346205993625e-08</v>
+        <v>1.333346205993614e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>1.359926463885699e-08</v>
+        <v>1.359926463885673e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>1.310859158861823e-08</v>
+        <v>1.310859158861832e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>1.343353054759363e-08</v>
+        <v>1.343353054759352e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>1.715574830979845e-08</v>
+        <v>1.715574830979864e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>1.308594269911607e-08</v>
+        <v>1.308594269911618e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>1.317851107712551e-08</v>
+        <v>1.317851107712562e-08</v>
       </c>
     </row>
     <row r="5">
@@ -3011,37 +3011,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.397174764048444e-08</v>
+        <v>2.397174764048449e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>2.488356794073456e-08</v>
+        <v>2.488356794073425e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>2.840395861627363e-08</v>
+        <v>2.84039586162736e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>3.718422861553661e-08</v>
+        <v>3.718422861553663e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>3.718422861553661e-08</v>
+        <v>3.718422861553663e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>4.315394729148649e-08</v>
+        <v>4.315394729148677e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>3.740297765516637e-08</v>
+        <v>3.740297765516548e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>3.718442319348632e-08</v>
+        <v>3.718442319349077e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>1.077982695709204e-07</v>
+        <v>1.077982695709211e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>3.40384907158887e-08</v>
+        <v>3.403849071588833e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>3.929810141077833e-08</v>
+        <v>3.929810141077817e-08</v>
       </c>
     </row>
     <row r="6">
@@ -3051,37 +3051,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.408925521450221e-08</v>
+        <v>1.408925521450208e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>1.397061851324098e-08</v>
+        <v>1.397061851324089e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>1.432540652822884e-08</v>
+        <v>1.963423758082622e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>1.474354617313506e-08</v>
+        <v>1.474354617313526e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>1.505173449561523e-08</v>
+        <v>1.505173449561503e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>2.016759405456602e-08</v>
+        <v>1.522060237448688e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>2.125327045664309e-08</v>
+        <v>2.125327045664303e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>2.000185996330269e-08</v>
+        <v>2.000185996330197e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>1.901056698688928e-08</v>
+        <v>2.403246637461861e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>1.465312026748269e-08</v>
+        <v>1.465312026748254e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>1.480869229691835e-08</v>
+        <v>1.480869229691829e-08</v>
       </c>
     </row>
     <row r="7">
@@ -3091,37 +3091,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.575184143821765e-08</v>
+        <v>1.575184143821753e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>1.580592774285453e-08</v>
+        <v>1.580592774285439e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>1.604388257455506e-08</v>
+        <v>1.604388257455497e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>1.670206977814853e-08</v>
+        <v>1.670206977814833e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>1.670206977814853e-08</v>
+        <v>1.670206977814833e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>1.688318859820229e-08</v>
+        <v>1.688318859820249e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>1.639251554796403e-08</v>
+        <v>1.639251554796385e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>1.671745450693943e-08</v>
+        <v>1.671745450693919e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>2.043967226914422e-08</v>
+        <v>2.043967226914416e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>1.636986665846183e-08</v>
+        <v>1.636986665846171e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>1.64624350364713e-08</v>
+        <v>1.646243503647119e-08</v>
       </c>
     </row>
     <row r="8">
@@ -3131,37 +3131,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.022509901795573e-08</v>
+        <v>2.022509901795594e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>2.67406494064626e-08</v>
+        <v>2.674064940615777e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>2.833445063352733e-08</v>
+        <v>2.833445063352764e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>2.588265128552738e-08</v>
+        <v>2.588265128552745e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>2.138675681376426e-08</v>
+        <v>2.13867568137643e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>2.783108874771389e-08</v>
+        <v>2.783108874771436e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>2.734041569759136e-08</v>
+        <v>2.734041569759164e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>2.766535465645101e-08</v>
+        <v>2.766535465645119e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>3.138884484949492e-08</v>
+        <v>3.138884484949528e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>2.072285443019229e-08</v>
+        <v>2.072285443019252e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>3.417364073092452e-08</v>
+        <v>3.417364073092488e-08</v>
       </c>
     </row>
     <row r="9">
@@ -3171,37 +3171,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.174369587768475e-08</v>
+        <v>4.174369587768447e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>5.056696689497744e-08</v>
+        <v>5.056696689497702e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>5.080503402365213e-08</v>
+        <v>5.08050340236517e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>6.159775454728101e-08</v>
+        <v>6.15977545472804e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>5.147829820001963e-08</v>
+        <v>5.14782982000191e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>5.164422775032538e-08</v>
+        <v>5.164422775032506e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>5.115355470008692e-08</v>
+        <v>5.115355470008646e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>5.147849365906237e-08</v>
+        <v>5.147849365906177e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>5.520071142126723e-08</v>
+        <v>5.520071142126678e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>4.008893600412368e-08</v>
+        <v>4.60500073055704e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>5.122347418859434e-08</v>
+        <v>5.122347418859381e-08</v>
       </c>
     </row>
   </sheetData>
@@ -3287,37 +3287,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.990903701160585e-08</v>
+        <v>1.279225448213051e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>2.128377353039321e-07</v>
+        <v>2.300492411876965e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>9.037161511455274e-08</v>
+        <v>1.27946889388109e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>1.408342396933717e-07</v>
+        <v>1.697317112529842e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>1.408342396933717e-07</v>
+        <v>1.697317046494768e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>9.058878265473349e-08</v>
+        <v>1.279583184844194e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>9.079717553629245e-08</v>
+        <v>1.279626179109987e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>9.06523737046672e-08</v>
+        <v>1.279616963807235e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>2.422702513348341e-07</v>
+        <v>2.526858768040597e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>1.078339248319997e-07</v>
+        <v>1.428293553530268e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>9.02400229593151e-08</v>
+        <v>1.279381349108303e-07</v>
       </c>
     </row>
     <row r="3">
@@ -3327,37 +3327,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.026752647913192e-07</v>
+        <v>1.2166524399951e-07</v>
       </c>
       <c r="C3" t="n">
-        <v>2.256357332434252e-07</v>
+        <v>2.903219258177995e-07</v>
       </c>
       <c r="D3" t="n">
-        <v>1.032073254324735e-07</v>
+        <v>1.218376599027977e-07</v>
       </c>
       <c r="E3" t="n">
-        <v>1.5371221108081e-07</v>
+        <v>1.908920956775192e-07</v>
       </c>
       <c r="F3" t="n">
-        <v>1.5371221108081e-07</v>
+        <v>1.908920890740119e-07</v>
       </c>
       <c r="G3" t="n">
-        <v>1.034571130898018e-07</v>
+        <v>1.219200630842336e-07</v>
       </c>
       <c r="H3" t="n">
-        <v>1.03699806368947e-07</v>
+        <v>1.219956346819594e-07</v>
       </c>
       <c r="I3" t="n">
-        <v>1.035273106430811e-07</v>
+        <v>1.219434657726252e-07</v>
       </c>
       <c r="J3" t="n">
-        <v>2.554328283660024e-07</v>
+        <v>3.283724648520528e-07</v>
       </c>
       <c r="K3" t="n">
-        <v>1.206027183229304e-07</v>
+        <v>1.462757026420925e-07</v>
       </c>
       <c r="L3" t="n">
-        <v>1.030553862612485e-07</v>
+        <v>1.217905967564015e-07</v>
       </c>
     </row>
     <row r="4">
@@ -3367,37 +3367,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.119965072344851e-08</v>
+        <v>1.119965072344912e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>1.062895636503081e-08</v>
+        <v>1.062895636503075e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>1.147463380455349e-08</v>
+        <v>1.147463380455387e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>1.162395412062144e-08</v>
+        <v>1.162395412062249e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>1.162395412062242e-08</v>
+        <v>1.162395412062249e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>1.163145452372479e-08</v>
+        <v>1.163145452372498e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>1.172802336892244e-08</v>
+        <v>1.172802336892182e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>1.182644842030576e-08</v>
+        <v>1.182644842030742e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>1.276823674765779e-08</v>
+        <v>1.276823674765818e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>1.120980474478915e-08</v>
+        <v>1.120980474478912e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>1.139628591984745e-08</v>
+        <v>1.139628591984697e-08</v>
       </c>
     </row>
     <row r="5">
@@ -3407,37 +3407,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.096534388239871e-08</v>
+        <v>2.096534388239816e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>2.322090929807402e-08</v>
+        <v>2.322090929807386e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>2.513834753655085e-08</v>
+        <v>2.513834753654973e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>2.834689769150478e-08</v>
+        <v>2.834689769150555e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>2.834689769150478e-08</v>
+        <v>2.834689769150555e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>2.788112263454743e-08</v>
+        <v>2.788112263454707e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>3.199064453800289e-08</v>
+        <v>3.199064453800334e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>2.83471729868686e-08</v>
+        <v>2.834717298687138e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>4.902774916942997e-08</v>
+        <v>4.902774916942944e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>2.068211653599924e-08</v>
+        <v>2.068211653599865e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>2.595991399003248e-08</v>
+        <v>2.595991399003259e-08</v>
       </c>
     </row>
     <row r="6">
@@ -3447,37 +3447,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.689682923644887e-08</v>
+        <v>1.689682923644882e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>1.247230831015388e-08</v>
+        <v>1.247230831015395e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>1.27328998807273e-08</v>
+        <v>1.273289988072637e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>1.285682463638584e-08</v>
+        <v>1.285682463638511e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>1.309705527818069e-08</v>
+        <v>1.309705527818251e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>1.732863303672547e-08</v>
+        <v>1.732863303672392e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>1.852275164334245e-08</v>
+        <v>1.302637255704208e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>1.310839670089668e-08</v>
+        <v>1.752362693330753e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>1.862430238497547e-08</v>
+        <v>1.422088805710279e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>1.241594223663079e-08</v>
+        <v>1.241594223663052e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>1.268745247297833e-08</v>
+        <v>1.268745247297829e-08</v>
       </c>
     </row>
     <row r="7">
@@ -3487,37 +3487,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.40178557259343e-08</v>
+        <v>1.401785572593429e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>1.415125377381429e-08</v>
+        <v>1.415125377381411e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>1.429272690420123e-08</v>
+        <v>1.429272690420093e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>1.459508779762204e-08</v>
+        <v>1.459508779762156e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>1.459508779762204e-08</v>
+        <v>1.459508779762156e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>1.444965952621019e-08</v>
+        <v>1.44496595262101e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>1.454622837140825e-08</v>
+        <v>1.454622837140765e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>1.464465342279288e-08</v>
+        <v>1.464465342279194e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>1.55864417501436e-08</v>
+        <v>1.558644175014333e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>1.402800974727494e-08</v>
+        <v>1.402800974727375e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>1.421449092233326e-08</v>
+        <v>1.421449092233296e-08</v>
       </c>
     </row>
     <row r="8">
@@ -3527,37 +3527,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.793950931677087e-08</v>
+        <v>1.793950931677055e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>2.353187487105216e-08</v>
+        <v>2.353187487128631e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>2.486091881054478e-08</v>
+        <v>2.486091881054483e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>2.252435284898222e-08</v>
+        <v>2.252435284898027e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>1.871119253916477e-08</v>
+        <v>1.871119253916381e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>2.387625414685891e-08</v>
+        <v>2.38762541468588e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>2.397282299212673e-08</v>
+        <v>2.397282299212662e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>2.407124804344251e-08</v>
+        <v>2.407124804344263e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>2.501411823356452e-08</v>
+        <v>2.501411823356354e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>1.784740623352381e-08</v>
+        <v>1.784740623352307e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>2.939145674985762e-08</v>
+        <v>2.939145674985688e-08</v>
       </c>
     </row>
     <row r="9">
@@ -3567,37 +3567,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.706206972641633e-08</v>
+        <v>3.706206972641619e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>4.487995121077656e-08</v>
+        <v>4.487995121077619e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>4.502153913302152e-08</v>
+        <v>4.502153913302025e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>5.424080795253119e-08</v>
+        <v>5.42408079525318e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>4.537307462694971e-08</v>
+        <v>4.53730746269493e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>4.517835696317266e-08</v>
+        <v>4.51783569631718e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>4.527492580837048e-08</v>
+        <v>4.527492580837106e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>4.537335085975369e-08</v>
+        <v>4.537335085975408e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>4.631513918710585e-08</v>
+        <v>4.631513918710528e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>4.0123648150166e-08</v>
+        <v>4.030428851695564e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>4.49431883592955e-08</v>
+        <v>4.494318835929526e-08</v>
       </c>
     </row>
   </sheetData>
@@ -3683,37 +3683,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.004053293809182e-07</v>
+        <v>1.363860673174059e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>2.133634322171046e-07</v>
+        <v>2.308480025787443e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>1.003939183432686e-07</v>
+        <v>1.363854667771589e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>1.440756876922425e-07</v>
+        <v>1.712623357824294e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>1.440756876922425e-07</v>
+        <v>1.712623476028123e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>1.03857381060055e-07</v>
+        <v>1.365677419409525e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>1.026188066099517e-07</v>
+        <v>1.364931014094551e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>1.022951070261372e-07</v>
+        <v>1.364855803678189e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>2.575995464950279e-07</v>
+        <v>2.555933589008609e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>1.134771654975234e-07</v>
+        <v>1.449089496310682e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>1.023054270066431e-07</v>
+        <v>1.364821765700505e-07</v>
       </c>
     </row>
     <row r="3">
@@ -3723,37 +3723,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.136827272201114e-07</v>
+        <v>1.348830065837668e-07</v>
       </c>
       <c r="C3" t="n">
-        <v>2.265494916303551e-07</v>
+        <v>2.906551059596572e-07</v>
       </c>
       <c r="D3" t="n">
-        <v>1.136696021630251e-07</v>
+        <v>1.348772379462096e-07</v>
       </c>
       <c r="E3" t="n">
-        <v>1.576371086312557e-07</v>
+        <v>1.929959079267071e-07</v>
       </c>
       <c r="F3" t="n">
-        <v>1.576371086312555e-07</v>
+        <v>1.9299591974709e-07</v>
       </c>
       <c r="G3" t="n">
-        <v>1.176533017414697e-07</v>
+        <v>1.361785512683159e-07</v>
       </c>
       <c r="H3" t="n">
-        <v>1.162334814311475e-07</v>
+        <v>1.357129904347862e-07</v>
       </c>
       <c r="I3" t="n">
-        <v>1.158583424690152e-07</v>
+        <v>1.355910204481995e-07</v>
       </c>
       <c r="J3" t="n">
-        <v>2.731185422917824e-07</v>
+        <v>3.359688526752217e-07</v>
       </c>
       <c r="K3" t="n">
-        <v>1.272087467685692e-07</v>
+        <v>1.498211633898493e-07</v>
       </c>
       <c r="L3" t="n">
-        <v>1.158677634061753e-07</v>
+        <v>1.356018217249818e-07</v>
       </c>
     </row>
     <row r="4">
@@ -3763,37 +3763,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.35074054800105e-08</v>
+        <v>1.350740548001108e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>1.242545611169527e-08</v>
+        <v>1.24254561116953e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>1.350062210165459e-08</v>
+        <v>1.350062210165504e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>1.473956780415945e-08</v>
+        <v>1.473956780415953e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>1.473956780415945e-08</v>
+        <v>1.473956780415953e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>1.558674381685895e-08</v>
+        <v>1.558674381685931e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>1.482407129709496e-08</v>
+        <v>1.482407129709538e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>1.481300001484448e-08</v>
+        <v>1.481300001484497e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>2.23787209050328e-08</v>
+        <v>2.237872090503324e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>1.530487521413072e-08</v>
+        <v>1.530487521413091e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>1.463735029094989e-08</v>
+        <v>1.463735029095007e-08</v>
       </c>
     </row>
     <row r="5">
@@ -3803,37 +3803,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.435484402941996e-08</v>
+        <v>3.435484402942018e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>2.78004171001651e-08</v>
+        <v>2.780041710016518e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>3.341741400277429e-08</v>
+        <v>3.341741400277493e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>5.425069404764191e-08</v>
+        <v>5.425069404764e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>5.425069404764191e-08</v>
+        <v>5.425069404764e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>7.1997721458189e-08</v>
+        <v>7.199772145818879e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>6.301411345329886e-08</v>
+        <v>6.301411345330021e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>5.425074723468734e-08</v>
+        <v>5.425074723468681e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>2.014090694334945e-07</v>
+        <v>2.014090694334948e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>6.591613742203553e-08</v>
+        <v>6.591613742203483e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>6.019738415189589e-08</v>
+        <v>6.019738415189673e-08</v>
       </c>
     </row>
     <row r="6">
@@ -3843,37 +3843,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.535257597567248e-08</v>
+        <v>1.53525759756733e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>1.479346548361607e-08</v>
+        <v>1.479346548361609e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>1.524870237697237e-08</v>
+        <v>1.524870237697264e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>1.630512119943578e-08</v>
+        <v>1.630512119943602e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>1.665724249302433e-08</v>
+        <v>1.665724249302446e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>2.284008858125167e-08</v>
+        <v>1.743191431252146e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>2.36640880805363e-08</v>
+        <v>2.366408808053632e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>2.206634477923769e-08</v>
+        <v>1.665817051050731e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>2.996054249888529e-08</v>
+        <v>2.450525958573854e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>1.710977063678583e-08</v>
+        <v>1.710977063678578e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>1.649138682813439e-08</v>
+        <v>1.64913868281345e-08</v>
       </c>
     </row>
     <row r="7">
@@ -3883,37 +3883,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.717301300007731e-08</v>
+        <v>1.717301300007777e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>1.681755016173493e-08</v>
+        <v>1.681755016173512e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>1.716608443391206e-08</v>
+        <v>1.716608443391202e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>1.847067113717759e-08</v>
+        <v>1.847067113717786e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>1.847067113717759e-08</v>
+        <v>1.847067113717786e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>1.925235133692569e-08</v>
+        <v>1.925235133692628e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>1.848967881716154e-08</v>
+        <v>1.848967881716213e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>1.847860753491148e-08</v>
+        <v>1.847860753491178e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>2.604432842509981e-08</v>
+        <v>2.604432842510039e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>1.897048273419711e-08</v>
+        <v>1.897048273419753e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>1.83029578110168e-08</v>
+        <v>1.830295781101717e-08</v>
       </c>
     </row>
     <row r="8">
@@ -3923,37 +3923,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.203453894719173e-08</v>
+        <v>2.203453894719137e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>2.880223639905436e-08</v>
+        <v>2.880223639871575e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>3.063521760057232e-08</v>
+        <v>3.063521760057262e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>2.851413369225891e-08</v>
+        <v>2.851413369225887e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>2.356144820389879e-08</v>
+        <v>2.356144820389867e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>3.124305738177902e-08</v>
+        <v>3.124305738177906e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>3.048038486210972e-08</v>
+        <v>3.048038486210949e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>3.046931357976492e-08</v>
+        <v>3.046931357976489e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>3.80364355337084e-08</v>
+        <v>3.803643553370946e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>2.369958050290181e-08</v>
+        <v>2.369958050290139e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>3.774068857792615e-08</v>
+        <v>3.77406885779263e-08</v>
       </c>
     </row>
     <row r="9">
@@ -3963,37 +3963,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.872143677884904e-08</v>
+        <v>4.872143677884571e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>5.884936760553165e-08</v>
+        <v>5.884936760552655e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>5.919805147341373e-08</v>
+        <v>5.919805147340932e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>7.260798836264699e-08</v>
+        <v>7.260798836264065e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>6.051037065626643e-08</v>
+        <v>6.05103706562614e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>6.128416878072233e-08</v>
+        <v>6.128416878071769e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>6.052149626095832e-08</v>
+        <v>6.052149626095379e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>6.051042497870833e-08</v>
+        <v>6.051042497870325e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>6.807614586889643e-08</v>
+        <v>6.807614586889177e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>5.492818257095809e-08</v>
+        <v>5.492818257095412e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>6.033477525481339e-08</v>
+        <v>6.033477525480868e-08</v>
       </c>
     </row>
   </sheetData>
@@ -4079,37 +4079,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.795514146741952e-08</v>
+        <v>1.179713488976529e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>2.123106631064706e-07</v>
+        <v>2.29700948757851e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>7.837419367133641e-08</v>
+        <v>1.179934027828403e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>1.409687076024574e-07</v>
+        <v>1.697982630607848e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>1.409687076024574e-07</v>
+        <v>1.697982673210405e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>7.862486432881873e-08</v>
+        <v>1.180065950816715e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>7.891112394525106e-08</v>
+        <v>1.180146787240874e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>7.875494806266016e-08</v>
+        <v>1.180134901860921e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>2.418362256939369e-07</v>
+        <v>2.534975342819923e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>1.085426807112779e-07</v>
+        <v>1.433682806395989e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>7.821850100120281e-08</v>
+        <v>1.17983054025884e-07</v>
       </c>
     </row>
     <row r="3">
@@ -4119,37 +4119,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9.090944064621904e-08</v>
+        <v>1.049953410017468e-07</v>
       </c>
       <c r="C3" t="n">
-        <v>2.252787979762051e-07</v>
+        <v>2.894698957860295e-07</v>
       </c>
       <c r="D3" t="n">
-        <v>9.139143748712614e-08</v>
+        <v>1.051513575277972e-07</v>
       </c>
       <c r="E3" t="n">
-        <v>1.540432834617857e-07</v>
+        <v>1.907746024795143e-07</v>
       </c>
       <c r="F3" t="n">
-        <v>1.540432834617861e-07</v>
+        <v>1.9077460673977e-07</v>
       </c>
       <c r="G3" t="n">
-        <v>9.167976066950113e-08</v>
+        <v>1.052464245754384e-07</v>
       </c>
       <c r="H3" t="n">
-        <v>9.201275924315458e-08</v>
+        <v>1.053514403376653e-07</v>
       </c>
       <c r="I3" t="n">
-        <v>9.182782578960816e-08</v>
+        <v>1.052948195595453e-07</v>
       </c>
       <c r="J3" t="n">
-        <v>2.549607055518286e-07</v>
+        <v>3.290336968304722e-07</v>
       </c>
       <c r="K3" t="n">
-        <v>1.215091549711544e-07</v>
+        <v>1.469400217861888e-07</v>
       </c>
       <c r="L3" t="n">
-        <v>9.121184618797325e-08</v>
+        <v>1.050953633197885e-07</v>
       </c>
     </row>
     <row r="4">
@@ -4159,37 +4159,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.206258281197867e-08</v>
+        <v>1.206258281197807e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>1.141113836994236e-08</v>
+        <v>1.141113836994167e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>1.23116915904591e-08</v>
+        <v>1.231169159045849e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>1.255222374218273e-08</v>
+        <v>1.255222374218221e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>1.255222374218273e-08</v>
+        <v>1.255222374218221e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>1.248817927615156e-08</v>
+        <v>1.248817927615109e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>1.263131280149303e-08</v>
+        <v>1.263131280149243e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>1.272172209267409e-08</v>
+        <v>1.27217220926735e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>1.273608738864783e-08</v>
+        <v>1.273608738864722e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>1.21107667355027e-08</v>
+        <v>1.211076673550211e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>1.221909100207616e-08</v>
+        <v>1.221909100207555e-08</v>
       </c>
     </row>
     <row r="5">
@@ -4199,37 +4199,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.348613457606376e-08</v>
+        <v>2.348613457606259e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>2.452357833917522e-08</v>
+        <v>2.45235783391731e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>2.71752509056641e-08</v>
+        <v>2.717525090566204e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>3.142153305896547e-08</v>
+        <v>3.142153305896359e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>3.142153305896547e-08</v>
+        <v>3.142153305896359e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>3.031138267855531e-08</v>
+        <v>3.031138267855179e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>3.549727009950459e-08</v>
+        <v>3.549727009950327e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>3.142181203929642e-08</v>
+        <v>3.142181203929415e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>3.562891321424191e-08</v>
+        <v>3.562891321423986e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>2.381592747072587e-08</v>
+        <v>2.381592747072421e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>2.795565101389713e-08</v>
+        <v>2.795565101389488e-08</v>
       </c>
     </row>
     <row r="6">
@@ -4239,37 +4239,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.348879091662546e-08</v>
+        <v>1.822337035145504e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>1.3403140114299e-08</v>
+        <v>1.34031401142975e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>1.369080626879345e-08</v>
+        <v>1.369086122990171e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>1.386244894796356e-08</v>
+        <v>1.386244894796248e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>1.41393844957433e-08</v>
+        <v>1.413938449574218e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>1.391438738079777e-08</v>
+        <v>1.39143873807969e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>2.0362447001295e-08</v>
+        <v>2.036244700129368e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>1.888250963215307e-08</v>
+        <v>1.888250963215048e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>1.91738915082965e-08</v>
+        <v>1.435463942344296e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>1.344797531609854e-08</v>
+        <v>1.344797531609772e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>1.365401603238351e-08</v>
+        <v>1.365401603238223e-08</v>
       </c>
     </row>
     <row r="7">
@@ -4279,37 +4279,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.511537428283781e-08</v>
+        <v>1.511537428283556e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>1.517781120280123e-08</v>
+        <v>1.517781120279914e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>1.536437084934313e-08</v>
+        <v>1.536437084934086e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>1.573728428357852e-08</v>
+        <v>1.573728428357659e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>1.573728428357852e-08</v>
+        <v>1.573728428357659e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>1.554097074701066e-08</v>
+        <v>1.554097074700856e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>1.568410427235218e-08</v>
+        <v>1.568410427234995e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>1.577451356353297e-08</v>
+        <v>1.577451356353103e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>1.578887885950698e-08</v>
+        <v>1.578887885950474e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>1.516355820636183e-08</v>
+        <v>1.516355820635963e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>1.52718824729353e-08</v>
+        <v>1.527188247293311e-08</v>
       </c>
     </row>
     <row r="8">
@@ -4319,37 +4319,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.93650493809916e-08</v>
+        <v>1.936504938099027e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>2.547205078442996e-08</v>
+        <v>2.547205078442877e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>2.695321408991223e-08</v>
+        <v>2.695321408991007e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>2.440965955903995e-08</v>
+        <v>2.440965955903812e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>2.01946167087425e-08</v>
+        <v>2.019461670874117e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>2.586926127010076e-08</v>
+        <v>2.586926127009907e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>2.601239479557311e-08</v>
+        <v>2.601239479557128e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>2.610280408662291e-08</v>
+        <v>2.610280408662122e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>2.611836398448121e-08</v>
+        <v>2.611836398447955e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>1.930031990390874e-08</v>
+        <v>1.930031990390746e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>3.194979507452617e-08</v>
+        <v>3.19497950745239e-08</v>
       </c>
     </row>
     <row r="9">
@@ -4359,37 +4359,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.087568419173972e-08</v>
+        <v>4.087568419173495e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>4.953273217936335e-08</v>
+        <v>4.953273217935752e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>4.971940721567351e-08</v>
+        <v>4.971940721566755e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>6.004715622609884e-08</v>
+        <v>6.004715622609148e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>5.012915464519647e-08</v>
+        <v>5.012915464519046e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>4.989589172357289e-08</v>
+        <v>4.989589172356695e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>5.003902524891436e-08</v>
+        <v>5.00390252489084e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>5.01294345400955e-08</v>
+        <v>5.012943454008949e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>5.014379983606917e-08</v>
+        <v>5.01437998360632e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>4.45387291132463e-08</v>
+        <v>3.869632889247067e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>4.96268034494975e-08</v>
+        <v>4.962680344949158e-08</v>
       </c>
     </row>
   </sheetData>
@@ -4475,37 +4475,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.525194700867863e-08</v>
+        <v>1.238265500940218e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>2.112416635158429e-07</v>
+        <v>2.285233020266652e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>8.562368080421096e-08</v>
+        <v>1.238461137053578e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>1.398408941086834e-07</v>
+        <v>1.689752466690989e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>1.398408941086834e-07</v>
+        <v>1.689752332649895e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>8.563816371646391e-08</v>
+        <v>1.238468759122644e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>8.611052017531826e-08</v>
+        <v>1.238658199714363e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>8.562361262783097e-08</v>
+        <v>1.238461309872297e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>2.398156473563049e-07</v>
+        <v>2.518209547959584e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>1.07244279159854e-07</v>
+        <v>1.421031871266839e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>8.552936782835797e-08</v>
+        <v>1.238396569935507e-07</v>
       </c>
     </row>
     <row r="3">
@@ -4515,37 +4515,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9.787312997034314e-08</v>
+        <v>1.153217362811227e-07</v>
       </c>
       <c r="C3" t="n">
-        <v>2.238909546422294e-07</v>
+        <v>2.882120828673955e-07</v>
       </c>
       <c r="D3" t="n">
-        <v>9.830070083962911e-08</v>
+        <v>1.154600910059474e-07</v>
       </c>
       <c r="E3" t="n">
-        <v>1.525179634687963e-07</v>
+        <v>1.899539417763592e-07</v>
       </c>
       <c r="F3" t="n">
-        <v>1.525179634687963e-07</v>
+        <v>1.899539283722498e-07</v>
       </c>
       <c r="G3" t="n">
-        <v>9.831735918884666e-08</v>
+        <v>1.154663455130997e-07</v>
       </c>
       <c r="H3" t="n">
-        <v>9.886315229537237e-08</v>
+        <v>1.15641578205341e-07</v>
       </c>
       <c r="I3" t="n">
-        <v>9.82970280429486e-08</v>
+        <v>1.15460488253991e-07</v>
       </c>
       <c r="J3" t="n">
-        <v>2.525639132150173e-07</v>
+        <v>3.268444573510042e-07</v>
       </c>
       <c r="K3" t="n">
-        <v>1.198710695709262e-07</v>
+        <v>1.455005296869462e-07</v>
       </c>
       <c r="L3" t="n">
-        <v>9.819162901873138e-08</v>
+        <v>1.154270474768781e-07</v>
       </c>
     </row>
     <row r="4">
@@ -4555,37 +4555,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.075233437947176e-08</v>
+        <v>1.075233437947177e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>1.020717666805376e-08</v>
+        <v>1.020717666805377e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>1.097331436921863e-08</v>
+        <v>1.097331436921866e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>1.094781351812156e-08</v>
+        <v>1.094781351812155e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>1.094781351812156e-08</v>
+        <v>1.094781351812155e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>1.100970422198943e-08</v>
+        <v>1.100970422198942e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>1.126301567376642e-08</v>
+        <v>1.126301567376641e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>1.115827486592582e-08</v>
+        <v>1.115827486592583e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>1.125527580169836e-08</v>
+        <v>1.125527580169837e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>1.077452633956743e-08</v>
+        <v>1.077452633956746e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>1.091703709223966e-08</v>
+        <v>1.09170370922397e-08</v>
       </c>
     </row>
     <row r="5">
@@ -4595,37 +4595,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.043594462648524e-08</v>
+        <v>2.043594462648526e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>2.240828268483194e-08</v>
+        <v>2.240828268483195e-08</v>
       </c>
       <c r="D5" t="n">
         <v>2.368529097327197e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>2.401519186091682e-08</v>
+        <v>2.401519186091691e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>2.401519186091682e-08</v>
+        <v>2.401519186091691e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>2.428748919348703e-08</v>
+        <v>2.428748919348681e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>3.107917179603738e-08</v>
+        <v>3.10791717960374e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>2.401545395777792e-08</v>
+        <v>2.401545395777791e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>2.945479550648946e-08</v>
+        <v>2.945479550648954e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>2.035122659190405e-08</v>
+        <v>2.035122659190409e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>2.475752418200639e-08</v>
+        <v>2.475752418200645e-08</v>
       </c>
     </row>
     <row r="6">
@@ -4635,37 +4635,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.184840692180794e-08</v>
+        <v>1.601402977519213e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>1.183268830941844e-08</v>
+        <v>1.183268830941845e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>1.201823955229964e-08</v>
+        <v>1.20181919397549e-08</v>
       </c>
       <c r="E6" t="n">
         <v>1.203084918700671e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>1.224108674712078e-08</v>
+        <v>1.22410867471208e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>1.627139961770979e-08</v>
+        <v>1.210577676432568e-08</v>
       </c>
       <c r="H6" t="n">
         <v>1.765791294971737e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>1.641997026164609e-08</v>
+        <v>1.225434740826202e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>1.249516941227595e-08</v>
+        <v>1.664078918627885e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>1.177344713633434e-08</v>
+        <v>1.177344713633441e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>1.201818428444342e-08</v>
+        <v>1.201818428444348e-08</v>
       </c>
     </row>
     <row r="7">
@@ -4675,37 +4675,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.336817754676363e-08</v>
+        <v>1.33681775467637e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>1.348602035589932e-08</v>
+        <v>1.348602035589931e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>1.358903899357505e-08</v>
+        <v>1.35890389935751e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>1.372117692945373e-08</v>
+        <v>1.372117692945372e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>1.372117692945373e-08</v>
+        <v>1.372117692945372e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>1.362554738928135e-08</v>
+        <v>1.362554738928133e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>1.387885884105831e-08</v>
+        <v>1.387885884105834e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>1.37741180332177e-08</v>
+        <v>1.377411803321771e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>1.387111896899023e-08</v>
+        <v>1.387111896899027e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>1.33903695068593e-08</v>
+        <v>1.339036950685937e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>1.353288025953155e-08</v>
+        <v>1.353288025953159e-08</v>
       </c>
     </row>
     <row r="8">
@@ -4715,37 +4715,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.705569872112701e-08</v>
+        <v>1.70556987211271e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>2.221357759592807e-08</v>
+        <v>2.221357759571117e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>2.342130603104492e-08</v>
+        <v>2.342130603104493e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>2.111478403205895e-08</v>
+        <v>2.111478403205899e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>1.75913459320664e-08</v>
+        <v>1.759134593206646e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>2.240239159939684e-08</v>
+        <v>2.240239159939705e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>2.265570305126561e-08</v>
+        <v>2.265570305126571e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>2.255096224333336e-08</v>
+        <v>2.255096224333341e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>2.264896336382057e-08</v>
+        <v>2.264896336382067e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>1.698335389398733e-08</v>
+        <v>1.698335389398745e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>2.762594793094825e-08</v>
+        <v>2.76259479309483e-08</v>
       </c>
     </row>
     <row r="9">
@@ -4755,37 +4755,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.63283845708587e-08</v>
+        <v>3.632838457085876e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>4.399132984263039e-08</v>
+        <v>4.399132984263048e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>4.409446962861109e-08</v>
+        <v>4.409446962861115e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>5.2986054871786e-08</v>
+        <v>5.298605487178603e-08</v>
       </c>
       <c r="F9" t="n">
         <v>4.427916448999455e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>4.413085687601229e-08</v>
+        <v>4.413085687601248e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>4.438416832778943e-08</v>
+        <v>4.43841683277894e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>4.427942751994883e-08</v>
+        <v>4.427942751994878e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>4.437642845572133e-08</v>
+        <v>4.437642845572135e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>3.9346654179873e-08</v>
+        <v>3.934665417987306e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>4.403818974626267e-08</v>
+        <v>4.403818974626268e-08</v>
       </c>
     </row>
   </sheetData>
@@ -4871,37 +4871,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.478869597436293e-07</v>
+        <v>1.928904216071942e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>3.732555823088587e-07</v>
+        <v>3.762303280455425e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>1.464128921206035e-07</v>
+        <v>1.928128443559284e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>4.01691181531555e-07</v>
+        <v>3.999202330429616e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>2.638127103639794e-07</v>
+        <v>2.851543836233018e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>1.55661857378822e-07</v>
+        <v>1.932995990275439e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>1.493111642892181e-07</v>
+        <v>1.929507474152355e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>1.533080508107494e-07</v>
+        <v>1.931759175403262e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>3.529528443471387e-07</v>
+        <v>3.08354876188043e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>1.264951152782647e-07</v>
+        <v>1.713492550351139e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>1.484308858033812e-07</v>
+        <v>1.92909624770253e-07</v>
       </c>
     </row>
     <row r="3">
@@ -4911,37 +4911,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.659272470966602e-07</v>
+        <v>1.968636123970294e-07</v>
       </c>
       <c r="C3" t="n">
-        <v>3.921073475925796e-07</v>
+        <v>5.010708473185743e-07</v>
       </c>
       <c r="D3" t="n">
-        <v>1.642317639779923e-07</v>
+        <v>1.963133535026746e-07</v>
       </c>
       <c r="E3" t="n">
-        <v>4.205463111547988e-07</v>
+        <v>5.40159161256006e-07</v>
       </c>
       <c r="F3" t="n">
-        <v>2.826678399872232e-07</v>
+        <v>3.507171290612117e-07</v>
       </c>
       <c r="G3" t="n">
-        <v>1.748699899423251e-07</v>
+        <v>1.997827589799028e-07</v>
       </c>
       <c r="H3" t="n">
-        <v>1.675697784609578e-07</v>
+        <v>1.974013998457744e-07</v>
       </c>
       <c r="I3" t="n">
-        <v>1.72176156435315e-07</v>
+        <v>1.988903788469433e-07</v>
       </c>
       <c r="J3" t="n">
-        <v>3.816317338957999e-07</v>
+        <v>4.079230928324965e-07</v>
       </c>
       <c r="K3" t="n">
-        <v>1.45254950105737e-07</v>
+        <v>1.626855239292868e-07</v>
       </c>
       <c r="L3" t="n">
-        <v>1.665527345453488e-07</v>
+        <v>1.970792286799584e-07</v>
       </c>
     </row>
     <row r="4">
@@ -4951,37 +4951,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.67410717321485e-08</v>
+        <v>1.674107173214905e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>2.044126936011949e-08</v>
+        <v>2.044126936011947e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>1.586480099180328e-08</v>
+        <v>1.586480099180386e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>2.06513104501668e-08</v>
+        <v>2.065131045016677e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>2.06513104501668e-08</v>
+        <v>2.065131045016677e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>2.144519231348112e-08</v>
+        <v>2.144519231348142e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>1.758970939288751e-08</v>
+        <v>1.758970939288807e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>2.051371555901334e-08</v>
+        <v>2.051371555901332e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>5.884424881634207e-08</v>
+        <v>5.884424881634249e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>1.958874233584274e-08</v>
+        <v>1.958874233584316e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>1.706639106122176e-08</v>
+        <v>1.706639106122228e-08</v>
       </c>
     </row>
     <row r="5">
@@ -4991,37 +4991,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.802742871341891e-08</v>
+        <v>6.802742871341977e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>1.235252860998916e-07</v>
+        <v>1.235252860998913e-07</v>
       </c>
       <c r="D5" t="n">
-        <v>5.335758630291295e-08</v>
+        <v>5.335758630291314e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>1.235252852743392e-07</v>
+        <v>1.235252852743388e-07</v>
       </c>
       <c r="F5" t="n">
-        <v>1.235252852743392e-07</v>
+        <v>1.235252852743388e-07</v>
       </c>
       <c r="G5" t="n">
-        <v>1.548467450460437e-07</v>
+        <v>1.548467450460389e-07</v>
       </c>
       <c r="H5" t="n">
-        <v>9.31830447513233e-08</v>
+        <v>9.318304475132362e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>1.235252401459532e-07</v>
+        <v>1.235252401459531e-07</v>
       </c>
       <c r="J5" t="n">
-        <v>8.71976319262993e-07</v>
+        <v>8.719763192629936e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>1.198665873802335e-07</v>
+        <v>1.198665873802343e-07</v>
       </c>
       <c r="L5" t="n">
-        <v>1.682518189472684e-07</v>
+        <v>1.682518189472685e-07</v>
       </c>
     </row>
     <row r="6">
@@ -5031,37 +5031,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.469474495686573e-08</v>
+        <v>1.962682106801766e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>2.331607770620354e-08</v>
+        <v>2.331607770620352e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>1.84540008427513e-08</v>
+        <v>1.845403347274234e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>2.300937115841858e-08</v>
+        <v>2.300937115841854e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>2.340840462839903e-08</v>
+        <v>2.3408404628399e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>2.939886553819787e-08</v>
+        <v>2.43309416493501e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>2.699036136773197e-08</v>
+        <v>2.699036136773256e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>2.846738878373013e-08</v>
+        <v>2.846738878373017e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>6.758546917889889e-08</v>
+        <v>6.224324838614534e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>2.242671311504865e-08</v>
+        <v>2.242671311504882e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>1.994845824483967e-08</v>
+        <v>1.994845824484015e-08</v>
       </c>
     </row>
     <row r="7">
@@ -5071,37 +5071,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.062501483501282e-08</v>
+        <v>2.062501483501281e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>2.439770461581568e-08</v>
+        <v>2.439770461581565e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>1.974848750896646e-08</v>
+        <v>1.974848750896696e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>2.443920853645994e-08</v>
+        <v>2.443920853645989e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>2.443920853645994e-08</v>
+        <v>2.443920853645989e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>2.532913541634525e-08</v>
+        <v>2.532913541634547e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>2.147365249575185e-08</v>
+        <v>2.147365249575184e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>2.439765866187743e-08</v>
+        <v>2.439765866187741e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>6.272819191920637e-08</v>
+        <v>6.272819191920652e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>2.347268543870697e-08</v>
+        <v>2.347268543870724e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>2.0950334164086e-08</v>
+        <v>2.095033416408601e-08</v>
       </c>
     </row>
     <row r="8">
@@ -5111,37 +5111,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.524468268688429e-08</v>
+        <v>2.524468268688468e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>3.6057574203474e-08</v>
+        <v>3.605757420378747e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>3.281861814077583e-08</v>
+        <v>3.281861814077602e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>3.413908656582473e-08</v>
+        <v>3.413908656582466e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>2.92641396557862e-08</v>
+        <v>2.926413965578615e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>3.694773531129764e-08</v>
+        <v>3.694773531129793e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>3.30922523907324e-08</v>
+        <v>3.309225239073297e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>3.601625855682987e-08</v>
+        <v>3.601625855682982e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>7.434816728189455e-08</v>
+        <v>7.434816728189488e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>2.796234453649968e-08</v>
+        <v>2.796234453650027e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>3.987990379803696e-08</v>
+        <v>3.987990379803698e-08</v>
       </c>
     </row>
     <row r="9">
@@ -5151,37 +5151,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5.5212243322537e-08</v>
+        <v>5.521224332253763e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>7.031891965204893e-08</v>
+        <v>7.031891965204885e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>6.566996367962909e-08</v>
+        <v>6.566996367962926e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>8.339809998304946e-08</v>
+        <v>8.339809998304938e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>7.031891633587662e-08</v>
+        <v>7.031891633587652e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>7.125035045257844e-08</v>
+        <v>7.125035045257866e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>6.739486753198502e-08</v>
+        <v>6.739486753198529e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>7.031887369811074e-08</v>
+        <v>7.031887369811068e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>1.086494069554396e-07</v>
+        <v>1.0864940695544e-07</v>
       </c>
       <c r="K9" t="n">
-        <v>6.282694606979508e-08</v>
+        <v>6.282694606979541e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>6.687154920031924e-08</v>
+        <v>6.687154920031941e-08</v>
       </c>
     </row>
   </sheetData>
@@ -5267,37 +5267,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.447054623720318e-07</v>
+        <v>1.918588630702578e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>3.71376448141274e-07</v>
+        <v>3.748251987761085e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>1.458709969085536e-07</v>
+        <v>1.91920202837977e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>3.996024987591929e-07</v>
+        <v>3.983372709636941e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>2.623295514511806e-07</v>
+        <v>2.840754324717537e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>1.52673695612712e-07</v>
+        <v>1.922782153595289e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>1.484872143486829e-07</v>
+        <v>1.92045888450927e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>1.520003859032245e-07</v>
+        <v>1.922429581353663e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>3.443127993726602e-07</v>
+        <v>3.058997554443459e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>1.24324646436262e-07</v>
+        <v>1.697547201673176e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>1.468979566754965e-07</v>
+        <v>1.919666575002016e-07</v>
       </c>
     </row>
     <row r="3">
@@ -5307,37 +5307,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.622132237701421e-07</v>
+        <v>1.951772611319074e-07</v>
       </c>
       <c r="C3" t="n">
-        <v>3.899762094452743e-07</v>
+        <v>4.993015429773913e-07</v>
       </c>
       <c r="D3" t="n">
-        <v>1.635538299268938e-07</v>
+        <v>1.956140026781688e-07</v>
       </c>
       <c r="E3" t="n">
-        <v>4.182065170860689e-07</v>
+        <v>5.380987315660784e-07</v>
       </c>
       <c r="F3" t="n">
-        <v>2.809335697780565e-07</v>
+        <v>3.49488667303666e-07</v>
       </c>
       <c r="G3" t="n">
-        <v>1.713783426114675e-07</v>
+        <v>1.981644074155127e-07</v>
       </c>
       <c r="H3" t="n">
-        <v>1.665661336765494e-07</v>
+        <v>1.965984938340256e-07</v>
       </c>
       <c r="I3" t="n">
-        <v>1.706068779732987e-07</v>
+        <v>1.97902783494829e-07</v>
       </c>
       <c r="J3" t="n">
-        <v>3.718581416649306e-07</v>
+        <v>4.027273791567924e-07</v>
       </c>
       <c r="K3" t="n">
-        <v>1.428225190790279e-07</v>
+        <v>1.605782830388808e-07</v>
       </c>
       <c r="L3" t="n">
-        <v>1.647348458168196e-07</v>
+        <v>1.960077454061006e-07</v>
       </c>
     </row>
     <row r="4">
@@ -5347,37 +5347,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.374158269643737e-08</v>
+        <v>1.374158269643729e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>1.828487936770512e-08</v>
+        <v>1.828487936770513e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>1.443444359051179e-08</v>
+        <v>1.443444359051178e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>1.847564192667506e-08</v>
+        <v>1.847564192667507e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>1.847564192667506e-08</v>
+        <v>1.847564192667507e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>1.856068437330652e-08</v>
+        <v>1.856068437330653e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>1.599110047386023e-08</v>
+        <v>1.599110047386016e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>1.862837844289902e-08</v>
+        <v>1.862837844289903e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>5.346616663260141e-08</v>
+        <v>5.346616663260131e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>1.76600325360147e-08</v>
+        <v>1.766003253601468e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>1.504638225603215e-08</v>
+        <v>1.504638225603205e-08</v>
       </c>
     </row>
     <row r="5">
@@ -5387,37 +5387,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.820430022967531e-08</v>
+        <v>3.820430022967539e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>1.073071686245919e-07</v>
+        <v>1.073071686245918e-07</v>
       </c>
       <c r="D5" t="n">
-        <v>4.991795527766009e-08</v>
+        <v>4.991795527766089e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>1.073071759071376e-07</v>
+        <v>1.073071759071374e-07</v>
       </c>
       <c r="F5" t="n">
-        <v>1.073071759071376e-07</v>
+        <v>1.073071759071374e-07</v>
       </c>
       <c r="G5" t="n">
-        <v>1.190628318378226e-07</v>
+        <v>1.190628318378231e-07</v>
       </c>
       <c r="H5" t="n">
-        <v>8.420902633762572e-08</v>
+        <v>8.42090263376256e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>1.073073585090705e-07</v>
+        <v>1.073073585090704e-07</v>
       </c>
       <c r="J5" t="n">
-        <v>7.459544564182326e-07</v>
+        <v>7.459544564182325e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>9.958445093705976e-08</v>
+        <v>9.958445093705999e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>1.836976007801316e-07</v>
+        <v>1.836976007801314e-07</v>
       </c>
     </row>
     <row r="6">
@@ -5427,37 +5427,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.043584388172025e-08</v>
+        <v>1.626714940241645e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>2.103030437314675e-08</v>
+        <v>2.103030437314677e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>1.670244021358129e-08</v>
+        <v>1.670244021358173e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>2.078869903232408e-08</v>
+        <v>2.078869903232409e-08</v>
       </c>
       <c r="F6" t="n">
         <v>2.112437413833638e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>2.525494555858933e-08</v>
+        <v>2.108625107928558e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>2.389285259052646e-08</v>
+        <v>2.389285259052648e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>2.53226396281818e-08</v>
+        <v>2.532263962818177e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>6.084502666006187e-08</v>
+        <v>5.641023841467668e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>2.015407779808748e-08</v>
+        <v>2.01540777980875e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>1.755568986867511e-08</v>
+        <v>1.755568986867521e-08</v>
       </c>
     </row>
     <row r="7">
@@ -5467,13 +5467,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.687157158682711e-08</v>
+        <v>1.687157158682708e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>2.175817744881013e-08</v>
+        <v>2.175817744881014e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>1.756428750887995e-08</v>
+        <v>1.756428750887998e-08</v>
       </c>
       <c r="E7" t="n">
         <v>2.17136141767826e-08</v>
@@ -5482,16 +5482,16 @@
         <v>2.17136141767826e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>2.169067326369627e-08</v>
+        <v>2.169067326369626e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>1.91210893642499e-08</v>
+        <v>1.912108936424994e-08</v>
       </c>
       <c r="I7" t="n">
         <v>2.175836733328875e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>5.659615552299105e-08</v>
+        <v>5.659615552299106e-08</v>
       </c>
       <c r="K7" t="n">
         <v>2.079002142640444e-08</v>
@@ -5507,37 +5507,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.066936451142871e-08</v>
+        <v>2.066936451142855e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>3.114948040232857e-08</v>
+        <v>3.114948040232864e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>2.816564410650683e-08</v>
+        <v>2.816564410650695e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>2.961285207209086e-08</v>
+        <v>2.96128520720909e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>2.570809552303279e-08</v>
+        <v>2.570809552303282e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>3.112343698707999e-08</v>
+        <v>3.112343698708002e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>2.855385308767523e-08</v>
+        <v>2.855385308767529e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>3.11911310566725e-08</v>
+        <v>3.119113105667254e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>6.60300266623923e-08</v>
+        <v>6.603002666239218e-08</v>
       </c>
       <c r="K8" t="n">
         <v>2.448314187685076e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>3.349533304184531e-08</v>
+        <v>3.349533304184536e-08</v>
       </c>
     </row>
     <row r="9">
@@ -5550,34 +5550,34 @@
         <v>4.496150897141259e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>5.90188685855063e-08</v>
+        <v>5.901886858550637e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>5.482512682400868e-08</v>
+        <v>5.482512682400856e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>6.960173124028225e-08</v>
+        <v>6.960173124028228e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>5.901887354417856e-08</v>
+        <v>5.90188735441786e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>5.895136440039253e-08</v>
+        <v>5.895136440039249e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>5.638178050094612e-08</v>
+        <v>5.638178050094604e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>5.901905846998489e-08</v>
+        <v>5.901905846998498e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>9.385684665968725e-08</v>
+        <v>9.385684665968722e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>4.650309578440588e-08</v>
+        <v>5.273714317140203e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>5.543706228311806e-08</v>
+        <v>5.543706228311797e-08</v>
       </c>
     </row>
   </sheetData>
@@ -5663,37 +5663,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.453943319517156e-07</v>
+        <v>1.914966114836195e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>3.719619805008427e-07</v>
+        <v>3.74177654492164e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>1.466308855384402e-07</v>
+        <v>1.915616888428957e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>4.000469870682374e-07</v>
+        <v>3.975711348271355e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>2.631666670023152e-07</v>
+        <v>2.836361045269862e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>1.523841594287359e-07</v>
+        <v>1.918644722208201e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>1.481369228069668e-07</v>
+        <v>1.91629287058484e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>1.529465385845197e-07</v>
+        <v>1.918942297608754e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>3.37249000973766e-07</v>
+        <v>3.043717829441252e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>1.209087173182221e-07</v>
+        <v>1.686148678852294e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>1.45921823403636e-07</v>
+        <v>1.915164447454473e-07</v>
       </c>
     </row>
     <row r="3">
@@ -5703,37 +5703,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.629569683224947e-07</v>
+        <v>1.952332490482605e-07</v>
       </c>
       <c r="C3" t="n">
-        <v>3.906534971648034e-07</v>
+        <v>4.98957618491252e-07</v>
       </c>
       <c r="D3" t="n">
-        <v>1.643792610985317e-07</v>
+        <v>1.956959568273047e-07</v>
       </c>
       <c r="E3" t="n">
-        <v>4.187444773620203e-07</v>
+        <v>5.375598047579617e-07</v>
       </c>
       <c r="F3" t="n">
-        <v>2.818641572960987e-07</v>
+        <v>3.494891990267627e-07</v>
       </c>
       <c r="G3" t="n">
-        <v>1.709967178594814e-07</v>
+        <v>1.978510091790442e-07</v>
       </c>
       <c r="H3" t="n">
-        <v>1.661139684365587e-07</v>
+        <v>1.962629382803459e-07</v>
       </c>
       <c r="I3" t="n">
-        <v>1.716327118255593e-07</v>
+        <v>1.980527944075666e-07</v>
       </c>
       <c r="J3" t="n">
-        <v>3.638306758084356e-07</v>
+        <v>3.989048938080803e-07</v>
       </c>
       <c r="K3" t="n">
-        <v>1.389530746846534e-07</v>
+        <v>1.58376236288907e-07</v>
       </c>
       <c r="L3" t="n">
-        <v>1.635635696363546e-07</v>
+        <v>1.954376381079675e-07</v>
       </c>
     </row>
     <row r="4">
@@ -5743,37 +5743,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.366528419841214e-08</v>
+        <v>1.366528419841203e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>1.799937432643013e-08</v>
+        <v>1.799937432643047e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>1.44003629084997e-08</v>
+        <v>1.440036290850014e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>1.820295358174068e-08</v>
+        <v>1.820295358174088e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>1.820295358174053e-08</v>
+        <v>1.820295358174084e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>1.790266803544131e-08</v>
+        <v>1.790266803543598e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>1.529705360345978e-08</v>
+        <v>1.529705360346021e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>1.870436627827185e-08</v>
+        <v>1.870436627827181e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>4.935889944895157e-08</v>
+        <v>4.93588994489519e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>1.557173619390439e-08</v>
+        <v>1.557173619390437e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>1.398042287899002e-08</v>
+        <v>1.39804228789905e-08</v>
       </c>
     </row>
     <row r="5">
@@ -5783,37 +5783,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.623191256185422e-08</v>
+        <v>4.623191256185469e-08</v>
       </c>
       <c r="C5" t="n">
         <v>1.167439427493324e-07</v>
       </c>
       <c r="D5" t="n">
-        <v>5.832476317813272e-08</v>
+        <v>5.832476317813249e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>1.167439609202031e-07</v>
+        <v>1.167439609202019e-07</v>
       </c>
       <c r="F5" t="n">
-        <v>1.167439609202031e-07</v>
+        <v>1.167439609202019e-07</v>
       </c>
       <c r="G5" t="n">
-        <v>1.158248196031219e-07</v>
+        <v>1.158248196032246e-07</v>
       </c>
       <c r="H5" t="n">
-        <v>8.050303926553948e-08</v>
+        <v>8.050303926553893e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>1.16744305348975e-07</v>
+        <v>1.167443053489753e-07</v>
       </c>
       <c r="J5" t="n">
         <v>6.845853505063394e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>7.347438729050909e-08</v>
+        <v>7.347438729050954e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>5.871599741363974e-08</v>
+        <v>6.554147010450556e-08</v>
       </c>
     </row>
     <row r="6">
@@ -5826,34 +5826,34 @@
         <v>1.605576579448227e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>2.095491612830384e-08</v>
+        <v>2.095491612830419e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>2.096858056477831e-08</v>
+        <v>1.657960649498203e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>2.074599917876256e-08</v>
+        <v>2.074599917876236e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>2.106728053867857e-08</v>
+        <v>2.106728053867919e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>2.029314963151034e-08</v>
+        <v>2.420798956308722e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>2.278529851238176e-08</v>
+        <v>2.278529851238236e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>2.500968780592239e-08</v>
+        <v>2.109484787434246e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>5.215851352706684e-08</v>
+        <v>5.636842160663734e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>1.790605002035053e-08</v>
+        <v>1.790605002035115e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>1.637719191290265e-08</v>
+        <v>1.637719191290374e-08</v>
       </c>
     </row>
     <row r="7">
@@ -5863,37 +5863,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.656509380863545e-08</v>
+        <v>1.656509380863429e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>2.160381328885068e-08</v>
+        <v>2.160381328885088e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>1.730010145172227e-08</v>
+        <v>1.730010145172127e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>2.145494393788341e-08</v>
+        <v>2.145494393788295e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>2.145494393788341e-08</v>
+        <v>2.14549439378831e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>2.0802477645649e-08</v>
+        <v>2.080247764565875e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>1.819686321368316e-08</v>
+        <v>1.819686321368288e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>2.160417588849442e-08</v>
+        <v>2.160417588849469e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>5.225870905917435e-08</v>
+        <v>5.225870905917489e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>1.847154580412686e-08</v>
+        <v>1.847154580412705e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>1.688023248921243e-08</v>
+        <v>1.688023248921331e-08</v>
       </c>
     </row>
     <row r="8">
@@ -5903,37 +5903,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.017581562625297e-08</v>
+        <v>2.017581562625355e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>3.031847714561085e-08</v>
+        <v>3.031847714561071e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>2.724388958222697e-08</v>
+        <v>2.724388958222729e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>2.889905803150591e-08</v>
+        <v>2.889905803150689e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>2.529204622138755e-08</v>
+        <v>2.529204622138734e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>2.965853932065823e-08</v>
+        <v>2.965853932066212e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>2.705292488872941e-08</v>
+        <v>2.705292488872852e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>3.04602375634976e-08</v>
+        <v>3.046023756349794e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>6.111580157900313e-08</v>
+        <v>6.111580157900309e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>2.198483274213305e-08</v>
+        <v>2.198483274213345e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>3.121549023988706e-08</v>
+        <v>3.121549023988709e-08</v>
       </c>
     </row>
     <row r="9">
@@ -5943,37 +5943,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.183238338186044e-08</v>
+        <v>4.183238338185845e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>5.514338631093496e-08</v>
+        <v>5.514338631093522e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>5.083974867977128e-08</v>
+        <v>5.083974867976911e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>6.468944446238921e-08</v>
+        <v>6.468944446238893e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>5.514340243683467e-08</v>
+        <v>5.514340243683098e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>5.434205066773831e-08</v>
+        <v>5.434205066774145e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>5.173643623576846e-08</v>
+        <v>5.173643623576659e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>5.514374891058114e-08</v>
+        <v>5.514374891057922e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>8.579828208125974e-08</v>
+        <v>8.579828208125659e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>4.721812662841421e-08</v>
+        <v>4.721812662841111e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>5.041980551129709e-08</v>
+        <v>5.041980551129633e-08</v>
       </c>
     </row>
   </sheetData>
@@ -6059,37 +6059,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.481329194312053e-07</v>
+        <v>1.919773793434669e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>3.678209271549114e-07</v>
+        <v>3.745084814093198e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>1.463898536767829e-07</v>
+        <v>1.918856452548192e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>3.960599139930794e-07</v>
+        <v>3.98030506051677e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>2.587446149738272e-07</v>
+        <v>2.837334196166632e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>1.521008094027648e-07</v>
+        <v>1.92186201511806e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>1.473614570508666e-07</v>
+        <v>1.919245596343395e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>1.485334064830803e-07</v>
+        <v>1.919986004204074e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>3.419718084803672e-07</v>
+        <v>3.056997321975581e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>1.245396328159713e-07</v>
+        <v>1.69644975437937e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>1.486592881636577e-07</v>
+        <v>1.919992299173016e-07</v>
       </c>
     </row>
     <row r="3">
@@ -6099,37 +6099,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.661406710082115e-07</v>
+        <v>1.964389586261343e-07</v>
       </c>
       <c r="C3" t="n">
-        <v>3.85883801849962e-07</v>
+        <v>4.978697944408165e-07</v>
       </c>
       <c r="D3" t="n">
-        <v>1.641357843156425e-07</v>
+        <v>1.957875367121539e-07</v>
       </c>
       <c r="E3" t="n">
-        <v>4.141282332647656e-07</v>
+        <v>5.366828976379185e-07</v>
       </c>
       <c r="F3" t="n">
-        <v>2.768129342455134e-07</v>
+        <v>3.480146473761675e-07</v>
       </c>
       <c r="G3" t="n">
-        <v>1.707045664214363e-07</v>
+        <v>1.979238708881271e-07</v>
       </c>
       <c r="H3" t="n">
-        <v>1.652561281353573e-07</v>
+        <v>1.961498448117152e-07</v>
       </c>
       <c r="I3" t="n">
-        <v>1.665963069738114e-07</v>
+        <v>1.965899606271674e-07</v>
       </c>
       <c r="J3" t="n">
-        <v>3.691535602099752e-07</v>
+        <v>4.018082592863404e-07</v>
       </c>
       <c r="K3" t="n">
-        <v>1.430663627386378e-07</v>
+        <v>1.605631499389061e-07</v>
       </c>
       <c r="L3" t="n">
-        <v>1.667458213520369e-07</v>
+        <v>1.966506620618475e-07</v>
       </c>
     </row>
     <row r="4">
@@ -6139,13 +6139,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.589597957816952e-08</v>
+        <v>1.589597957816956e-08</v>
       </c>
       <c r="C4" t="n">
         <v>1.609107436794786e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>1.485980084712675e-08</v>
+        <v>1.485980084712673e-08</v>
       </c>
       <c r="E4" t="n">
         <v>1.632648352398401e-08</v>
@@ -6154,22 +6154,22 @@
         <v>1.632648352398401e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>1.833589608359002e-08</v>
+        <v>1.833589608359004e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>1.543896681023783e-08</v>
+        <v>1.543896681023788e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>1.667637240220308e-08</v>
+        <v>1.667637240220305e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>5.220286895072917e-08</v>
+        <v>5.220286895072918e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>1.794988071935309e-08</v>
+        <v>1.794988071935314e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>1.620980044986481e-08</v>
+        <v>1.620980044986484e-08</v>
       </c>
     </row>
     <row r="5">
@@ -6179,37 +6179,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7.543752510860999e-08</v>
+        <v>7.543752510861097e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>8.025824918766462e-08</v>
+        <v>8.025824918766452e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>5.767465784502603e-08</v>
+        <v>5.767465784502618e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>8.025826183362338e-08</v>
+        <v>8.025826183362333e-08</v>
       </c>
       <c r="F5" t="n">
         <v>8.025826183362338e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>1.170798928671168e-07</v>
+        <v>1.170798928671162e-07</v>
       </c>
       <c r="H5" t="n">
-        <v>7.34758113296908e-08</v>
+        <v>7.347581132969072e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>8.025804732937007e-08</v>
+        <v>8.025804732937002e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>7.702457192160959e-07</v>
+        <v>7.702457192160962e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>1.088795602730586e-07</v>
+        <v>1.08879560273059e-07</v>
       </c>
       <c r="L5" t="n">
-        <v>9.21314824517318e-08</v>
+        <v>9.213148245173159e-08</v>
       </c>
     </row>
     <row r="6">
@@ -6219,10 +6219,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.841711562034515e-08</v>
+        <v>2.286240574322646e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>1.899948017719844e-08</v>
+        <v>1.89994801771984e-08</v>
       </c>
       <c r="D6" t="n">
         <v>2.221909476091599e-08</v>
@@ -6231,25 +6231,25 @@
         <v>1.875606545013872e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>1.91593246670968e-08</v>
+        <v>1.915932466709679e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>2.085703212576567e-08</v>
+        <v>2.5302322248647e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>2.388296120717399e-08</v>
+        <v>1.795373850932202e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>1.919750844437869e-08</v>
+        <v>2.364279856725995e-08</v>
       </c>
       <c r="J6" t="n">
         <v>6.0040347736947e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>2.04451984881987e-08</v>
+        <v>2.044519848819869e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>1.873665094011421e-08</v>
+        <v>1.873665094011416e-08</v>
       </c>
     </row>
     <row r="7">
@@ -6259,37 +6259,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.918742909745417e-08</v>
+        <v>1.918742909745421e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>1.99680237797823e-08</v>
+        <v>1.996802377978229e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>1.815113453683907e-08</v>
+        <v>1.815113453683909e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>1.987403188803686e-08</v>
+        <v>1.987403188803685e-08</v>
       </c>
       <c r="F7" t="n">
         <v>1.987403188803686e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>2.162734560287473e-08</v>
+        <v>2.162734560287474e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>1.873041632952259e-08</v>
+        <v>1.873041632952257e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>1.996782192148776e-08</v>
+        <v>1.996782192148774e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>5.549431847001387e-08</v>
+        <v>5.549431847001385e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>2.124133023863778e-08</v>
+        <v>2.124133023863777e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>1.950124996914954e-08</v>
+        <v>1.950124996914953e-08</v>
       </c>
     </row>
     <row r="8">
@@ -6299,37 +6299,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.333638190360927e-08</v>
+        <v>2.333638190360934e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>3.013185681709441e-08</v>
+        <v>3.013185681709436e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>2.966937762931208e-08</v>
+        <v>2.966937762931211e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>2.847210142018852e-08</v>
+        <v>2.847210142018849e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>2.425445353921422e-08</v>
+        <v>2.425445353921418e-08</v>
       </c>
       <c r="G8" t="n">
         <v>3.187985967732085e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>2.898293040399779e-08</v>
+        <v>2.898293040399775e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>3.022033599593388e-08</v>
+        <v>3.022033599593384e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>6.574803204964967e-08</v>
+        <v>6.574803204964958e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>2.527690626216482e-08</v>
+        <v>2.527690626216494e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>3.612944414199742e-08</v>
+        <v>3.61294441419974e-08</v>
       </c>
     </row>
     <row r="9">
@@ -6339,37 +6339,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5.290305196045489e-08</v>
+        <v>5.290305196045484e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>6.451705172952395e-08</v>
+        <v>6.451705172952393e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>6.27002826876474e-08</v>
+        <v>6.270028268764736e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>7.701858579147117e-08</v>
+        <v>7.70185857914712e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>6.451706253503958e-08</v>
+        <v>6.451706253503951e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>6.617637355261646e-08</v>
+        <v>6.617637355261639e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>6.327944427926425e-08</v>
+        <v>6.327944427926422e-08</v>
       </c>
       <c r="I9" t="n">
         <v>6.45168498712294e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>1.000433464197555e-07</v>
+        <v>1.000433464197556e-07</v>
       </c>
       <c r="K9" t="n">
-        <v>5.951344257368974e-08</v>
+        <v>5.95134425736897e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>6.405027791889111e-08</v>
+        <v>6.405027791889117e-08</v>
       </c>
     </row>
   </sheetData>
@@ -6455,37 +6455,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.439643543519589e-07</v>
+        <v>1.912777437733898e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>3.694493664377654e-07</v>
+        <v>3.736567669240318e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>1.512549788477943e-07</v>
+        <v>1.91661434860259e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>3.97439784996534e-07</v>
+        <v>3.969715511254349e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>2.608362134054413e-07</v>
+        <v>2.832668728993877e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>1.540195964462815e-07</v>
+        <v>1.918069311934946e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>1.467534820289276e-07</v>
+        <v>1.91410794754135e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>1.507490773053555e-07</v>
+        <v>1.916349236056892e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>3.18240668746046e-07</v>
+        <v>3.026281886751931e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>1.213529020039613e-07</v>
+        <v>1.684279957211196e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>1.431310772233749e-07</v>
+        <v>1.912224830804265e-07</v>
       </c>
     </row>
     <row r="3">
@@ -6495,37 +6495,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.61215439255475e-07</v>
+        <v>1.945915728110337e-07</v>
       </c>
       <c r="C3" t="n">
-        <v>3.877151918024673e-07</v>
+        <v>4.975984813756491e-07</v>
       </c>
       <c r="D3" t="n">
-        <v>1.696011676740001e-07</v>
+        <v>1.973068880755296e-07</v>
       </c>
       <c r="E3" t="n">
-        <v>4.157103072777814e-07</v>
+        <v>5.360699427839806e-07</v>
       </c>
       <c r="F3" t="n">
-        <v>2.791067356866886e-07</v>
+        <v>3.483795785150826e-07</v>
       </c>
       <c r="G3" t="n">
-        <v>1.727810506010708e-07</v>
+        <v>1.983462486710631e-07</v>
       </c>
       <c r="H3" t="n">
-        <v>1.644259449916247e-07</v>
+        <v>1.956284242213648e-07</v>
       </c>
       <c r="I3" t="n">
-        <v>1.690123921162226e-07</v>
+        <v>1.971246423575195e-07</v>
       </c>
       <c r="J3" t="n">
-        <v>3.419859052319353e-07</v>
+        <v>3.908318952392442e-07</v>
       </c>
       <c r="K3" t="n">
-        <v>1.393800574092529e-07</v>
+        <v>1.583525552266671e-07</v>
       </c>
       <c r="L3" t="n">
-        <v>1.602571762309859e-07</v>
+        <v>1.942747578396759e-07</v>
       </c>
     </row>
     <row r="4">
@@ -6535,37 +6535,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.268272955303494e-08</v>
+        <v>1.26827295530352e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>1.672629932387243e-08</v>
+        <v>1.672629932387244e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>1.701669688584347e-08</v>
+        <v>1.701669688584359e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>1.690640375336963e-08</v>
+        <v>1.690640375336965e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>1.690640375336963e-08</v>
+        <v>1.690640375336965e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>1.874121796619511e-08</v>
+        <v>1.874121796619516e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>1.434289113061983e-08</v>
+        <v>1.43428911306199e-08</v>
       </c>
       <c r="I4" t="n">
         <v>1.725691474474564e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>3.838388925957751e-08</v>
+        <v>3.83838892595776e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>1.575409486637426e-08</v>
+        <v>1.575409486637429e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>1.219000414248838e-08</v>
+        <v>1.219000414248851e-08</v>
       </c>
     </row>
     <row r="5">
@@ -6575,34 +6575,34 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.359883079207519e-08</v>
+        <v>3.359883079207523e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>9.713112212676899e-08</v>
+        <v>9.713112212676911e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>9.827749919364334e-08</v>
+        <v>9.827749919364368e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>9.713113443678226e-08</v>
+        <v>9.713113443678235e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>9.713113443678226e-08</v>
+        <v>9.713113443678235e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>1.279159090571069e-07</v>
+        <v>1.279159090571046e-07</v>
       </c>
       <c r="H5" t="n">
-        <v>6.389504005948801e-08</v>
+        <v>6.389504005948805e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>9.713096060184875e-08</v>
+        <v>9.713096060184878e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>4.636058510759405e-07</v>
+        <v>4.636058510759399e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>8.111594695691889e-08</v>
+        <v>8.111594695691894e-08</v>
       </c>
       <c r="L5" t="n">
         <v>1.017826668013008e-07</v>
@@ -6615,37 +6615,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.850248042543261e-08</v>
+        <v>1.850248042543253e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>1.912086532872278e-08</v>
+        <v>1.912086532872279e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>1.891857653267415e-08</v>
+        <v>1.891860349311789e-08</v>
       </c>
       <c r="E6" t="n">
         <v>1.895277692385186e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>1.924894659534741e-08</v>
+        <v>1.924894659534743e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>2.07424131841722e-08</v>
+        <v>2.456096883859241e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>1.63489111992531e-08</v>
+        <v>2.118973209106593e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>1.925810996272284e-08</v>
+        <v>2.307666561714297e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>4.495561731143066e-08</v>
+        <v>4.073311201300757e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>1.763580846471455e-08</v>
+        <v>1.763580846471454e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>1.421177837165607e-08</v>
+        <v>1.421177837165623e-08</v>
       </c>
     </row>
     <row r="7">
@@ -6655,37 +6655,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.546212816340037e-08</v>
+        <v>1.546212816340029e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>2.0036474880031e-08</v>
+        <v>2.003647488003101e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>1.979599039757384e-08</v>
+        <v>1.97959903975739e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>1.993731643269416e-08</v>
+        <v>1.993731643269418e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>1.993731643269416e-08</v>
+        <v>1.993731643269418e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>2.152061657656021e-08</v>
+        <v>2.152061657656027e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>1.712228974098488e-08</v>
+        <v>1.712228974098497e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>2.003631335511072e-08</v>
+        <v>2.003631335511073e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>4.116328786994251e-08</v>
+        <v>4.116328786994273e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>1.853349347673936e-08</v>
+        <v>1.853349347673938e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>1.496940275285352e-08</v>
+        <v>1.496940275285358e-08</v>
       </c>
     </row>
     <row r="8">
@@ -6695,34 +6695,34 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.887656097265029e-08</v>
+        <v>1.887656097265055e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>2.831480478597734e-08</v>
+        <v>2.831480478597736e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>2.919631618430801e-08</v>
+        <v>2.919631618430827e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>2.69689729930437e-08</v>
+        <v>2.696897299304373e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>2.354897597580752e-08</v>
+        <v>2.354897597580753e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>2.989281273779419e-08</v>
+        <v>2.989281273779429e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>2.549448590221621e-08</v>
+        <v>2.54944859022162e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>2.840850951634477e-08</v>
+        <v>2.840850951634479e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>4.953645836082507e-08</v>
+        <v>4.953645836082499e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>2.185583328740684e-08</v>
+        <v>2.185583328740688e-08</v>
       </c>
       <c r="L8" t="n">
         <v>2.852039728488282e-08</v>
@@ -6735,37 +6735,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.374246896387405e-08</v>
+        <v>4.374246896387412e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>5.735148846953674e-08</v>
+        <v>5.735148846953679e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>5.711111352281374e-08</v>
+        <v>5.711111352281388e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>6.777732400023125e-08</v>
+        <v>6.777732400023132e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>5.735149948123274e-08</v>
+        <v>5.735149948123275e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>5.883563016606602e-08</v>
+        <v>5.883563016606596e-08</v>
       </c>
       <c r="H9" t="n">
         <v>5.443730333049076e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>5.735132694461646e-08</v>
+        <v>5.735132694461653e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>7.847830145944836e-08</v>
+        <v>7.847830145944851e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>5.040140453083205e-08</v>
+        <v>5.061378403660822e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>5.228441634235906e-08</v>
+        <v>5.228441634235936e-08</v>
       </c>
     </row>
   </sheetData>
@@ -6851,37 +6851,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.439497173958562e-07</v>
+        <v>1.909391947227745e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>3.718426961636574e-07</v>
+        <v>3.733315829918805e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>1.485741346071223e-07</v>
+        <v>1.911825686157708e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>3.997244663528951e-07</v>
+        <v>3.965543667589736e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>2.634315593229395e-07</v>
+        <v>2.831082688524234e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>1.52207137241118e-07</v>
+        <v>1.913737663286738e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>1.474978818965508e-07</v>
+        <v>1.911143701736925e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>1.532892472112402e-07</v>
+        <v>1.914308565809445e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>3.086408297065353e-07</v>
+        <v>3.012744624096608e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>1.18844149386959e-07</v>
+        <v>1.677356636381502e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>1.442954211381382e-07</v>
+        <v>1.909485949383253e-07</v>
       </c>
     </row>
     <row r="3">
@@ -6891,37 +6891,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.610752456480753e-07</v>
+        <v>1.943875642151889e-07</v>
       </c>
       <c r="C3" t="n">
-        <v>3.903672252922401e-07</v>
+        <v>4.981490765300184e-07</v>
       </c>
       <c r="D3" t="n">
-        <v>1.663942833861706e-07</v>
+        <v>1.961138983990236e-07</v>
       </c>
       <c r="E3" t="n">
-        <v>4.182532610555082e-07</v>
+        <v>5.364709736634322e-07</v>
       </c>
       <c r="F3" t="n">
-        <v>2.819603540255528e-07</v>
+        <v>3.492074483504431e-07</v>
       </c>
       <c r="G3" t="n">
-        <v>1.705729889894941e-07</v>
+        <v>1.974755834464691e-07</v>
       </c>
       <c r="H3" t="n">
-        <v>1.65158394665563e-07</v>
+        <v>1.957148891917055e-07</v>
       </c>
       <c r="I3" t="n">
-        <v>1.718131419918002e-07</v>
+        <v>1.978774495989065e-07</v>
       </c>
       <c r="J3" t="n">
-        <v>3.309191286516037e-07</v>
+        <v>3.863972497225459e-07</v>
       </c>
       <c r="K3" t="n">
-        <v>1.364139802654413e-07</v>
+        <v>1.569308260645899e-07</v>
       </c>
       <c r="L3" t="n">
-        <v>1.614728998387487e-07</v>
+        <v>1.945174297772253e-07</v>
       </c>
     </row>
     <row r="4">
@@ -6931,37 +6931,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.251477235368977e-08</v>
+        <v>1.251477235368979e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>1.812871288188944e-08</v>
+        <v>1.812871288188914e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>1.52637924326079e-08</v>
+        <v>1.526379243260778e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>1.829179384776922e-08</v>
+        <v>1.82917938477691e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>1.829179384776922e-08</v>
+        <v>1.829179384776911e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>1.750596787193612e-08</v>
+        <v>1.750596787193595e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>1.462555137314437e-08</v>
+        <v>1.462555137314431e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>1.861761475764026e-08</v>
+        <v>1.861761475764018e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>3.290730259082886e-08</v>
+        <v>3.290730259082879e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>1.427313795553718e-08</v>
+        <v>1.427313795553713e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>1.272211884347012e-08</v>
+        <v>1.272211884346991e-08</v>
       </c>
     </row>
     <row r="5">
@@ -6971,37 +6971,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.527685649894521e-08</v>
+        <v>3.527685649894523e-08</v>
       </c>
       <c r="C5" t="n">
         <v>1.241358221186468e-07</v>
       </c>
       <c r="D5" t="n">
-        <v>7.838523765287822e-08</v>
+        <v>7.838523765287755e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>1.241358338468917e-07</v>
+        <v>1.241358338468912e-07</v>
       </c>
       <c r="F5" t="n">
-        <v>1.241358338468917e-07</v>
+        <v>1.241358338468912e-07</v>
       </c>
       <c r="G5" t="n">
-        <v>1.151608272754175e-07</v>
+        <v>1.151608272754177e-07</v>
       </c>
       <c r="H5" t="n">
-        <v>7.536692603560541e-08</v>
+        <v>7.536692603560499e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>1.241362536484336e-07</v>
+        <v>1.241362536484323e-07</v>
       </c>
       <c r="J5" t="n">
-        <v>3.83609835395063e-07</v>
+        <v>3.836098353950633e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>6.16473463903726e-08</v>
+        <v>6.164734639037219e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>4.299137430500288e-08</v>
+        <v>9.609086213653193e-08</v>
       </c>
     </row>
     <row r="6">
@@ -7011,37 +7011,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.440035532282541e-08</v>
+        <v>1.44003553228258e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>2.044395600736684e-08</v>
+        <v>2.044395600736661e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>1.703504218152682e-08</v>
+        <v>1.703504218152684e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>2.029622042165113e-08</v>
+        <v>2.029622042165101e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>2.051004794762376e-08</v>
+        <v>2.051004794762353e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>2.300426437892603e-08</v>
+        <v>1.939155084107199e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>2.099687513008249e-08</v>
+        <v>2.099687513008229e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>2.050319772677606e-08</v>
+        <v>2.050319772677613e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>3.912424441189511e-08</v>
+        <v>3.510429876631191e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>1.60193449326516e-08</v>
+        <v>1.60193449326517e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>1.463787605107953e-08</v>
+        <v>1.463787605107934e-08</v>
       </c>
     </row>
     <row r="7">
@@ -7051,37 +7051,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.513974123370386e-08</v>
+        <v>1.513974123370286e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>2.124215210786791e-08</v>
+        <v>2.124215210786753e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>1.788865539516173e-08</v>
+        <v>1.788865539516121e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>2.11418076286539e-08</v>
+        <v>2.114180762865351e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>2.11418076286539e-08</v>
+        <v>2.114180762865351e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>2.013093675195021e-08</v>
+        <v>2.013093675194972e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>1.725052025315848e-08</v>
+        <v>1.725052025315757e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>2.124258363765436e-08</v>
+        <v>2.124258363765424e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>3.553227147084294e-08</v>
+        <v>3.553227147084252e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>1.689810683555127e-08</v>
+        <v>1.689810683555125e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>1.534708772348421e-08</v>
+        <v>1.534708772348329e-08</v>
       </c>
     </row>
     <row r="8">
@@ -7091,37 +7091,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.832644446026432e-08</v>
+        <v>1.83264444602645e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>2.892868929081373e-08</v>
+        <v>2.892868929081337e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>2.662315617870639e-08</v>
+        <v>2.662315617870577e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>2.768222567050168e-08</v>
+        <v>2.768222567050161e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>2.451471438104066e-08</v>
+        <v>2.451471438104044e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>2.791254759210872e-08</v>
+        <v>2.791254759210846e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>2.503213109329494e-08</v>
+        <v>2.503213109329505e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>2.902419447781287e-08</v>
+        <v>2.902419447781236e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>4.331478533157063e-08</v>
+        <v>4.331478533157015e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>1.999945729494266e-08</v>
+        <v>1.999945729494281e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>2.792846377651211e-08</v>
+        <v>2.792846377651219e-08</v>
       </c>
     </row>
     <row r="9">
@@ -7131,37 +7131,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.046233505341445e-08</v>
+        <v>4.046233505341352e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>5.468648526993631e-08</v>
+        <v>5.468648526993301e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>5.133309793682619e-08</v>
+        <v>5.133309793682434e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>6.405881356091582e-08</v>
+        <v>6.405881356091376e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>5.468649575070045e-08</v>
+        <v>5.468649575069923e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>5.35752699140186e-08</v>
+        <v>5.357526991401843e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>5.069485341522688e-08</v>
+        <v>5.069485341522774e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>5.468691679972276e-08</v>
+        <v>5.46869167997231e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>6.897660463291132e-08</v>
+        <v>6.89766046329132e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>4.544575476219452e-08</v>
+        <v>4.544575476219425e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>4.879142088555259e-08</v>
+        <v>4.879142088555118e-08</v>
       </c>
     </row>
   </sheetData>
@@ -7247,37 +7247,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.505008500820457e-07</v>
+        <v>1.927530967857356e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>3.731600773213295e-07</v>
+        <v>3.757533763980267e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>1.458823603766315e-07</v>
+        <v>1.92510034845599e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>4.014874816495869e-07</v>
+        <v>3.993518325377969e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>2.639059323750007e-07</v>
+        <v>2.848331309158929e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>1.549415354621701e-07</v>
+        <v>1.9298680123738e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>1.493258523164602e-07</v>
+        <v>1.926774755422722e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>1.534671056885736e-07</v>
+        <v>1.929093911423036e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>3.334563028854979e-07</v>
+        <v>3.064464065658269e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>1.260883270155402e-07</v>
+        <v>1.708215516858771e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>1.478403562318453e-07</v>
+        <v>1.926039023375312e-07</v>
       </c>
     </row>
     <row r="3">
@@ -7287,37 +7287,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.689017787963965e-07</v>
+        <v>1.976857633983942e-07</v>
       </c>
       <c r="C3" t="n">
-        <v>3.920031239015599e-07</v>
+        <v>5.006265064728068e-07</v>
       </c>
       <c r="D3" t="n">
-        <v>1.635895589179101e-07</v>
+        <v>1.959602513049703e-07</v>
       </c>
       <c r="E3" t="n">
-        <v>4.203344946458753e-07</v>
+        <v>5.395648490448598e-07</v>
       </c>
       <c r="F3" t="n">
-        <v>2.827529453712891e-07</v>
+        <v>3.505307801352795e-07</v>
       </c>
       <c r="G3" t="n">
-        <v>1.740094868687449e-07</v>
+        <v>1.993526303427659e-07</v>
       </c>
       <c r="H3" t="n">
-        <v>1.675538391263257e-07</v>
+        <v>1.972471145011023e-07</v>
       </c>
       <c r="I3" t="n">
-        <v>1.723215277979423e-07</v>
+        <v>1.987943248010047e-07</v>
       </c>
       <c r="J3" t="n">
-        <v>3.592917191292127e-07</v>
+        <v>3.996655138411394e-07</v>
       </c>
       <c r="K3" t="n">
-        <v>1.447996531089557e-07</v>
+        <v>1.620782483421499e-07</v>
       </c>
       <c r="L3" t="n">
-        <v>1.658415326216653e-07</v>
+        <v>1.96702005698551e-07</v>
       </c>
     </row>
     <row r="4">
@@ -7327,37 +7327,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.801573295381429e-08</v>
+        <v>1.801573295381419e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>2.008213492822444e-08</v>
+        <v>2.008213492822454e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>1.527023652595542e-08</v>
+        <v>1.527023652595558e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>2.030218899448278e-08</v>
+        <v>2.030218899448274e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>2.030218899448278e-08</v>
+        <v>2.030218899448265e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>2.073789938831079e-08</v>
+        <v>2.073789938831064e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>1.731907552876887e-08</v>
+        <v>1.731907552876885e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>2.032973190317557e-08</v>
+        <v>2.032973190317552e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>4.74383525069366e-08</v>
+        <v>4.743835250693656e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>1.924415709985416e-08</v>
+        <v>1.924415709985414e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>1.643608526476127e-08</v>
+        <v>1.643608526476113e-08</v>
       </c>
     </row>
     <row r="5">
@@ -7367,37 +7367,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9.603220706582126e-08</v>
+        <v>9.603220706582137e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>1.261129055186538e-07</v>
+        <v>1.261129055186541e-07</v>
       </c>
       <c r="D5" t="n">
-        <v>4.925562682546642e-08</v>
+        <v>4.925562682547109e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>1.261129094619178e-07</v>
+        <v>1.26112909461918e-07</v>
       </c>
       <c r="F5" t="n">
-        <v>1.261129094619178e-07</v>
+        <v>1.26112909461918e-07</v>
       </c>
       <c r="G5" t="n">
-        <v>1.454195626792256e-07</v>
+        <v>1.454195626792257e-07</v>
       </c>
       <c r="H5" t="n">
-        <v>9.146927311444616e-08</v>
+        <v>9.146927311444606e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>1.261129837209642e-07</v>
+        <v>1.261129837209643e-07</v>
       </c>
       <c r="J5" t="n">
-        <v>6.618852444833668e-07</v>
+        <v>6.618852444833673e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>1.180644794392862e-07</v>
+        <v>1.180644794392861e-07</v>
       </c>
       <c r="L5" t="n">
-        <v>7.934018376050519e-08</v>
+        <v>2.886189570088825e-07</v>
       </c>
     </row>
     <row r="6">
@@ -7407,37 +7407,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.07595954053792e-08</v>
+        <v>2.075959540537939e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>2.298874599024415e-08</v>
+        <v>2.298874599024428e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>1.772119521649473e-08</v>
+        <v>1.772119521649501e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>2.270741564571043e-08</v>
+        <v>2.270741564571039e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>2.30856747213646e-08</v>
+        <v>2.308567472136467e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>2.840127223354218e-08</v>
+        <v>2.840127223354246e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>2.643842198409903e-08</v>
+        <v>2.64384219840991e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>2.799310474840696e-08</v>
+        <v>2.79931047484071e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>5.593844197833675e-08</v>
+        <v>5.593844197833714e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>2.195827034923156e-08</v>
+        <v>2.195827034923132e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>1.91883747034061e-08</v>
+        <v>1.918837470340606e-08</v>
       </c>
     </row>
     <row r="7">
@@ -7447,37 +7447,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.166357884757299e-08</v>
+        <v>2.166357884757285e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>2.397749959462394e-08</v>
+        <v>2.397749959462396e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>1.891787490616176e-08</v>
+        <v>1.891787490616181e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>2.397072956084219e-08</v>
+        <v>2.397072956084182e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>2.397072956084219e-08</v>
+        <v>2.397072956084182e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>2.438574528206947e-08</v>
+        <v>2.438574528206938e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>2.096692142252753e-08</v>
+        <v>2.096692142252728e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>2.397757779693425e-08</v>
+        <v>2.397757779693426e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>5.108619840069526e-08</v>
+        <v>5.108619840069511e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>2.289200299361284e-08</v>
+        <v>2.28920029936126e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>2.008393115851995e-08</v>
+        <v>2.00839311585198e-08</v>
       </c>
     </row>
     <row r="8">
@@ -7487,37 +7487,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.609299622635573e-08</v>
+        <v>2.609299622635592e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>3.505475095584309e-08</v>
+        <v>3.505475095557503e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>3.137988145207977e-08</v>
+        <v>3.137988145208065e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>3.323584579396039e-08</v>
+        <v>3.323584579396082e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>2.861388930922281e-08</v>
+        <v>2.861388930922295e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>3.546802911706477e-08</v>
+        <v>3.546802911706492e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>3.204920525754378e-08</v>
+        <v>3.204920525754417e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>3.505986163192952e-08</v>
+        <v>3.505986163192988e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>6.216978969263709e-08</v>
+        <v>6.216978969263719e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>2.719783996415451e-08</v>
+        <v>2.719783996415447e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>3.811569029047942e-08</v>
+        <v>3.811569029047926e-08</v>
       </c>
     </row>
     <row r="9">
@@ -7527,37 +7527,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5.614769294082201e-08</v>
+        <v>5.614769294082263e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>6.966907187505795e-08</v>
+        <v>6.966907187505815e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>6.460965925773957e-08</v>
+        <v>6.460965925774228e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>8.260224646626433e-08</v>
+        <v>8.2602246466263e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>6.966907375149504e-08</v>
+        <v>6.966907375149629e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>7.00773175625035e-08</v>
+        <v>7.007731756250242e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>6.665849370296157e-08</v>
+        <v>6.665849370296265e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>6.966915007736828e-08</v>
+        <v>6.966915007736963e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>9.677777068112931e-08</v>
+        <v>9.677777068113049e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>6.20899319022117e-08</v>
+        <v>6.208993190221104e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>6.577550343895397e-08</v>
+        <v>6.577550343895504e-08</v>
       </c>
     </row>
   </sheetData>
@@ -7643,37 +7643,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.446506909651486e-07</v>
+        <v>1.916617601056301e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>3.711206366524076e-07</v>
+        <v>3.744009792093902e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>1.499484010040387e-07</v>
+        <v>1.919405680628771e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>3.992432600964814e-07</v>
+        <v>3.978265306438884e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>2.622623629504779e-07</v>
+        <v>2.838077831546206e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>1.535971284303061e-07</v>
+        <v>1.921325933403653e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>1.466975562377995e-07</v>
+        <v>1.917558813056623e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>1.520232644521559e-07</v>
+        <v>1.920499169273543e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>3.29550807370557e-07</v>
+        <v>3.043305870456803e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>1.221500897778913e-07</v>
+        <v>1.691680637322154e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>1.515821131864731e-07</v>
+        <v>1.920216267368825e-07</v>
       </c>
     </row>
     <row r="3">
@@ -7683,37 +7683,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.621026039428046e-07</v>
+        <v>1.950531330747146e-07</v>
       </c>
       <c r="C3" t="n">
-        <v>3.896760688772225e-07</v>
+        <v>4.988238627277123e-07</v>
       </c>
       <c r="D3" t="n">
-        <v>1.681960679048566e-07</v>
+        <v>1.97029715315945e-07</v>
       </c>
       <c r="E3" t="n">
-        <v>4.178030227809353e-07</v>
+        <v>5.374782356527732e-07</v>
       </c>
       <c r="F3" t="n">
-        <v>2.808221256349317e-07</v>
+        <v>3.492694393084931e-07</v>
       </c>
       <c r="G3" t="n">
-        <v>1.723928602766737e-07</v>
+        <v>1.983987002904861e-07</v>
       </c>
       <c r="H3" t="n">
-        <v>1.644595997799792e-07</v>
+        <v>1.958152071377766e-07</v>
       </c>
       <c r="I3" t="n">
-        <v>1.705822896219226e-07</v>
+        <v>1.978066894200656e-07</v>
       </c>
       <c r="J3" t="n">
-        <v>3.549463788898258e-07</v>
+        <v>3.963118076710898e-07</v>
       </c>
       <c r="K3" t="n">
-        <v>1.403272589451283e-07</v>
+        <v>1.593049129841437e-07</v>
       </c>
       <c r="L3" t="n">
-        <v>1.700748349339997e-07</v>
+        <v>1.976708872193999e-07</v>
       </c>
     </row>
     <row r="4">
@@ -7723,37 +7723,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.34893742219578e-08</v>
+        <v>1.348937422195742e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>1.800663283309885e-08</v>
+        <v>1.800663283309854e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>1.663863835706119e-08</v>
+        <v>1.663863835706084e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>1.819343285283589e-08</v>
+        <v>1.819343285283552e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>1.819343285283591e-08</v>
+        <v>1.819343285283552e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>1.888954935880105e-08</v>
+        <v>1.888954935880072e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>1.470820318864203e-08</v>
+        <v>1.470820318864161e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>1.84191035626704e-08</v>
+        <v>1.841910356266999e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>4.492708155641102e-08</v>
+        <v>4.492708155641064e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>1.635963755353311e-08</v>
+        <v>1.635963755353269e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>1.761041124255881e-08</v>
+        <v>1.761041124255837e-08</v>
       </c>
     </row>
     <row r="5">
@@ -7763,37 +7763,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.847611447730255e-08</v>
+        <v>3.847611447730205e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>1.078927184039146e-07</v>
+        <v>1.078927184039139e-07</v>
       </c>
       <c r="D5" t="n">
-        <v>8.729192551125363e-08</v>
+        <v>8.729192551125239e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>1.078927275656361e-07</v>
+        <v>1.078927275656354e-07</v>
       </c>
       <c r="F5" t="n">
-        <v>1.078927275656361e-07</v>
+        <v>1.078927275656354e-07</v>
       </c>
       <c r="G5" t="n">
-        <v>1.249544087061983e-07</v>
+        <v>1.249544087061919e-07</v>
       </c>
       <c r="H5" t="n">
-        <v>6.300702787275868e-08</v>
+        <v>6.300702787275784e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>1.078927873448023e-07</v>
+        <v>1.078927873448015e-07</v>
       </c>
       <c r="J5" t="n">
-        <v>5.988592828948366e-07</v>
+        <v>5.988592828948354e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>8.282359120870808e-08</v>
+        <v>8.282359120870742e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>1.087390440264439e-07</v>
+        <v>1.211296536921322e-07</v>
       </c>
     </row>
     <row r="6">
@@ -7803,37 +7803,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.985630942916781e-08</v>
+        <v>1.985630942916649e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>2.062037498562396e-08</v>
+        <v>2.062037498562339e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>1.879687598350961e-08</v>
+        <v>1.879690385331235e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>2.040795807293921e-08</v>
+        <v>2.040795807293849e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>2.072357197976378e-08</v>
+        <v>2.072357197976321e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>2.120051612240378e-08</v>
+        <v>2.525648456600981e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>2.225844468889188e-08</v>
+        <v>2.225844468889114e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>2.478603876988042e-08</v>
+        <v>2.478603876987908e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>4.762769208668774e-08</v>
+        <v>4.762769208668729e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>1.859598676146138e-08</v>
+        <v>1.859598676146091e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>1.995274871434406e-08</v>
+        <v>1.995274871434356e-08</v>
       </c>
     </row>
     <row r="7">
@@ -7843,37 +7843,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.645507648358518e-08</v>
+        <v>1.645507648358466e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>2.138473688341001e-08</v>
+        <v>2.138473688340949e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>1.960421026584965e-08</v>
+        <v>1.960421026584907e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>2.131980966508512e-08</v>
+        <v>2.131980966508461e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>2.131980966508511e-08</v>
+        <v>2.131980966508461e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>2.185525162042863e-08</v>
+        <v>2.1855251620428e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>1.767390545026942e-08</v>
+        <v>1.767390545026889e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>2.138480582429777e-08</v>
+        <v>2.13848058242973e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>4.789278381803837e-08</v>
+        <v>4.789278381803773e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>1.932533981516048e-08</v>
+        <v>1.932533981515997e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>2.057611350418616e-08</v>
+        <v>2.057611350418565e-08</v>
       </c>
     </row>
     <row r="8">
@@ -7883,37 +7883,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.009330226018366e-08</v>
+        <v>2.009330226018287e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>3.030861571716767e-08</v>
+        <v>3.030861571716655e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>2.96979005523647e-08</v>
+        <v>2.969790055236341e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>2.885292007284524e-08</v>
+        <v>2.885292007284423e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>2.515379300242709e-08</v>
+        <v>2.515379300242635e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>3.084014516360962e-08</v>
+        <v>3.084014516360847e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>2.665879899347849e-08</v>
+        <v>2.665879899347723e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>3.036969936747887e-08</v>
+        <v>3.03696993674777e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>5.687872811900962e-08</v>
+        <v>5.687872811900836e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>2.286424849428409e-08</v>
+        <v>2.286424849428329e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>3.514604859627567e-08</v>
+        <v>3.514604859627415e-08</v>
       </c>
     </row>
     <row r="9">
@@ -7923,37 +7923,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.47283321493319e-08</v>
+        <v>4.472833214933125e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>5.879808714797116e-08</v>
+        <v>5.879808714797019e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>5.701769502894907e-08</v>
+        <v>5.701769502894807e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>6.934557357060875e-08</v>
+        <v>6.934557357060781e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>5.879809482775036e-08</v>
+        <v>5.879809482774959e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>5.926860188498956e-08</v>
+        <v>5.926860188498875e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>5.508725571483054e-08</v>
+        <v>5.508725571482955e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>5.879815608885894e-08</v>
+        <v>5.879815608885792e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>8.530613408259958e-08</v>
+        <v>8.530613408259857e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>4.52296784042231e-08</v>
+        <v>5.144288511691087e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>5.798946376874732e-08</v>
+        <v>5.798946376874646e-08</v>
       </c>
     </row>
   </sheetData>

--- a/Results/Ammonia/ammonia ozone depletion results.xlsx
+++ b/Results/Ammonia/ammonia ozone depletion results.xlsx
@@ -515,37 +515,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.939828529687403e-07</v>
+        <v>1.939828529687406e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>3.774485880753875e-07</v>
+        <v>3.774485880753876e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>1.937337025689106e-07</v>
+        <v>1.937337025689108e-07</v>
       </c>
       <c r="E2" t="n">
         <v>4.011908935608895e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>2.862527666108519e-07</v>
+        <v>2.86252766610852e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>1.943798671944613e-07</v>
+        <v>1.943798671944615e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>1.939639977614305e-07</v>
+        <v>1.939639977614308e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>1.941918156394274e-07</v>
+        <v>1.941918156394275e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>3.084735688504398e-07</v>
+        <v>3.0847356885044e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>1.725530027851797e-07</v>
+        <v>1.725530027851798e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>1.937816314799711e-07</v>
+        <v>1.937816314799714e-07</v>
       </c>
     </row>
     <row r="3">
@@ -555,37 +555,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.993449700289529e-07</v>
+        <v>1.993449700289531e-07</v>
       </c>
       <c r="C3" t="n">
         <v>5.033507094415488e-07</v>
       </c>
       <c r="D3" t="n">
-        <v>1.97575506003899e-07</v>
+        <v>1.975755060038992e-07</v>
       </c>
       <c r="E3" t="n">
         <v>5.42522551249911e-07</v>
       </c>
       <c r="F3" t="n">
-        <v>3.527961376661241e-07</v>
+        <v>3.527961376661243e-07</v>
       </c>
       <c r="G3" t="n">
-        <v>2.021835214798418e-07</v>
+        <v>2.021835214798421e-07</v>
       </c>
       <c r="H3" t="n">
-        <v>1.993446854339371e-07</v>
+        <v>1.993446854339373e-07</v>
       </c>
       <c r="I3" t="n">
-        <v>2.008332677274542e-07</v>
+        <v>2.008332677274545e-07</v>
       </c>
       <c r="J3" t="n">
         <v>4.016700398418609e-07</v>
       </c>
       <c r="K3" t="n">
-        <v>1.645395983736422e-07</v>
+        <v>1.645395983736423e-07</v>
       </c>
       <c r="L3" t="n">
-        <v>1.980201999865488e-07</v>
+        <v>1.980201999865491e-07</v>
       </c>
     </row>
     <row r="4">
@@ -595,13 +595,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.067154776891522e-08</v>
+        <v>2.067154776891521e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>2.340764277108324e-08</v>
+        <v>2.340764277108323e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>1.78572793879916e-08</v>
+        <v>1.785727938799159e-08</v>
       </c>
       <c r="E4" t="n">
         <v>2.36582570523567e-08</v>
@@ -610,16 +610,16 @@
         <v>2.36582570523567e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>2.523756191572218e-08</v>
+        <v>2.523756191572211e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>2.065388946473424e-08</v>
+        <v>2.065388946473423e-08</v>
       </c>
       <c r="I4" t="n">
         <v>2.357509547865113e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>4.809185229728946e-08</v>
+        <v>4.809185229728943e-08</v>
       </c>
       <c r="K4" t="n">
         <v>2.183703216647991e-08</v>
@@ -635,37 +635,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.25538955917345e-07</v>
+        <v>1.255389559173452e-07</v>
       </c>
       <c r="C5" t="n">
-        <v>1.717841694214576e-07</v>
+        <v>1.717841694214586e-07</v>
       </c>
       <c r="D5" t="n">
-        <v>7.405716942186374e-08</v>
+        <v>7.405716942186368e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>1.717841708349478e-07</v>
+        <v>1.717841708349475e-07</v>
       </c>
       <c r="F5" t="n">
-        <v>1.717841708349478e-07</v>
+        <v>1.717841708349475e-07</v>
       </c>
       <c r="G5" t="n">
-        <v>2.189240505146263e-07</v>
+        <v>2.189240505146248e-07</v>
       </c>
       <c r="H5" t="n">
-        <v>1.419230505448986e-07</v>
+        <v>1.419230505448987e-07</v>
       </c>
       <c r="I5" t="n">
-        <v>1.717839525102159e-07</v>
+        <v>1.717839525102169e-07</v>
       </c>
       <c r="J5" t="n">
-        <v>6.88868150997659e-07</v>
+        <v>6.888681509976589e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>1.504516511328487e-07</v>
+        <v>1.504516511328488e-07</v>
       </c>
       <c r="L5" t="n">
-        <v>9.933865124230263e-08</v>
+        <v>9.933865124230267e-08</v>
       </c>
     </row>
     <row r="6">
@@ -675,37 +675,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.384501117770813e-08</v>
+        <v>2.384501117770812e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>2.665225571685685e-08</v>
+        <v>2.665225571685691e-08</v>
       </c>
       <c r="D6" t="n">
         <v>2.079408276314312e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>2.631154823265195e-08</v>
+        <v>2.631154823265191e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>2.677516001707023e-08</v>
+        <v>2.677516001707025e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>3.444276286676229e-08</v>
+        <v>3.444276286676226e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>3.152208934945169e-08</v>
+        <v>3.15220893494517e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>3.278029642969132e-08</v>
+        <v>3.278029642969128e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>5.821677369809349e-08</v>
+        <v>5.821677369809347e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>2.492312695636273e-08</v>
+        <v>2.492312695636277e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>2.172796538229087e-08</v>
+        <v>2.172796538229085e-08</v>
       </c>
     </row>
     <row r="7">
@@ -715,37 +715,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.529244012494907e-08</v>
+        <v>2.529244012494909e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>2.819620474592652e-08</v>
+        <v>2.819620474592651e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>2.247788706073192e-08</v>
+        <v>2.24778870607319e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>2.822363611950125e-08</v>
+        <v>2.822363611950126e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>2.822363611950125e-08</v>
+        <v>2.822363611950126e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>2.985845427175596e-08</v>
+        <v>2.985845427175597e-08</v>
       </c>
       <c r="H7" t="n">
         <v>2.527478182076812e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>2.819598783468501e-08</v>
+        <v>2.819598783468499e-08</v>
       </c>
       <c r="J7" t="n">
         <v>5.271274465332333e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>2.645792452251378e-08</v>
+        <v>2.645792452251377e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>2.317350419551176e-08</v>
+        <v>2.317350419551174e-08</v>
       </c>
     </row>
     <row r="8">
@@ -755,34 +755,34 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.073071741808258e-08</v>
+        <v>3.073071741808259e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>4.196300333327895e-08</v>
+        <v>4.196300333327897e-08</v>
       </c>
       <c r="D8" t="n">
         <v>3.793801801118907e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>3.968996498162951e-08</v>
+        <v>3.968996498162953e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>3.391412716986144e-08</v>
+        <v>3.391412716986146e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>4.359715389787876e-08</v>
+        <v>4.359715389787881e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>3.901348144690698e-08</v>
+        <v>3.9013481446907e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>4.193468746080781e-08</v>
+        <v>4.193468746080779e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>6.64530755228759e-08</v>
+        <v>6.645307552287586e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>3.174201721163249e-08</v>
+        <v>3.174201721163247e-08</v>
       </c>
       <c r="L8" t="n">
         <v>4.558268899312163e-08</v>
@@ -795,37 +795,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6.919220043458579e-08</v>
+        <v>6.919220043458583e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>8.634546595784376e-08</v>
+        <v>8.634546595784375e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>8.0627438784795e-08</v>
+        <v>8.062743878479498e-08</v>
       </c>
       <c r="E9" t="n">
         <v>1.027890906002408e-07</v>
       </c>
       <c r="F9" t="n">
-        <v>8.63454642167281e-08</v>
+        <v>8.634546421672811e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>8.80077154836732e-08</v>
+        <v>8.800771548367318e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>8.342404303268531e-08</v>
+        <v>8.34240430326853e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>8.634524904660227e-08</v>
+        <v>8.634524904660224e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>1.108620058652406e-07</v>
+        <v>1.108620058652405e-07</v>
       </c>
       <c r="K9" t="n">
-        <v>6.666451906083247e-08</v>
+        <v>6.666451906083246e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>8.132276540742895e-08</v>
+        <v>8.132276540742892e-08</v>
       </c>
     </row>
   </sheetData>
@@ -914,34 +914,34 @@
         <v>1.912664331524365e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>3.739755976696588e-07</v>
+        <v>3.739755976696591e-07</v>
       </c>
       <c r="D2" t="n">
         <v>1.915792454484551e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>3.972946891369217e-07</v>
+        <v>3.972946891369218e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>2.835723427090761e-07</v>
+        <v>2.835723427090764e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>1.917425779400778e-07</v>
+        <v>1.917425779400775e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>1.914437030816892e-07</v>
+        <v>1.914437030816891e-07</v>
       </c>
       <c r="I2" t="n">
         <v>1.918261402551369e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>3.028833536885123e-07</v>
+        <v>3.028833536885121e-07</v>
       </c>
       <c r="K2" t="n">
         <v>1.687062499584337e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>1.912669321688527e-07</v>
+        <v>1.912669321688513e-07</v>
       </c>
     </row>
     <row r="3">
@@ -951,37 +951,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.944170031471494e-07</v>
+        <v>1.944170031471493e-07</v>
       </c>
       <c r="C3" t="n">
-        <v>4.990720161742948e-07</v>
+        <v>4.99072016174295e-07</v>
       </c>
       <c r="D3" t="n">
-        <v>1.966364552831768e-07</v>
+        <v>1.966364552831767e-07</v>
       </c>
       <c r="E3" t="n">
-        <v>5.37552243721489e-07</v>
+        <v>5.375522437214889e-07</v>
       </c>
       <c r="F3" t="n">
-        <v>3.498327150209507e-07</v>
+        <v>3.498327150209505e-07</v>
       </c>
       <c r="G3" t="n">
-        <v>1.978019329461532e-07</v>
+        <v>1.978019329461531e-07</v>
       </c>
       <c r="H3" t="n">
-        <v>1.957636840239529e-07</v>
+        <v>1.95763684023953e-07</v>
       </c>
       <c r="I3" t="n">
-        <v>1.983891760122078e-07</v>
+        <v>1.98389176012208e-07</v>
       </c>
       <c r="J3" t="n">
         <v>3.918868415174801e-07</v>
       </c>
       <c r="K3" t="n">
-        <v>1.595537266062411e-07</v>
+        <v>1.595537266062415e-07</v>
       </c>
       <c r="L3" t="n">
-        <v>1.944866204042515e-07</v>
+        <v>1.944866204042509e-07</v>
       </c>
     </row>
     <row r="4">
@@ -991,37 +991,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.249216551546011e-08</v>
+        <v>1.24921655154598e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>1.881481338912854e-08</v>
+        <v>1.88148133891288e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>1.602552429975662e-08</v>
+        <v>1.602552429975661e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>1.899720715022492e-08</v>
+        <v>1.899720715022508e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>1.899720715022511e-08</v>
+        <v>1.899720715022508e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>1.795309539285533e-08</v>
+        <v>1.795309539285504e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>1.463386837470349e-08</v>
+        <v>1.463386837470333e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>1.936476718121467e-08</v>
+        <v>1.936476718121491e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>3.972377888510097e-08</v>
+        <v>3.972377888510069e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>1.743480497988839e-08</v>
+        <v>1.7434804979888e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>1.2608914641759e-08</v>
+        <v>1.260891464175877e-08</v>
       </c>
     </row>
     <row r="5">
@@ -1031,37 +1031,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.887306980372699e-08</v>
+        <v>2.887306980372689e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>1.29588573050132e-07</v>
+        <v>1.295885730501325e-07</v>
       </c>
       <c r="D5" t="n">
-        <v>8.457511189419743e-08</v>
+        <v>8.457511189419739e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>1.295885868302396e-07</v>
+        <v>1.295885868302398e-07</v>
       </c>
       <c r="F5" t="n">
-        <v>1.295885868302396e-07</v>
+        <v>1.295885868302398e-07</v>
       </c>
       <c r="G5" t="n">
-        <v>1.171666353497743e-07</v>
+        <v>1.171666353497742e-07</v>
       </c>
       <c r="H5" t="n">
-        <v>6.974839959644092e-08</v>
+        <v>6.974839959644059e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>1.295890734808158e-07</v>
+        <v>1.295890734808164e-07</v>
       </c>
       <c r="J5" t="n">
-        <v>5.099351585490165e-07</v>
+        <v>5.099351585490134e-07</v>
       </c>
       <c r="K5" t="n">
         <v>1.037119547831257e-07</v>
       </c>
       <c r="L5" t="n">
-        <v>3.388464814137234e-08</v>
+        <v>3.388464814137197e-08</v>
       </c>
     </row>
     <row r="6">
@@ -1071,37 +1071,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.46174416050213e-08</v>
+        <v>1.461744160502087e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>2.141924367887406e-08</v>
+        <v>2.141924367887423e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>2.223978320071518e-08</v>
+        <v>2.223978320071475e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>2.123942446624117e-08</v>
+        <v>2.123942446624155e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>2.149725085271799e-08</v>
+        <v>2.149725085271843e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>2.384192075995921e-08</v>
+        <v>2.384192075995916e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>2.168544510504261e-08</v>
+        <v>2.168544510504253e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>2.149004327077587e-08</v>
+        <v>2.149004327077613e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>4.221249397393195e-08</v>
+        <v>4.221249397393173e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>1.952189750753946e-08</v>
+        <v>1.952189750753918e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>1.475848468401758e-08</v>
+        <v>1.475848468401713e-08</v>
       </c>
     </row>
     <row r="7">
@@ -1111,37 +1111,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.528511330783289e-08</v>
+        <v>1.528511330783282e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>2.215721454290397e-08</v>
+        <v>2.215721454290417e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>1.881837272182792e-08</v>
+        <v>1.881837272182779e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>2.204458524977524e-08</v>
+        <v>2.204458524977564e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>2.204458524977524e-08</v>
+        <v>2.204458524977564e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>2.074604318522825e-08</v>
+        <v>2.07460431852282e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>1.742681616707656e-08</v>
+        <v>1.742681616707633e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>2.215771497358797e-08</v>
+        <v>2.2157714973588e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>4.251672667747396e-08</v>
+        <v>4.251672667747377e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>2.02277527722611e-08</v>
+        <v>2.022775277226108e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>1.540186243413186e-08</v>
+        <v>1.540186243413179e-08</v>
       </c>
     </row>
     <row r="8">
@@ -1151,37 +1151,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.869849636727527e-08</v>
+        <v>1.869849636727519e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>3.043476110468898e-08</v>
+        <v>3.043476110468913e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>2.823352746990534e-08</v>
+        <v>2.823352746990542e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>2.908670421954435e-08</v>
+        <v>2.908670421954422e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>2.566104408843442e-08</v>
+        <v>2.56610440884342e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>2.913034597533347e-08</v>
+        <v>2.913034597533338e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>2.581111895721225e-08</v>
+        <v>2.581111895721193e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>3.054201776369306e-08</v>
+        <v>3.054201776369325e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>5.090200638257556e-08</v>
+        <v>5.090200638257536e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>2.354879844667612e-08</v>
+        <v>2.354879844667595e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>2.897870653241299e-08</v>
+        <v>2.897870653241289e-08</v>
       </c>
     </row>
     <row r="9">
@@ -1191,37 +1191,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.065324566878633e-08</v>
+        <v>4.065324566878602e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>5.576065115406671e-08</v>
+        <v>5.576065115406698e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>5.242191232502154e-08</v>
+        <v>5.242191232502145e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>6.52640330945136e-08</v>
+        <v>6.526403309451372e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>5.576066365280535e-08</v>
+        <v>5.576066365280553e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>5.434947979639113e-08</v>
+        <v>5.434947979639099e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>5.103025277823937e-08</v>
+        <v>5.103025277823916e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>5.576115158475077e-08</v>
+        <v>5.576115158475083e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>7.612016328863661e-08</v>
+        <v>7.61201632886368e-08</v>
       </c>
       <c r="K9" t="n">
         <v>4.90596232816014e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>4.90052990452946e-08</v>
+        <v>4.900529904529459e-08</v>
       </c>
     </row>
   </sheetData>
@@ -1310,34 +1310,34 @@
         <v>1.431291159746e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>2.317959224429214e-07</v>
+        <v>2.317959224429213e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>1.43098460185233e-07</v>
+        <v>1.430984601852331e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>1.718932782533722e-07</v>
+        <v>1.718932782533729e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>1.718932868253196e-07</v>
+        <v>1.718932868253195e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>1.433367964676488e-07</v>
+        <v>1.433367964676486e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>1.432119013917055e-07</v>
+        <v>1.432119013917062e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>1.43321724938002e-07</v>
+        <v>1.433217249380022e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>2.560240479771768e-07</v>
+        <v>2.560240479771773e-07</v>
       </c>
       <c r="K2" t="n">
         <v>1.455839874042471e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>1.433601947860985e-07</v>
+        <v>1.43360194786099e-07</v>
       </c>
     </row>
     <row r="3">
@@ -1347,37 +1347,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.461685475469527e-07</v>
+        <v>1.461685475469526e-07</v>
       </c>
       <c r="C3" t="n">
-        <v>2.928907412244925e-07</v>
+        <v>2.928907412244926e-07</v>
       </c>
       <c r="D3" t="n">
-        <v>1.459478403225792e-07</v>
+        <v>1.459478403225801e-07</v>
       </c>
       <c r="E3" t="n">
-        <v>1.94701374381938e-07</v>
+        <v>1.947013743819381e-07</v>
       </c>
       <c r="F3" t="n">
-        <v>1.947013829538846e-07</v>
+        <v>1.947013829538845e-07</v>
       </c>
       <c r="G3" t="n">
-        <v>1.476495562310534e-07</v>
+        <v>1.476495562310539e-07</v>
       </c>
       <c r="H3" t="n">
-        <v>1.468346897467069e-07</v>
+        <v>1.468346897467066e-07</v>
       </c>
       <c r="I3" t="n">
-        <v>1.475393353992756e-07</v>
+        <v>1.47539335399276e-07</v>
       </c>
       <c r="J3" t="n">
-        <v>3.370818933381487e-07</v>
+        <v>3.37081893338149e-07</v>
       </c>
       <c r="K3" t="n">
-        <v>1.516412289427225e-07</v>
+        <v>1.516412289427218e-07</v>
       </c>
       <c r="L3" t="n">
-        <v>1.478521584498601e-07</v>
+        <v>1.478521584498599e-07</v>
       </c>
     </row>
     <row r="4">
@@ -1387,37 +1387,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.467035277897833e-08</v>
+        <v>1.467035277897839e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>1.472308863787618e-08</v>
+        <v>1.472308863787626e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>1.432408153571925e-08</v>
+        <v>1.432408153571911e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>1.710522057969072e-08</v>
+        <v>1.710522057969079e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>1.710522057969078e-08</v>
+        <v>1.710522057969079e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>1.704410693861075e-08</v>
+        <v>1.704410693861063e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>1.572607596995207e-08</v>
+        <v>1.572607596995178e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>1.703181867416241e-08</v>
+        <v>1.703181867416282e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>2.404899347581385e-08</v>
+        <v>2.404899347581404e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>1.760638718366179e-08</v>
+        <v>1.760638718366173e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>1.731129809742546e-08</v>
+        <v>1.731129809742554e-08</v>
       </c>
     </row>
     <row r="5">
@@ -1427,34 +1427,34 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.153754173130083e-08</v>
+        <v>5.153754173130144e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>6.445431477811884e-08</v>
+        <v>6.445431477811913e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>4.404299819637745e-08</v>
+        <v>4.404299819637709e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>9.010856008604114e-08</v>
+        <v>9.010856008604073e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>9.010856008604114e-08</v>
+        <v>9.010856008604074e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>9.457262457877008e-08</v>
+        <v>9.45726245787693e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>7.65328145026228e-08</v>
+        <v>7.653281450262266e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>9.010879278374364e-08</v>
+        <v>9.010879278374406e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>2.284688003813708e-07</v>
+        <v>2.2846880038137e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>1.031305388733923e-07</v>
+        <v>1.031305388733918e-07</v>
       </c>
       <c r="L5" t="n">
         <v>1.103634007596612e-07</v>
@@ -1467,37 +1467,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.204210656697847e-08</v>
+        <v>2.204210656697885e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>1.707867888547362e-08</v>
+        <v>1.707867888547307e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>1.607221466438917e-08</v>
+        <v>1.607221466439059e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>1.859780973187631e-08</v>
+        <v>1.85978097318771e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>1.891613148956441e-08</v>
+        <v>1.891613148956449e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>1.891340305695881e-08</v>
+        <v>1.891340305695812e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>2.457195648610539e-08</v>
+        <v>2.457195648610896e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>1.89011147925073e-08</v>
+        <v>1.890111479251033e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>3.171927225521312e-08</v>
+        <v>3.171927225521085e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>1.944631506186962e-08</v>
+        <v>1.944631506187207e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>1.919833619610589e-08</v>
+        <v>1.919833619610658e-08</v>
       </c>
     </row>
     <row r="7">
@@ -1507,37 +1507,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.852704451232705e-08</v>
+        <v>1.852704451232649e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>1.923497951729123e-08</v>
+        <v>1.923497951729032e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>1.818060901729046e-08</v>
+        <v>1.818060901728991e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>2.091809705518394e-08</v>
+        <v>2.091809705518416e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>2.091809705518394e-08</v>
+        <v>2.091809705518416e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>2.090079867195814e-08</v>
+        <v>2.090079867195873e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>1.95827677033005e-08</v>
+        <v>1.958276770329988e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>2.08885104075111e-08</v>
+        <v>2.088851040751093e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>2.790568520916173e-08</v>
+        <v>2.790568520916215e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>2.14630789170098e-08</v>
+        <v>2.146307891700982e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>2.116798983077377e-08</v>
+        <v>2.116798983077362e-08</v>
       </c>
     </row>
     <row r="8">
@@ -1547,37 +1547,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.342906238839068e-08</v>
+        <v>2.342906238839028e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>3.143955055374137e-08</v>
+        <v>3.143955055374052e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>3.186327345286474e-08</v>
+        <v>3.186327345286565e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>3.110073010387096e-08</v>
+        <v>3.11007301038704e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>2.603870882011031e-08</v>
+        <v>2.603870882011045e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>3.307530168770118e-08</v>
+        <v>3.307530168770132e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>3.175727071912428e-08</v>
+        <v>3.175727071912374e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>3.306301342325361e-08</v>
+        <v>3.306301342325355e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>4.00816174531936e-08</v>
+        <v>4.008161745319282e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>2.623000664986847e-08</v>
+        <v>2.62300066498687e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>4.093921166874015e-08</v>
+        <v>4.093921166873967e-08</v>
       </c>
     </row>
     <row r="9">
@@ -1587,37 +1587,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5.06111429582508e-08</v>
+        <v>5.06111429582525e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>6.200179084196796e-08</v>
+        <v>6.200179084196836e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>6.094758911743028e-08</v>
+        <v>6.094758911742845e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>7.598271573115922e-08</v>
+        <v>7.598271573115791e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>6.365508779878957e-08</v>
+        <v>6.365508779879156e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>6.366760999663859e-08</v>
+        <v>6.366760999663672e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>6.234957902797621e-08</v>
+        <v>6.234957902797788e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>6.365532173218863e-08</v>
+        <v>6.365532173218892e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>7.067249653384025e-08</v>
+        <v>7.067249653384012e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>5.804028634812958e-08</v>
+        <v>5.804028634813097e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>6.393480115545305e-08</v>
+        <v>6.393480115545164e-08</v>
       </c>
     </row>
   </sheetData>
@@ -1703,37 +1703,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.406211312686572e-07</v>
+        <v>1.406211312686549e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>2.310514326509913e-07</v>
+        <v>2.310514326509909e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>1.406054621088727e-07</v>
+        <v>1.406054621088709e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>1.708749499219225e-07</v>
+        <v>1.708749499219221e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>1.708749491345869e-07</v>
+        <v>1.708749491345864e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>1.40798148947029e-07</v>
+        <v>1.407981489470271e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>1.406821675233036e-07</v>
+        <v>1.406821675233022e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>1.407204672757418e-07</v>
+        <v>1.407204672757409e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>2.547085064485532e-07</v>
+        <v>2.547085064485499e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>1.443557704243709e-07</v>
+        <v>1.443557704243628e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>1.408231446703122e-07</v>
+        <v>1.408231446703109e-07</v>
       </c>
     </row>
     <row r="3">
@@ -1743,37 +1743,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.422966769949385e-07</v>
+        <v>1.422966769949358e-07</v>
       </c>
       <c r="C3" t="n">
         <v>2.919175361166917e-07</v>
       </c>
       <c r="D3" t="n">
-        <v>1.421833265755543e-07</v>
+        <v>1.421833265755539e-07</v>
       </c>
       <c r="E3" t="n">
-        <v>1.927782528883521e-07</v>
+        <v>1.927782528883518e-07</v>
       </c>
       <c r="F3" t="n">
         <v>1.927782521010162e-07</v>
       </c>
       <c r="G3" t="n">
-        <v>1.435589834724974e-07</v>
+        <v>1.435589834724969e-07</v>
       </c>
       <c r="H3" t="n">
-        <v>1.42798356901174e-07</v>
+        <v>1.427983569011724e-07</v>
       </c>
       <c r="I3" t="n">
-        <v>1.430032483326222e-07</v>
+        <v>1.430032483326199e-07</v>
       </c>
       <c r="J3" t="n">
-        <v>3.34607289514754e-07</v>
+        <v>3.346072895147535e-07</v>
       </c>
       <c r="K3" t="n">
-        <v>1.4932533877479e-07</v>
+        <v>1.49325338774781e-07</v>
       </c>
       <c r="L3" t="n">
-        <v>1.437651534398646e-07</v>
+        <v>1.43765153439863e-07</v>
       </c>
     </row>
     <row r="4">
@@ -1783,37 +1783,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.311799961947066e-08</v>
+        <v>1.311799961947069e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>1.324185053307579e-08</v>
+        <v>1.324185053307565e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>1.294100925153483e-08</v>
+        <v>1.294100925153434e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>1.439028701993079e-08</v>
+        <v>1.439028701993069e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>1.439028701993079e-08</v>
+        <v>1.439028701993071e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>1.514490595828534e-08</v>
+        <v>1.514490595828522e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>1.391627593360301e-08</v>
+        <v>1.391627593360277e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>1.442249677757198e-08</v>
+        <v>1.442249677757188e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>2.132262036490899e-08</v>
+        <v>2.132262036490884e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>1.490433658705748e-08</v>
+        <v>1.490433658705729e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>1.542340169628255e-08</v>
+        <v>1.542340169628216e-08</v>
       </c>
     </row>
     <row r="5">
@@ -1823,37 +1823,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.740130405734024e-08</v>
+        <v>3.740130405733987e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>4.931079471609413e-08</v>
+        <v>4.931079471609375e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>3.348383445287092e-08</v>
+        <v>3.348383445286971e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>5.618793052090805e-08</v>
+        <v>5.618793052090758e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>5.618793052090805e-08</v>
+        <v>5.618793052090758e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>7.223470616924077e-08</v>
+        <v>7.223470616923958e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>5.510839213338025e-08</v>
+        <v>5.510839213337924e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>5.618799751924433e-08</v>
+        <v>5.61879975192438e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>1.84281717990956e-07</v>
+        <v>1.842817179909546e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>6.708165763612837e-08</v>
+        <v>6.708165763612512e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>8.537526023856225e-08</v>
+        <v>8.537526023856161e-08</v>
       </c>
     </row>
     <row r="6">
@@ -1863,37 +1863,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.945475245016327e-08</v>
+        <v>1.945475245016252e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>1.513093363340016e-08</v>
+        <v>1.513093363339994e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>1.948350419479827e-08</v>
+        <v>1.948350419479756e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>1.561571011863637e-08</v>
+        <v>1.561571011863641e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>1.589100376881341e-08</v>
+        <v>1.589100376881313e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>2.148165878897791e-08</v>
+        <v>2.148165878897706e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>2.157728152389593e-08</v>
+        <v>2.157728152389577e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>1.588931358000591e-08</v>
+        <v>1.588931358000573e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>2.300729622687071e-08</v>
+        <v>2.30072962268703e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>1.629521336035697e-08</v>
+        <v>1.629521336035641e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>1.691532296473642e-08</v>
+        <v>1.691532296473609e-08</v>
       </c>
     </row>
     <row r="7">
@@ -1903,37 +1903,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.64671808779506e-08</v>
+        <v>1.646718087794988e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>1.715300457115489e-08</v>
+        <v>1.71530045711544e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>1.629003484392273e-08</v>
+        <v>1.629003484392222e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>1.777512281043626e-08</v>
+        <v>1.777512281043586e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>1.777512281043625e-08</v>
+        <v>1.777512281043586e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>1.849408721676529e-08</v>
+        <v>1.849408721676464e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>1.726545719208292e-08</v>
+        <v>1.72654571920823e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>1.777167803605191e-08</v>
+        <v>1.77716780360516e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>2.46718016233889e-08</v>
+        <v>2.467180162338854e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>1.825351784553738e-08</v>
+        <v>1.825351784553666e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>1.877258295476245e-08</v>
+        <v>1.877258295476205e-08</v>
       </c>
     </row>
     <row r="8">
@@ -1943,37 +1943,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.082930531011744e-08</v>
+        <v>2.082930531011745e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>2.783865523602139e-08</v>
+        <v>2.783865523602085e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>2.828133767566046e-08</v>
+        <v>2.828133767565963e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>2.672863397343115e-08</v>
+        <v>2.672863397343066e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>2.233621892157044e-08</v>
+        <v>2.233621892157005e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>2.917499375161599e-08</v>
+        <v>2.917499375161537e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>2.794636372702979e-08</v>
+        <v>2.794636372702932e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>2.845258457090261e-08</v>
+        <v>2.8452584570902e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>3.535394996177586e-08</v>
+        <v>3.535394996177521e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>2.249826765759792e-08</v>
+        <v>2.249826765759745e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>3.60539857473494e-08</v>
+        <v>3.605398574734875e-08</v>
       </c>
     </row>
     <row r="9">
@@ -1983,37 +1983,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.290937857376453e-08</v>
+        <v>4.290937857376296e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>5.245182711885776e-08</v>
+        <v>5.245182711885881e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>5.158901694732507e-08</v>
+        <v>5.158901694732397e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>6.329079296083011e-08</v>
+        <v>6.329079296082629e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>5.307043244221191e-08</v>
+        <v>5.307043244220989e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>5.379290976446816e-08</v>
+        <v>5.379290976446521e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>5.256427973978576e-08</v>
+        <v>5.256427973978551e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>5.307050058375472e-08</v>
+        <v>5.307050058375372e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>5.997062417109172e-08</v>
+        <v>5.997062417109158e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>4.842077880735922e-08</v>
+        <v>4.842077880735633e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>5.407140550246533e-08</v>
+        <v>5.407140550246512e-08</v>
       </c>
     </row>
   </sheetData>
@@ -2099,37 +2099,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.376068834844599e-07</v>
+        <v>1.376068834844597e-07</v>
       </c>
       <c r="C2" t="n">
         <v>2.302801033525496e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>1.37606982682498e-07</v>
+        <v>1.376069826824978e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>1.699349486497027e-07</v>
+        <v>1.699349486497028e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>1.699349364301613e-07</v>
+        <v>1.699349364301616e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>1.377730137557765e-07</v>
+        <v>1.377730137557764e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>1.376703298359379e-07</v>
+        <v>1.376703298359377e-07</v>
       </c>
       <c r="I2" t="n">
         <v>1.37650012819666e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>2.53354629424318e-07</v>
+        <v>2.533546294243181e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>1.430952724525822e-07</v>
+        <v>1.430952724525802e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>1.377202879872075e-07</v>
+        <v>1.377202879872073e-07</v>
       </c>
     </row>
     <row r="3">
@@ -2139,37 +2139,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.376819553241704e-07</v>
+        <v>1.376819553241702e-07</v>
       </c>
       <c r="C3" t="n">
-        <v>2.909789826737826e-07</v>
+        <v>2.909789826737825e-07</v>
       </c>
       <c r="D3" t="n">
-        <v>1.376813787854503e-07</v>
+        <v>1.3768137878545e-07</v>
       </c>
       <c r="E3" t="n">
-        <v>1.912800843645565e-07</v>
+        <v>1.912800843645564e-07</v>
       </c>
       <c r="F3" t="n">
-        <v>1.912800721450149e-07</v>
+        <v>1.912800721450154e-07</v>
       </c>
       <c r="G3" t="n">
-        <v>1.388665948838403e-07</v>
+        <v>1.388665948838402e-07</v>
       </c>
       <c r="H3" t="n">
-        <v>1.381937038837309e-07</v>
+        <v>1.381937038837306e-07</v>
       </c>
       <c r="I3" t="n">
-        <v>1.379883260087878e-07</v>
+        <v>1.379883260087875e-07</v>
       </c>
       <c r="J3" t="n">
-        <v>3.326519548087884e-07</v>
+        <v>3.326519548087894e-07</v>
       </c>
       <c r="K3" t="n">
-        <v>1.472046987956958e-07</v>
+        <v>1.472046987956929e-07</v>
       </c>
       <c r="L3" t="n">
-        <v>1.385158549240617e-07</v>
+        <v>1.385158549240614e-07</v>
       </c>
     </row>
     <row r="4">
@@ -2179,37 +2179,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.177068453260468e-08</v>
+        <v>1.177068453260484e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>1.204089537115568e-08</v>
+        <v>1.204089537115574e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>1.177180502007904e-08</v>
+        <v>1.177180502007923e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>1.228131134591378e-08</v>
+        <v>1.228131134591388e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>1.22813113459138e-08</v>
+        <v>1.228131134591387e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>1.367450066054404e-08</v>
+        <v>1.367450066054408e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>1.258603710913789e-08</v>
+        <v>1.258603710913806e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>1.243930654670604e-08</v>
+        <v>1.243930654670624e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>1.980869386425819e-08</v>
+        <v>1.980869386425836e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>1.27289624384283e-08</v>
+        <v>1.272896243842843e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>1.308138413778765e-08</v>
+        <v>1.308138413778784e-08</v>
       </c>
     </row>
     <row r="5">
@@ -2219,37 +2219,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.788207165006908e-08</v>
+        <v>2.78820716500693e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>3.891978227772972e-08</v>
+        <v>3.891978227772984e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>2.723621932376381e-08</v>
+        <v>2.723621932376417e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>3.593079770053784e-08</v>
+        <v>3.593079770053815e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>3.593079770053784e-08</v>
+        <v>3.593079770053815e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>6.055948788444316e-08</v>
+        <v>6.055948788444541e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>4.505201044990932e-08</v>
+        <v>4.505201044990964e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>3.593074725168482e-08</v>
+        <v>3.593074725168515e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>1.715910956460764e-07</v>
+        <v>1.715910956460767e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>4.364064835393818e-08</v>
+        <v>4.364064835393771e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>5.539928379362417e-08</v>
+        <v>5.539928379362441e-08</v>
       </c>
     </row>
     <row r="6">
@@ -2259,37 +2259,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.294970145129609e-08</v>
+        <v>1.294970145129604e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>1.348715744135499e-08</v>
+        <v>1.3487157441355e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>1.284776803244139e-08</v>
+        <v>1.284776803244142e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>1.336716772799443e-08</v>
+        <v>1.336716772799449e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>1.360757735647147e-08</v>
+        <v>1.360757735647141e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>1.935728954981137e-08</v>
+        <v>1.935728954981123e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>1.914876380886459e-08</v>
+        <v>1.914876380886474e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>1.812209543597364e-08</v>
+        <v>1.812209543597331e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>2.555515893312892e-08</v>
+        <v>2.555515893312902e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>1.380306658803253e-08</v>
+        <v>1.380306658803237e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>1.429056961518824e-08</v>
+        <v>1.429056961518835e-08</v>
       </c>
     </row>
     <row r="7">
@@ -2299,37 +2299,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.477082245861171e-08</v>
+        <v>1.4770822458612e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>1.540617605990792e-08</v>
+        <v>1.540617605990813e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>1.477176218972341e-08</v>
+        <v>1.47717621897237e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>1.540563321133128e-08</v>
+        <v>1.540563321133158e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>1.540563321133128e-08</v>
+        <v>1.540563321133158e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>1.667463858655106e-08</v>
+        <v>1.667463858655133e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>1.558617503514495e-08</v>
+        <v>1.558617503514524e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>1.543944447271307e-08</v>
+        <v>1.543944447271342e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>2.280883179026528e-08</v>
+        <v>2.280883179026553e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>1.572910036443533e-08</v>
+        <v>1.572910036443559e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>1.608152206379471e-08</v>
+        <v>1.608152206379499e-08</v>
       </c>
     </row>
     <row r="8">
@@ -2339,37 +2339,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.874163629887981e-08</v>
+        <v>1.874163629888007e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>2.494764703952437e-08</v>
+        <v>2.494764703952483e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>2.550605559531908e-08</v>
+        <v>2.550605559531954e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>2.345222002276482e-08</v>
+        <v>2.345222002276527e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>1.956778299419069e-08</v>
+        <v>1.956778299419096e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>2.624719369320738e-08</v>
+        <v>2.624719369320785e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>2.515873014184948e-08</v>
+        <v>2.515873014185013e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>2.501199957936906e-08</v>
+        <v>2.50119995793699e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>3.238248778628768e-08</v>
+        <v>3.238248778628826e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>1.959585898581635e-08</v>
+        <v>1.959585898581651e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>3.150556432120432e-08</v>
+        <v>3.150556432120468e-08</v>
       </c>
     </row>
     <row r="9">
@@ -2379,37 +2379,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.821255593152837e-08</v>
+        <v>3.821255593152737e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>4.667086565434541e-08</v>
+        <v>4.667086565434424e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>4.603663590369701e-08</v>
+        <v>4.603663590369582e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>5.573171148735943e-08</v>
+        <v>5.573171148735783e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>4.670418326828233e-08</v>
+        <v>4.670418326828102e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>4.793932818098866e-08</v>
+        <v>4.793932818098731e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>4.685086462958258e-08</v>
+        <v>4.685086462958131e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>4.670413406715066e-08</v>
+        <v>4.670413406714949e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>5.407352138470278e-08</v>
+        <v>5.407352138470154e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>4.22772443974748e-08</v>
+        <v>4.227724439747374e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>4.734621165823227e-08</v>
+        <v>4.734621165823113e-08</v>
       </c>
     </row>
   </sheetData>
@@ -2498,16 +2498,16 @@
         <v>1.403153706868169e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>2.315748206890791e-07</v>
+        <v>2.315748206890792e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>1.403036441772396e-07</v>
+        <v>1.403036441772395e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>1.716599060585056e-07</v>
+        <v>1.716599060585058e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>1.716599184206518e-07</v>
+        <v>1.716599184206519e-07</v>
       </c>
       <c r="G2" t="n">
         <v>1.405070360724592e-07</v>
@@ -2516,16 +2516,16 @@
         <v>1.404047130244351e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>1.404676767612367e-07</v>
+        <v>1.404676767612369e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>2.558545340678017e-07</v>
+        <v>2.55854534067802e-07</v>
       </c>
       <c r="K2" t="n">
         <v>1.45322384628633e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>1.404313563036363e-07</v>
+        <v>1.404313563036365e-07</v>
       </c>
     </row>
     <row r="3">
@@ -2538,34 +2538,34 @@
         <v>1.413522491734683e-07</v>
       </c>
       <c r="C3" t="n">
-        <v>2.921087725948305e-07</v>
+        <v>2.921087725948303e-07</v>
       </c>
       <c r="D3" t="n">
-        <v>1.412668726355786e-07</v>
+        <v>1.412668726355787e-07</v>
       </c>
       <c r="E3" t="n">
         <v>1.939241623461013e-07</v>
       </c>
       <c r="F3" t="n">
-        <v>1.939241747082473e-07</v>
+        <v>1.939241747082475e-07</v>
       </c>
       <c r="G3" t="n">
         <v>1.427190448598757e-07</v>
       </c>
       <c r="H3" t="n">
-        <v>1.420604511984624e-07</v>
+        <v>1.420604511984625e-07</v>
       </c>
       <c r="I3" t="n">
         <v>1.424361999823637e-07</v>
       </c>
       <c r="J3" t="n">
-        <v>3.361575387421808e-07</v>
+        <v>3.36157538742181e-07</v>
       </c>
       <c r="K3" t="n">
         <v>1.507450942594519e-07</v>
       </c>
       <c r="L3" t="n">
-        <v>1.422154799974043e-07</v>
+        <v>1.422154799974044e-07</v>
       </c>
     </row>
     <row r="4">
@@ -2575,37 +2575,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.408429267818364e-08</v>
+        <v>1.408429267818365e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>1.355235340174775e-08</v>
+        <v>1.355235340174778e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>1.395183635804622e-08</v>
+        <v>1.395183635804628e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>1.594346860381679e-08</v>
+        <v>1.594346860381684e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>1.59434686038168e-08</v>
+        <v>1.594346860381684e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>1.627678110319711e-08</v>
+        <v>1.627678110319717e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>1.520812283301342e-08</v>
+        <v>1.520812283301352e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>1.598824243113657e-08</v>
+        <v>1.598824243113666e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>2.249081397973278e-08</v>
+        <v>2.249081397973283e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>1.641547313216468e-08</v>
+        <v>1.641547313216472e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>1.543925204579816e-08</v>
+        <v>1.543925204579817e-08</v>
       </c>
     </row>
     <row r="5">
@@ -2615,37 +2615,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.159357376370729e-08</v>
+        <v>4.159357376370744e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>4.525361230582738e-08</v>
+        <v>4.52536123058275e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>3.820632119057654e-08</v>
+        <v>3.820632119057665e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>7.212842960624937e-08</v>
+        <v>7.212842960625605e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>7.212842960624937e-08</v>
+        <v>7.212842960625605e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>8.130840562727278e-08</v>
+        <v>8.130840562727154e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>6.703558963436697e-08</v>
+        <v>6.703558963436734e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>7.212859470817588e-08</v>
+        <v>7.212859470818484e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>2.000590425914103e-07</v>
+        <v>2.000590425914107e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>8.256680168683891e-08</v>
+        <v>8.256680168683893e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>7.287511996784632e-08</v>
+        <v>7.287511996784643e-08</v>
       </c>
     </row>
     <row r="6">
@@ -2655,37 +2655,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.598868122052802e-08</v>
+        <v>1.598868122052812e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>1.599830538720904e-08</v>
+        <v>1.599830538720873e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>1.574877445614261e-08</v>
+        <v>1.574877445614268e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>1.755172261126268e-08</v>
+        <v>1.755172261126284e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>1.78976367173617e-08</v>
+        <v>1.789763671736177e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>1.818116964554148e-08</v>
+        <v>1.81811696455416e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>2.419571160509412e-08</v>
+        <v>2.419571160509424e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>2.338950123170136e-08</v>
+        <v>2.338950123170149e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>2.467873841729774e-08</v>
+        <v>2.467873841729782e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>1.829507434914948e-08</v>
+        <v>1.829507434914957e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>1.735320334738968e-08</v>
+        <v>1.735320334738971e-08</v>
       </c>
     </row>
     <row r="7">
@@ -2695,37 +2695,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.785805529245471e-08</v>
+        <v>1.785805529245476e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>1.80601964796565e-08</v>
+        <v>1.806019647965659e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>1.772545532438093e-08</v>
+        <v>1.772545532438099e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>1.976055368782207e-08</v>
+        <v>1.976055368782215e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>1.976055368782207e-08</v>
+        <v>1.976055368782215e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>2.005054371746818e-08</v>
+        <v>2.005054371746826e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>1.898188544728449e-08</v>
+        <v>1.898188544728463e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>1.976200504540765e-08</v>
+        <v>1.976200504540773e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>2.626457659400385e-08</v>
+        <v>2.626457659400396e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>2.018923574643575e-08</v>
+        <v>2.018923574643584e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>1.921301466006923e-08</v>
+        <v>1.921301466006931e-08</v>
       </c>
     </row>
     <row r="8">
@@ -2735,37 +2735,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.279938169577293e-08</v>
+        <v>2.279938169577299e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>3.028093774100545e-08</v>
+        <v>3.028093774100559e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>3.145539945995824e-08</v>
+        <v>3.145539945995834e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>2.999180505308754e-08</v>
+        <v>2.999180505308766e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>2.49332211092319e-08</v>
+        <v>2.493322110923196e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>3.227097449560774e-08</v>
+        <v>3.227097449560786e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>3.120231622551559e-08</v>
+        <v>3.120231622551573e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>3.198243582354723e-08</v>
+        <v>3.198243582354736e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>3.848643790005194e-08</v>
+        <v>3.848643790005206e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>2.499534905094815e-08</v>
+        <v>2.499534905094823e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>3.903707860389397e-08</v>
+        <v>3.903707860389406e-08</v>
       </c>
     </row>
     <row r="9">
@@ -2775,37 +2775,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.965713451125922e-08</v>
+        <v>4.965713451125939e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>6.045517511441343e-08</v>
+        <v>6.045517511441374e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>6.012058215210118e-08</v>
+        <v>6.01205821521015e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>7.438426456584381e-08</v>
+        <v>7.438426456584413e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>6.21568174761177e-08</v>
+        <v>6.215681747611788e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>6.244552235222513e-08</v>
+        <v>6.244552235222539e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>6.137686408204147e-08</v>
+        <v>6.137686408204162e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>6.215698368016461e-08</v>
+        <v>6.215698368016485e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>6.865955522876079e-08</v>
+        <v>6.865955522876099e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>5.644491055790178e-08</v>
+        <v>5.644491055790199e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>6.160799329482618e-08</v>
+        <v>6.160799329482631e-08</v>
       </c>
     </row>
   </sheetData>
@@ -2891,37 +2891,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.351782065610463e-07</v>
+        <v>1.351782065610469e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>2.309226864796251e-07</v>
+        <v>2.309226864796253e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>1.352040709111041e-07</v>
+        <v>1.352040709110991e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>1.707748074425265e-07</v>
+        <v>1.70774807442524e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>1.707748156411621e-07</v>
+        <v>1.707748156411622e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>1.352759372117062e-07</v>
+        <v>1.352759372117045e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>1.352265750359589e-07</v>
+        <v>1.352265750359598e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>1.352474982989548e-07</v>
+        <v>1.352474982989553e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>2.546106963683099e-07</v>
+        <v>2.546106963683093e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>1.442351527040745e-07</v>
+        <v>1.442351527040781e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>1.352384210288733e-07</v>
+        <v>1.352384210288741e-07</v>
       </c>
     </row>
     <row r="3">
@@ -2931,37 +2931,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.329528823540035e-07</v>
+        <v>1.329528823540017e-07</v>
       </c>
       <c r="C3" t="n">
-        <v>2.91038716262606e-07</v>
+        <v>2.910387162626061e-07</v>
       </c>
       <c r="D3" t="n">
-        <v>1.331360593234495e-07</v>
+        <v>1.331360593234479e-07</v>
       </c>
       <c r="E3" t="n">
-        <v>1.92089686370914e-07</v>
+        <v>1.920896863709085e-07</v>
       </c>
       <c r="F3" t="n">
-        <v>1.920896945695494e-07</v>
+        <v>1.920896945695468e-07</v>
       </c>
       <c r="G3" t="n">
-        <v>1.336496773827212e-07</v>
+        <v>1.336496773827203e-07</v>
       </c>
       <c r="H3" t="n">
-        <v>1.333533939245334e-07</v>
+        <v>1.333533939245344e-07</v>
       </c>
       <c r="I3" t="n">
-        <v>1.334458515854021e-07</v>
+        <v>1.334458515854003e-07</v>
       </c>
       <c r="J3" t="n">
-        <v>3.323767825678263e-07</v>
+        <v>3.323767825678228e-07</v>
       </c>
       <c r="K3" t="n">
-        <v>1.482015463908876e-07</v>
+        <v>1.482015463908907e-07</v>
       </c>
       <c r="L3" t="n">
-        <v>1.334044992271889e-07</v>
+        <v>1.334044992271898e-07</v>
       </c>
     </row>
     <row r="4">
@@ -2971,37 +2971,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.246791747887201e-08</v>
+        <v>1.246791747887195e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>1.176627515079523e-08</v>
+        <v>1.176627515079517e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>1.27600672109007e-08</v>
+        <v>1.276006721090068e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>1.333346205993614e-08</v>
+        <v>1.333346205993626e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>1.333346205993614e-08</v>
+        <v>1.333346205993626e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>1.359926463885673e-08</v>
+        <v>1.359926463885671e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>1.310859158861832e-08</v>
+        <v>1.310859158861831e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>1.343353054759352e-08</v>
+        <v>1.343353054759363e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>1.715574830979864e-08</v>
+        <v>1.715574830979848e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>1.308594269911618e-08</v>
+        <v>1.308594269911612e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>1.317851107712562e-08</v>
+        <v>1.317851107712558e-08</v>
       </c>
     </row>
     <row r="5">
@@ -3011,37 +3011,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.397174764048449e-08</v>
+        <v>2.397174764048441e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>2.488356794073425e-08</v>
+        <v>2.488356794073453e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>2.84039586162736e-08</v>
+        <v>2.840395861627357e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>3.718422861553663e-08</v>
+        <v>3.718422861553735e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>3.718422861553663e-08</v>
+        <v>3.718422861553735e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>4.315394729148677e-08</v>
+        <v>4.31539472914879e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>3.740297765516548e-08</v>
+        <v>3.740297765516628e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>3.718442319349077e-08</v>
+        <v>3.718442319349146e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>1.077982695709211e-07</v>
+        <v>1.077982695709203e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>3.403849071588833e-08</v>
+        <v>3.403849071588862e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>3.929810141077817e-08</v>
+        <v>3.92981014107785e-08</v>
       </c>
     </row>
     <row r="6">
@@ -3051,37 +3051,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.408925521450208e-08</v>
+        <v>1.408925521450204e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>1.397061851324089e-08</v>
+        <v>1.397061851324098e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>1.963423758082622e-08</v>
+        <v>1.963423758082608e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>1.474354617313526e-08</v>
+        <v>1.474354617313523e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>1.505173449561503e-08</v>
+        <v>1.505173449561526e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>1.522060237448688e-08</v>
+        <v>1.522060237448704e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>2.125327045664303e-08</v>
+        <v>2.125327045664308e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>2.000185996330197e-08</v>
+        <v>2.00018599633027e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>2.403246637461861e-08</v>
+        <v>2.403246637461825e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>1.465312026748254e-08</v>
+        <v>1.465312026748243e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>1.480869229691829e-08</v>
+        <v>1.480869229691841e-08</v>
       </c>
     </row>
     <row r="7">
@@ -3091,37 +3091,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.575184143821753e-08</v>
+        <v>1.575184143821743e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>1.580592774285439e-08</v>
+        <v>1.580592774285451e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>1.604388257455497e-08</v>
+        <v>1.604388257455501e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>1.670206977814833e-08</v>
+        <v>1.670206977814853e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>1.670206977814833e-08</v>
+        <v>1.670206977814853e-08</v>
       </c>
       <c r="G7" t="n">
         <v>1.688318859820249e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>1.639251554796385e-08</v>
+        <v>1.63925155479638e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>1.671745450693919e-08</v>
+        <v>1.67174545069394e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>2.043967226914416e-08</v>
+        <v>2.043967226914401e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>1.636986665846171e-08</v>
+        <v>1.636986665846163e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>1.646243503647119e-08</v>
+        <v>1.64624350364715e-08</v>
       </c>
     </row>
     <row r="8">
@@ -3131,37 +3131,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.022509901795594e-08</v>
+        <v>2.022509901795565e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>2.674064940615777e-08</v>
+        <v>2.674064940615747e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>2.833445063352764e-08</v>
+        <v>2.833445063352729e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>2.588265128552745e-08</v>
+        <v>2.588265128552738e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>2.13867568137643e-08</v>
+        <v>2.138675681376429e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>2.783108874771436e-08</v>
+        <v>2.783108874771418e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>2.734041569759164e-08</v>
+        <v>2.734041569759134e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>2.766535465645119e-08</v>
+        <v>2.766535465645105e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>3.138884484949528e-08</v>
+        <v>3.138884484949478e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>2.072285443019252e-08</v>
+        <v>2.072285443019238e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>3.417364073092488e-08</v>
+        <v>3.417364073092455e-08</v>
       </c>
     </row>
     <row r="9">
@@ -3171,37 +3171,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.174369587768447e-08</v>
+        <v>4.174369587768492e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>5.056696689497702e-08</v>
+        <v>5.056696689497747e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>5.08050340236517e-08</v>
+        <v>5.080503402365215e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>6.15977545472804e-08</v>
+        <v>6.159775454728114e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>5.14782982000191e-08</v>
+        <v>5.147829820001969e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>5.164422775032506e-08</v>
+        <v>5.164422775032553e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>5.115355470008646e-08</v>
+        <v>5.115355470008722e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>5.147849365906177e-08</v>
+        <v>5.147849365906238e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>5.520071142126678e-08</v>
+        <v>5.520071142126736e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>4.60500073055704e-08</v>
+        <v>4.605000730557082e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>5.122347418859381e-08</v>
+        <v>5.122347418859426e-08</v>
       </c>
     </row>
   </sheetData>
@@ -3290,19 +3290,19 @@
         <v>1.279225448213051e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>2.300492411876965e-07</v>
+        <v>2.300492411876963e-07</v>
       </c>
       <c r="D2" t="n">
         <v>1.27946889388109e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>1.697317112529842e-07</v>
+        <v>1.697317112529843e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>1.697317046494768e-07</v>
+        <v>1.697317046494769e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>1.279583184844194e-07</v>
+        <v>1.279583184844193e-07</v>
       </c>
       <c r="H2" t="n">
         <v>1.279626179109987e-07</v>
@@ -3311,7 +3311,7 @@
         <v>1.279616963807235e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>2.526858768040597e-07</v>
+        <v>2.526858768040598e-07</v>
       </c>
       <c r="K2" t="n">
         <v>1.428293553530268e-07</v>
@@ -3327,22 +3327,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.2166524399951e-07</v>
+        <v>1.216652439995102e-07</v>
       </c>
       <c r="C3" t="n">
-        <v>2.903219258177995e-07</v>
+        <v>2.903219258177997e-07</v>
       </c>
       <c r="D3" t="n">
-        <v>1.218376599027977e-07</v>
+        <v>1.218376599027976e-07</v>
       </c>
       <c r="E3" t="n">
-        <v>1.908920956775192e-07</v>
+        <v>1.908920956775195e-07</v>
       </c>
       <c r="F3" t="n">
         <v>1.908920890740119e-07</v>
       </c>
       <c r="G3" t="n">
-        <v>1.219200630842336e-07</v>
+        <v>1.219200630842338e-07</v>
       </c>
       <c r="H3" t="n">
         <v>1.219956346819594e-07</v>
@@ -3351,13 +3351,13 @@
         <v>1.219434657726252e-07</v>
       </c>
       <c r="J3" t="n">
-        <v>3.283724648520528e-07</v>
+        <v>3.283724648520529e-07</v>
       </c>
       <c r="K3" t="n">
-        <v>1.462757026420925e-07</v>
+        <v>1.462757026420926e-07</v>
       </c>
       <c r="L3" t="n">
-        <v>1.217905967564015e-07</v>
+        <v>1.217905967564017e-07</v>
       </c>
     </row>
     <row r="4">
@@ -3367,37 +3367,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.119965072344912e-08</v>
+        <v>1.119965072344853e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>1.062895636503075e-08</v>
+        <v>1.062895636503074e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>1.147463380455387e-08</v>
+        <v>1.14746338045535e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>1.162395412062249e-08</v>
+        <v>1.16239541206229e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>1.162395412062249e-08</v>
+        <v>1.16239541206229e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>1.163145452372498e-08</v>
+        <v>1.163145452372471e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>1.172802336892182e-08</v>
+        <v>1.172802336892246e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>1.182644842030742e-08</v>
+        <v>1.182644842030765e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>1.276823674765818e-08</v>
+        <v>1.276823674765783e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>1.120980474478912e-08</v>
+        <v>1.120980474478916e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>1.139628591984697e-08</v>
+        <v>1.139628591984748e-08</v>
       </c>
     </row>
     <row r="5">
@@ -3407,37 +3407,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.096534388239816e-08</v>
+        <v>2.096534388239876e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>2.322090929807386e-08</v>
+        <v>2.322090929807402e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>2.513834753654973e-08</v>
+        <v>2.513834753655085e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>2.834689769150555e-08</v>
+        <v>2.834689769150683e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>2.834689769150555e-08</v>
+        <v>2.834689769150681e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>2.788112263454707e-08</v>
+        <v>2.788112263454712e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>3.199064453800334e-08</v>
+        <v>3.19906445380032e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>2.834717298687138e-08</v>
+        <v>2.834717298687108e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>4.902774916942944e-08</v>
+        <v>4.902774916942955e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>2.068211653599865e-08</v>
+        <v>2.068211653599928e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>2.595991399003259e-08</v>
+        <v>2.595991399003255e-08</v>
       </c>
     </row>
     <row r="6">
@@ -3447,37 +3447,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.689682923644882e-08</v>
+        <v>1.689682923644924e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>1.247230831015395e-08</v>
+        <v>1.247230831015391e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>1.273289988072637e-08</v>
+        <v>1.273289988072735e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>1.285682463638511e-08</v>
+        <v>1.285682463638576e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>1.309705527818251e-08</v>
+        <v>1.309705527818109e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>1.732863303672392e-08</v>
+        <v>1.732863303672543e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>1.302637255704208e-08</v>
+        <v>1.302637255704215e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>1.752362693330753e-08</v>
+        <v>1.752362693330838e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>1.422088805710279e-08</v>
+        <v>1.422088805710295e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>1.241594223663052e-08</v>
+        <v>1.241594223663064e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>1.268745247297829e-08</v>
+        <v>1.268745247297836e-08</v>
       </c>
     </row>
     <row r="7">
@@ -3487,37 +3487,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.401785572593429e-08</v>
+        <v>1.401785572593435e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>1.415125377381411e-08</v>
+        <v>1.415125377381427e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>1.429272690420093e-08</v>
+        <v>1.429272690420126e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>1.459508779762156e-08</v>
+        <v>1.459508779762168e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>1.459508779762156e-08</v>
+        <v>1.459508779762169e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>1.44496595262101e-08</v>
+        <v>1.44496595262105e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>1.454622837140765e-08</v>
+        <v>1.454622837140827e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>1.464465342279194e-08</v>
+        <v>1.464465342279347e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>1.558644175014333e-08</v>
+        <v>1.558644175014363e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>1.402800974727375e-08</v>
+        <v>1.402800974727498e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>1.421449092233296e-08</v>
+        <v>1.42144909223333e-08</v>
       </c>
     </row>
     <row r="8">
@@ -3527,37 +3527,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.793950931677055e-08</v>
+        <v>1.793950931677089e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>2.353187487128631e-08</v>
+        <v>2.353187487128628e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>2.486091881054483e-08</v>
+        <v>2.486091881054484e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>2.252435284898027e-08</v>
+        <v>2.252435284898199e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>1.871119253916381e-08</v>
+        <v>1.871119253916399e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>2.38762541468588e-08</v>
+        <v>2.387625414685927e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>2.397282299212662e-08</v>
+        <v>2.397282299212678e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>2.407124804344263e-08</v>
+        <v>2.407124804344221e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>2.501411823356354e-08</v>
+        <v>2.501411823356455e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>1.784740623352307e-08</v>
+        <v>1.784740623352383e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>2.939145674985688e-08</v>
+        <v>2.939145674985767e-08</v>
       </c>
     </row>
     <row r="9">
@@ -3567,37 +3567,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.706206972641619e-08</v>
+        <v>3.706206972641641e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>4.487995121077619e-08</v>
+        <v>4.487995121077665e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>4.502153913302025e-08</v>
+        <v>4.502153913302163e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>5.42408079525318e-08</v>
+        <v>5.424080795253267e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>4.53730746269493e-08</v>
+        <v>4.537307462695159e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>4.51783569631718e-08</v>
+        <v>4.517835696317284e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>4.527492580837106e-08</v>
+        <v>4.52749258083706e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>4.537335085975408e-08</v>
+        <v>4.537335085975579e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>4.631513918710528e-08</v>
+        <v>4.631513918710597e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>4.030428851695564e-08</v>
+        <v>4.030428851695548e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>4.494318835929526e-08</v>
+        <v>4.49431883592956e-08</v>
       </c>
     </row>
   </sheetData>
@@ -3683,28 +3683,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.363860673174059e-07</v>
+        <v>1.36386067317406e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>2.308480025787443e-07</v>
+        <v>2.308480025787446e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>1.363854667771589e-07</v>
+        <v>1.363854667771586e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>1.712623357824294e-07</v>
+        <v>1.712623357824297e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>1.712623476028123e-07</v>
+        <v>1.712623476028126e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>1.365677419409525e-07</v>
+        <v>1.365677419409521e-07</v>
       </c>
       <c r="H2" t="n">
         <v>1.364931014094551e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>1.364855803678189e-07</v>
+        <v>1.364855803678187e-07</v>
       </c>
       <c r="J2" t="n">
         <v>2.555933589008609e-07</v>
@@ -3713,7 +3713,7 @@
         <v>1.449089496310682e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>1.364821765700505e-07</v>
+        <v>1.364821765700503e-07</v>
       </c>
     </row>
     <row r="3">
@@ -3729,13 +3729,13 @@
         <v>2.906551059596572e-07</v>
       </c>
       <c r="D3" t="n">
-        <v>1.348772379462096e-07</v>
+        <v>1.348772379462095e-07</v>
       </c>
       <c r="E3" t="n">
-        <v>1.929959079267071e-07</v>
+        <v>1.929959079267068e-07</v>
       </c>
       <c r="F3" t="n">
-        <v>1.9299591974709e-07</v>
+        <v>1.929959197470897e-07</v>
       </c>
       <c r="G3" t="n">
         <v>1.361785512683159e-07</v>
@@ -3744,13 +3744,13 @@
         <v>1.357129904347862e-07</v>
       </c>
       <c r="I3" t="n">
-        <v>1.355910204481995e-07</v>
+        <v>1.355910204481996e-07</v>
       </c>
       <c r="J3" t="n">
-        <v>3.359688526752217e-07</v>
+        <v>3.359688526752219e-07</v>
       </c>
       <c r="K3" t="n">
-        <v>1.498211633898493e-07</v>
+        <v>1.498211633898494e-07</v>
       </c>
       <c r="L3" t="n">
         <v>1.356018217249818e-07</v>
@@ -3763,37 +3763,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.350740548001108e-08</v>
+        <v>1.350740548001095e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>1.24254561116953e-08</v>
+        <v>1.242545611167855e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>1.350062210165504e-08</v>
+        <v>1.350062210165491e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>1.473956780415953e-08</v>
+        <v>1.473956780415955e-08</v>
       </c>
       <c r="F4" t="n">
         <v>1.473956780415953e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>1.558674381685931e-08</v>
+        <v>1.558674381685944e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>1.482407129709538e-08</v>
+        <v>1.482407129709504e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>1.481300001484497e-08</v>
+        <v>1.481300001484499e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>2.237872090503324e-08</v>
+        <v>2.237872090503338e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>1.530487521413091e-08</v>
+        <v>1.530487521413099e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>1.463735029095007e-08</v>
+        <v>1.463735029095042e-08</v>
       </c>
     </row>
     <row r="5">
@@ -3803,37 +3803,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.435484402942018e-08</v>
+        <v>3.435484402942029e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>2.780041710016518e-08</v>
+        <v>2.780041710022679e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>3.341741400277493e-08</v>
+        <v>3.341741400277457e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>5.425069404764e-08</v>
+        <v>5.425069404763871e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>5.425069404764e-08</v>
+        <v>5.425069404763871e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>7.199772145818879e-08</v>
+        <v>7.199772145818376e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>6.301411345330021e-08</v>
+        <v>6.301411345329982e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>5.425074723468681e-08</v>
+        <v>5.42507472346872e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>2.014090694334948e-07</v>
+        <v>2.014090694334958e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>6.591613742203483e-08</v>
+        <v>6.59161374220348e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>6.019738415189673e-08</v>
+        <v>6.019738415189665e-08</v>
       </c>
     </row>
     <row r="6">
@@ -3843,37 +3843,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.53525759756733e-08</v>
+        <v>1.535257597567329e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>1.479346548361609e-08</v>
+        <v>1.479346548359172e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>1.524870237697264e-08</v>
+        <v>1.524870237697263e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>1.630512119943602e-08</v>
+        <v>1.630512119943601e-08</v>
       </c>
       <c r="F6" t="n">
         <v>1.665724249302446e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>1.743191431252146e-08</v>
+        <v>1.743191431252169e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>2.366408808053632e-08</v>
+        <v>2.366408808053641e-08</v>
       </c>
       <c r="I6" t="n">
         <v>1.665817051050731e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>2.450525958573854e-08</v>
+        <v>2.450525958573845e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>1.710977063678578e-08</v>
+        <v>1.710977063678591e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>1.64913868281345e-08</v>
+        <v>1.649138682813467e-08</v>
       </c>
     </row>
     <row r="7">
@@ -3883,13 +3883,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.717301300007777e-08</v>
+        <v>1.717301300007779e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>1.681755016173512e-08</v>
+        <v>1.681755016178905e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>1.716608443391202e-08</v>
+        <v>1.716608443391203e-08</v>
       </c>
       <c r="E7" t="n">
         <v>1.847067113717786e-08</v>
@@ -3898,22 +3898,22 @@
         <v>1.847067113717786e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>1.925235133692628e-08</v>
+        <v>1.925235133692615e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>1.848967881716213e-08</v>
+        <v>1.848967881716193e-08</v>
       </c>
       <c r="I7" t="n">
         <v>1.847860753491178e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>2.604432842510039e-08</v>
+        <v>2.604432842510017e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>1.897048273419753e-08</v>
+        <v>1.89704827341978e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>1.830295781101717e-08</v>
+        <v>1.830295781101728e-08</v>
       </c>
     </row>
     <row r="8">
@@ -3923,37 +3923,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.203453894719137e-08</v>
+        <v>2.203453894719132e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>2.880223639871575e-08</v>
+        <v>2.880223639872369e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>3.063521760057262e-08</v>
+        <v>3.06352176005727e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>2.851413369225887e-08</v>
+        <v>2.851413369225884e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>2.356144820389867e-08</v>
+        <v>2.356144820389868e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>3.124305738177906e-08</v>
+        <v>3.124305738177902e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>3.048038486210949e-08</v>
+        <v>3.048038486210947e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>3.046931357976489e-08</v>
+        <v>3.046931357976485e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>3.803643553370946e-08</v>
+        <v>3.803643553370884e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>2.369958050290139e-08</v>
+        <v>2.36995805029014e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>3.77406885779263e-08</v>
+        <v>3.774068857792611e-08</v>
       </c>
     </row>
     <row r="9">
@@ -3963,37 +3963,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.872143677884571e-08</v>
+        <v>4.872143677884573e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>5.884936760552655e-08</v>
+        <v>5.88493676054912e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>5.919805147340932e-08</v>
+        <v>5.919805147340931e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>7.260798836264065e-08</v>
+        <v>7.260798836264094e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>6.05103706562614e-08</v>
+        <v>6.051037065626148e-08</v>
       </c>
       <c r="G9" t="n">
         <v>6.128416878071769e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>6.052149626095379e-08</v>
+        <v>6.052149626095333e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>6.051042497870325e-08</v>
+        <v>6.051042497870335e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>6.807614586889177e-08</v>
+        <v>6.807614586889167e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>5.492818257095412e-08</v>
+        <v>5.492818257095399e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>6.033477525480868e-08</v>
+        <v>6.033477525480879e-08</v>
       </c>
     </row>
   </sheetData>
@@ -4079,37 +4079,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.179713488976529e-07</v>
+        <v>1.17971348897652e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>2.29700948757851e-07</v>
+        <v>2.297009487578506e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>1.179934027828403e-07</v>
+        <v>1.179934027828395e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>1.697982630607848e-07</v>
+        <v>1.697982630607844e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>1.697982673210405e-07</v>
+        <v>1.697982673210399e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>1.180065950816715e-07</v>
+        <v>1.180065950816707e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>1.180146787240874e-07</v>
+        <v>1.180146787240867e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>1.180134901860921e-07</v>
+        <v>1.180134901860913e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>2.534975342819923e-07</v>
+        <v>2.534975342819919e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>1.433682806395989e-07</v>
+        <v>1.433682806395957e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>1.17983054025884e-07</v>
+        <v>1.179830540258833e-07</v>
       </c>
     </row>
     <row r="3">
@@ -4119,37 +4119,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.049953410017468e-07</v>
+        <v>1.049953410017459e-07</v>
       </c>
       <c r="C3" t="n">
         <v>2.894698957860295e-07</v>
       </c>
       <c r="D3" t="n">
-        <v>1.051513575277972e-07</v>
+        <v>1.051513575277963e-07</v>
       </c>
       <c r="E3" t="n">
-        <v>1.907746024795143e-07</v>
+        <v>1.907746024795141e-07</v>
       </c>
       <c r="F3" t="n">
-        <v>1.9077460673977e-07</v>
+        <v>1.907746067397701e-07</v>
       </c>
       <c r="G3" t="n">
-        <v>1.052464245754384e-07</v>
+        <v>1.052464245754375e-07</v>
       </c>
       <c r="H3" t="n">
-        <v>1.053514403376653e-07</v>
+        <v>1.053514403376646e-07</v>
       </c>
       <c r="I3" t="n">
-        <v>1.052948195595453e-07</v>
+        <v>1.052948195595445e-07</v>
       </c>
       <c r="J3" t="n">
-        <v>3.290336968304722e-07</v>
+        <v>3.290336968304719e-07</v>
       </c>
       <c r="K3" t="n">
-        <v>1.469400217861888e-07</v>
+        <v>1.46940021786184e-07</v>
       </c>
       <c r="L3" t="n">
-        <v>1.050953633197885e-07</v>
+        <v>1.050953633197877e-07</v>
       </c>
     </row>
     <row r="4">
@@ -4159,37 +4159,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.206258281197807e-08</v>
+        <v>1.206258281197799e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>1.141113836994167e-08</v>
+        <v>1.141113836994117e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>1.231169159045849e-08</v>
+        <v>1.231169159045853e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>1.255222374218221e-08</v>
+        <v>1.25522237421821e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>1.255222374218221e-08</v>
+        <v>1.255222374218209e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>1.248817927615109e-08</v>
+        <v>1.248817927615101e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>1.263131280149243e-08</v>
+        <v>1.263131280149236e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>1.27217220926735e-08</v>
+        <v>1.272172209267334e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>1.273608738864722e-08</v>
+        <v>1.273608738864704e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>1.211076673550211e-08</v>
+        <v>1.211076673550149e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>1.221909100207555e-08</v>
+        <v>1.221909100207531e-08</v>
       </c>
     </row>
     <row r="5">
@@ -4199,37 +4199,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.348613457606259e-08</v>
+        <v>2.348613457606227e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>2.45235783391731e-08</v>
+        <v>2.452357833917221e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>2.717525090566204e-08</v>
+        <v>2.717525090566174e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>3.142153305896359e-08</v>
+        <v>3.142153305896294e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>3.142153305896359e-08</v>
+        <v>3.142153305896294e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>3.031138267855179e-08</v>
+        <v>3.031138267855224e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>3.549727009950327e-08</v>
+        <v>3.549727009950195e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>3.142181203929415e-08</v>
+        <v>3.142181203929369e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>3.562891321423986e-08</v>
+        <v>3.562891321423897e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>2.381592747072421e-08</v>
+        <v>2.381592747072401e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>2.795565101389488e-08</v>
+        <v>2.795565101389433e-08</v>
       </c>
     </row>
     <row r="6">
@@ -4239,37 +4239,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.822337035145504e-08</v>
+        <v>1.822337035145497e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>1.34031401142975e-08</v>
+        <v>1.340314011429683e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>1.369086122990171e-08</v>
+        <v>1.36908612299014e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>1.386244894796248e-08</v>
+        <v>1.38624489479623e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>1.413938449574218e-08</v>
+        <v>1.413938449574191e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>1.39143873807969e-08</v>
+        <v>1.391438738079665e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>2.036244700129368e-08</v>
+        <v>2.036244700129357e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>1.888250963215048e-08</v>
+        <v>1.888250963215029e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>1.435463942344296e-08</v>
+        <v>1.435463942344278e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>1.344797531609772e-08</v>
+        <v>1.344797531609702e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>1.365401603238223e-08</v>
+        <v>1.365401603238182e-08</v>
       </c>
     </row>
     <row r="7">
@@ -4279,37 +4279,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.511537428283556e-08</v>
+        <v>1.511537428283531e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>1.517781120279914e-08</v>
+        <v>1.517781120279906e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>1.536437084934086e-08</v>
+        <v>1.536437084934089e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>1.573728428357659e-08</v>
+        <v>1.57372842835766e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>1.573728428357659e-08</v>
+        <v>1.57372842835766e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>1.554097074700856e-08</v>
+        <v>1.554097074700844e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>1.568410427234995e-08</v>
+        <v>1.568410427234962e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>1.577451356353103e-08</v>
+        <v>1.577451356353106e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>1.578887885950474e-08</v>
+        <v>1.578887885950486e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>1.516355820635963e-08</v>
+        <v>1.51635582063595e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>1.527188247293311e-08</v>
+        <v>1.527188247293314e-08</v>
       </c>
     </row>
     <row r="8">
@@ -4319,37 +4319,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.936504938099027e-08</v>
+        <v>1.936504938099031e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>2.547205078442877e-08</v>
+        <v>2.547205078442733e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>2.695321408991007e-08</v>
+        <v>2.695321408990998e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>2.440965955903812e-08</v>
+        <v>2.440965955903783e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>2.019461670874117e-08</v>
+        <v>2.01946167087409e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>2.586926127009907e-08</v>
+        <v>2.586926127009821e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>2.601239479557128e-08</v>
+        <v>2.601239479557039e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>2.610280408662122e-08</v>
+        <v>2.610280408662102e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>2.611836398447955e-08</v>
+        <v>2.61183639844788e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>1.930031990390746e-08</v>
+        <v>1.930031990390698e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>3.19497950745239e-08</v>
+        <v>3.19497950745233e-08</v>
       </c>
     </row>
     <row r="9">
@@ -4359,37 +4359,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.087568419173495e-08</v>
+        <v>4.087568419173454e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>4.953273217935752e-08</v>
+        <v>4.953273217935671e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>4.971940721566755e-08</v>
+        <v>4.971940721566667e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>6.004715622609148e-08</v>
+        <v>6.004715622609073e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>5.012915464519046e-08</v>
+        <v>5.012915464518993e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>4.989589172356695e-08</v>
+        <v>4.98958917235665e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>5.00390252489084e-08</v>
+        <v>5.003902524890771e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>5.012943454008949e-08</v>
+        <v>5.012943454008889e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>5.01437998360632e-08</v>
+        <v>5.014379983606266e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>3.869632889247067e-08</v>
+        <v>3.869632889246972e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>4.962680344949158e-08</v>
+        <v>4.962680344949117e-08</v>
       </c>
     </row>
   </sheetData>
@@ -4475,37 +4475,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.238265500940218e-07</v>
+        <v>1.238265500940223e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>2.285233020266652e-07</v>
+        <v>2.285233020266655e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>1.238461137053578e-07</v>
+        <v>1.238461137053584e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>1.689752466690989e-07</v>
+        <v>1.689752466690994e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>1.689752332649895e-07</v>
+        <v>1.689752332649901e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>1.238468759122644e-07</v>
+        <v>1.23846875912265e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>1.238658199714363e-07</v>
+        <v>1.238658199714368e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>1.238461309872297e-07</v>
+        <v>1.238461309872303e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>2.518209547959584e-07</v>
+        <v>2.518209547959591e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>1.421031871266839e-07</v>
+        <v>1.421031871266857e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>1.238396569935507e-07</v>
+        <v>1.238396569935512e-07</v>
       </c>
     </row>
     <row r="3">
@@ -4515,37 +4515,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.153217362811227e-07</v>
+        <v>1.153217362811232e-07</v>
       </c>
       <c r="C3" t="n">
-        <v>2.882120828673955e-07</v>
+        <v>2.882120828673958e-07</v>
       </c>
       <c r="D3" t="n">
-        <v>1.154600910059474e-07</v>
+        <v>1.154600910059478e-07</v>
       </c>
       <c r="E3" t="n">
-        <v>1.899539417763592e-07</v>
+        <v>1.899539417763596e-07</v>
       </c>
       <c r="F3" t="n">
-        <v>1.899539283722498e-07</v>
+        <v>1.899539283722501e-07</v>
       </c>
       <c r="G3" t="n">
-        <v>1.154663455130997e-07</v>
+        <v>1.154663455131004e-07</v>
       </c>
       <c r="H3" t="n">
-        <v>1.15641578205341e-07</v>
+        <v>1.156415782053416e-07</v>
       </c>
       <c r="I3" t="n">
-        <v>1.15460488253991e-07</v>
+        <v>1.154604882539915e-07</v>
       </c>
       <c r="J3" t="n">
-        <v>3.268444573510042e-07</v>
+        <v>3.268444573510055e-07</v>
       </c>
       <c r="K3" t="n">
-        <v>1.455005296869462e-07</v>
+        <v>1.455005296869489e-07</v>
       </c>
       <c r="L3" t="n">
-        <v>1.154270474768781e-07</v>
+        <v>1.154270474768786e-07</v>
       </c>
     </row>
     <row r="4">
@@ -4555,37 +4555,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.075233437947177e-08</v>
+        <v>1.075233437947213e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>1.020717666805377e-08</v>
+        <v>1.020717666805402e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>1.097331436921866e-08</v>
+        <v>1.097331436921903e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>1.094781351812155e-08</v>
+        <v>1.09478135181208e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>1.094781351812155e-08</v>
+        <v>1.09478135181208e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>1.100970422198942e-08</v>
+        <v>1.100970422198967e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>1.126301567376641e-08</v>
+        <v>1.126301567376682e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>1.115827486592583e-08</v>
+        <v>1.115827486592626e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>1.125527580169837e-08</v>
+        <v>1.125527580169876e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>1.077452633956746e-08</v>
+        <v>1.07745263395678e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>1.09170370922397e-08</v>
+        <v>1.091703709224004e-08</v>
       </c>
     </row>
     <row r="5">
@@ -4595,37 +4595,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.043594462648526e-08</v>
+        <v>2.043594462648598e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>2.240828268483195e-08</v>
+        <v>2.240828268483106e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>2.368529097327197e-08</v>
+        <v>2.368529097327262e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>2.401519186091691e-08</v>
+        <v>2.401519186091729e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>2.401519186091691e-08</v>
+        <v>2.401519186091729e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>2.428748919348681e-08</v>
+        <v>2.428748919349118e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>3.10791717960374e-08</v>
+        <v>3.107917179603825e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>2.401545395777791e-08</v>
+        <v>2.401545395777931e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>2.945479550648954e-08</v>
+        <v>2.945479550649123e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>2.035122659190409e-08</v>
+        <v>2.035122659190452e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>2.475752418200645e-08</v>
+        <v>2.475752418200678e-08</v>
       </c>
     </row>
     <row r="6">
@@ -4635,37 +4635,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.601402977519213e-08</v>
+        <v>1.601402977519379e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>1.183268830941845e-08</v>
+        <v>1.183268830941883e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>1.20181919397549e-08</v>
+        <v>1.201819193975539e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>1.203084918700671e-08</v>
+        <v>1.203084918700691e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>1.22410867471208e-08</v>
+        <v>1.224108674712089e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>1.210577676432568e-08</v>
+        <v>1.210577676432594e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>1.765791294971737e-08</v>
+        <v>1.76579129497174e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>1.225434740826202e-08</v>
+        <v>1.225434740826342e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>1.664078918627885e-08</v>
+        <v>1.66407891862793e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>1.177344713633441e-08</v>
+        <v>1.177344713633501e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>1.201818428444348e-08</v>
+        <v>1.201818428444409e-08</v>
       </c>
     </row>
     <row r="7">
@@ -4675,37 +4675,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.33681775467637e-08</v>
+        <v>1.336817754676443e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>1.348602035589931e-08</v>
+        <v>1.348602035590021e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>1.35890389935751e-08</v>
+        <v>1.358903899357588e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>1.372117692945372e-08</v>
+        <v>1.372117692945369e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>1.372117692945372e-08</v>
+        <v>1.372117692945369e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>1.362554738928133e-08</v>
+        <v>1.362554738928202e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>1.387885884105834e-08</v>
+        <v>1.387885884105911e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>1.377411803321771e-08</v>
+        <v>1.377411803321735e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>1.387111896899027e-08</v>
+        <v>1.387111896899113e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>1.339036950685937e-08</v>
+        <v>1.339036950686011e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>1.353288025953159e-08</v>
+        <v>1.353288025953234e-08</v>
       </c>
     </row>
     <row r="8">
@@ -4715,37 +4715,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.70556987211271e-08</v>
+        <v>1.705569872112742e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>2.221357759571117e-08</v>
+        <v>2.221357759571172e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>2.342130603104493e-08</v>
+        <v>2.342130603104548e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>2.111478403205899e-08</v>
+        <v>2.111478403205847e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>1.759134593206646e-08</v>
+        <v>1.759134593206601e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>2.240239159939705e-08</v>
+        <v>2.240239159939736e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>2.265570305126571e-08</v>
+        <v>2.265570305126616e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>2.255096224333341e-08</v>
+        <v>2.255096224333273e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>2.264896336382067e-08</v>
+        <v>2.26489633638212e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>1.698335389398745e-08</v>
+        <v>1.698335389398769e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>2.76259479309483e-08</v>
+        <v>2.762594793094889e-08</v>
       </c>
     </row>
     <row r="9">
@@ -4755,37 +4755,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.632838457085876e-08</v>
+        <v>3.632838457086155e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>4.399132984263048e-08</v>
+        <v>4.399132984263382e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>4.409446962861115e-08</v>
+        <v>4.409446962861457e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>5.298605487178603e-08</v>
+        <v>5.298605487179014e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>4.427916448999455e-08</v>
+        <v>4.427916448999735e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>4.413085687601248e-08</v>
+        <v>4.413085687601575e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>4.43841683277894e-08</v>
+        <v>4.438416832779283e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>4.427942751994878e-08</v>
+        <v>4.427942751995251e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>4.437642845572135e-08</v>
+        <v>4.437642845572489e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>3.934665417987306e-08</v>
+        <v>3.934665417987604e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>4.403818974626268e-08</v>
+        <v>4.403818974626609e-08</v>
       </c>
     </row>
   </sheetData>
@@ -4874,22 +4874,22 @@
         <v>1.928904216071942e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>3.762303280455425e-07</v>
+        <v>3.762303280455424e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>1.928128443559284e-07</v>
+        <v>1.928128443559286e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>3.999202330429616e-07</v>
+        <v>3.999202330429617e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>2.851543836233018e-07</v>
+        <v>2.851543836233019e-07</v>
       </c>
       <c r="G2" t="n">
         <v>1.932995990275439e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>1.929507474152355e-07</v>
+        <v>1.929507474152356e-07</v>
       </c>
       <c r="I2" t="n">
         <v>1.931759175403262e-07</v>
@@ -4911,22 +4911,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.968636123970294e-07</v>
+        <v>1.968636123970293e-07</v>
       </c>
       <c r="C3" t="n">
-        <v>5.010708473185743e-07</v>
+        <v>5.010708473185736e-07</v>
       </c>
       <c r="D3" t="n">
-        <v>1.963133535026746e-07</v>
+        <v>1.963133535026748e-07</v>
       </c>
       <c r="E3" t="n">
-        <v>5.40159161256006e-07</v>
+        <v>5.401591612560059e-07</v>
       </c>
       <c r="F3" t="n">
         <v>3.507171290612117e-07</v>
       </c>
       <c r="G3" t="n">
-        <v>1.997827589799028e-07</v>
+        <v>1.997827589799026e-07</v>
       </c>
       <c r="H3" t="n">
         <v>1.974013998457744e-07</v>
@@ -4935,10 +4935,10 @@
         <v>1.988903788469433e-07</v>
       </c>
       <c r="J3" t="n">
-        <v>4.079230928324965e-07</v>
+        <v>4.079230928324963e-07</v>
       </c>
       <c r="K3" t="n">
-        <v>1.626855239292868e-07</v>
+        <v>1.626855239292867e-07</v>
       </c>
       <c r="L3" t="n">
         <v>1.970792286799584e-07</v>
@@ -4951,37 +4951,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.674107173214905e-08</v>
+        <v>1.67410717321486e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>2.044126936011947e-08</v>
+        <v>2.044126936011949e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>1.586480099180386e-08</v>
+        <v>1.586480099180347e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>2.065131045016677e-08</v>
+        <v>2.065131045016679e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>2.065131045016677e-08</v>
+        <v>2.065131045016679e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>2.144519231348142e-08</v>
+        <v>2.144519231348117e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>1.758970939288807e-08</v>
+        <v>1.758970939288771e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>2.051371555901332e-08</v>
+        <v>2.051371555901334e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>5.884424881634249e-08</v>
+        <v>5.884424881634234e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>1.958874233584316e-08</v>
+        <v>1.958874233584288e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>1.706639106122228e-08</v>
+        <v>1.706639106122189e-08</v>
       </c>
     </row>
     <row r="5">
@@ -4991,37 +4991,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.802742871341977e-08</v>
+        <v>6.802742871341981e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>1.235252860998913e-07</v>
+        <v>1.235252860998915e-07</v>
       </c>
       <c r="D5" t="n">
-        <v>5.335758630291314e-08</v>
+        <v>5.335758630291297e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>1.235252852743388e-07</v>
+        <v>1.23525285274339e-07</v>
       </c>
       <c r="F5" t="n">
-        <v>1.235252852743388e-07</v>
+        <v>1.235252852743391e-07</v>
       </c>
       <c r="G5" t="n">
-        <v>1.548467450460389e-07</v>
+        <v>1.548467450460452e-07</v>
       </c>
       <c r="H5" t="n">
-        <v>9.318304475132362e-08</v>
+        <v>9.318304475132335e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>1.235252401459531e-07</v>
+        <v>1.235252401459532e-07</v>
       </c>
       <c r="J5" t="n">
-        <v>8.719763192629936e-07</v>
+        <v>8.719763192629932e-07</v>
       </c>
       <c r="K5" t="n">
         <v>1.198665873802343e-07</v>
       </c>
       <c r="L5" t="n">
-        <v>1.682518189472685e-07</v>
+        <v>1.682518189472684e-07</v>
       </c>
     </row>
     <row r="6">
@@ -5031,37 +5031,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.962682106801766e-08</v>
+        <v>1.962682106801729e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>2.331607770620352e-08</v>
+        <v>2.331607770620357e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>1.845403347274234e-08</v>
+        <v>1.845403347274207e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>2.300937115841854e-08</v>
+        <v>2.300937115841855e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>2.3408404628399e-08</v>
+        <v>2.340840462839902e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>2.43309416493501e-08</v>
+        <v>2.433094164934986e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>2.699036136773256e-08</v>
+        <v>2.699036136773224e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>2.846738878373017e-08</v>
+        <v>2.846738878373016e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>6.224324838614534e-08</v>
+        <v>6.22432483861451e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>2.242671311504882e-08</v>
+        <v>2.242671311504881e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>1.994845824484015e-08</v>
+        <v>1.994845824483983e-08</v>
       </c>
     </row>
     <row r="7">
@@ -5071,37 +5071,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.062501483501281e-08</v>
+        <v>2.062501483501266e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>2.439770461581565e-08</v>
+        <v>2.439770461581567e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>1.974848750896696e-08</v>
+        <v>1.974848750896636e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>2.443920853645989e-08</v>
+        <v>2.443920853645994e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>2.443920853645989e-08</v>
+        <v>2.443920853645993e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>2.532913541634547e-08</v>
+        <v>2.532913541634533e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>2.147365249575184e-08</v>
+        <v>2.147365249575182e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>2.439765866187741e-08</v>
+        <v>2.439765866187744e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>6.272819191920652e-08</v>
+        <v>6.272819191920644e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>2.347268543870724e-08</v>
+        <v>2.347268543870703e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>2.095033416408601e-08</v>
+        <v>2.095033416408599e-08</v>
       </c>
     </row>
     <row r="8">
@@ -5111,37 +5111,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.524468268688468e-08</v>
+        <v>2.524468268688421e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>3.605757420378747e-08</v>
+        <v>3.605757420378754e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>3.281861814077602e-08</v>
+        <v>3.281861814077585e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>3.413908656582466e-08</v>
+        <v>3.41390865658247e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>2.926413965578615e-08</v>
+        <v>2.926413965578613e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>3.694773531129793e-08</v>
+        <v>3.694773531129762e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>3.309225239073297e-08</v>
+        <v>3.309225239073244e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>3.601625855682982e-08</v>
+        <v>3.601625855682984e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>7.434816728189488e-08</v>
+        <v>7.434816728189456e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>2.796234453650027e-08</v>
+        <v>2.796234453649991e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>3.987990379803698e-08</v>
+        <v>3.987990379803703e-08</v>
       </c>
     </row>
     <row r="9">
@@ -5151,37 +5151,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5.521224332253763e-08</v>
+        <v>5.521224332253723e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>7.031891965204885e-08</v>
+        <v>7.031891965204891e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>6.566996367962926e-08</v>
+        <v>6.566996367962908e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>8.339809998304938e-08</v>
+        <v>8.339809998304942e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>7.031891633587652e-08</v>
+        <v>7.031891633587658e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>7.125035045257866e-08</v>
+        <v>7.125035045257847e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>6.739486753198529e-08</v>
+        <v>6.739486753198495e-08</v>
       </c>
       <c r="I9" t="n">
         <v>7.031887369811068e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>1.0864940695544e-07</v>
+        <v>1.086494069554396e-07</v>
       </c>
       <c r="K9" t="n">
-        <v>6.282694606979541e-08</v>
+        <v>6.282694606979512e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>6.687154920031941e-08</v>
+        <v>6.687154920031919e-08</v>
       </c>
     </row>
   </sheetData>
@@ -5267,37 +5267,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.918588630702578e-07</v>
+        <v>1.918588630702579e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>3.748251987761085e-07</v>
+        <v>3.748251987761086e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>1.91920202837977e-07</v>
+        <v>1.919202028379771e-07</v>
       </c>
       <c r="E2" t="n">
         <v>3.983372709636941e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>2.840754324717537e-07</v>
+        <v>2.840754324717538e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>1.922782153595289e-07</v>
+        <v>1.92278215359529e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>1.92045888450927e-07</v>
+        <v>1.920458884509272e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>1.922429581353663e-07</v>
+        <v>1.922429581353664e-07</v>
       </c>
       <c r="J2" t="n">
         <v>3.058997554443459e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>1.697547201673176e-07</v>
+        <v>1.697547201673175e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>1.919666575002016e-07</v>
+        <v>1.919666575002018e-07</v>
       </c>
     </row>
     <row r="3">
@@ -5307,37 +5307,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.951772611319074e-07</v>
+        <v>1.951772611319076e-07</v>
       </c>
       <c r="C3" t="n">
-        <v>4.993015429773913e-07</v>
+        <v>4.99301542977392e-07</v>
       </c>
       <c r="D3" t="n">
         <v>1.956140026781688e-07</v>
       </c>
       <c r="E3" t="n">
-        <v>5.380987315660784e-07</v>
+        <v>5.38098731566079e-07</v>
       </c>
       <c r="F3" t="n">
         <v>3.49488667303666e-07</v>
       </c>
       <c r="G3" t="n">
-        <v>1.981644074155127e-07</v>
+        <v>1.981644074155128e-07</v>
       </c>
       <c r="H3" t="n">
-        <v>1.965984938340256e-07</v>
+        <v>1.965984938340258e-07</v>
       </c>
       <c r="I3" t="n">
         <v>1.97902783494829e-07</v>
       </c>
       <c r="J3" t="n">
-        <v>4.027273791567924e-07</v>
+        <v>4.027273791567922e-07</v>
       </c>
       <c r="K3" t="n">
         <v>1.605782830388808e-07</v>
       </c>
       <c r="L3" t="n">
-        <v>1.960077454061006e-07</v>
+        <v>1.960077454061009e-07</v>
       </c>
     </row>
     <row r="4">
@@ -5347,37 +5347,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.374158269643729e-08</v>
+        <v>1.374158269643737e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>1.828487936770513e-08</v>
+        <v>1.828487936770512e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>1.443444359051178e-08</v>
+        <v>1.44344435905118e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>1.847564192667507e-08</v>
+        <v>1.847564192667504e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>1.847564192667507e-08</v>
+        <v>1.847564192667504e-08</v>
       </c>
       <c r="G4" t="n">
         <v>1.856068437330653e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>1.599110047386016e-08</v>
+        <v>1.599110047386012e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>1.862837844289903e-08</v>
+        <v>1.862837844289902e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>5.346616663260131e-08</v>
+        <v>5.346616663260133e-08</v>
       </c>
       <c r="K4" t="n">
         <v>1.766003253601468e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>1.504638225603205e-08</v>
+        <v>1.504638225603201e-08</v>
       </c>
     </row>
     <row r="5">
@@ -5387,37 +5387,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.820430022967539e-08</v>
+        <v>3.82043002296756e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>1.073071686245918e-07</v>
+        <v>1.073071686245921e-07</v>
       </c>
       <c r="D5" t="n">
-        <v>4.991795527766089e-08</v>
+        <v>4.991795527766139e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>1.073071759071374e-07</v>
+        <v>1.073071759071375e-07</v>
       </c>
       <c r="F5" t="n">
-        <v>1.073071759071374e-07</v>
+        <v>1.073071759071375e-07</v>
       </c>
       <c r="G5" t="n">
-        <v>1.190628318378231e-07</v>
+        <v>1.190628318378234e-07</v>
       </c>
       <c r="H5" t="n">
-        <v>8.42090263376256e-08</v>
+        <v>8.420902633762536e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>1.073073585090704e-07</v>
+        <v>1.073073585090707e-07</v>
       </c>
       <c r="J5" t="n">
         <v>7.459544564182325e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>9.958445093705999e-08</v>
+        <v>9.958445093705961e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>1.836976007801314e-07</v>
+        <v>1.836976007801311e-07</v>
       </c>
     </row>
     <row r="6">
@@ -5427,37 +5427,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.626714940241645e-08</v>
+        <v>1.626714940241647e-08</v>
       </c>
       <c r="C6" t="n">
         <v>2.103030437314677e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>1.670244021358173e-08</v>
+        <v>1.67024402135816e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>2.078869903232409e-08</v>
+        <v>2.078869903232408e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>2.112437413833638e-08</v>
+        <v>2.112437413833636e-08</v>
       </c>
       <c r="G6" t="n">
         <v>2.108625107928558e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>2.389285259052648e-08</v>
+        <v>2.389285259052649e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>2.532263962818177e-08</v>
+        <v>2.532263962818178e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>5.641023841467668e-08</v>
+        <v>5.641023841467671e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>2.01540777980875e-08</v>
+        <v>2.015407779808742e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>1.755568986867521e-08</v>
+        <v>1.755568986867509e-08</v>
       </c>
     </row>
     <row r="7">
@@ -5467,25 +5467,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.687157158682708e-08</v>
+        <v>1.687157158682704e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>2.175817744881014e-08</v>
+        <v>2.175817744881012e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>1.756428750887998e-08</v>
+        <v>1.756428750888e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>2.17136141767826e-08</v>
+        <v>2.171361417678259e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>2.17136141767826e-08</v>
+        <v>2.171361417678259e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>2.169067326369626e-08</v>
+        <v>2.169067326369628e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>1.912108936424994e-08</v>
+        <v>1.912108936424981e-08</v>
       </c>
       <c r="I7" t="n">
         <v>2.175836733328875e-08</v>
@@ -5494,10 +5494,10 @@
         <v>5.659615552299106e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>2.079002142640444e-08</v>
+        <v>2.079002142640436e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>1.817637114642181e-08</v>
+        <v>1.817637114642179e-08</v>
       </c>
     </row>
     <row r="8">
@@ -5507,37 +5507,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.066936451142855e-08</v>
+        <v>2.066936451142856e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>3.114948040232864e-08</v>
+        <v>3.114948040232856e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>2.816564410650695e-08</v>
+        <v>2.816564410650682e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>2.96128520720909e-08</v>
+        <v>2.961285207209086e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>2.570809552303282e-08</v>
+        <v>2.570809552303279e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>3.112343698708002e-08</v>
+        <v>3.112343698708005e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>2.855385308767529e-08</v>
+        <v>2.855385308767518e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>3.119113105667254e-08</v>
+        <v>3.119113105667248e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>6.603002666239218e-08</v>
+        <v>6.603002666239224e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>2.448314187685076e-08</v>
+        <v>2.448314187685069e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>3.349533304184536e-08</v>
+        <v>3.349533304184528e-08</v>
       </c>
     </row>
     <row r="9">
@@ -5547,37 +5547,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.496150897141259e-08</v>
+        <v>4.496150897141253e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>5.901886858550637e-08</v>
+        <v>5.90188685855063e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>5.482512682400856e-08</v>
+        <v>5.482512682400863e-08</v>
       </c>
       <c r="E9" t="n">
         <v>6.960173124028228e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>5.90188735441786e-08</v>
+        <v>5.901887354417861e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>5.895136440039249e-08</v>
+        <v>5.895136440039257e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>5.638178050094604e-08</v>
+        <v>5.638178050094607e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>5.901905846998498e-08</v>
+        <v>5.901905846998497e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>9.385684665968722e-08</v>
+        <v>9.38568466596873e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>5.273714317140203e-08</v>
+        <v>5.273714317140194e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>5.543706228311797e-08</v>
+        <v>5.543706228311802e-08</v>
       </c>
     </row>
   </sheetData>
@@ -5663,37 +5663,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.914966114836195e-07</v>
+        <v>1.9149661148362e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>3.74177654492164e-07</v>
+        <v>3.741776544921644e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>1.915616888428957e-07</v>
+        <v>1.915616888428964e-07</v>
       </c>
       <c r="E2" t="n">
         <v>3.975711348271355e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>2.836361045269862e-07</v>
+        <v>2.836361045269868e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>1.918644722208201e-07</v>
+        <v>1.918644722208208e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>1.91629287058484e-07</v>
+        <v>1.916292870584845e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>1.918942297608754e-07</v>
+        <v>1.918942297608755e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>3.043717829441252e-07</v>
+        <v>3.043717829441251e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>1.686148678852294e-07</v>
+        <v>1.686148678852295e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>1.915164447454473e-07</v>
+        <v>1.915164447454474e-07</v>
       </c>
     </row>
     <row r="3">
@@ -5703,37 +5703,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.952332490482605e-07</v>
+        <v>1.952332490482611e-07</v>
       </c>
       <c r="C3" t="n">
-        <v>4.98957618491252e-07</v>
+        <v>4.989576184912525e-07</v>
       </c>
       <c r="D3" t="n">
-        <v>1.956959568273047e-07</v>
+        <v>1.956959568273046e-07</v>
       </c>
       <c r="E3" t="n">
-        <v>5.375598047579617e-07</v>
+        <v>5.375598047579619e-07</v>
       </c>
       <c r="F3" t="n">
-        <v>3.494891990267627e-07</v>
+        <v>3.494891990267628e-07</v>
       </c>
       <c r="G3" t="n">
-        <v>1.978510091790442e-07</v>
+        <v>1.978510091790439e-07</v>
       </c>
       <c r="H3" t="n">
-        <v>1.962629382803459e-07</v>
+        <v>1.962629382803458e-07</v>
       </c>
       <c r="I3" t="n">
-        <v>1.980527944075666e-07</v>
+        <v>1.980527944075658e-07</v>
       </c>
       <c r="J3" t="n">
-        <v>3.989048938080803e-07</v>
+        <v>3.989048938080808e-07</v>
       </c>
       <c r="K3" t="n">
-        <v>1.58376236288907e-07</v>
+        <v>1.583762362889075e-07</v>
       </c>
       <c r="L3" t="n">
-        <v>1.954376381079675e-07</v>
+        <v>1.954376381079681e-07</v>
       </c>
     </row>
     <row r="4">
@@ -5743,37 +5743,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.366528419841203e-08</v>
+        <v>1.366528419841272e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>1.799937432643047e-08</v>
+        <v>1.799937432643028e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>1.440036290850014e-08</v>
+        <v>1.440036290850021e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>1.820295358174088e-08</v>
+        <v>1.820295358174083e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>1.820295358174084e-08</v>
+        <v>1.820295358174093e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>1.790266803543598e-08</v>
+        <v>1.790266803543568e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>1.529705360346021e-08</v>
+        <v>1.529705360346074e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>1.870436627827181e-08</v>
+        <v>1.870436627827197e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>4.93588994489519e-08</v>
+        <v>4.935889944895235e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>1.557173619390437e-08</v>
+        <v>1.557173619390439e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>1.39804228789905e-08</v>
+        <v>1.398042287899085e-08</v>
       </c>
     </row>
     <row r="5">
@@ -5783,37 +5783,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.623191256185469e-08</v>
+        <v>4.62319125618549e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>1.167439427493324e-07</v>
+        <v>1.167439427493332e-07</v>
       </c>
       <c r="D5" t="n">
-        <v>5.832476317813249e-08</v>
+        <v>5.832476317813348e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>1.167439609202019e-07</v>
+        <v>1.167439609202026e-07</v>
       </c>
       <c r="F5" t="n">
-        <v>1.167439609202019e-07</v>
+        <v>1.167439609202026e-07</v>
       </c>
       <c r="G5" t="n">
-        <v>1.158248196032246e-07</v>
+        <v>1.158248196032242e-07</v>
       </c>
       <c r="H5" t="n">
-        <v>8.050303926553893e-08</v>
+        <v>8.050303926554025e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>1.167443053489753e-07</v>
+        <v>1.167443053489764e-07</v>
       </c>
       <c r="J5" t="n">
-        <v>6.845853505063394e-07</v>
+        <v>6.845853505063423e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>7.347438729050954e-08</v>
+        <v>7.347438729050986e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>6.554147010450556e-08</v>
+        <v>6.554147010450547e-08</v>
       </c>
     </row>
     <row r="6">
@@ -5823,37 +5823,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.605576579448227e-08</v>
+        <v>1.605576579448199e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>2.095491612830419e-08</v>
+        <v>2.095491612830475e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>1.657960649498203e-08</v>
+        <v>1.657960649498242e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>2.074599917876236e-08</v>
+        <v>2.074599917876263e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>2.106728053867919e-08</v>
+        <v>2.10672805386786e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>2.420798956308722e-08</v>
+        <v>2.420798956308849e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>2.278529851238236e-08</v>
+        <v>2.278529851238271e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>2.109484787434246e-08</v>
+        <v>2.109484787434194e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>5.636842160663734e-08</v>
+        <v>5.636842160663838e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>1.790605002035115e-08</v>
+        <v>1.790605002035107e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>1.637719191290374e-08</v>
+        <v>1.637719191290273e-08</v>
       </c>
     </row>
     <row r="7">
@@ -5863,37 +5863,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.656509380863429e-08</v>
+        <v>1.65650938086356e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>2.160381328885088e-08</v>
+        <v>2.160381328885224e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>1.730010145172127e-08</v>
+        <v>1.73001014517235e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>2.145494393788295e-08</v>
+        <v>2.145494393788429e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>2.14549439378831e-08</v>
+        <v>2.145494393788429e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>2.080247764565875e-08</v>
+        <v>2.080247764565916e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>1.819686321368288e-08</v>
+        <v>1.819686321368373e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>2.160417588849469e-08</v>
+        <v>2.160417588849496e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>5.225870905917489e-08</v>
+        <v>5.225870905917519e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>1.847154580412705e-08</v>
+        <v>1.84715458041275e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>1.688023248921331e-08</v>
+        <v>1.688023248921375e-08</v>
       </c>
     </row>
     <row r="8">
@@ -5903,37 +5903,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.017581562625355e-08</v>
+        <v>2.01758156262543e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>3.031847714561071e-08</v>
+        <v>3.031847714561096e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>2.724388958222729e-08</v>
+        <v>2.724388958222783e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>2.889905803150689e-08</v>
+        <v>2.889905803150729e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>2.529204622138734e-08</v>
+        <v>2.52920462213872e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>2.965853932066212e-08</v>
+        <v>2.965853932066323e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>2.705292488872852e-08</v>
+        <v>2.705292488873044e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>3.046023756349794e-08</v>
+        <v>3.046023756349868e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>6.111580157900309e-08</v>
+        <v>6.111580157900414e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>2.198483274213345e-08</v>
+        <v>2.198483274213413e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>3.121549023988709e-08</v>
+        <v>3.121549023988839e-08</v>
       </c>
     </row>
     <row r="9">
@@ -5943,37 +5943,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.183238338185845e-08</v>
+        <v>4.183238338186209e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>5.514338631093522e-08</v>
+        <v>5.514338631093697e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>5.083974867976911e-08</v>
+        <v>5.083974867977221e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>6.468944446238893e-08</v>
+        <v>6.468944446239134e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>5.514340243683098e-08</v>
+        <v>5.51434024368367e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>5.434205066774145e-08</v>
+        <v>5.434205066774402e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>5.173643623576659e-08</v>
+        <v>5.173643623577015e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>5.514374891057922e-08</v>
+        <v>5.514374891058404e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>8.579828208125659e-08</v>
+        <v>8.579828208126172e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>4.721812662841111e-08</v>
+        <v>4.721812662841528e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>5.041980551129633e-08</v>
+        <v>5.041980551130149e-08</v>
       </c>
     </row>
   </sheetData>
@@ -6059,7 +6059,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.919773793434669e-07</v>
+        <v>1.91977379343467e-07</v>
       </c>
       <c r="C2" t="n">
         <v>3.745084814093198e-07</v>
@@ -6068,10 +6068,10 @@
         <v>1.918856452548192e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>3.98030506051677e-07</v>
+        <v>3.980305060516769e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>2.837334196166632e-07</v>
+        <v>2.837334196166631e-07</v>
       </c>
       <c r="G2" t="n">
         <v>1.92186201511806e-07</v>
@@ -6080,16 +6080,16 @@
         <v>1.919245596343395e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>1.919986004204074e-07</v>
+        <v>1.919986004204073e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>3.056997321975581e-07</v>
+        <v>3.056997321975582e-07</v>
       </c>
       <c r="K2" t="n">
         <v>1.69644975437937e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>1.919992299173016e-07</v>
+        <v>1.919992299173015e-07</v>
       </c>
     </row>
     <row r="3">
@@ -6099,34 +6099,34 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.964389586261343e-07</v>
+        <v>1.964389586261341e-07</v>
       </c>
       <c r="C3" t="n">
-        <v>4.978697944408165e-07</v>
+        <v>4.978697944408164e-07</v>
       </c>
       <c r="D3" t="n">
-        <v>1.957875367121539e-07</v>
+        <v>1.957875367121538e-07</v>
       </c>
       <c r="E3" t="n">
-        <v>5.366828976379185e-07</v>
+        <v>5.366828976379182e-07</v>
       </c>
       <c r="F3" t="n">
-        <v>3.480146473761675e-07</v>
+        <v>3.480146473761673e-07</v>
       </c>
       <c r="G3" t="n">
-        <v>1.979238708881271e-07</v>
+        <v>1.97923870888127e-07</v>
       </c>
       <c r="H3" t="n">
-        <v>1.961498448117152e-07</v>
+        <v>1.961498448117151e-07</v>
       </c>
       <c r="I3" t="n">
-        <v>1.965899606271674e-07</v>
+        <v>1.965899606271673e-07</v>
       </c>
       <c r="J3" t="n">
-        <v>4.018082592863404e-07</v>
+        <v>4.01808259286341e-07</v>
       </c>
       <c r="K3" t="n">
-        <v>1.605631499389061e-07</v>
+        <v>1.605631499389063e-07</v>
       </c>
       <c r="L3" t="n">
         <v>1.966506620618475e-07</v>
@@ -6139,13 +6139,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.589597957816956e-08</v>
+        <v>1.589597957816953e-08</v>
       </c>
       <c r="C4" t="n">
         <v>1.609107436794786e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>1.485980084712673e-08</v>
+        <v>1.485980084712675e-08</v>
       </c>
       <c r="E4" t="n">
         <v>1.632648352398401e-08</v>
@@ -6154,22 +6154,22 @@
         <v>1.632648352398401e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>1.833589608359004e-08</v>
+        <v>1.833589608359006e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>1.543896681023788e-08</v>
+        <v>1.543896681023789e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>1.667637240220305e-08</v>
+        <v>1.667637240220306e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>5.220286895072918e-08</v>
+        <v>5.220286895072925e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>1.794988071935314e-08</v>
+        <v>1.794988071935313e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>1.620980044986484e-08</v>
+        <v>1.620980044986485e-08</v>
       </c>
     </row>
     <row r="5">
@@ -6179,37 +6179,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7.543752510861097e-08</v>
+        <v>7.543752510861007e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>8.025824918766452e-08</v>
+        <v>8.025824918766459e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>5.767465784502618e-08</v>
+        <v>5.767465784502607e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>8.025826183362333e-08</v>
+        <v>8.025826183362337e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>8.025826183362338e-08</v>
+        <v>8.025826183362337e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>1.170798928671162e-07</v>
+        <v>1.170798928671163e-07</v>
       </c>
       <c r="H5" t="n">
-        <v>7.347581132969072e-08</v>
+        <v>7.347581132969067e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>8.025804732937002e-08</v>
+        <v>8.025804732937009e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>7.702457192160962e-07</v>
+        <v>7.702457192160974e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>1.08879560273059e-07</v>
+        <v>1.088795602730586e-07</v>
       </c>
       <c r="L5" t="n">
-        <v>9.213148245173159e-08</v>
+        <v>9.213148245173157e-08</v>
       </c>
     </row>
     <row r="6">
@@ -6219,37 +6219,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.286240574322646e-08</v>
+        <v>2.286240574322642e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>1.89994801771984e-08</v>
+        <v>1.899948017719846e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>2.221909476091599e-08</v>
+        <v>2.221909476091601e-08</v>
       </c>
       <c r="E6" t="n">
         <v>1.875606545013872e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>1.915932466709679e-08</v>
+        <v>1.91593246670968e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>2.5302322248647e-08</v>
+        <v>2.530232224864697e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>1.795373850932202e-08</v>
+        <v>1.795373850932204e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>2.364279856725995e-08</v>
+        <v>2.364279856725996e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>6.0040347736947e-08</v>
+        <v>6.004034773694712e-08</v>
       </c>
       <c r="K6" t="n">
         <v>2.044519848819869e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>1.873665094011416e-08</v>
+        <v>1.873665094011419e-08</v>
       </c>
     </row>
     <row r="7">
@@ -6259,37 +6259,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.918742909745421e-08</v>
+        <v>1.918742909745422e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>1.996802377978229e-08</v>
+        <v>1.99680237797823e-08</v>
       </c>
       <c r="D7" t="n">
         <v>1.815113453683909e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>1.987403188803685e-08</v>
+        <v>1.987403188803687e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>1.987403188803686e-08</v>
+        <v>1.987403188803687e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>2.162734560287474e-08</v>
+        <v>2.162734560287475e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>1.873041632952257e-08</v>
+        <v>1.873041632952258e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>1.996782192148774e-08</v>
+        <v>1.996782192148775e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>5.549431847001385e-08</v>
+        <v>5.549431847001394e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>2.124133023863777e-08</v>
+        <v>2.124133023863782e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>1.950124996914953e-08</v>
+        <v>1.950124996914955e-08</v>
       </c>
     </row>
     <row r="8">
@@ -6299,37 +6299,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.333638190360934e-08</v>
+        <v>2.333638190360933e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>3.013185681709436e-08</v>
+        <v>3.013185681709439e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>2.966937762931211e-08</v>
+        <v>2.966937762931213e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>2.847210142018849e-08</v>
+        <v>2.84721014201885e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>2.425445353921418e-08</v>
+        <v>2.425445353921421e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>3.187985967732085e-08</v>
+        <v>3.187985967732087e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>2.898293040399775e-08</v>
+        <v>2.898293040399782e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>3.022033599593384e-08</v>
+        <v>3.022033599593385e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>6.574803204964958e-08</v>
+        <v>6.574803204964973e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>2.527690626216494e-08</v>
+        <v>2.527690626216491e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>3.61294441419974e-08</v>
+        <v>3.612944414199748e-08</v>
       </c>
     </row>
     <row r="9">
@@ -6339,37 +6339,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5.290305196045484e-08</v>
+        <v>5.290305196045486e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>6.451705172952393e-08</v>
+        <v>6.45170517295239e-08</v>
       </c>
       <c r="D9" t="n">
         <v>6.270028268764736e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>7.70185857914712e-08</v>
+        <v>7.701858579147115e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>6.451706253503951e-08</v>
+        <v>6.451706253503954e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>6.617637355261639e-08</v>
+        <v>6.617637355261638e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>6.327944427926422e-08</v>
+        <v>6.327944427926417e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>6.45168498712294e-08</v>
+        <v>6.451684987122936e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>1.000433464197556e-07</v>
+        <v>1.000433464197555e-07</v>
       </c>
       <c r="K9" t="n">
-        <v>5.95134425736897e-08</v>
+        <v>5.951344257368968e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>6.405027791889117e-08</v>
+        <v>6.405027791889113e-08</v>
       </c>
     </row>
   </sheetData>
@@ -6455,37 +6455,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.912777437733898e-07</v>
+        <v>1.912777437733895e-07</v>
       </c>
       <c r="C2" t="n">
         <v>3.736567669240318e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>1.91661434860259e-07</v>
+        <v>1.916614348602589e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>3.969715511254349e-07</v>
+        <v>3.969715511254348e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>2.832668728993877e-07</v>
+        <v>2.832668728993881e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>1.918069311934946e-07</v>
+        <v>1.918069311934945e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>1.91410794754135e-07</v>
+        <v>1.914107947541349e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>1.916349236056892e-07</v>
+        <v>1.916349236056891e-07</v>
       </c>
       <c r="J2" t="n">
         <v>3.026281886751931e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>1.684279957211196e-07</v>
+        <v>1.684279957211195e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>1.912224830804265e-07</v>
+        <v>1.912224830804264e-07</v>
       </c>
     </row>
     <row r="3">
@@ -6495,37 +6495,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.945915728110337e-07</v>
+        <v>1.945915728110336e-07</v>
       </c>
       <c r="C3" t="n">
         <v>4.975984813756491e-07</v>
       </c>
       <c r="D3" t="n">
-        <v>1.973068880755296e-07</v>
+        <v>1.973068880755294e-07</v>
       </c>
       <c r="E3" t="n">
-        <v>5.360699427839806e-07</v>
+        <v>5.360699427839811e-07</v>
       </c>
       <c r="F3" t="n">
-        <v>3.483795785150826e-07</v>
+        <v>3.483795785150824e-07</v>
       </c>
       <c r="G3" t="n">
-        <v>1.983462486710631e-07</v>
+        <v>1.983462486710632e-07</v>
       </c>
       <c r="H3" t="n">
         <v>1.956284242213648e-07</v>
       </c>
       <c r="I3" t="n">
-        <v>1.971246423575195e-07</v>
+        <v>1.971246423575193e-07</v>
       </c>
       <c r="J3" t="n">
-        <v>3.908318952392442e-07</v>
+        <v>3.908318952392438e-07</v>
       </c>
       <c r="K3" t="n">
         <v>1.583525552266671e-07</v>
       </c>
       <c r="L3" t="n">
-        <v>1.942747578396759e-07</v>
+        <v>1.942747578396762e-07</v>
       </c>
     </row>
     <row r="4">
@@ -6535,37 +6535,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.26827295530352e-08</v>
+        <v>1.268272955303524e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>1.672629932387244e-08</v>
+        <v>1.672629932387243e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>1.701669688584359e-08</v>
+        <v>1.701669688584362e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>1.690640375336965e-08</v>
+        <v>1.690640375336963e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>1.690640375336965e-08</v>
+        <v>1.690640375336963e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>1.874121796619516e-08</v>
+        <v>1.874121796619517e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>1.43428911306199e-08</v>
+        <v>1.434289113061991e-08</v>
       </c>
       <c r="I4" t="n">
         <v>1.725691474474564e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>3.83838892595776e-08</v>
+        <v>3.838388925957768e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>1.575409486637429e-08</v>
+        <v>1.575409486637433e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>1.219000414248851e-08</v>
+        <v>1.219000414248852e-08</v>
       </c>
     </row>
     <row r="5">
@@ -6575,37 +6575,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.359883079207523e-08</v>
+        <v>3.359883079207529e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>9.713112212676911e-08</v>
+        <v>9.71311221267691e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>9.827749919364368e-08</v>
+        <v>9.827749919364364e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>9.713113443678235e-08</v>
+        <v>9.713113443678226e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>9.713113443678235e-08</v>
+        <v>9.713113443678226e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>1.279159090571046e-07</v>
+        <v>1.279159090571071e-07</v>
       </c>
       <c r="H5" t="n">
-        <v>6.389504005948805e-08</v>
+        <v>6.389504005948808e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>9.713096060184878e-08</v>
+        <v>9.713096060184875e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>4.636058510759399e-07</v>
+        <v>4.636058510759395e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>8.111594695691894e-08</v>
+        <v>8.111594695691902e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>1.017826668013008e-07</v>
+        <v>1.01782666801301e-07</v>
       </c>
     </row>
     <row r="6">
@@ -6615,37 +6615,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.850248042543253e-08</v>
+        <v>1.850248042543257e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>1.912086532872279e-08</v>
+        <v>1.912086532872274e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>1.891860349311789e-08</v>
+        <v>1.891860349311791e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>1.895277692385186e-08</v>
+        <v>1.895277692385185e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>1.924894659534743e-08</v>
+        <v>1.924894659534741e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>2.456096883859241e-08</v>
+        <v>2.456096883859248e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>2.118973209106593e-08</v>
+        <v>2.118973209106596e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>2.307666561714297e-08</v>
+        <v>2.307666561714296e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>4.073311201300757e-08</v>
+        <v>4.073311201300765e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>1.763580846471454e-08</v>
+        <v>1.763580846471457e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>1.421177837165623e-08</v>
+        <v>1.421177837165624e-08</v>
       </c>
     </row>
     <row r="7">
@@ -6655,37 +6655,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.546212816340029e-08</v>
+        <v>1.546212816340033e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>2.003647488003101e-08</v>
+        <v>2.0036474880031e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>1.97959903975739e-08</v>
+        <v>1.979599039757391e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>1.993731643269418e-08</v>
+        <v>1.993731643269416e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>1.993731643269418e-08</v>
+        <v>1.993731643269416e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>2.152061657656027e-08</v>
+        <v>2.152061657656023e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>1.712228974098497e-08</v>
+        <v>1.712228974098499e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>2.003631335511073e-08</v>
+        <v>2.003631335511072e-08</v>
       </c>
       <c r="J7" t="n">
         <v>4.116328786994273e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>1.853349347673938e-08</v>
+        <v>1.853349347673941e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>1.496940275285358e-08</v>
+        <v>1.496940275285359e-08</v>
       </c>
     </row>
     <row r="8">
@@ -6695,37 +6695,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.887656097265055e-08</v>
+        <v>1.887656097265052e-08</v>
       </c>
       <c r="C8" t="n">
         <v>2.831480478597736e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>2.919631618430827e-08</v>
+        <v>2.919631618430825e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>2.696897299304373e-08</v>
+        <v>2.696897299304371e-08</v>
       </c>
       <c r="F8" t="n">
         <v>2.354897597580753e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>2.989281273779429e-08</v>
+        <v>2.989281273779431e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>2.54944859022162e-08</v>
+        <v>2.549448590221625e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>2.840850951634479e-08</v>
+        <v>2.840850951634476e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>4.953645836082499e-08</v>
+        <v>4.953645836082509e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>2.185583328740688e-08</v>
+        <v>2.185583328740691e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>2.852039728488282e-08</v>
+        <v>2.852039728488284e-08</v>
       </c>
     </row>
     <row r="9">
@@ -6735,34 +6735,34 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.374246896387412e-08</v>
+        <v>4.374246896387406e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>5.735148846953679e-08</v>
+        <v>5.735148846953672e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>5.711111352281388e-08</v>
+        <v>5.711111352281387e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>6.777732400023132e-08</v>
+        <v>6.777732400023126e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>5.735149948123275e-08</v>
+        <v>5.735149948123273e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>5.883563016606596e-08</v>
+        <v>5.883563016606598e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>5.443730333049076e-08</v>
+        <v>5.443730333049072e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>5.735132694461653e-08</v>
+        <v>5.735132694461645e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>7.847830145944851e-08</v>
+        <v>7.847830145944847e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>5.061378403660822e-08</v>
+        <v>5.061378403660817e-08</v>
       </c>
       <c r="L9" t="n">
         <v>5.228441634235936e-08</v>
@@ -6851,37 +6851,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.909391947227745e-07</v>
+        <v>1.909391947227746e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>3.733315829918805e-07</v>
+        <v>3.733315829918807e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>1.911825686157708e-07</v>
+        <v>1.91182568615771e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>3.965543667589736e-07</v>
+        <v>3.96554366758974e-07</v>
       </c>
       <c r="F2" t="n">
         <v>2.831082688524234e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>1.913737663286738e-07</v>
+        <v>1.91373766328674e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>1.911143701736925e-07</v>
+        <v>1.911143701736923e-07</v>
       </c>
       <c r="I2" t="n">
         <v>1.914308565809445e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>3.012744624096608e-07</v>
+        <v>3.012744624096609e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>1.677356636381502e-07</v>
+        <v>1.677356636381501e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>1.909485949383253e-07</v>
+        <v>1.909485949383254e-07</v>
       </c>
     </row>
     <row r="3">
@@ -6891,37 +6891,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.943875642151889e-07</v>
+        <v>1.943875642151891e-07</v>
       </c>
       <c r="C3" t="n">
-        <v>4.981490765300184e-07</v>
+        <v>4.981490765300186e-07</v>
       </c>
       <c r="D3" t="n">
-        <v>1.961138983990236e-07</v>
+        <v>1.961138983990235e-07</v>
       </c>
       <c r="E3" t="n">
-        <v>5.364709736634322e-07</v>
+        <v>5.364709736634326e-07</v>
       </c>
       <c r="F3" t="n">
         <v>3.492074483504431e-07</v>
       </c>
       <c r="G3" t="n">
-        <v>1.974755834464691e-07</v>
+        <v>1.974755834464692e-07</v>
       </c>
       <c r="H3" t="n">
-        <v>1.957148891917055e-07</v>
+        <v>1.957148891917057e-07</v>
       </c>
       <c r="I3" t="n">
-        <v>1.978774495989065e-07</v>
+        <v>1.978774495989064e-07</v>
       </c>
       <c r="J3" t="n">
-        <v>3.863972497225459e-07</v>
+        <v>3.863972497225464e-07</v>
       </c>
       <c r="K3" t="n">
-        <v>1.569308260645899e-07</v>
+        <v>1.569308260645898e-07</v>
       </c>
       <c r="L3" t="n">
-        <v>1.945174297772253e-07</v>
+        <v>1.945174297772252e-07</v>
       </c>
     </row>
     <row r="4">
@@ -6931,37 +6931,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.251477235368979e-08</v>
+        <v>1.251477235368975e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>1.812871288188914e-08</v>
+        <v>1.812871288188946e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>1.526379243260778e-08</v>
+        <v>1.526379243260789e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>1.82917938477691e-08</v>
+        <v>1.829179384776923e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>1.829179384776911e-08</v>
+        <v>1.829179384776923e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>1.750596787193595e-08</v>
+        <v>1.750596787193609e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>1.462555137314431e-08</v>
+        <v>1.462555137314437e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>1.861761475764018e-08</v>
+        <v>1.861761475764026e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>3.290730259082879e-08</v>
+        <v>3.290730259082882e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>1.427313795553713e-08</v>
+        <v>1.427313795553717e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>1.272211884346991e-08</v>
+        <v>1.27221188434701e-08</v>
       </c>
     </row>
     <row r="5">
@@ -6971,37 +6971,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.527685649894523e-08</v>
+        <v>3.527685649894517e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>1.241358221186468e-07</v>
+        <v>1.241358221186471e-07</v>
       </c>
       <c r="D5" t="n">
-        <v>7.838523765287755e-08</v>
+        <v>7.838523765287808e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>1.241358338468912e-07</v>
+        <v>1.241358338468919e-07</v>
       </c>
       <c r="F5" t="n">
-        <v>1.241358338468912e-07</v>
+        <v>1.241358338468919e-07</v>
       </c>
       <c r="G5" t="n">
-        <v>1.151608272754177e-07</v>
+        <v>1.151608272754173e-07</v>
       </c>
       <c r="H5" t="n">
-        <v>7.536692603560499e-08</v>
+        <v>7.536692603560533e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>1.241362536484323e-07</v>
+        <v>1.241362536484337e-07</v>
       </c>
       <c r="J5" t="n">
-        <v>3.836098353950633e-07</v>
+        <v>3.836098353950638e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>6.164734639037219e-08</v>
+        <v>6.164734639037257e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>9.609086213653193e-08</v>
+        <v>9.609086213653234e-08</v>
       </c>
     </row>
     <row r="6">
@@ -7011,37 +7011,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.44003553228258e-08</v>
+        <v>1.44003553228254e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>2.044395600736661e-08</v>
+        <v>2.044395600736683e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>1.703504218152684e-08</v>
+        <v>1.703504218152679e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>2.029622042165101e-08</v>
+        <v>2.029622042165118e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>2.051004794762353e-08</v>
+        <v>2.051004794762376e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>1.939155084107199e-08</v>
+        <v>1.939155084107175e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>2.099687513008229e-08</v>
+        <v>2.099687513008248e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>2.050319772677613e-08</v>
+        <v>2.050319772677593e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>3.510429876631191e-08</v>
+        <v>3.510429876631235e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>1.60193449326517e-08</v>
+        <v>1.601934493265158e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>1.463787605107934e-08</v>
+        <v>1.463787605107952e-08</v>
       </c>
     </row>
     <row r="7">
@@ -7051,37 +7051,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.513974123370286e-08</v>
+        <v>1.513974123370383e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>2.124215210786753e-08</v>
+        <v>2.124215210786789e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>1.788865539516121e-08</v>
+        <v>1.788865539516171e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>2.114180762865351e-08</v>
+        <v>2.114180762865388e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>2.114180762865351e-08</v>
+        <v>2.114180762865388e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>2.013093675194972e-08</v>
+        <v>2.01309367519502e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>1.725052025315757e-08</v>
+        <v>1.725052025315845e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>2.124258363765424e-08</v>
+        <v>2.124258363765436e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>3.553227147084252e-08</v>
+        <v>3.553227147084292e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>1.689810683555125e-08</v>
+        <v>1.689810683555126e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>1.534708772348329e-08</v>
+        <v>1.534708772348419e-08</v>
       </c>
     </row>
     <row r="8">
@@ -7091,37 +7091,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.83264444602645e-08</v>
+        <v>1.832644446026431e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>2.892868929081337e-08</v>
+        <v>2.892868929081371e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>2.662315617870577e-08</v>
+        <v>2.66231561787064e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>2.768222567050161e-08</v>
+        <v>2.768222567050168e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>2.451471438104044e-08</v>
+        <v>2.451471438104069e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>2.791254759210846e-08</v>
+        <v>2.791254759210864e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>2.503213109329505e-08</v>
+        <v>2.50321310932949e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>2.902419447781236e-08</v>
+        <v>2.902419447781277e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>4.331478533157015e-08</v>
+        <v>4.331478533157064e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>1.999945729494281e-08</v>
+        <v>1.999945729494265e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>2.792846377651219e-08</v>
+        <v>2.792846377651208e-08</v>
       </c>
     </row>
     <row r="9">
@@ -7131,37 +7131,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.046233505341352e-08</v>
+        <v>4.046233505341444e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>5.468648526993301e-08</v>
+        <v>5.468648526993629e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>5.133309793682434e-08</v>
+        <v>5.133309793682616e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>6.405881356091376e-08</v>
+        <v>6.405881356091579e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>5.468649575069923e-08</v>
+        <v>5.468649575070045e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>5.357526991401843e-08</v>
+        <v>5.357526991401861e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>5.069485341522774e-08</v>
+        <v>5.069485341522684e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>5.46869167997231e-08</v>
+        <v>5.468691679972279e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>6.89766046329132e-08</v>
+        <v>6.897660463291137e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>4.544575476219425e-08</v>
+        <v>4.544575476219451e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>4.879142088555118e-08</v>
+        <v>4.879142088555261e-08</v>
       </c>
     </row>
   </sheetData>
@@ -7247,37 +7247,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.927530967857356e-07</v>
+        <v>1.927530967857333e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>3.757533763980267e-07</v>
+        <v>3.757533763980264e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>1.92510034845599e-07</v>
+        <v>1.925100348455967e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>3.993518325377969e-07</v>
+        <v>3.993518325377943e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>2.848331309158929e-07</v>
+        <v>2.848331309158881e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>1.9298680123738e-07</v>
+        <v>1.929868012373776e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>1.926774755422722e-07</v>
+        <v>1.926774755422719e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>1.929093911423036e-07</v>
+        <v>1.929093911423011e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>3.064464065658269e-07</v>
+        <v>3.06446406565825e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>1.708215516858771e-07</v>
+        <v>1.70821551685877e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>1.926039023375312e-07</v>
+        <v>1.926039023375308e-07</v>
       </c>
     </row>
     <row r="3">
@@ -7287,34 +7287,34 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.976857633983942e-07</v>
+        <v>1.976857633983901e-07</v>
       </c>
       <c r="C3" t="n">
         <v>5.006265064728068e-07</v>
       </c>
       <c r="D3" t="n">
-        <v>1.959602513049703e-07</v>
+        <v>1.959602513049662e-07</v>
       </c>
       <c r="E3" t="n">
-        <v>5.395648490448598e-07</v>
+        <v>5.395648490448592e-07</v>
       </c>
       <c r="F3" t="n">
-        <v>3.505307801352795e-07</v>
+        <v>3.505307801352769e-07</v>
       </c>
       <c r="G3" t="n">
-        <v>1.993526303427659e-07</v>
+        <v>1.993526303427618e-07</v>
       </c>
       <c r="H3" t="n">
-        <v>1.972471145011023e-07</v>
+        <v>1.97247114501102e-07</v>
       </c>
       <c r="I3" t="n">
-        <v>1.987943248010047e-07</v>
+        <v>1.98794324801003e-07</v>
       </c>
       <c r="J3" t="n">
-        <v>3.996655138411394e-07</v>
+        <v>3.996655138411364e-07</v>
       </c>
       <c r="K3" t="n">
-        <v>1.620782483421499e-07</v>
+        <v>1.620782483421505e-07</v>
       </c>
       <c r="L3" t="n">
         <v>1.96702005698551e-07</v>
@@ -7327,37 +7327,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.801573295381419e-08</v>
+        <v>1.801573295381427e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>2.008213492822454e-08</v>
+        <v>2.008213492822443e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>1.527023652595558e-08</v>
+        <v>1.52702365259554e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>2.030218899448274e-08</v>
+        <v>2.030218899448276e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>2.030218899448265e-08</v>
+        <v>2.030218899448276e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>2.073789938831064e-08</v>
+        <v>2.073789938831078e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>1.731907552876885e-08</v>
+        <v>1.731907552876882e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>2.032973190317552e-08</v>
+        <v>2.032973190317554e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>4.743835250693656e-08</v>
+        <v>4.743835250693658e-08</v>
       </c>
       <c r="K4" t="n">
         <v>1.924415709985414e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>1.643608526476113e-08</v>
+        <v>1.643608526476124e-08</v>
       </c>
     </row>
     <row r="5">
@@ -7367,37 +7367,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9.603220706582137e-08</v>
+        <v>9.603220706582104e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>1.261129055186541e-07</v>
+        <v>1.261129055186535e-07</v>
       </c>
       <c r="D5" t="n">
-        <v>4.925562682547109e-08</v>
+        <v>4.925562682546644e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>1.26112909461918e-07</v>
+        <v>1.261129094619175e-07</v>
       </c>
       <c r="F5" t="n">
-        <v>1.26112909461918e-07</v>
+        <v>1.261129094619175e-07</v>
       </c>
       <c r="G5" t="n">
-        <v>1.454195626792257e-07</v>
+        <v>1.454195626792249e-07</v>
       </c>
       <c r="H5" t="n">
-        <v>9.146927311444606e-08</v>
+        <v>9.146927311444578e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>1.261129837209643e-07</v>
+        <v>1.261129837209638e-07</v>
       </c>
       <c r="J5" t="n">
-        <v>6.618852444833673e-07</v>
+        <v>6.618852444833666e-07</v>
       </c>
       <c r="K5" t="n">
         <v>1.180644794392861e-07</v>
       </c>
       <c r="L5" t="n">
-        <v>2.886189570088825e-07</v>
+        <v>2.886189570088831e-07</v>
       </c>
     </row>
     <row r="6">
@@ -7407,37 +7407,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.075959540537939e-08</v>
+        <v>2.075959540537919e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>2.298874599024428e-08</v>
+        <v>2.298874599024412e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>1.772119521649501e-08</v>
+        <v>1.772119521649474e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>2.270741564571039e-08</v>
+        <v>2.270741564571042e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>2.308567472136467e-08</v>
+        <v>2.30856747213646e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>2.840127223354246e-08</v>
+        <v>2.840127223354216e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>2.64384219840991e-08</v>
+        <v>2.643842198409899e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>2.79931047484071e-08</v>
+        <v>2.79931047484069e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>5.593844197833714e-08</v>
+        <v>5.593844197833668e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>2.195827034923132e-08</v>
+        <v>2.195827034923155e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>1.918837470340606e-08</v>
+        <v>1.918837470340607e-08</v>
       </c>
     </row>
     <row r="7">
@@ -7447,37 +7447,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.166357884757285e-08</v>
+        <v>2.166357884757296e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>2.397749959462396e-08</v>
+        <v>2.397749959462391e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>1.891787490616181e-08</v>
+        <v>1.891787490616175e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>2.397072956084182e-08</v>
+        <v>2.397072956084215e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>2.397072956084182e-08</v>
+        <v>2.397072956084214e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>2.438574528206938e-08</v>
+        <v>2.438574528206945e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>2.096692142252728e-08</v>
+        <v>2.096692142252749e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>2.397757779693426e-08</v>
+        <v>2.397757779693422e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>5.108619840069511e-08</v>
+        <v>5.108619840069523e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>2.28920029936126e-08</v>
+        <v>2.289200299361281e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>2.00839311585198e-08</v>
+        <v>2.008393115851992e-08</v>
       </c>
     </row>
     <row r="8">
@@ -7487,37 +7487,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.609299622635592e-08</v>
+        <v>2.609299622635568e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>3.505475095557503e-08</v>
+        <v>3.505475095557451e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>3.137988145208065e-08</v>
+        <v>3.137988145207969e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>3.323584579396082e-08</v>
+        <v>3.323584579396032e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>2.861388930922295e-08</v>
+        <v>2.861388930922274e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>3.546802911706492e-08</v>
+        <v>3.546802911706467e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>3.204920525754417e-08</v>
+        <v>3.20492052575437e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>3.505986163192988e-08</v>
+        <v>3.505986163192944e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>6.216978969263719e-08</v>
+        <v>6.216978969263701e-08</v>
       </c>
       <c r="K8" t="n">
         <v>2.719783996415447e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>3.811569029047926e-08</v>
+        <v>3.811569029047934e-08</v>
       </c>
     </row>
     <row r="9">
@@ -7527,37 +7527,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5.614769294082263e-08</v>
+        <v>5.614769294082192e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>6.966907187505815e-08</v>
+        <v>6.966907187505793e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>6.460965925774228e-08</v>
+        <v>6.460965925773955e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>8.2602246466263e-08</v>
+        <v>8.260224646626427e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>6.966907375149629e-08</v>
+        <v>6.966907375149498e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>7.007731756250242e-08</v>
+        <v>7.007731756250347e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>6.665849370296265e-08</v>
+        <v>6.665849370296147e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>6.966915007736963e-08</v>
+        <v>6.966915007736822e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>9.677777068113049e-08</v>
+        <v>9.677777068112926e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>6.208993190221104e-08</v>
+        <v>6.208993190221167e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>6.577550343895504e-08</v>
+        <v>6.577550343895393e-08</v>
       </c>
     </row>
   </sheetData>
@@ -7643,37 +7643,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.916617601056301e-07</v>
+        <v>1.916617601056304e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>3.744009792093902e-07</v>
+        <v>3.744009792093907e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>1.919405680628771e-07</v>
+        <v>1.919405680628775e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>3.978265306438884e-07</v>
+        <v>3.978265306438894e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>2.838077831546206e-07</v>
+        <v>2.838077831546214e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>1.921325933403653e-07</v>
+        <v>1.921325933403654e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>1.917558813056623e-07</v>
+        <v>1.917558813056626e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>1.920499169273543e-07</v>
+        <v>1.92049916927355e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>3.043305870456803e-07</v>
+        <v>3.043305870456812e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>1.691680637322154e-07</v>
+        <v>1.691680637322161e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>1.920216267368825e-07</v>
+        <v>1.92021626736883e-07</v>
       </c>
     </row>
     <row r="3">
@@ -7683,37 +7683,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.950531330747146e-07</v>
+        <v>1.950531330747153e-07</v>
       </c>
       <c r="C3" t="n">
-        <v>4.988238627277123e-07</v>
+        <v>4.988238627277132e-07</v>
       </c>
       <c r="D3" t="n">
-        <v>1.97029715315945e-07</v>
+        <v>1.970297153159455e-07</v>
       </c>
       <c r="E3" t="n">
-        <v>5.374782356527732e-07</v>
+        <v>5.374782356527739e-07</v>
       </c>
       <c r="F3" t="n">
-        <v>3.492694393084931e-07</v>
+        <v>3.492694393084938e-07</v>
       </c>
       <c r="G3" t="n">
-        <v>1.983987002904861e-07</v>
+        <v>1.983987002904869e-07</v>
       </c>
       <c r="H3" t="n">
-        <v>1.958152071377766e-07</v>
+        <v>1.958152071377773e-07</v>
       </c>
       <c r="I3" t="n">
-        <v>1.978066894200656e-07</v>
+        <v>1.978066894200661e-07</v>
       </c>
       <c r="J3" t="n">
-        <v>3.963118076710898e-07</v>
+        <v>3.96311807671091e-07</v>
       </c>
       <c r="K3" t="n">
-        <v>1.593049129841437e-07</v>
+        <v>1.59304912984144e-07</v>
       </c>
       <c r="L3" t="n">
-        <v>1.976708872193999e-07</v>
+        <v>1.976708872194004e-07</v>
       </c>
     </row>
     <row r="4">
@@ -7723,37 +7723,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.348937422195742e-08</v>
+        <v>1.348937422195763e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>1.800663283309854e-08</v>
+        <v>1.800663283309882e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>1.663863835706084e-08</v>
+        <v>1.663863835706104e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>1.819343285283552e-08</v>
+        <v>1.819343285283603e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>1.819343285283552e-08</v>
+        <v>1.819343285283606e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>1.888954935880072e-08</v>
+        <v>1.88895493588009e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>1.470820318864161e-08</v>
+        <v>1.470820318864192e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>1.841910356266999e-08</v>
+        <v>1.841910356267064e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>4.492708155641064e-08</v>
+        <v>4.492708155641075e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>1.635963755353269e-08</v>
+        <v>1.635963755353324e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>1.761041124255837e-08</v>
+        <v>1.761041124255874e-08</v>
       </c>
     </row>
     <row r="5">
@@ -7763,37 +7763,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.847611447730205e-08</v>
+        <v>3.847611447730275e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>1.078927184039139e-07</v>
+        <v>1.078927184039147e-07</v>
       </c>
       <c r="D5" t="n">
-        <v>8.729192551125239e-08</v>
+        <v>8.729192551125279e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>1.078927275656354e-07</v>
+        <v>1.078927275656356e-07</v>
       </c>
       <c r="F5" t="n">
-        <v>1.078927275656354e-07</v>
+        <v>1.078927275656356e-07</v>
       </c>
       <c r="G5" t="n">
-        <v>1.249544087061919e-07</v>
+        <v>1.249544087061929e-07</v>
       </c>
       <c r="H5" t="n">
-        <v>6.300702787275784e-08</v>
+        <v>6.300702787275882e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>1.078927873448015e-07</v>
+        <v>1.078927873448029e-07</v>
       </c>
       <c r="J5" t="n">
-        <v>5.988592828948354e-07</v>
+        <v>5.988592828948363e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>8.282359120870742e-08</v>
+        <v>8.282359120870847e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>1.211296536921322e-07</v>
+        <v>1.211296536921331e-07</v>
       </c>
     </row>
     <row r="6">
@@ -7803,37 +7803,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.985630942916649e-08</v>
+        <v>1.985630942916724e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>2.062037498562339e-08</v>
+        <v>2.062037498562345e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>1.879690385331235e-08</v>
+        <v>1.879690385331244e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>2.040795807293849e-08</v>
+        <v>2.040795807293879e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>2.072357197976321e-08</v>
+        <v>2.072357197976345e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>2.525648456600981e-08</v>
+        <v>2.52564845660122e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>2.225844468889114e-08</v>
+        <v>2.225844468889145e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>2.478603876987908e-08</v>
+        <v>2.478603876988034e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>4.762769208668729e-08</v>
+        <v>4.76276920866875e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>1.859598676146091e-08</v>
+        <v>1.859598676146132e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>1.995274871434356e-08</v>
+        <v>1.995274871434359e-08</v>
       </c>
     </row>
     <row r="7">
@@ -7843,37 +7843,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.645507648358466e-08</v>
+        <v>1.645507648358477e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>2.138473688340949e-08</v>
+        <v>2.138473688341054e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>1.960421026584907e-08</v>
+        <v>1.960421026584952e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>2.131980966508461e-08</v>
+        <v>2.131980966508517e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>2.131980966508461e-08</v>
+        <v>2.131980966508517e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>2.1855251620428e-08</v>
+        <v>2.185525162042773e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>1.767390545026889e-08</v>
+        <v>1.767390545026897e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>2.13848058242973e-08</v>
+        <v>2.13848058242978e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>4.789278381803773e-08</v>
+        <v>4.789278381803844e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>1.932533981515997e-08</v>
+        <v>1.932533981515938e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>2.057611350418565e-08</v>
+        <v>2.057611350418579e-08</v>
       </c>
     </row>
     <row r="8">
@@ -7883,37 +7883,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.009330226018287e-08</v>
+        <v>2.009330226018384e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>3.030861571716655e-08</v>
+        <v>3.030861571716761e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>2.969790055236341e-08</v>
+        <v>2.96979005523649e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>2.885292007284423e-08</v>
+        <v>2.885292007284466e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>2.515379300242635e-08</v>
+        <v>2.515379300242763e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>3.084014516360847e-08</v>
+        <v>3.084014516360991e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>2.665879899347723e-08</v>
+        <v>2.665879899347832e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>3.03696993674777e-08</v>
+        <v>3.036969936747909e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>5.687872811900836e-08</v>
+        <v>5.687872811900955e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>2.286424849428329e-08</v>
+        <v>2.286424849428362e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>3.514604859627415e-08</v>
+        <v>3.5146048596275e-08</v>
       </c>
     </row>
     <row r="9">
@@ -7923,37 +7923,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.472833214933125e-08</v>
+        <v>4.472833214932952e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>5.879808714797019e-08</v>
+        <v>5.879808714796959e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>5.701769502894807e-08</v>
+        <v>5.701769502894952e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>6.934557357060781e-08</v>
+        <v>6.934557357060581e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>5.879809482774959e-08</v>
+        <v>5.879809482774661e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>5.926860188498875e-08</v>
+        <v>5.926860188498971e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>5.508725571482955e-08</v>
+        <v>5.508725571482651e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>5.879815608885792e-08</v>
+        <v>5.879815608885647e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>8.530613408259857e-08</v>
+        <v>8.530613408259161e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>5.144288511691087e-08</v>
+        <v>5.144288511691395e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>5.798946376874646e-08</v>
+        <v>5.798946376874919e-08</v>
       </c>
     </row>
   </sheetData>
